--- a/模块开发/录入表.xlsx
+++ b/模块开发/录入表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentli/PycharmProjects/PythonProject/2026-4 群控/yolo/整合详情页采集/模块开发/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979A0E41-CDE2-3A4E-BBF8-2F5BB60F4224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20EAEF3-08F5-2847-9F26-9DBEB3199658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19940" yWindow="1200" windowWidth="29820" windowHeight="25020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="组套" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">单支!$A$1:$K$443</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">单支!$A$1:$I$443</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">组套!$C$1:$F$58</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="1420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="1418">
   <si>
     <t>商品条码</t>
   </si>
@@ -4335,12 +4335,6 @@
   <si>
     <t xml:space="preserve">否 </t>
     <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>调整价格范围（最高）仅限通姆平台参考</t>
-  </si>
-  <si>
-    <t>调整价格范围（最低）仅限通姆平台参考</t>
   </si>
 </sst>
 </file>
@@ -4398,7 +4392,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4423,18 +4417,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0CECE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -4450,7 +4432,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4533,23 +4515,18 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="83">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -5029,13 +5006,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5570,7 +5540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K444"/>
+  <dimension ref="A1:I443"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="8.33203125" customWidth="1"/>
@@ -5580,11 +5550,10 @@
     <col min="6" max="6" width="35.33203125" style="2" customWidth="1"/>
     <col min="7" max="7" width="29.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="15" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15" style="4" customWidth="1"/>
-    <col min="11" max="11" width="5.83203125" style="10" customWidth="1"/>
+    <col min="9" max="9" width="5.83203125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>1413</v>
       </c>
@@ -5609,17 +5578,11 @@
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="30" t="s">
-        <v>1418</v>
-      </c>
-      <c r="J1" s="30" t="s">
-        <v>1419</v>
-      </c>
-      <c r="K1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>1116</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15">
+    <row r="2" spans="1:9" ht="15">
       <c r="A2">
         <v>409</v>
       </c>
@@ -5641,17 +5604,11 @@
         <f t="shared" ref="H2:H10" si="0">D2+1095</f>
         <v>1095</v>
       </c>
-      <c r="I2" s="31">
-        <v>490</v>
-      </c>
-      <c r="J2" s="31">
-        <v>245</v>
-      </c>
-      <c r="K2" s="10">
+      <c r="I2" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15">
+    <row r="3" spans="1:9" ht="15">
       <c r="A3" s="22">
         <v>209</v>
       </c>
@@ -5673,17 +5630,11 @@
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="I3" s="31">
-        <v>250</v>
-      </c>
-      <c r="J3" s="31">
-        <v>150</v>
-      </c>
-      <c r="K3" s="10">
+      <c r="I3" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15">
+    <row r="4" spans="1:9" ht="15">
       <c r="A4" s="22">
         <v>278</v>
       </c>
@@ -5705,17 +5656,11 @@
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="I4" s="31">
-        <v>288</v>
-      </c>
-      <c r="J4" s="31">
-        <v>180</v>
-      </c>
-      <c r="K4" s="10">
+      <c r="I4" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15">
+    <row r="5" spans="1:9" ht="15">
       <c r="A5" s="22">
         <v>289</v>
       </c>
@@ -5737,17 +5682,11 @@
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="I5" s="31">
-        <v>220</v>
-      </c>
-      <c r="J5" s="31">
-        <v>170</v>
-      </c>
-      <c r="K5" s="10">
+      <c r="I5" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15">
+    <row r="6" spans="1:9" ht="15">
       <c r="A6" s="22">
         <v>102.63</v>
       </c>
@@ -5769,17 +5708,11 @@
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="I6" s="31">
-        <v>110</v>
-      </c>
-      <c r="J6" s="31">
-        <v>90</v>
-      </c>
-      <c r="K6" s="10">
+      <c r="I6" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15">
+    <row r="7" spans="1:9" ht="15">
       <c r="A7" s="22">
         <v>74.900000000000006</v>
       </c>
@@ -5801,17 +5734,11 @@
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="I7" s="31">
-        <v>150</v>
-      </c>
-      <c r="J7" s="31">
-        <v>60</v>
-      </c>
-      <c r="K7" s="10">
+      <c r="I7" s="10">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15">
+    <row r="8" spans="1:9" ht="15">
       <c r="A8" s="22">
         <v>190.1</v>
       </c>
@@ -5833,17 +5760,11 @@
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="I8" s="31">
-        <v>170</v>
-      </c>
-      <c r="J8" s="31">
-        <v>120</v>
-      </c>
-      <c r="K8" s="10">
+      <c r="I8" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15">
+    <row r="9" spans="1:9" ht="15">
       <c r="A9">
         <v>588</v>
       </c>
@@ -5865,17 +5786,11 @@
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="I9" s="31">
-        <v>349</v>
-      </c>
-      <c r="J9" s="31">
-        <v>278</v>
-      </c>
-      <c r="K9" s="10">
+      <c r="I9" s="10">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15">
+    <row r="10" spans="1:9" ht="15">
       <c r="A10" s="22">
         <v>236</v>
       </c>
@@ -5897,17 +5812,11 @@
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="I10" s="31">
-        <v>260</v>
-      </c>
-      <c r="J10" s="31">
-        <v>189</v>
-      </c>
-      <c r="K10" s="10">
+      <c r="I10" s="10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15">
+    <row r="11" spans="1:9" ht="15">
       <c r="A11" s="22">
         <v>220</v>
       </c>
@@ -5929,17 +5838,11 @@
         <f t="shared" ref="H11:H19" si="1">D11+1095</f>
         <v>1095</v>
       </c>
-      <c r="I11" s="31">
-        <v>260</v>
-      </c>
-      <c r="J11" s="31">
-        <v>189</v>
-      </c>
-      <c r="K11" s="10">
+      <c r="I11" s="10">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15">
+    <row r="12" spans="1:9" ht="15">
       <c r="A12" s="22">
         <v>164</v>
       </c>
@@ -5961,17 +5864,11 @@
         <f t="shared" si="1"/>
         <v>1095</v>
       </c>
-      <c r="I12" s="31">
-        <v>260</v>
-      </c>
-      <c r="J12" s="31">
-        <v>189</v>
-      </c>
-      <c r="K12" s="10">
+      <c r="I12" s="10">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15">
+    <row r="13" spans="1:9" ht="15">
       <c r="A13" s="22">
         <v>358</v>
       </c>
@@ -5993,17 +5890,11 @@
         <f t="shared" si="1"/>
         <v>1095</v>
       </c>
-      <c r="I13" s="31">
-        <v>260</v>
-      </c>
-      <c r="J13" s="31">
-        <v>145</v>
-      </c>
-      <c r="K13" s="10">
+      <c r="I13" s="10">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15">
+    <row r="14" spans="1:9" ht="15">
       <c r="A14" s="22">
         <v>142.15</v>
       </c>
@@ -6025,17 +5916,11 @@
         <f t="shared" si="1"/>
         <v>1095</v>
       </c>
-      <c r="I14" s="31">
-        <v>240</v>
-      </c>
-      <c r="J14" s="31">
-        <v>169</v>
-      </c>
-      <c r="K14" s="10">
+      <c r="I14" s="10">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15">
+    <row r="15" spans="1:9" ht="15">
       <c r="A15" s="23">
         <v>84.5</v>
       </c>
@@ -6056,17 +5941,11 @@
         <f t="shared" si="1"/>
         <v>1095</v>
       </c>
-      <c r="I15" s="31">
-        <v>305</v>
-      </c>
-      <c r="J15" s="31">
-        <v>175</v>
-      </c>
-      <c r="K15" s="10">
+      <c r="I15" s="10">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15">
+    <row r="16" spans="1:9" ht="15">
       <c r="A16" s="22">
         <v>128</v>
       </c>
@@ -6088,17 +5967,11 @@
         <f t="shared" si="1"/>
         <v>1095</v>
       </c>
-      <c r="I16" s="31">
-        <v>160</v>
-      </c>
-      <c r="J16" s="31">
-        <v>138</v>
-      </c>
-      <c r="K16" s="10">
+      <c r="I16" s="10">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15">
+    <row r="17" spans="1:9" ht="15">
       <c r="A17" s="22">
         <v>222</v>
       </c>
@@ -6120,17 +5993,11 @@
         <f t="shared" si="1"/>
         <v>1095</v>
       </c>
-      <c r="I17" s="31">
-        <v>200</v>
-      </c>
-      <c r="J17" s="31">
-        <v>163</v>
-      </c>
-      <c r="K17" s="10">
+      <c r="I17" s="10">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15">
+    <row r="18" spans="1:9" ht="15">
       <c r="A18" s="23" t="s">
         <v>1111</v>
       </c>
@@ -6152,17 +6019,11 @@
         <f t="shared" si="1"/>
         <v>1095</v>
       </c>
-      <c r="I18" s="31">
-        <v>180</v>
-      </c>
-      <c r="J18" s="31">
-        <v>150</v>
-      </c>
-      <c r="K18" s="10">
+      <c r="I18" s="10">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15">
+    <row r="19" spans="1:9" ht="15">
       <c r="A19" s="22">
         <v>179</v>
       </c>
@@ -6184,17 +6045,11 @@
         <f t="shared" si="1"/>
         <v>1095</v>
       </c>
-      <c r="I19" s="31">
-        <v>108</v>
-      </c>
-      <c r="J19" s="31">
-        <v>80</v>
-      </c>
-      <c r="K19" s="10">
+      <c r="I19" s="10">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15">
+    <row r="20" spans="1:9" ht="15">
       <c r="A20" s="22">
         <v>178</v>
       </c>
@@ -6216,17 +6071,11 @@
         <f>D20+1825</f>
         <v>1825</v>
       </c>
-      <c r="I20" s="31">
-        <v>148</v>
-      </c>
-      <c r="J20" s="31">
-        <v>65</v>
-      </c>
-      <c r="K20" s="10">
+      <c r="I20" s="10">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15">
+    <row r="21" spans="1:9" ht="15">
       <c r="A21" s="22">
         <v>108.96</v>
       </c>
@@ -6248,17 +6097,11 @@
         <f>D21+1095</f>
         <v>1095</v>
       </c>
-      <c r="I21" s="31">
-        <v>135</v>
-      </c>
-      <c r="J21" s="31">
-        <v>65</v>
-      </c>
-      <c r="K21" s="10">
+      <c r="I21" s="10">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15">
+    <row r="22" spans="1:9" ht="15">
       <c r="A22" s="22">
         <v>149</v>
       </c>
@@ -6280,17 +6123,11 @@
         <f>D22+1825</f>
         <v>1825</v>
       </c>
-      <c r="I22" s="31">
-        <v>135</v>
-      </c>
-      <c r="J22" s="31">
-        <v>65</v>
-      </c>
-      <c r="K22" s="10">
+      <c r="I22" s="10">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15">
+    <row r="23" spans="1:9" ht="15">
       <c r="A23" s="22">
         <v>19</v>
       </c>
@@ -6312,17 +6149,11 @@
         <f>D23+1825</f>
         <v>1825</v>
       </c>
-      <c r="I23" s="31">
-        <v>25</v>
-      </c>
-      <c r="J23" s="31">
-        <v>15</v>
-      </c>
-      <c r="K23" s="10">
+      <c r="I23" s="10">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15">
+    <row r="24" spans="1:9" ht="15">
       <c r="A24" s="22">
         <v>832</v>
       </c>
@@ -6344,17 +6175,11 @@
         <f>D24+1095</f>
         <v>1095</v>
       </c>
-      <c r="I24" s="31">
-        <v>743</v>
-      </c>
-      <c r="J24" s="31">
-        <v>650</v>
-      </c>
-      <c r="K24" s="10">
+      <c r="I24" s="10">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15">
+    <row r="25" spans="1:9" ht="15">
       <c r="A25" s="22">
         <v>1300</v>
       </c>
@@ -6376,17 +6201,11 @@
         <f>D25+1095</f>
         <v>1095</v>
       </c>
-      <c r="I25" s="31">
-        <v>850</v>
-      </c>
-      <c r="J25" s="31">
-        <v>550</v>
-      </c>
-      <c r="K25" s="10">
+      <c r="I25" s="10">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15">
+    <row r="26" spans="1:9" ht="15">
       <c r="A26" s="22">
         <v>910</v>
       </c>
@@ -6408,17 +6227,11 @@
         <f>D26+1095</f>
         <v>1095</v>
       </c>
-      <c r="I26" s="31">
-        <v>1100</v>
-      </c>
-      <c r="J26" s="31">
-        <v>940</v>
-      </c>
-      <c r="K26" s="10">
+      <c r="I26" s="10">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15">
+    <row r="27" spans="1:9" ht="15">
       <c r="A27" s="22">
         <v>450</v>
       </c>
@@ -6440,17 +6253,11 @@
         <f>D27+1095</f>
         <v>1095</v>
       </c>
-      <c r="I27" s="31">
-        <v>270</v>
-      </c>
-      <c r="J27" s="31">
-        <v>190</v>
-      </c>
-      <c r="K27" s="10">
+      <c r="I27" s="10">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15">
+    <row r="28" spans="1:9" ht="15">
       <c r="A28" s="22">
         <v>731</v>
       </c>
@@ -6472,17 +6279,11 @@
         <f>D28+1095</f>
         <v>1095</v>
       </c>
-      <c r="I28" s="31">
-        <v>885</v>
-      </c>
-      <c r="J28" s="31">
-        <v>805</v>
-      </c>
-      <c r="K28" s="10">
+      <c r="I28" s="10">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15">
+    <row r="29" spans="1:9" ht="15">
       <c r="A29">
         <v>2290</v>
       </c>
@@ -6504,17 +6305,11 @@
         <f t="shared" ref="H29:H45" si="2">D29+1095</f>
         <v>1095</v>
       </c>
-      <c r="I29" s="31">
-        <v>1300</v>
-      </c>
-      <c r="J29" s="31">
-        <v>800</v>
-      </c>
-      <c r="K29" s="10">
+      <c r="I29" s="10">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15">
+    <row r="30" spans="1:9" ht="15">
       <c r="A30">
         <v>2290</v>
       </c>
@@ -6536,17 +6331,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I30" s="31">
-        <v>1300</v>
-      </c>
-      <c r="J30" s="31">
-        <v>800</v>
-      </c>
-      <c r="K30" s="10">
+      <c r="I30" s="10">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15">
+    <row r="31" spans="1:9" ht="15">
       <c r="A31">
         <v>1996</v>
       </c>
@@ -6568,17 +6357,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I31" s="31">
-        <v>900</v>
-      </c>
-      <c r="J31" s="31">
-        <v>750</v>
-      </c>
-      <c r="K31" s="10">
+      <c r="I31" s="10">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15">
+    <row r="32" spans="1:9" ht="15">
       <c r="A32" s="22">
         <v>1788</v>
       </c>
@@ -6600,17 +6383,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I32" s="31">
-        <v>1530</v>
-      </c>
-      <c r="J32" s="31">
-        <v>790</v>
-      </c>
-      <c r="K32" s="10">
+      <c r="I32" s="10">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15">
+    <row r="33" spans="1:9" ht="15">
       <c r="A33" s="22">
         <v>299</v>
       </c>
@@ -6632,17 +6409,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I33" s="31">
-        <v>248</v>
-      </c>
-      <c r="J33" s="31">
-        <v>140</v>
-      </c>
-      <c r="K33" s="10">
+      <c r="I33" s="10">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15">
+    <row r="34" spans="1:9" ht="15">
       <c r="A34" s="22">
         <v>520</v>
       </c>
@@ -6664,17 +6435,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I34" s="31">
-        <v>200</v>
-      </c>
-      <c r="J34" s="31">
-        <v>100</v>
-      </c>
-      <c r="K34" s="10">
+      <c r="I34" s="10">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15">
+    <row r="35" spans="1:9" ht="15">
       <c r="A35" s="22">
         <v>298</v>
       </c>
@@ -6696,17 +6461,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I35" s="31">
-        <v>500</v>
-      </c>
-      <c r="J35" s="31">
-        <v>200</v>
-      </c>
-      <c r="K35" s="10">
+      <c r="I35" s="10">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15">
+    <row r="36" spans="1:9" ht="15">
       <c r="A36" s="22">
         <v>580</v>
       </c>
@@ -6728,17 +6487,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I36" s="31">
-        <v>550</v>
-      </c>
-      <c r="J36" s="31">
-        <v>400</v>
-      </c>
-      <c r="K36" s="10">
+      <c r="I36" s="10">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15">
+    <row r="37" spans="1:9" ht="15">
       <c r="A37" s="22">
         <v>196.89</v>
       </c>
@@ -6760,17 +6513,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I37" s="31">
-        <v>305</v>
-      </c>
-      <c r="J37" s="31">
-        <v>220</v>
-      </c>
-      <c r="K37" s="10">
+      <c r="I37" s="10">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15">
+    <row r="38" spans="1:9" ht="15">
       <c r="A38" s="22">
         <v>2999</v>
       </c>
@@ -6792,17 +6539,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I38" s="31">
-        <v>2000</v>
-      </c>
-      <c r="J38" s="31">
-        <v>1200</v>
-      </c>
-      <c r="K38" s="10">
+      <c r="I38" s="10">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15">
+    <row r="39" spans="1:9" ht="15">
       <c r="A39" s="22">
         <v>350</v>
       </c>
@@ -6824,17 +6565,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I39" s="31">
-        <v>236</v>
-      </c>
-      <c r="J39" s="31">
-        <v>147</v>
-      </c>
-      <c r="K39" s="10">
+      <c r="I39" s="10">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15">
+    <row r="40" spans="1:9" ht="15">
       <c r="A40" s="22">
         <v>38.76</v>
       </c>
@@ -6856,17 +6591,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I40" s="31">
-        <v>35</v>
-      </c>
-      <c r="J40" s="31">
-        <v>20</v>
-      </c>
-      <c r="K40" s="10">
+      <c r="I40" s="10">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15">
+    <row r="41" spans="1:9" ht="15">
       <c r="A41" s="23" t="s">
         <v>1111</v>
       </c>
@@ -6887,17 +6616,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I41" s="31">
-        <v>150</v>
-      </c>
-      <c r="J41" s="31">
-        <v>100</v>
-      </c>
-      <c r="K41" s="10">
+      <c r="I41" s="10">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15">
+    <row r="42" spans="1:9" ht="15">
       <c r="A42" s="22">
         <v>249</v>
       </c>
@@ -6919,17 +6642,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I42" s="31">
-        <v>250</v>
-      </c>
-      <c r="J42" s="31">
-        <v>120</v>
-      </c>
-      <c r="K42" s="10">
+      <c r="I42" s="10">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="15">
+    <row r="43" spans="1:9" ht="15">
       <c r="A43" s="22">
         <v>249</v>
       </c>
@@ -6951,17 +6668,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I43" s="31">
-        <v>180</v>
-      </c>
-      <c r="J43" s="31">
-        <v>120</v>
-      </c>
-      <c r="K43" s="10">
+      <c r="I43" s="10">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15">
+    <row r="44" spans="1:9" ht="15">
       <c r="A44" s="22">
         <v>423.1</v>
       </c>
@@ -6983,17 +6694,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I44" s="31">
-        <v>560</v>
-      </c>
-      <c r="J44" s="31">
-        <v>425</v>
-      </c>
-      <c r="K44" s="10">
+      <c r="I44" s="10">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15">
+    <row r="45" spans="1:9" ht="15">
       <c r="A45" s="22">
         <v>257.89999999999998</v>
       </c>
@@ -7015,17 +6720,11 @@
         <f t="shared" si="2"/>
         <v>1095</v>
       </c>
-      <c r="I45" s="31">
-        <v>250</v>
-      </c>
-      <c r="J45" s="31">
-        <v>150</v>
-      </c>
-      <c r="K45" s="10">
+      <c r="I45" s="10">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="15">
+    <row r="46" spans="1:9" ht="15">
       <c r="A46">
         <v>475</v>
       </c>
@@ -7047,17 +6746,11 @@
         <f>D46+1825</f>
         <v>1825</v>
       </c>
-      <c r="I46" s="31">
-        <v>340</v>
-      </c>
-      <c r="J46" s="31">
-        <v>175</v>
-      </c>
-      <c r="K46" s="10">
+      <c r="I46" s="10">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15">
+    <row r="47" spans="1:9" ht="15">
       <c r="A47" s="22">
         <v>302.60000000000002</v>
       </c>
@@ -7079,17 +6772,11 @@
         <f>D47+1096</f>
         <v>1096</v>
       </c>
-      <c r="I47" s="31">
-        <v>260</v>
-      </c>
-      <c r="J47" s="31">
-        <v>175</v>
-      </c>
-      <c r="K47" s="10">
+      <c r="I47" s="10">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15">
+    <row r="48" spans="1:9" ht="15">
       <c r="A48" s="22">
         <v>389.5</v>
       </c>
@@ -7111,17 +6798,11 @@
         <f>D48+1095</f>
         <v>1095</v>
       </c>
-      <c r="I48" s="31">
-        <v>660</v>
-      </c>
-      <c r="J48" s="31">
-        <v>215</v>
-      </c>
-      <c r="K48" s="10">
+      <c r="I48" s="10">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15">
+    <row r="49" spans="1:9" ht="15">
       <c r="A49">
         <v>278</v>
       </c>
@@ -7142,17 +6823,11 @@
         <f>D49+1096</f>
         <v>1096</v>
       </c>
-      <c r="I49" s="31">
-        <v>245</v>
-      </c>
-      <c r="J49" s="31">
-        <v>100</v>
-      </c>
-      <c r="K49" s="10">
+      <c r="I49" s="10">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15">
+    <row r="50" spans="1:9" ht="15">
       <c r="A50" s="22">
         <v>257.89999999999998</v>
       </c>
@@ -7174,17 +6849,11 @@
         <f>D50+1825</f>
         <v>1825</v>
       </c>
-      <c r="I50" s="31">
-        <v>280</v>
-      </c>
-      <c r="J50" s="31">
-        <v>160</v>
-      </c>
-      <c r="K50" s="10">
+      <c r="I50" s="10">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15">
+    <row r="51" spans="1:9" ht="15">
       <c r="A51" s="22">
         <v>400</v>
       </c>
@@ -7206,17 +6875,11 @@
         <f>D51+1095</f>
         <v>1095</v>
       </c>
-      <c r="I51" s="31">
-        <v>450</v>
-      </c>
-      <c r="J51" s="31">
-        <v>280</v>
-      </c>
-      <c r="K51" s="10">
+      <c r="I51" s="10">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="15">
+    <row r="52" spans="1:9" ht="15">
       <c r="A52" s="26"/>
       <c r="B52" s="22"/>
       <c r="C52" s="24" t="s">
@@ -7236,17 +6899,11 @@
         <f t="shared" ref="H52:H53" si="3">D52+1095</f>
         <v>1095</v>
       </c>
-      <c r="I52" s="31">
-        <v>400</v>
-      </c>
-      <c r="J52" s="31">
-        <v>200</v>
-      </c>
-      <c r="K52" s="10">
+      <c r="I52" s="10">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15">
+    <row r="53" spans="1:9" ht="15">
       <c r="A53" s="22">
         <v>350</v>
       </c>
@@ -7268,17 +6925,11 @@
         <f t="shared" si="3"/>
         <v>1095</v>
       </c>
-      <c r="I53" s="31">
-        <v>275</v>
-      </c>
-      <c r="J53" s="31">
-        <v>100</v>
-      </c>
-      <c r="K53" s="10">
+      <c r="I53" s="10">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15">
+    <row r="54" spans="1:9" ht="15">
       <c r="A54" s="22">
         <v>317.10000000000002</v>
       </c>
@@ -7300,17 +6951,11 @@
         <f>D54+1095</f>
         <v>1095</v>
       </c>
-      <c r="I54" s="31">
-        <v>400</v>
-      </c>
-      <c r="J54" s="31">
-        <v>300</v>
-      </c>
-      <c r="K54" s="10">
+      <c r="I54" s="10">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="15">
+    <row r="55" spans="1:9" ht="15">
       <c r="A55" s="22">
         <v>398</v>
       </c>
@@ -7332,17 +6977,11 @@
         <f>D55+1095</f>
         <v>1095</v>
       </c>
-      <c r="I55" s="31">
-        <v>500</v>
-      </c>
-      <c r="J55" s="31">
-        <v>430</v>
-      </c>
-      <c r="K55" s="10">
+      <c r="I55" s="10">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="15">
+    <row r="56" spans="1:9" ht="15">
       <c r="A56" s="22">
         <v>799</v>
       </c>
@@ -7364,17 +7003,11 @@
         <f>D56+1095</f>
         <v>1095</v>
       </c>
-      <c r="I56" s="31">
-        <v>700</v>
-      </c>
-      <c r="J56" s="31">
-        <v>550</v>
-      </c>
-      <c r="K56" s="10">
+      <c r="I56" s="10">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="15">
+    <row r="57" spans="1:9" ht="15">
       <c r="A57" s="22">
         <v>308</v>
       </c>
@@ -7396,17 +7029,11 @@
         <f>D57+1095</f>
         <v>1095</v>
       </c>
-      <c r="I57" s="31">
-        <v>380</v>
-      </c>
-      <c r="J57" s="31">
-        <v>320</v>
-      </c>
-      <c r="K57" s="10">
+      <c r="I57" s="10">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="15">
+    <row r="58" spans="1:9" ht="15">
       <c r="A58" s="22">
         <v>161</v>
       </c>
@@ -7428,17 +7055,11 @@
         <f>D58+1095</f>
         <v>1095</v>
       </c>
-      <c r="I58" s="31">
-        <v>390</v>
-      </c>
-      <c r="J58" s="31">
-        <v>105</v>
-      </c>
-      <c r="K58" s="10">
+      <c r="I58" s="10">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="15">
+    <row r="59" spans="1:9" ht="15">
       <c r="A59" s="22">
         <v>153.9</v>
       </c>
@@ -7460,17 +7081,11 @@
         <f>D59+1825</f>
         <v>1825</v>
       </c>
-      <c r="I59" s="31">
-        <v>200</v>
-      </c>
-      <c r="J59" s="31">
-        <v>100</v>
-      </c>
-      <c r="K59" s="10">
+      <c r="I59" s="10">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="15">
+    <row r="60" spans="1:9" ht="15">
       <c r="A60" s="22">
         <v>137.80000000000001</v>
       </c>
@@ -7492,17 +7107,11 @@
         <f>D60+1825</f>
         <v>1825</v>
       </c>
-      <c r="I60" s="31">
-        <v>231</v>
-      </c>
-      <c r="J60" s="31">
-        <v>100</v>
-      </c>
-      <c r="K60" s="10">
+      <c r="I60" s="10">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="15">
+    <row r="61" spans="1:9" ht="15">
       <c r="A61" s="22">
         <v>121</v>
       </c>
@@ -7524,17 +7133,11 @@
         <f>D61+1095</f>
         <v>1095</v>
       </c>
-      <c r="I61" s="31">
-        <v>150</v>
-      </c>
-      <c r="J61" s="31">
-        <v>90</v>
-      </c>
-      <c r="K61" s="10">
+      <c r="I61" s="10">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="15">
+    <row r="62" spans="1:9" ht="15">
       <c r="A62" s="22">
         <v>299</v>
       </c>
@@ -7556,17 +7159,11 @@
         <f>D62+1095</f>
         <v>1095</v>
       </c>
-      <c r="I62" s="31">
-        <v>300</v>
-      </c>
-      <c r="J62" s="31">
-        <v>170</v>
-      </c>
-      <c r="K62" s="10">
+      <c r="I62" s="10">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="15">
+    <row r="63" spans="1:9" ht="15">
       <c r="A63" s="22">
         <v>181</v>
       </c>
@@ -7588,17 +7185,11 @@
         <f>D63+1095</f>
         <v>1095</v>
       </c>
-      <c r="I63" s="31">
-        <v>260</v>
-      </c>
-      <c r="J63" s="31">
-        <v>100</v>
-      </c>
-      <c r="K63" s="10">
+      <c r="I63" s="10">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="15">
+    <row r="64" spans="1:9" ht="15">
       <c r="A64">
         <v>60</v>
       </c>
@@ -7620,17 +7211,11 @@
         <f>D64+1825</f>
         <v>1825</v>
       </c>
-      <c r="I64" s="31">
-        <v>195</v>
-      </c>
-      <c r="J64" s="31">
-        <v>100</v>
-      </c>
-      <c r="K64" s="10">
+      <c r="I64" s="10">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="15">
+    <row r="65" spans="1:9" ht="15">
       <c r="A65" s="22">
         <v>299</v>
       </c>
@@ -7652,17 +7237,11 @@
         <f>D65+1095</f>
         <v>1095</v>
       </c>
-      <c r="I65" s="31">
-        <v>297</v>
-      </c>
-      <c r="J65" s="31">
-        <v>160</v>
-      </c>
-      <c r="K65" s="10">
+      <c r="I65" s="10">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="15">
+    <row r="66" spans="1:9" ht="15">
       <c r="A66" s="22">
         <v>198</v>
       </c>
@@ -7684,17 +7263,11 @@
         <f>D66+1095</f>
         <v>1095</v>
       </c>
-      <c r="I66" s="31">
-        <v>303</v>
-      </c>
-      <c r="J66" s="31">
-        <v>150</v>
-      </c>
-      <c r="K66" s="10">
+      <c r="I66" s="10">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="15">
+    <row r="67" spans="1:9" ht="15">
       <c r="A67" s="22">
         <v>399</v>
       </c>
@@ -7716,17 +7289,11 @@
         <f>D67+1825</f>
         <v>1825</v>
       </c>
-      <c r="I67" s="31">
-        <v>300</v>
-      </c>
-      <c r="J67" s="31">
-        <v>230</v>
-      </c>
-      <c r="K67" s="10">
+      <c r="I67" s="10">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="15">
+    <row r="68" spans="1:9" ht="15">
       <c r="A68" s="22">
         <v>355</v>
       </c>
@@ -7748,17 +7315,11 @@
         <f t="shared" ref="H68:H78" si="4">D68+1095</f>
         <v>1095</v>
       </c>
-      <c r="I68" s="31">
-        <v>250</v>
-      </c>
-      <c r="J68" s="31">
-        <v>100</v>
-      </c>
-      <c r="K68" s="10">
+      <c r="I68" s="10">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="15">
+    <row r="69" spans="1:9" ht="15">
       <c r="A69" s="22">
         <v>1399</v>
       </c>
@@ -7780,17 +7341,11 @@
         <f t="shared" si="4"/>
         <v>1095</v>
       </c>
-      <c r="I69" s="31">
-        <v>900</v>
-      </c>
-      <c r="J69" s="31">
-        <v>700</v>
-      </c>
-      <c r="K69" s="10">
+      <c r="I69" s="10">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="15">
+    <row r="70" spans="1:9" ht="15">
       <c r="A70" s="22">
         <v>110</v>
       </c>
@@ -7812,17 +7367,11 @@
         <f t="shared" si="4"/>
         <v>1095</v>
       </c>
-      <c r="I70" s="31">
-        <v>150</v>
-      </c>
-      <c r="J70" s="31">
-        <v>85</v>
-      </c>
-      <c r="K70" s="10">
+      <c r="I70" s="10">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="15">
+    <row r="71" spans="1:9" ht="15">
       <c r="A71" s="22">
         <v>120</v>
       </c>
@@ -7844,17 +7393,11 @@
         <f t="shared" si="4"/>
         <v>1095</v>
       </c>
-      <c r="I71" s="31">
-        <v>180</v>
-      </c>
-      <c r="J71" s="31">
-        <v>100</v>
-      </c>
-      <c r="K71" s="10">
+      <c r="I71" s="10">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="15">
+    <row r="72" spans="1:9" ht="15">
       <c r="A72" s="22">
         <v>96</v>
       </c>
@@ -7876,17 +7419,11 @@
         <f t="shared" si="4"/>
         <v>1095</v>
       </c>
-      <c r="I72" s="31">
-        <v>145</v>
-      </c>
-      <c r="J72" s="31">
-        <v>100</v>
-      </c>
-      <c r="K72" s="10">
+      <c r="I72" s="10">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="15">
+    <row r="73" spans="1:9" ht="15">
       <c r="A73" s="22">
         <v>109</v>
       </c>
@@ -7908,17 +7445,11 @@
         <f t="shared" si="4"/>
         <v>1095</v>
       </c>
-      <c r="I73" s="31">
-        <v>180</v>
-      </c>
-      <c r="J73" s="31">
-        <v>120</v>
-      </c>
-      <c r="K73" s="10">
+      <c r="I73" s="10">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="15">
+    <row r="74" spans="1:9" ht="15">
       <c r="A74" s="22">
         <v>125</v>
       </c>
@@ -7940,17 +7471,11 @@
         <f t="shared" si="4"/>
         <v>1095</v>
       </c>
-      <c r="I74" s="31">
-        <v>180</v>
-      </c>
-      <c r="J74" s="31">
-        <v>120</v>
-      </c>
-      <c r="K74" s="10">
+      <c r="I74" s="10">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="15">
+    <row r="75" spans="1:9" ht="15">
       <c r="A75" s="22">
         <v>435</v>
       </c>
@@ -7972,17 +7497,11 @@
         <f t="shared" si="4"/>
         <v>1095</v>
       </c>
-      <c r="I75" s="31">
-        <v>400</v>
-      </c>
-      <c r="J75" s="31">
-        <v>275</v>
-      </c>
-      <c r="K75" s="10">
+      <c r="I75" s="10">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="15">
+    <row r="76" spans="1:9" ht="15">
       <c r="A76" s="22">
         <v>218</v>
       </c>
@@ -8004,17 +7523,11 @@
         <f t="shared" si="4"/>
         <v>1095</v>
       </c>
-      <c r="I76" s="31">
-        <v>600</v>
-      </c>
-      <c r="J76" s="31">
-        <v>190</v>
-      </c>
-      <c r="K76" s="10">
+      <c r="I76" s="10">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="15">
+    <row r="77" spans="1:9" ht="15">
       <c r="A77" s="22">
         <v>580</v>
       </c>
@@ -8036,17 +7549,11 @@
         <f t="shared" si="4"/>
         <v>1095</v>
       </c>
-      <c r="I77" s="31">
-        <v>400</v>
-      </c>
-      <c r="J77" s="31">
-        <v>300</v>
-      </c>
-      <c r="K77" s="10">
+      <c r="I77" s="10">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="15">
+    <row r="78" spans="1:9" ht="15">
       <c r="A78" s="22">
         <v>289</v>
       </c>
@@ -8068,17 +7575,11 @@
         <f t="shared" si="4"/>
         <v>1095</v>
       </c>
-      <c r="I78" s="31">
-        <v>457</v>
-      </c>
-      <c r="J78" s="31">
-        <v>280</v>
-      </c>
-      <c r="K78" s="10">
+      <c r="I78" s="10">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="15">
+    <row r="79" spans="1:9" ht="15">
       <c r="A79" s="22">
         <v>349</v>
       </c>
@@ -8100,17 +7601,11 @@
         <f>D79+1095</f>
         <v>1095</v>
       </c>
-      <c r="I79" s="31">
-        <v>444</v>
-      </c>
-      <c r="J79" s="31">
-        <v>280</v>
-      </c>
-      <c r="K79" s="10">
+      <c r="I79" s="10">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="15">
+    <row r="80" spans="1:9" ht="15">
       <c r="A80" s="22">
         <v>135</v>
       </c>
@@ -8132,17 +7627,11 @@
         <f t="shared" ref="H80" si="5">D80+1095</f>
         <v>1095</v>
       </c>
-      <c r="I80" s="31">
-        <v>230</v>
-      </c>
-      <c r="J80" s="31">
-        <v>150</v>
-      </c>
-      <c r="K80" s="10">
+      <c r="I80" s="10">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="15">
+    <row r="81" spans="1:9" ht="15">
       <c r="A81" s="22">
         <v>88.9</v>
       </c>
@@ -8164,17 +7653,11 @@
         <f>D81+1095</f>
         <v>1095</v>
       </c>
-      <c r="I81" s="31">
-        <v>240</v>
-      </c>
-      <c r="J81" s="31">
-        <v>90</v>
-      </c>
-      <c r="K81" s="10">
+      <c r="I81" s="10">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="15">
+    <row r="82" spans="1:9" ht="15">
       <c r="A82" s="22">
         <v>94.8</v>
       </c>
@@ -8196,17 +7679,11 @@
         <f>D82+1825</f>
         <v>1825</v>
       </c>
-      <c r="I82" s="31">
-        <v>189</v>
-      </c>
-      <c r="J82" s="31">
-        <v>120</v>
-      </c>
-      <c r="K82" s="10">
+      <c r="I82" s="10">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="15">
+    <row r="83" spans="1:9" ht="15">
       <c r="A83" s="22">
         <v>146</v>
       </c>
@@ -8228,17 +7705,11 @@
         <f>D83+1825</f>
         <v>1825</v>
       </c>
-      <c r="I83" s="31">
-        <v>200</v>
-      </c>
-      <c r="J83" s="31">
-        <v>130</v>
-      </c>
-      <c r="K83" s="10">
+      <c r="I83" s="10">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="15">
+    <row r="84" spans="1:9" ht="15">
       <c r="A84" s="22">
         <v>169</v>
       </c>
@@ -8260,17 +7731,11 @@
         <f>D84+1095</f>
         <v>1095</v>
       </c>
-      <c r="I84" s="31">
-        <v>200</v>
-      </c>
-      <c r="J84" s="31">
-        <v>100</v>
-      </c>
-      <c r="K84" s="10">
+      <c r="I84" s="10">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="15">
+    <row r="85" spans="1:9" ht="15">
       <c r="A85" s="22">
         <v>145.9</v>
       </c>
@@ -8292,17 +7757,11 @@
         <f>D85+1825</f>
         <v>1825</v>
       </c>
-      <c r="I85" s="31">
-        <v>218</v>
-      </c>
-      <c r="J85" s="31">
-        <v>130</v>
-      </c>
-      <c r="K85" s="10">
+      <c r="I85" s="10">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="15">
+    <row r="86" spans="1:9" ht="15">
       <c r="A86" s="22">
         <v>118</v>
       </c>
@@ -8324,17 +7783,11 @@
         <f>D86+1095</f>
         <v>1095</v>
       </c>
-      <c r="I86" s="31">
-        <v>200</v>
-      </c>
-      <c r="J86" s="31">
-        <v>80</v>
-      </c>
-      <c r="K86" s="10">
+      <c r="I86" s="10">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="15">
+    <row r="87" spans="1:9" ht="15">
       <c r="A87" s="22">
         <v>227</v>
       </c>
@@ -8356,17 +7809,11 @@
         <f>D87+1095</f>
         <v>1095</v>
       </c>
-      <c r="I87" s="31">
-        <v>180</v>
-      </c>
-      <c r="J87" s="31">
-        <v>100</v>
-      </c>
-      <c r="K87" s="10">
+      <c r="I87" s="10">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="15">
+    <row r="88" spans="1:9" ht="15">
       <c r="A88">
         <v>79.900000000000006</v>
       </c>
@@ -8388,17 +7835,11 @@
         <f>D88+1095</f>
         <v>1095</v>
       </c>
-      <c r="I88" s="31">
-        <v>90</v>
-      </c>
-      <c r="J88" s="31">
-        <v>40</v>
-      </c>
-      <c r="K88" s="10">
+      <c r="I88" s="10">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="15">
+    <row r="89" spans="1:9" ht="15">
       <c r="A89" s="22">
         <v>63</v>
       </c>
@@ -8420,17 +7861,11 @@
         <f>D89+1825</f>
         <v>1825</v>
       </c>
-      <c r="I89" s="31">
-        <v>118</v>
-      </c>
-      <c r="J89" s="31">
-        <v>65</v>
-      </c>
-      <c r="K89" s="10">
+      <c r="I89" s="10">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="15">
+    <row r="90" spans="1:9" ht="15">
       <c r="A90" s="22">
         <v>268</v>
       </c>
@@ -8452,17 +7887,11 @@
         <f>D90+1095</f>
         <v>1095</v>
       </c>
-      <c r="I90" s="31">
-        <v>450</v>
-      </c>
-      <c r="J90" s="31">
-        <v>300</v>
-      </c>
-      <c r="K90" s="10">
+      <c r="I90" s="10">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="15">
+    <row r="91" spans="1:9" ht="15">
       <c r="A91" s="22">
         <v>178</v>
       </c>
@@ -8484,17 +7913,11 @@
         <f>D91+1095</f>
         <v>1095</v>
       </c>
-      <c r="I91" s="31">
-        <v>200</v>
-      </c>
-      <c r="J91" s="31">
-        <v>120</v>
-      </c>
-      <c r="K91" s="10">
+      <c r="I91" s="10">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="15">
+    <row r="92" spans="1:9" ht="15">
       <c r="A92" s="22">
         <v>130</v>
       </c>
@@ -8516,17 +7939,11 @@
         <f>D92+1825</f>
         <v>1825</v>
       </c>
-      <c r="I92" s="31">
-        <v>189</v>
-      </c>
-      <c r="J92" s="31">
-        <v>100</v>
-      </c>
-      <c r="K92" s="10">
+      <c r="I92" s="10">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="15">
+    <row r="93" spans="1:9" ht="15">
       <c r="A93" s="22">
         <v>181</v>
       </c>
@@ -8548,17 +7965,11 @@
         <f>D93+1095</f>
         <v>1095</v>
       </c>
-      <c r="I93" s="31">
-        <v>300</v>
-      </c>
-      <c r="J93" s="31">
-        <v>200</v>
-      </c>
-      <c r="K93" s="10">
+      <c r="I93" s="10">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="15">
+    <row r="94" spans="1:9" ht="15">
       <c r="A94" s="22">
         <v>185</v>
       </c>
@@ -8580,17 +7991,11 @@
         <f>D94+1095</f>
         <v>1095</v>
       </c>
-      <c r="I94" s="31">
-        <v>175</v>
-      </c>
-      <c r="J94" s="31">
-        <v>120</v>
-      </c>
-      <c r="K94" s="10">
+      <c r="I94" s="10">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="15">
+    <row r="95" spans="1:9" ht="15">
       <c r="A95" s="22">
         <v>174</v>
       </c>
@@ -8612,17 +8017,11 @@
         <f>D95+1825</f>
         <v>1825</v>
       </c>
-      <c r="I95" s="31">
-        <v>250</v>
-      </c>
-      <c r="J95" s="31">
-        <v>120</v>
-      </c>
-      <c r="K95" s="10">
+      <c r="I95" s="10">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="15">
+    <row r="96" spans="1:9" ht="15">
       <c r="A96" s="22">
         <v>90.33</v>
       </c>
@@ -8644,17 +8043,11 @@
         <f>D96+1095</f>
         <v>1095</v>
       </c>
-      <c r="I96" s="31">
-        <v>260</v>
-      </c>
-      <c r="J96" s="31">
-        <v>110</v>
-      </c>
-      <c r="K96" s="10">
+      <c r="I96" s="10">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="15">
+    <row r="97" spans="1:9" ht="15">
       <c r="A97" s="22">
         <v>319</v>
       </c>
@@ -8676,17 +8069,11 @@
         <f>D97+1095</f>
         <v>1095</v>
       </c>
-      <c r="I97" s="31">
-        <v>380</v>
-      </c>
-      <c r="J97" s="31">
-        <v>250</v>
-      </c>
-      <c r="K97" s="10">
+      <c r="I97" s="10">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15">
+    <row r="98" spans="1:9" ht="15">
       <c r="A98" s="22">
         <v>352</v>
       </c>
@@ -8708,17 +8095,11 @@
         <f>D98+1095</f>
         <v>1095</v>
       </c>
-      <c r="I98" s="31">
-        <v>380</v>
-      </c>
-      <c r="J98" s="31">
-        <v>215</v>
-      </c>
-      <c r="K98" s="10">
+      <c r="I98" s="10">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="15">
+    <row r="99" spans="1:9" ht="15">
       <c r="A99" s="22">
         <v>329</v>
       </c>
@@ -8740,17 +8121,11 @@
         <f>D99+1825</f>
         <v>1825</v>
       </c>
-      <c r="I99" s="31">
-        <v>300</v>
-      </c>
-      <c r="J99" s="31">
-        <v>250</v>
-      </c>
-      <c r="K99" s="10">
+      <c r="I99" s="10">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="15">
+    <row r="100" spans="1:9" ht="15">
       <c r="A100" s="22">
         <v>780</v>
       </c>
@@ -8772,17 +8147,11 @@
         <f t="shared" ref="H100:H133" si="6">D100+1095</f>
         <v>1095</v>
       </c>
-      <c r="I100" s="31">
-        <v>798</v>
-      </c>
-      <c r="J100" s="31">
-        <v>238</v>
-      </c>
-      <c r="K100" s="10">
+      <c r="I100" s="10">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="15">
+    <row r="101" spans="1:9" ht="15">
       <c r="A101" s="22">
         <v>540</v>
       </c>
@@ -8804,17 +8173,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I101" s="31">
-        <v>775</v>
-      </c>
-      <c r="J101" s="31">
-        <v>211</v>
-      </c>
-      <c r="K101" s="10">
+      <c r="I101" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="15">
+    <row r="102" spans="1:9" ht="15">
       <c r="A102" s="22">
         <v>1158</v>
       </c>
@@ -8836,17 +8199,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I102" s="31">
-        <v>1400</v>
-      </c>
-      <c r="J102" s="31">
-        <v>1000</v>
-      </c>
-      <c r="K102" s="10">
+      <c r="I102" s="10">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="15">
+    <row r="103" spans="1:9" ht="15">
       <c r="A103" s="22">
         <v>839</v>
       </c>
@@ -8868,17 +8225,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I103" s="31">
-        <v>800</v>
-      </c>
-      <c r="J103" s="31">
-        <v>500</v>
-      </c>
-      <c r="K103" s="10">
+      <c r="I103" s="10">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="15">
+    <row r="104" spans="1:9" ht="15">
       <c r="A104" s="22">
         <v>1690</v>
       </c>
@@ -8900,17 +8251,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I104" s="31">
-        <v>2000</v>
-      </c>
-      <c r="J104" s="31">
-        <v>1400</v>
-      </c>
-      <c r="K104" s="10">
+      <c r="I104" s="10">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="15">
+    <row r="105" spans="1:9" ht="15">
       <c r="A105" s="22">
         <v>818</v>
       </c>
@@ -8932,17 +8277,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I105" s="31">
-        <v>650</v>
-      </c>
-      <c r="J105" s="31">
-        <v>450</v>
-      </c>
-      <c r="K105" s="10">
+      <c r="I105" s="10">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="15">
+    <row r="106" spans="1:9" ht="15">
       <c r="A106" s="22">
         <v>1790</v>
       </c>
@@ -8964,17 +8303,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I106" s="31">
-        <v>2000</v>
-      </c>
-      <c r="J106" s="31">
-        <v>1400</v>
-      </c>
-      <c r="K106" s="10">
+      <c r="I106" s="10">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="15">
+    <row r="107" spans="1:9" ht="15">
       <c r="A107" s="22">
         <v>3000</v>
       </c>
@@ -8996,17 +8329,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I107" s="31">
-        <v>3000</v>
-      </c>
-      <c r="J107" s="31">
-        <v>2500</v>
-      </c>
-      <c r="K107" s="10">
+      <c r="I107" s="10">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="15">
+    <row r="108" spans="1:9" ht="15">
       <c r="A108" s="23" t="s">
         <v>1111</v>
       </c>
@@ -9027,17 +8354,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I108" s="31">
-        <v>2800</v>
-      </c>
-      <c r="J108" s="31">
-        <v>2400</v>
-      </c>
-      <c r="K108" s="10">
+      <c r="I108" s="10">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="15">
+    <row r="109" spans="1:9" ht="15">
       <c r="A109" s="22">
         <v>1895</v>
       </c>
@@ -9059,17 +8380,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I109" s="31">
-        <v>800</v>
-      </c>
-      <c r="J109" s="31">
-        <v>650</v>
-      </c>
-      <c r="K109" s="10">
+      <c r="I109" s="10">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="15">
+    <row r="110" spans="1:9" ht="15">
       <c r="A110" s="22">
         <v>799.98</v>
       </c>
@@ -9091,17 +8406,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I110" s="31">
-        <v>1100</v>
-      </c>
-      <c r="J110" s="31">
-        <v>800</v>
-      </c>
-      <c r="K110" s="10">
+      <c r="I110" s="10">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="15">
+    <row r="111" spans="1:9" ht="15">
       <c r="A111" s="22">
         <v>639</v>
       </c>
@@ -9123,17 +8432,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I111" s="31">
-        <v>900</v>
-      </c>
-      <c r="J111" s="31">
-        <v>700</v>
-      </c>
-      <c r="K111" s="10">
+      <c r="I111" s="10">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="15">
+    <row r="112" spans="1:9" ht="15">
       <c r="A112" s="22">
         <v>96.8</v>
       </c>
@@ -9155,17 +8458,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I112" s="31">
-        <v>150</v>
-      </c>
-      <c r="J112" s="31">
-        <v>100</v>
-      </c>
-      <c r="K112" s="10">
+      <c r="I112" s="10">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="15">
+    <row r="113" spans="1:9" ht="15">
       <c r="A113" s="22">
         <v>67</v>
       </c>
@@ -9187,17 +8484,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I113" s="31">
-        <v>180</v>
-      </c>
-      <c r="J113" s="31">
-        <v>60</v>
-      </c>
-      <c r="K113" s="10">
+      <c r="I113" s="10">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="15">
+    <row r="114" spans="1:9" ht="15">
       <c r="A114" s="22">
         <v>96.8</v>
       </c>
@@ -9219,17 +8510,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I114" s="31">
-        <v>150</v>
-      </c>
-      <c r="J114" s="31">
-        <v>100</v>
-      </c>
-      <c r="K114" s="10">
+      <c r="I114" s="10">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="15">
+    <row r="115" spans="1:9" ht="15">
       <c r="A115" s="22">
         <v>94</v>
       </c>
@@ -9251,17 +8536,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I115" s="31">
-        <v>200</v>
-      </c>
-      <c r="J115" s="31">
-        <v>100</v>
-      </c>
-      <c r="K115" s="10">
+      <c r="I115" s="10">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="15">
+    <row r="116" spans="1:9" ht="15">
       <c r="A116" s="22">
         <v>65</v>
       </c>
@@ -9283,17 +8562,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I116" s="31">
-        <v>100</v>
-      </c>
-      <c r="J116" s="31">
-        <v>60</v>
-      </c>
-      <c r="K116" s="10">
+      <c r="I116" s="10">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="15">
+    <row r="117" spans="1:9" ht="15">
       <c r="A117" s="22">
         <v>115.75</v>
       </c>
@@ -9315,17 +8588,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I117" s="31">
-        <v>348</v>
-      </c>
-      <c r="J117" s="31">
-        <v>100</v>
-      </c>
-      <c r="K117" s="10">
+      <c r="I117" s="10">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="15">
+    <row r="118" spans="1:9" ht="15">
       <c r="A118" s="22">
         <v>399</v>
       </c>
@@ -9347,17 +8614,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I118" s="31">
-        <v>337</v>
-      </c>
-      <c r="J118" s="31">
-        <v>100</v>
-      </c>
-      <c r="K118" s="10">
+      <c r="I118" s="10">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="15">
+    <row r="119" spans="1:9" ht="15">
       <c r="A119" s="22">
         <v>63</v>
       </c>
@@ -9379,17 +8640,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I119" s="31">
-        <v>180</v>
-      </c>
-      <c r="J119" s="31">
-        <v>70</v>
-      </c>
-      <c r="K119" s="10">
+      <c r="I119" s="10">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="15">
+    <row r="120" spans="1:9" ht="15">
       <c r="A120" s="22">
         <v>220</v>
       </c>
@@ -9411,17 +8666,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I120" s="31">
-        <v>200</v>
-      </c>
-      <c r="J120" s="31">
-        <v>130</v>
-      </c>
-      <c r="K120" s="10">
+      <c r="I120" s="10">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="15">
+    <row r="121" spans="1:9" ht="15">
       <c r="A121" s="22">
         <v>299</v>
       </c>
@@ -9443,17 +8692,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I121" s="31">
-        <v>200</v>
-      </c>
-      <c r="J121" s="31">
-        <v>130</v>
-      </c>
-      <c r="K121" s="10">
+      <c r="I121" s="10">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="15">
+    <row r="122" spans="1:9" ht="15">
       <c r="A122" s="22">
         <v>269</v>
       </c>
@@ -9475,17 +8718,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I122" s="31">
-        <v>200</v>
-      </c>
-      <c r="J122" s="31">
-        <v>130</v>
-      </c>
-      <c r="K122" s="10">
+      <c r="I122" s="10">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="15">
+    <row r="123" spans="1:9" ht="15">
       <c r="A123" s="22">
         <v>202</v>
       </c>
@@ -9507,17 +8744,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I123" s="31">
-        <v>210</v>
-      </c>
-      <c r="J123" s="31">
-        <v>150</v>
-      </c>
-      <c r="K123" s="10">
+      <c r="I123" s="10">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="15">
+    <row r="124" spans="1:9" ht="15">
       <c r="A124" s="22">
         <v>126</v>
       </c>
@@ -9539,17 +8770,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I124" s="31">
-        <v>180</v>
-      </c>
-      <c r="J124" s="31">
-        <v>150</v>
-      </c>
-      <c r="K124" s="10">
+      <c r="I124" s="10">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="15">
+    <row r="125" spans="1:9" ht="15">
       <c r="A125" s="22">
         <v>350</v>
       </c>
@@ -9571,17 +8796,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I125" s="31">
-        <v>250</v>
-      </c>
-      <c r="J125" s="31">
-        <v>180</v>
-      </c>
-      <c r="K125" s="10">
+      <c r="I125" s="10">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="15">
+    <row r="126" spans="1:9" ht="15">
       <c r="A126" s="22">
         <v>499</v>
       </c>
@@ -9603,17 +8822,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I126" s="31">
-        <v>700</v>
-      </c>
-      <c r="J126" s="31">
-        <v>480</v>
-      </c>
-      <c r="K126" s="10">
+      <c r="I126" s="10">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="15">
+    <row r="127" spans="1:9" ht="15">
       <c r="A127" s="22">
         <v>195</v>
       </c>
@@ -9635,17 +8848,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I127" s="31">
-        <v>220</v>
-      </c>
-      <c r="J127" s="31">
-        <v>180</v>
-      </c>
-      <c r="K127" s="10">
+      <c r="I127" s="10">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="15">
+    <row r="128" spans="1:9" ht="15">
       <c r="A128">
         <v>499</v>
       </c>
@@ -9667,17 +8874,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I128" s="31">
-        <v>480</v>
-      </c>
-      <c r="J128" s="31">
-        <v>340</v>
-      </c>
-      <c r="K128" s="10">
+      <c r="I128" s="10">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="15">
+    <row r="129" spans="1:9" ht="15">
       <c r="A129" s="22">
         <v>599</v>
       </c>
@@ -9699,17 +8900,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I129" s="31">
-        <v>500</v>
-      </c>
-      <c r="J129" s="31">
-        <v>350</v>
-      </c>
-      <c r="K129" s="10">
+      <c r="I129" s="10">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="15">
+    <row r="130" spans="1:9" ht="15">
       <c r="A130" s="22">
         <v>599</v>
       </c>
@@ -9731,17 +8926,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I130" s="31">
-        <v>400</v>
-      </c>
-      <c r="J130" s="31">
-        <v>250</v>
-      </c>
-      <c r="K130" s="10">
+      <c r="I130" s="10">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="15">
+    <row r="131" spans="1:9" ht="15">
       <c r="A131" s="22">
         <v>205</v>
       </c>
@@ -9763,17 +8952,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I131" s="31">
-        <v>260</v>
-      </c>
-      <c r="J131" s="31">
-        <v>200</v>
-      </c>
-      <c r="K131" s="10">
+      <c r="I131" s="10">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="15">
+    <row r="132" spans="1:9" ht="15">
       <c r="A132" s="22">
         <v>216</v>
       </c>
@@ -9795,17 +8978,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I132" s="31">
-        <v>180</v>
-      </c>
-      <c r="J132" s="31">
-        <v>130</v>
-      </c>
-      <c r="K132" s="10">
+      <c r="I132" s="10">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="15">
+    <row r="133" spans="1:9" ht="15">
       <c r="A133" s="22">
         <v>429</v>
       </c>
@@ -9827,17 +9004,11 @@
         <f t="shared" si="6"/>
         <v>1095</v>
       </c>
-      <c r="I133" s="31">
-        <v>280</v>
-      </c>
-      <c r="J133" s="31">
-        <v>240</v>
-      </c>
-      <c r="K133" s="10">
+      <c r="I133" s="10">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="15">
+    <row r="134" spans="1:9" ht="15">
       <c r="A134" s="22">
         <v>219</v>
       </c>
@@ -9859,17 +9030,11 @@
         <f>D134+1825</f>
         <v>1825</v>
       </c>
-      <c r="I134" s="31">
-        <v>200</v>
-      </c>
-      <c r="J134" s="31">
-        <v>120</v>
-      </c>
-      <c r="K134" s="10">
+      <c r="I134" s="10">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="15">
+    <row r="135" spans="1:9" ht="15">
       <c r="A135">
         <v>606</v>
       </c>
@@ -9891,17 +9056,11 @@
         <f t="shared" ref="H135:H144" si="7">D135+1095</f>
         <v>1095</v>
       </c>
-      <c r="I135" s="31">
-        <v>357</v>
-      </c>
-      <c r="J135" s="31">
-        <v>104</v>
-      </c>
-      <c r="K135" s="10">
+      <c r="I135" s="10">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="15">
+    <row r="136" spans="1:9" ht="15">
       <c r="A136" s="22">
         <v>199</v>
       </c>
@@ -9923,17 +9082,11 @@
         <f t="shared" si="7"/>
         <v>1095</v>
       </c>
-      <c r="I136" s="31">
-        <v>250</v>
-      </c>
-      <c r="J136" s="31">
-        <v>160</v>
-      </c>
-      <c r="K136" s="10">
+      <c r="I136" s="10">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="15">
+    <row r="137" spans="1:9" ht="15">
       <c r="A137" s="22">
         <v>259</v>
       </c>
@@ -9955,17 +9108,11 @@
         <f t="shared" si="7"/>
         <v>1095</v>
       </c>
-      <c r="I137" s="31">
-        <v>200</v>
-      </c>
-      <c r="J137" s="31">
-        <v>110</v>
-      </c>
-      <c r="K137" s="10">
+      <c r="I137" s="10">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="15">
+    <row r="138" spans="1:9" ht="15">
       <c r="A138" s="22">
         <v>195</v>
       </c>
@@ -9987,17 +9134,11 @@
         <f t="shared" si="7"/>
         <v>1095</v>
       </c>
-      <c r="I138" s="31">
-        <v>300</v>
-      </c>
-      <c r="J138" s="31">
-        <v>200</v>
-      </c>
-      <c r="K138" s="10">
+      <c r="I138" s="10">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="15">
+    <row r="139" spans="1:9" ht="15">
       <c r="A139" s="22">
         <v>459.99</v>
       </c>
@@ -10019,17 +9160,11 @@
         <f t="shared" si="7"/>
         <v>1095</v>
       </c>
-      <c r="I139" s="31">
-        <v>600</v>
-      </c>
-      <c r="J139" s="31">
-        <v>320</v>
-      </c>
-      <c r="K139" s="10">
+      <c r="I139" s="10">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="15">
+    <row r="140" spans="1:9" ht="15">
       <c r="A140" s="22">
         <v>609</v>
       </c>
@@ -10051,17 +9186,11 @@
         <f t="shared" si="7"/>
         <v>1095</v>
       </c>
-      <c r="I140" s="31">
-        <v>600</v>
-      </c>
-      <c r="J140" s="31">
-        <v>400</v>
-      </c>
-      <c r="K140" s="10">
+      <c r="I140" s="10">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="15">
+    <row r="141" spans="1:9" ht="15">
       <c r="A141" s="22">
         <v>429</v>
       </c>
@@ -10083,17 +9212,11 @@
         <f t="shared" si="7"/>
         <v>1095</v>
       </c>
-      <c r="I141" s="31">
-        <v>345</v>
-      </c>
-      <c r="J141" s="31">
-        <v>105</v>
-      </c>
-      <c r="K141" s="10">
+      <c r="I141" s="10">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="15">
+    <row r="142" spans="1:9" ht="15">
       <c r="A142" s="22">
         <v>169</v>
       </c>
@@ -10115,17 +9238,11 @@
         <f t="shared" si="7"/>
         <v>1095</v>
       </c>
-      <c r="I142" s="31">
-        <v>200</v>
-      </c>
-      <c r="J142" s="31">
-        <v>110</v>
-      </c>
-      <c r="K142" s="10">
+      <c r="I142" s="10">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="15">
+    <row r="143" spans="1:9" ht="15">
       <c r="A143" s="22">
         <v>210</v>
       </c>
@@ -10147,17 +9264,11 @@
         <f t="shared" si="7"/>
         <v>1095</v>
       </c>
-      <c r="I143" s="31">
-        <v>180</v>
-      </c>
-      <c r="J143" s="31">
-        <v>90</v>
-      </c>
-      <c r="K143" s="10">
+      <c r="I143" s="10">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="15">
+    <row r="144" spans="1:9" ht="15">
       <c r="A144" s="22">
         <v>595</v>
       </c>
@@ -10179,17 +9290,11 @@
         <f t="shared" si="7"/>
         <v>1095</v>
       </c>
-      <c r="I144" s="31">
-        <v>500</v>
-      </c>
-      <c r="J144" s="31">
-        <v>350</v>
-      </c>
-      <c r="K144" s="10">
+      <c r="I144" s="10">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="15">
+    <row r="145" spans="1:9" ht="15">
       <c r="A145" s="23" t="s">
         <v>1111</v>
       </c>
@@ -10210,17 +9315,11 @@
         <f>D145+1895</f>
         <v>1895</v>
       </c>
-      <c r="I145" s="31">
-        <v>500</v>
-      </c>
-      <c r="J145" s="31">
-        <v>250</v>
-      </c>
-      <c r="K145" s="10">
+      <c r="I145" s="10">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="15">
+    <row r="146" spans="1:9" ht="15">
       <c r="A146" s="22">
         <v>289</v>
       </c>
@@ -10242,17 +9341,11 @@
         <f>D146+1895</f>
         <v>1895</v>
       </c>
-      <c r="I146" s="31">
-        <v>450</v>
-      </c>
-      <c r="J146" s="31">
-        <v>300</v>
-      </c>
-      <c r="K146" s="10">
+      <c r="I146" s="10">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="15">
+    <row r="147" spans="1:9" ht="15">
       <c r="A147" s="23" t="s">
         <v>1111</v>
       </c>
@@ -10274,17 +9367,11 @@
         <f t="shared" ref="H147:H153" si="8">D147+1095</f>
         <v>1095</v>
       </c>
-      <c r="I147" s="31">
-        <v>500</v>
-      </c>
-      <c r="J147" s="31">
-        <v>250</v>
-      </c>
-      <c r="K147" s="10">
+      <c r="I147" s="10">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="15">
+    <row r="148" spans="1:9" ht="15">
       <c r="A148" s="23" t="s">
         <v>1111</v>
       </c>
@@ -10305,17 +9392,11 @@
         <f t="shared" si="8"/>
         <v>1095</v>
       </c>
-      <c r="I148" s="31">
-        <v>453</v>
-      </c>
-      <c r="J148" s="31">
-        <v>200</v>
-      </c>
-      <c r="K148" s="10">
+      <c r="I148" s="10">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="15">
+    <row r="149" spans="1:9" ht="15">
       <c r="A149" s="23" t="s">
         <v>1111</v>
       </c>
@@ -10337,17 +9418,11 @@
         <f t="shared" si="8"/>
         <v>1095</v>
       </c>
-      <c r="I149" s="31">
-        <v>453</v>
-      </c>
-      <c r="J149" s="31">
-        <v>200</v>
-      </c>
-      <c r="K149" s="10">
+      <c r="I149" s="10">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="15">
+    <row r="150" spans="1:9" ht="15">
       <c r="A150" s="23" t="s">
         <v>1111</v>
       </c>
@@ -10369,17 +9444,11 @@
         <f t="shared" si="8"/>
         <v>1095</v>
       </c>
-      <c r="I150" s="31">
-        <v>500</v>
-      </c>
-      <c r="J150" s="31">
-        <v>250</v>
-      </c>
-      <c r="K150" s="10">
+      <c r="I150" s="10">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="15">
+    <row r="151" spans="1:9" ht="15">
       <c r="A151" s="23" t="s">
         <v>1111</v>
       </c>
@@ -10400,17 +9469,11 @@
         <f t="shared" si="8"/>
         <v>1095</v>
       </c>
-      <c r="I151" s="31">
-        <v>453</v>
-      </c>
-      <c r="J151" s="31">
-        <v>200</v>
-      </c>
-      <c r="K151" s="10">
+      <c r="I151" s="10">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="15">
+    <row r="152" spans="1:9" ht="15">
       <c r="A152" s="23" t="s">
         <v>1111</v>
       </c>
@@ -10432,17 +9495,11 @@
         <f t="shared" si="8"/>
         <v>1095</v>
       </c>
-      <c r="I152" s="31">
-        <v>580</v>
-      </c>
-      <c r="J152" s="31">
-        <v>250</v>
-      </c>
-      <c r="K152" s="10">
+      <c r="I152" s="10">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="15">
+    <row r="153" spans="1:9" ht="15">
       <c r="A153" s="23" t="s">
         <v>1111</v>
       </c>
@@ -10464,17 +9521,11 @@
         <f t="shared" si="8"/>
         <v>1095</v>
       </c>
-      <c r="I153" s="31">
-        <v>450</v>
-      </c>
-      <c r="J153" s="31">
-        <v>350</v>
-      </c>
-      <c r="K153" s="10">
+      <c r="I153" s="10">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="15">
+    <row r="154" spans="1:9" ht="15">
       <c r="A154" s="22">
         <v>598</v>
       </c>
@@ -10496,17 +9547,11 @@
         <f t="shared" ref="H154:H170" si="9">D154+1095</f>
         <v>1095</v>
       </c>
-      <c r="I154" s="31">
-        <v>580</v>
-      </c>
-      <c r="J154" s="31">
-        <v>250</v>
-      </c>
-      <c r="K154" s="10">
+      <c r="I154" s="10">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="15">
+    <row r="155" spans="1:9" ht="15">
       <c r="A155" s="23" t="s">
         <v>1111</v>
       </c>
@@ -10528,17 +9573,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I155" s="31">
-        <v>350</v>
-      </c>
-      <c r="J155" s="31">
-        <v>200</v>
-      </c>
-      <c r="K155" s="10">
+      <c r="I155" s="10">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="15">
+    <row r="156" spans="1:9" ht="15">
       <c r="A156">
         <v>111.9</v>
       </c>
@@ -10560,17 +9599,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I156" s="31">
-        <v>200</v>
-      </c>
-      <c r="J156" s="31">
-        <v>100</v>
-      </c>
-      <c r="K156" s="10">
+      <c r="I156" s="10">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="15">
+    <row r="157" spans="1:9" ht="15">
       <c r="A157" s="22">
         <v>2700</v>
       </c>
@@ -10592,17 +9625,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I157" s="31">
-        <v>2000</v>
-      </c>
-      <c r="J157" s="31">
-        <v>1300</v>
-      </c>
-      <c r="K157" s="10">
+      <c r="I157" s="10">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="15">
+    <row r="158" spans="1:9" ht="15">
       <c r="A158" s="22">
         <v>259</v>
       </c>
@@ -10624,17 +9651,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I158" s="31">
-        <v>250</v>
-      </c>
-      <c r="J158" s="31">
-        <v>150</v>
-      </c>
-      <c r="K158" s="10">
+      <c r="I158" s="10">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="15">
+    <row r="159" spans="1:9" ht="15">
       <c r="A159" s="22">
         <v>333</v>
       </c>
@@ -10656,17 +9677,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I159" s="31">
-        <v>450</v>
-      </c>
-      <c r="J159" s="31">
-        <v>300</v>
-      </c>
-      <c r="K159" s="10">
+      <c r="I159" s="10">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="15">
+    <row r="160" spans="1:9" ht="15">
       <c r="A160" s="22">
         <v>438</v>
       </c>
@@ -10688,17 +9703,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I160" s="31">
-        <v>600</v>
-      </c>
-      <c r="J160" s="31">
-        <v>500</v>
-      </c>
-      <c r="K160" s="10">
+      <c r="I160" s="10">
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="15">
+    <row r="161" spans="1:9" ht="15">
       <c r="A161" s="23" t="s">
         <v>1111</v>
       </c>
@@ -10720,17 +9729,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I161" s="31">
-        <v>600</v>
-      </c>
-      <c r="J161" s="31">
-        <v>450</v>
-      </c>
-      <c r="K161" s="10">
+      <c r="I161" s="10">
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="15">
+    <row r="162" spans="1:9" ht="15">
       <c r="A162" s="22">
         <v>320</v>
       </c>
@@ -10752,17 +9755,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I162" s="31">
-        <v>230</v>
-      </c>
-      <c r="J162" s="31">
-        <v>120</v>
-      </c>
-      <c r="K162" s="10">
+      <c r="I162" s="10">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="15">
+    <row r="163" spans="1:9" ht="15">
       <c r="A163" s="22">
         <v>129</v>
       </c>
@@ -10784,17 +9781,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I163" s="31">
-        <v>250</v>
-      </c>
-      <c r="J163" s="31">
-        <v>150</v>
-      </c>
-      <c r="K163" s="10">
+      <c r="I163" s="10">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="15">
+    <row r="164" spans="1:9" ht="15">
       <c r="A164" s="22">
         <v>606</v>
       </c>
@@ -10816,17 +9807,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I164" s="31">
-        <v>750</v>
-      </c>
-      <c r="J164" s="31">
-        <v>420</v>
-      </c>
-      <c r="K164" s="10">
+      <c r="I164" s="10">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="15">
+    <row r="165" spans="1:9" ht="15">
       <c r="A165" s="22">
         <v>160</v>
       </c>
@@ -10848,17 +9833,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I165" s="31">
-        <v>200</v>
-      </c>
-      <c r="J165" s="31">
-        <v>90</v>
-      </c>
-      <c r="K165" s="10">
+      <c r="I165" s="10">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="15">
+    <row r="166" spans="1:9" ht="15">
       <c r="A166" s="22">
         <v>240</v>
       </c>
@@ -10880,17 +9859,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I166" s="31">
-        <v>450</v>
-      </c>
-      <c r="J166" s="31">
-        <v>200</v>
-      </c>
-      <c r="K166" s="10">
+      <c r="I166" s="10">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="15">
+    <row r="167" spans="1:9" ht="15">
       <c r="A167" s="22">
         <v>200</v>
       </c>
@@ -10912,17 +9885,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I167" s="31">
-        <v>200</v>
-      </c>
-      <c r="J167" s="31">
-        <v>100</v>
-      </c>
-      <c r="K167" s="10">
+      <c r="I167" s="10">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="15">
+    <row r="168" spans="1:9" ht="15">
       <c r="A168" s="22">
         <v>209</v>
       </c>
@@ -10944,17 +9911,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I168" s="31">
-        <v>372</v>
-      </c>
-      <c r="J168" s="31">
-        <v>119</v>
-      </c>
-      <c r="K168" s="10">
+      <c r="I168" s="10">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="15">
+    <row r="169" spans="1:9" ht="15">
       <c r="A169" s="22">
         <v>370</v>
       </c>
@@ -10976,17 +9937,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I169" s="31">
-        <v>280</v>
-      </c>
-      <c r="J169" s="31">
-        <v>200</v>
-      </c>
-      <c r="K169" s="10">
+      <c r="I169" s="10">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="15">
+    <row r="170" spans="1:9" ht="15">
       <c r="A170" s="22">
         <v>450</v>
       </c>
@@ -11008,17 +9963,11 @@
         <f t="shared" si="9"/>
         <v>1095</v>
       </c>
-      <c r="I170" s="31">
-        <v>500</v>
-      </c>
-      <c r="J170" s="31">
-        <v>400</v>
-      </c>
-      <c r="K170" s="10">
+      <c r="I170" s="10">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="15">
+    <row r="171" spans="1:9" ht="15">
       <c r="A171" s="22">
         <v>382</v>
       </c>
@@ -11040,17 +9989,11 @@
         <f>D171+1825</f>
         <v>1825</v>
       </c>
-      <c r="I171" s="31">
-        <v>400</v>
-      </c>
-      <c r="J171" s="31">
-        <v>300</v>
-      </c>
-      <c r="K171" s="10">
+      <c r="I171" s="10">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="15">
+    <row r="172" spans="1:9" ht="15">
       <c r="A172" s="22">
         <v>1212</v>
       </c>
@@ -11072,17 +10015,11 @@
         <f>D172+1095</f>
         <v>1095</v>
       </c>
-      <c r="I172" s="31">
-        <v>700</v>
-      </c>
-      <c r="J172" s="31">
-        <v>500</v>
-      </c>
-      <c r="K172" s="10">
+      <c r="I172" s="10">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="15">
+    <row r="173" spans="1:9" ht="15">
       <c r="A173" s="22">
         <v>388</v>
       </c>
@@ -11104,17 +10041,11 @@
         <f>D173+1095</f>
         <v>1095</v>
       </c>
-      <c r="I173" s="31">
-        <v>350</v>
-      </c>
-      <c r="J173" s="31">
-        <v>150</v>
-      </c>
-      <c r="K173" s="10">
+      <c r="I173" s="10">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="15">
+    <row r="174" spans="1:9" ht="15">
       <c r="A174" s="22">
         <v>399</v>
       </c>
@@ -11136,17 +10067,11 @@
         <f>D174+1095</f>
         <v>1095</v>
       </c>
-      <c r="I174" s="31">
-        <v>200</v>
-      </c>
-      <c r="J174" s="31">
-        <v>100</v>
-      </c>
-      <c r="K174" s="10">
+      <c r="I174" s="10">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="15">
+    <row r="175" spans="1:9" ht="15">
       <c r="A175" s="22">
         <v>149</v>
       </c>
@@ -11168,17 +10093,11 @@
         <f>D175+1095</f>
         <v>1095</v>
       </c>
-      <c r="I175" s="31">
-        <v>150</v>
-      </c>
-      <c r="J175" s="31">
-        <v>100</v>
-      </c>
-      <c r="K175" s="10">
+      <c r="I175" s="10">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="15">
+    <row r="176" spans="1:9" ht="15">
       <c r="A176" s="22">
         <v>499</v>
       </c>
@@ -11200,17 +10119,11 @@
         <f>D176+1895</f>
         <v>1895</v>
       </c>
-      <c r="I176" s="31">
-        <v>600</v>
-      </c>
-      <c r="J176" s="31">
-        <v>300</v>
-      </c>
-      <c r="K176" s="10">
+      <c r="I176" s="10">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="15">
+    <row r="177" spans="1:9" ht="15">
       <c r="A177" s="22">
         <v>499</v>
       </c>
@@ -11232,17 +10145,11 @@
         <f>D177+1825</f>
         <v>1825</v>
       </c>
-      <c r="I177" s="31">
-        <v>400</v>
-      </c>
-      <c r="J177" s="31">
-        <v>200</v>
-      </c>
-      <c r="K177" s="10">
+      <c r="I177" s="10">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="15">
+    <row r="178" spans="1:9" ht="15">
       <c r="A178" s="22">
         <v>75</v>
       </c>
@@ -11264,17 +10171,11 @@
         <f>D178+1095</f>
         <v>1095</v>
       </c>
-      <c r="I178" s="31">
-        <v>150</v>
-      </c>
-      <c r="J178" s="31">
-        <v>50</v>
-      </c>
-      <c r="K178" s="10">
+      <c r="I178" s="10">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="15">
+    <row r="179" spans="1:9" ht="15">
       <c r="A179" s="22">
         <v>521</v>
       </c>
@@ -11296,17 +10197,11 @@
         <f>D179+1095</f>
         <v>1095</v>
       </c>
-      <c r="I179" s="31">
-        <v>700</v>
-      </c>
-      <c r="J179" s="31">
-        <v>400</v>
-      </c>
-      <c r="K179" s="10">
+      <c r="I179" s="10">
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="15">
+    <row r="180" spans="1:9" ht="15">
       <c r="A180" s="23" t="s">
         <v>1111</v>
       </c>
@@ -11327,17 +10222,11 @@
         <f>D180+1825</f>
         <v>1825</v>
       </c>
-      <c r="I180" s="31">
-        <v>700</v>
-      </c>
-      <c r="J180" s="31">
-        <v>400</v>
-      </c>
-      <c r="K180" s="10">
+      <c r="I180" s="10">
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="15">
+    <row r="181" spans="1:9" ht="15">
       <c r="A181" s="26">
         <v>300</v>
       </c>
@@ -11359,17 +10248,11 @@
         <f t="shared" ref="H181" si="10">D181+1095</f>
         <v>1095</v>
       </c>
-      <c r="I181" s="31">
-        <v>300</v>
-      </c>
-      <c r="J181" s="31">
-        <v>210</v>
-      </c>
-      <c r="K181" s="10">
+      <c r="I181" s="10">
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="15">
+    <row r="182" spans="1:9" ht="15">
       <c r="A182" s="22">
         <v>253</v>
       </c>
@@ -11391,17 +10274,11 @@
         <f>D182+1825</f>
         <v>1825</v>
       </c>
-      <c r="I182" s="31">
-        <v>300</v>
-      </c>
-      <c r="J182" s="31">
-        <v>210</v>
-      </c>
-      <c r="K182" s="10">
+      <c r="I182" s="10">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="15">
+    <row r="183" spans="1:9" ht="15">
       <c r="A183" s="22">
         <v>236</v>
       </c>
@@ -11423,17 +10300,11 @@
         <f t="shared" ref="H183" si="11">D183+1095</f>
         <v>1095</v>
       </c>
-      <c r="I183" s="31">
-        <v>300</v>
-      </c>
-      <c r="J183" s="31">
-        <v>210</v>
-      </c>
-      <c r="K183" s="10">
+      <c r="I183" s="10">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="15">
+    <row r="184" spans="1:9" ht="15">
       <c r="A184" s="22">
         <v>236</v>
       </c>
@@ -11455,17 +10326,11 @@
         <f>D184+1825</f>
         <v>1825</v>
       </c>
-      <c r="I184" s="31">
-        <v>300</v>
-      </c>
-      <c r="J184" s="31">
-        <v>210</v>
-      </c>
-      <c r="K184" s="10">
+      <c r="I184" s="10">
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="15">
+    <row r="185" spans="1:9" ht="15">
       <c r="A185" s="22">
         <v>14.49</v>
       </c>
@@ -11487,17 +10352,11 @@
         <f>D185+1095</f>
         <v>1095</v>
       </c>
-      <c r="I185" s="31">
-        <v>30</v>
-      </c>
-      <c r="J185" s="31">
-        <v>15</v>
-      </c>
-      <c r="K185" s="10">
+      <c r="I185" s="10">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="15">
+    <row r="186" spans="1:9" ht="15">
       <c r="A186" s="22">
         <v>89.9</v>
       </c>
@@ -11519,17 +10378,11 @@
         <f>D186+1095</f>
         <v>1095</v>
       </c>
-      <c r="I186" s="31">
-        <v>100</v>
-      </c>
-      <c r="J186" s="31">
-        <v>70</v>
-      </c>
-      <c r="K186" s="10">
+      <c r="I186" s="10">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="15">
+    <row r="187" spans="1:9" ht="15">
       <c r="A187" s="22">
         <v>123</v>
       </c>
@@ -11551,17 +10404,11 @@
         <f>D187+1095</f>
         <v>1095</v>
       </c>
-      <c r="I187" s="32">
-        <v>150</v>
-      </c>
-      <c r="J187" s="32">
-        <v>70</v>
-      </c>
-      <c r="K187" s="10">
+      <c r="I187" s="10">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="15">
+    <row r="188" spans="1:9" ht="15">
       <c r="A188" s="22">
         <v>98</v>
       </c>
@@ -11583,17 +10430,11 @@
         <f>D188+1000</f>
         <v>1000</v>
       </c>
-      <c r="I188" s="31">
-        <v>78</v>
-      </c>
-      <c r="J188" s="31">
-        <v>17</v>
-      </c>
-      <c r="K188" s="10">
+      <c r="I188" s="10">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="15">
+    <row r="189" spans="1:9" ht="15">
       <c r="A189" s="22">
         <v>360</v>
       </c>
@@ -11615,17 +10456,11 @@
         <f>D189+912</f>
         <v>912</v>
       </c>
-      <c r="I189" s="31">
-        <v>129</v>
-      </c>
-      <c r="J189" s="31">
-        <v>31</v>
-      </c>
-      <c r="K189" s="10">
+      <c r="I189" s="10">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="15">
+    <row r="190" spans="1:9" ht="15">
       <c r="A190" s="22">
         <v>369</v>
       </c>
@@ -11647,17 +10482,11 @@
         <f>D190+1095</f>
         <v>1095</v>
       </c>
-      <c r="I190" s="31">
-        <v>160</v>
-      </c>
-      <c r="J190" s="31">
-        <v>45</v>
-      </c>
-      <c r="K190" s="10">
+      <c r="I190" s="10">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="15">
+    <row r="191" spans="1:9" ht="15">
       <c r="A191" s="22">
         <v>185</v>
       </c>
@@ -11679,17 +10508,11 @@
         <f>D191+1460</f>
         <v>1460</v>
       </c>
-      <c r="I191" s="31">
-        <v>150</v>
-      </c>
-      <c r="J191" s="31">
-        <v>60</v>
-      </c>
-      <c r="K191" s="10">
+      <c r="I191" s="10">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="15">
+    <row r="192" spans="1:9" ht="15">
       <c r="A192" s="22">
         <v>306</v>
       </c>
@@ -11711,17 +10534,11 @@
         <f>D192+1095</f>
         <v>1095</v>
       </c>
-      <c r="I192" s="31">
-        <v>555</v>
-      </c>
-      <c r="J192" s="31">
-        <v>177</v>
-      </c>
-      <c r="K192" s="10">
+      <c r="I192" s="10">
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="15">
+    <row r="193" spans="1:9" ht="15">
       <c r="A193" s="22">
         <v>749</v>
       </c>
@@ -11743,17 +10560,11 @@
         <f>D193+1095</f>
         <v>1095</v>
       </c>
-      <c r="I193" s="31">
-        <v>500</v>
-      </c>
-      <c r="J193" s="31">
-        <v>400</v>
-      </c>
-      <c r="K193" s="10">
+      <c r="I193" s="10">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="15">
+    <row r="194" spans="1:9" ht="15">
       <c r="A194" s="22">
         <v>112</v>
       </c>
@@ -11775,17 +10586,11 @@
         <f>D194+1095</f>
         <v>1095</v>
       </c>
-      <c r="I194" s="31">
-        <v>150</v>
-      </c>
-      <c r="J194" s="31">
-        <v>90</v>
-      </c>
-      <c r="K194" s="10">
+      <c r="I194" s="10">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="15">
+    <row r="195" spans="1:9" ht="15">
       <c r="A195" s="22">
         <v>444</v>
       </c>
@@ -11807,17 +10612,11 @@
         <f>D195+1095</f>
         <v>1095</v>
       </c>
-      <c r="I195" s="31">
-        <v>200</v>
-      </c>
-      <c r="J195" s="31">
-        <v>120</v>
-      </c>
-      <c r="K195" s="10">
+      <c r="I195" s="10">
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="15">
+    <row r="196" spans="1:9" ht="15">
       <c r="A196" s="22">
         <v>589</v>
       </c>
@@ -11839,17 +10638,11 @@
         <f>D196+1095</f>
         <v>1095</v>
       </c>
-      <c r="I196" s="31">
-        <v>500</v>
-      </c>
-      <c r="J196" s="31">
-        <v>300</v>
-      </c>
-      <c r="K196" s="10">
+      <c r="I196" s="10">
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="15">
+    <row r="197" spans="1:9" ht="15">
       <c r="A197" s="22">
         <v>98</v>
       </c>
@@ -11871,17 +10664,11 @@
         <f>D197+1000</f>
         <v>1000</v>
       </c>
-      <c r="I197" s="31">
-        <v>60</v>
-      </c>
-      <c r="J197" s="31">
-        <v>40</v>
-      </c>
-      <c r="K197" s="10">
+      <c r="I197" s="10">
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="15">
+    <row r="198" spans="1:9" ht="15">
       <c r="A198" s="22">
         <v>1498</v>
       </c>
@@ -11903,17 +10690,11 @@
         <f t="shared" ref="H198:H216" si="12">D198+1095</f>
         <v>1095</v>
       </c>
-      <c r="I198" s="31">
-        <v>550</v>
-      </c>
-      <c r="J198" s="31">
-        <v>400</v>
-      </c>
-      <c r="K198" s="10">
+      <c r="I198" s="10">
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="15">
+    <row r="199" spans="1:9" ht="15">
       <c r="A199" s="22">
         <v>379</v>
       </c>
@@ -11935,17 +10716,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I199" s="31">
-        <v>500</v>
-      </c>
-      <c r="J199" s="31">
-        <v>300</v>
-      </c>
-      <c r="K199" s="10">
+      <c r="I199" s="10">
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="15">
+    <row r="200" spans="1:9" ht="15">
       <c r="A200" s="22">
         <v>186</v>
       </c>
@@ -11967,17 +10742,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I200" s="31">
-        <v>300</v>
-      </c>
-      <c r="J200" s="31">
-        <v>180</v>
-      </c>
-      <c r="K200" s="10">
+      <c r="I200" s="10">
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="15">
+    <row r="201" spans="1:9" ht="15">
       <c r="A201">
         <v>599</v>
       </c>
@@ -11999,17 +10768,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I201" s="31">
-        <v>550</v>
-      </c>
-      <c r="J201" s="31">
-        <v>400</v>
-      </c>
-      <c r="K201" s="10">
+      <c r="I201" s="10">
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="15">
+    <row r="202" spans="1:9" ht="15">
       <c r="A202" s="22">
         <v>129</v>
       </c>
@@ -12031,17 +10794,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I202" s="31">
-        <v>150</v>
-      </c>
-      <c r="J202" s="31">
-        <v>80</v>
-      </c>
-      <c r="K202" s="10">
+      <c r="I202" s="10">
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="15">
+    <row r="203" spans="1:9" ht="15">
       <c r="A203" s="22">
         <v>119</v>
       </c>
@@ -12063,17 +10820,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I203" s="31">
-        <v>150</v>
-      </c>
-      <c r="J203" s="31">
-        <v>70</v>
-      </c>
-      <c r="K203" s="10">
+      <c r="I203" s="10">
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="15">
+    <row r="204" spans="1:9" ht="15">
       <c r="A204" s="22">
         <v>399</v>
       </c>
@@ -12095,17 +10846,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I204" s="31">
-        <v>350</v>
-      </c>
-      <c r="J204" s="31">
-        <v>200</v>
-      </c>
-      <c r="K204" s="10">
+      <c r="I204" s="10">
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="15">
+    <row r="205" spans="1:9" ht="15">
       <c r="A205" s="22">
         <v>105</v>
       </c>
@@ -12127,17 +10872,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I205" s="31">
-        <v>180</v>
-      </c>
-      <c r="J205" s="31">
-        <v>100</v>
-      </c>
-      <c r="K205" s="10">
+      <c r="I205" s="10">
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="15">
+    <row r="206" spans="1:9" ht="15">
       <c r="A206" s="22">
         <v>94</v>
       </c>
@@ -12159,17 +10898,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I206" s="31">
-        <v>150</v>
-      </c>
-      <c r="J206" s="31">
-        <v>100</v>
-      </c>
-      <c r="K206" s="10">
+      <c r="I206" s="10">
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="15">
+    <row r="207" spans="1:9" ht="15">
       <c r="A207" s="22">
         <v>94</v>
       </c>
@@ -12191,17 +10924,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I207" s="31">
-        <v>300</v>
-      </c>
-      <c r="J207" s="31">
-        <v>200</v>
-      </c>
-      <c r="K207" s="10">
+      <c r="I207" s="10">
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="15">
+    <row r="208" spans="1:9" ht="15">
       <c r="A208" s="22">
         <v>239</v>
       </c>
@@ -12223,17 +10950,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I208" s="31">
-        <v>200</v>
-      </c>
-      <c r="J208" s="31">
-        <v>100</v>
-      </c>
-      <c r="K208" s="10">
+      <c r="I208" s="10">
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="15">
+    <row r="209" spans="1:9" ht="15">
       <c r="A209" s="22">
         <v>61.9</v>
       </c>
@@ -12255,17 +10976,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I209" s="31">
-        <v>60</v>
-      </c>
-      <c r="J209" s="31">
-        <v>40</v>
-      </c>
-      <c r="K209" s="10">
+      <c r="I209" s="10">
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="15">
+    <row r="210" spans="1:9" ht="15">
       <c r="A210" s="22">
         <v>78.900000000000006</v>
       </c>
@@ -12287,17 +11002,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I210" s="31">
-        <v>80</v>
-      </c>
-      <c r="J210" s="31">
-        <v>60</v>
-      </c>
-      <c r="K210" s="10">
+      <c r="I210" s="10">
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="15">
+    <row r="211" spans="1:9" ht="15">
       <c r="A211" s="22">
         <v>73.400000000000006</v>
       </c>
@@ -12319,17 +11028,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I211" s="31">
-        <v>130</v>
-      </c>
-      <c r="J211" s="31">
-        <v>60</v>
-      </c>
-      <c r="K211" s="10">
+      <c r="I211" s="10">
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="15">
+    <row r="212" spans="1:9" ht="15">
       <c r="A212" s="22">
         <v>109</v>
       </c>
@@ -12351,17 +11054,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I212" s="31">
-        <v>135</v>
-      </c>
-      <c r="J212" s="31">
-        <v>100</v>
-      </c>
-      <c r="K212" s="10">
+      <c r="I212" s="10">
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="15">
+    <row r="213" spans="1:9" ht="15">
       <c r="A213" s="22">
         <v>92.9</v>
       </c>
@@ -12383,17 +11080,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I213" s="31">
-        <v>190</v>
-      </c>
-      <c r="J213" s="31">
-        <v>100</v>
-      </c>
-      <c r="K213" s="10">
+      <c r="I213" s="10">
         <v>212</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="15">
+    <row r="214" spans="1:9" ht="15">
       <c r="A214" s="22">
         <v>206</v>
       </c>
@@ -12415,17 +11106,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I214" s="31">
-        <v>300</v>
-      </c>
-      <c r="J214" s="31">
-        <v>170</v>
-      </c>
-      <c r="K214" s="10">
+      <c r="I214" s="10">
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="15">
+    <row r="215" spans="1:9" ht="15">
       <c r="A215" s="22">
         <v>206</v>
       </c>
@@ -12447,17 +11132,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I215" s="31">
-        <v>300</v>
-      </c>
-      <c r="J215" s="31">
-        <v>170</v>
-      </c>
-      <c r="K215" s="10">
+      <c r="I215" s="10">
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="15">
+    <row r="216" spans="1:9" ht="15">
       <c r="A216" s="22">
         <v>211</v>
       </c>
@@ -12479,17 +11158,11 @@
         <f t="shared" si="12"/>
         <v>1095</v>
       </c>
-      <c r="I216" s="31">
-        <v>200</v>
-      </c>
-      <c r="J216" s="31">
-        <v>150</v>
-      </c>
-      <c r="K216" s="10">
+      <c r="I216" s="10">
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="15">
+    <row r="217" spans="1:9" ht="15">
       <c r="A217" s="23">
         <v>185</v>
       </c>
@@ -12511,17 +11184,11 @@
         <f>D217+1460</f>
         <v>1460</v>
       </c>
-      <c r="I217" s="31">
-        <v>230</v>
-      </c>
-      <c r="J217" s="31">
-        <v>120</v>
-      </c>
-      <c r="K217" s="10">
+      <c r="I217" s="10">
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="15">
+    <row r="218" spans="1:9" ht="15">
       <c r="A218" s="22">
         <v>201.29</v>
       </c>
@@ -12543,17 +11210,11 @@
         <f>D218+1094</f>
         <v>1094</v>
       </c>
-      <c r="I218" s="31">
-        <v>200</v>
-      </c>
-      <c r="J218" s="31">
-        <v>120</v>
-      </c>
-      <c r="K218" s="10">
+      <c r="I218" s="10">
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="15">
+    <row r="219" spans="1:9" ht="15">
       <c r="A219" s="22">
         <v>598</v>
       </c>
@@ -12575,17 +11236,11 @@
         <f>D219+1094</f>
         <v>1094</v>
       </c>
-      <c r="I219" s="31">
-        <v>600</v>
-      </c>
-      <c r="J219" s="31">
-        <v>450</v>
-      </c>
-      <c r="K219" s="10">
+      <c r="I219" s="10">
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="15">
+    <row r="220" spans="1:9" ht="15">
       <c r="A220" s="22">
         <v>400</v>
       </c>
@@ -12607,17 +11262,11 @@
         <f>D220+1825</f>
         <v>1825</v>
       </c>
-      <c r="I220" s="31">
-        <v>320</v>
-      </c>
-      <c r="J220" s="31">
-        <v>200</v>
-      </c>
-      <c r="K220" s="10">
+      <c r="I220" s="10">
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="15">
+    <row r="221" spans="1:9" ht="15">
       <c r="A221">
         <v>289</v>
       </c>
@@ -12639,17 +11288,11 @@
         <f>D221+1825</f>
         <v>1825</v>
       </c>
-      <c r="I221" s="31">
-        <v>300</v>
-      </c>
-      <c r="J221" s="31">
-        <v>170</v>
-      </c>
-      <c r="K221" s="10">
+      <c r="I221" s="10">
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="15">
+    <row r="222" spans="1:9" ht="15">
       <c r="A222">
         <v>275</v>
       </c>
@@ -12671,17 +11314,11 @@
         <f t="shared" ref="H222" si="13">D222+1095</f>
         <v>1095</v>
       </c>
-      <c r="I222" s="31">
-        <v>350</v>
-      </c>
-      <c r="J222" s="31">
-        <v>200</v>
-      </c>
-      <c r="K222" s="10">
+      <c r="I222" s="10">
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="15">
+    <row r="223" spans="1:9" ht="15">
       <c r="A223">
         <v>298</v>
       </c>
@@ -12702,17 +11339,11 @@
         <f>D223+1095</f>
         <v>1095</v>
       </c>
-      <c r="I223" s="31">
-        <v>350</v>
-      </c>
-      <c r="J223" s="31">
-        <v>200</v>
-      </c>
-      <c r="K223" s="10">
+      <c r="I223" s="10">
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="15">
+    <row r="224" spans="1:9" ht="15">
       <c r="A224" s="22">
         <v>299</v>
       </c>
@@ -12734,17 +11365,11 @@
         <f>D224+1095</f>
         <v>1095</v>
       </c>
-      <c r="I224" s="31">
-        <v>547</v>
-      </c>
-      <c r="J224" s="31">
-        <v>160</v>
-      </c>
-      <c r="K224" s="10">
+      <c r="I224" s="10">
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="1:11" ht="15">
+    <row r="225" spans="1:9" ht="15">
       <c r="A225" s="22">
         <v>121</v>
       </c>
@@ -12766,17 +11391,11 @@
         <f>D225+1825</f>
         <v>1825</v>
       </c>
-      <c r="I225" s="31">
-        <v>200</v>
-      </c>
-      <c r="J225" s="31">
-        <v>130</v>
-      </c>
-      <c r="K225" s="10">
+      <c r="I225" s="10">
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="1:11" ht="15">
+    <row r="226" spans="1:9" ht="15">
       <c r="A226" s="22">
         <v>190</v>
       </c>
@@ -12798,17 +11417,11 @@
         <f>D226+1095</f>
         <v>1095</v>
       </c>
-      <c r="I226" s="31">
-        <v>300</v>
-      </c>
-      <c r="J226" s="31">
-        <v>250</v>
-      </c>
-      <c r="K226" s="10">
+      <c r="I226" s="10">
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="15">
+    <row r="227" spans="1:9" ht="15">
       <c r="A227" s="22">
         <v>588</v>
       </c>
@@ -12830,17 +11443,11 @@
         <f>D227+1095</f>
         <v>1095</v>
       </c>
-      <c r="I227" s="31">
-        <v>500</v>
-      </c>
-      <c r="J227" s="31">
-        <v>300</v>
-      </c>
-      <c r="K227" s="10">
+      <c r="I227" s="10">
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="15">
+    <row r="228" spans="1:9" ht="15">
       <c r="A228" s="22">
         <v>276.89999999999998</v>
       </c>
@@ -12862,17 +11469,11 @@
         <f>D228+1825</f>
         <v>1825</v>
       </c>
-      <c r="I228" s="31">
-        <v>398</v>
-      </c>
-      <c r="J228" s="31">
-        <v>304</v>
-      </c>
-      <c r="K228" s="10">
+      <c r="I228" s="10">
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="15">
+    <row r="229" spans="1:9" ht="15">
       <c r="A229" s="22">
         <v>599</v>
       </c>
@@ -12894,17 +11495,11 @@
         <f>D229+1095</f>
         <v>1095</v>
       </c>
-      <c r="I229" s="31">
-        <v>230</v>
-      </c>
-      <c r="J229" s="31">
-        <v>408</v>
-      </c>
-      <c r="K229" s="10">
+      <c r="I229" s="10">
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="1:11" ht="15">
+    <row r="230" spans="1:9" ht="15">
       <c r="A230" s="23" t="s">
         <v>1111</v>
       </c>
@@ -12925,17 +11520,11 @@
         <f>D230+1095</f>
         <v>1095</v>
       </c>
-      <c r="I230" s="31">
-        <v>45</v>
-      </c>
-      <c r="J230" s="31">
-        <v>34</v>
-      </c>
-      <c r="K230" s="10">
+      <c r="I230" s="10">
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="1:11" ht="15">
+    <row r="231" spans="1:9" ht="15">
       <c r="A231" s="23" t="s">
         <v>1111</v>
       </c>
@@ -12957,17 +11546,11 @@
         <f t="shared" ref="H231:H237" si="14">D231+1095</f>
         <v>1095</v>
       </c>
-      <c r="I231" s="31">
-        <v>46</v>
-      </c>
-      <c r="J231" s="31">
-        <v>35</v>
-      </c>
-      <c r="K231" s="10">
+      <c r="I231" s="10">
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="15">
+    <row r="232" spans="1:9" ht="15">
       <c r="A232" s="23" t="s">
         <v>1111</v>
       </c>
@@ -12989,17 +11572,11 @@
         <f t="shared" si="14"/>
         <v>1095</v>
       </c>
-      <c r="I232" s="31">
-        <v>45</v>
-      </c>
-      <c r="J232" s="31">
-        <v>34</v>
-      </c>
-      <c r="K232" s="10">
+      <c r="I232" s="10">
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="15">
+    <row r="233" spans="1:9" ht="15">
       <c r="A233" s="23" t="s">
         <v>1111</v>
       </c>
@@ -13021,17 +11598,11 @@
         <f t="shared" si="14"/>
         <v>1095</v>
       </c>
-      <c r="I233" s="31">
-        <v>44</v>
-      </c>
-      <c r="J233" s="31">
-        <v>34</v>
-      </c>
-      <c r="K233" s="10">
+      <c r="I233" s="10">
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="15">
+    <row r="234" spans="1:9" ht="15">
       <c r="A234" s="23" t="s">
         <v>1111</v>
       </c>
@@ -13053,17 +11624,11 @@
         <f t="shared" si="14"/>
         <v>1095</v>
       </c>
-      <c r="I234" s="31">
-        <v>44</v>
-      </c>
-      <c r="J234" s="31">
-        <v>33</v>
-      </c>
-      <c r="K234" s="10">
+      <c r="I234" s="10">
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:11" ht="15">
+    <row r="235" spans="1:9" ht="15">
       <c r="A235" s="23" t="s">
         <v>1111</v>
       </c>
@@ -13085,17 +11650,11 @@
         <f t="shared" si="14"/>
         <v>1095</v>
       </c>
-      <c r="I235" s="31">
-        <v>44</v>
-      </c>
-      <c r="J235" s="31">
-        <v>33</v>
-      </c>
-      <c r="K235" s="10">
+      <c r="I235" s="10">
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:11" ht="15">
+    <row r="236" spans="1:9" ht="15">
       <c r="A236" s="23" t="s">
         <v>1111</v>
       </c>
@@ -13116,17 +11675,11 @@
         <f t="shared" si="14"/>
         <v>1095</v>
       </c>
-      <c r="I236" s="31">
-        <v>44</v>
-      </c>
-      <c r="J236" s="31">
-        <v>33</v>
-      </c>
-      <c r="K236" s="10">
+      <c r="I236" s="10">
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="15">
+    <row r="237" spans="1:9" ht="15">
       <c r="A237" s="23" t="s">
         <v>1111</v>
       </c>
@@ -13147,17 +11700,11 @@
         <f t="shared" si="14"/>
         <v>1095</v>
       </c>
-      <c r="I237" s="31">
-        <v>50</v>
-      </c>
-      <c r="J237" s="31">
-        <v>39</v>
-      </c>
-      <c r="K237" s="10">
+      <c r="I237" s="10">
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="15">
+    <row r="238" spans="1:9" ht="15">
       <c r="A238" s="22">
         <v>120.1</v>
       </c>
@@ -13179,17 +11726,11 @@
         <f t="shared" ref="H238:H257" si="15">D238+1095</f>
         <v>1095</v>
       </c>
-      <c r="I238" s="31">
-        <v>178</v>
-      </c>
-      <c r="J238" s="31">
-        <v>85</v>
-      </c>
-      <c r="K238" s="10">
+      <c r="I238" s="10">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="15">
+    <row r="239" spans="1:9" ht="15">
       <c r="A239" s="22">
         <v>656</v>
       </c>
@@ -13211,17 +11752,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I239" s="31">
-        <v>1300</v>
-      </c>
-      <c r="J239" s="31">
-        <v>500</v>
-      </c>
-      <c r="K239" s="10">
+      <c r="I239" s="10">
         <v>238</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="15">
+    <row r="240" spans="1:9" ht="15">
       <c r="A240" s="22">
         <v>69</v>
       </c>
@@ -13243,17 +11778,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I240" s="31">
-        <v>100</v>
-      </c>
-      <c r="J240" s="31">
-        <v>70</v>
-      </c>
-      <c r="K240" s="10">
+      <c r="I240" s="10">
         <v>239</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="15">
+    <row r="241" spans="1:9" ht="15">
       <c r="A241" s="22">
         <v>93</v>
       </c>
@@ -13275,17 +11804,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I241" s="31">
-        <v>200</v>
-      </c>
-      <c r="J241" s="31">
-        <v>90</v>
-      </c>
-      <c r="K241" s="10">
+      <c r="I241" s="10">
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="15">
+    <row r="242" spans="1:9" ht="15">
       <c r="A242" s="22">
         <v>415</v>
       </c>
@@ -13307,17 +11830,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I242" s="31">
-        <v>380</v>
-      </c>
-      <c r="J242" s="31">
-        <v>180</v>
-      </c>
-      <c r="K242" s="10">
+      <c r="I242" s="10">
         <v>241</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="15">
+    <row r="243" spans="1:9" ht="15">
       <c r="A243" s="22">
         <v>249.9</v>
       </c>
@@ -13339,17 +11856,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I243" s="31">
-        <v>520</v>
-      </c>
-      <c r="J243" s="31">
-        <v>210</v>
-      </c>
-      <c r="K243" s="10">
+      <c r="I243" s="10">
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="15">
+    <row r="244" spans="1:9" ht="15">
       <c r="A244" s="22">
         <v>330</v>
       </c>
@@ -13371,17 +11882,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I244" s="31">
-        <v>430</v>
-      </c>
-      <c r="J244" s="31">
-        <v>180</v>
-      </c>
-      <c r="K244" s="10">
+      <c r="I244" s="10">
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="15">
+    <row r="245" spans="1:9" ht="15">
       <c r="A245" s="22">
         <v>94.8</v>
       </c>
@@ -13403,17 +11908,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I245" s="31">
-        <v>135</v>
-      </c>
-      <c r="J245" s="31">
-        <v>60</v>
-      </c>
-      <c r="K245" s="10">
+      <c r="I245" s="10">
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="15">
+    <row r="246" spans="1:9" ht="15">
       <c r="A246" s="22">
         <v>159.9</v>
       </c>
@@ -13435,17 +11934,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I246" s="31">
-        <v>290</v>
-      </c>
-      <c r="J246" s="31">
-        <v>140</v>
-      </c>
-      <c r="K246" s="10">
+      <c r="I246" s="10">
         <v>245</v>
       </c>
     </row>
-    <row r="247" spans="1:11" ht="15">
+    <row r="247" spans="1:9" ht="15">
       <c r="A247">
         <v>258</v>
       </c>
@@ -13467,17 +11960,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I247" s="31">
-        <v>360</v>
-      </c>
-      <c r="J247" s="31">
-        <v>120</v>
-      </c>
-      <c r="K247" s="10">
+      <c r="I247" s="10">
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="15">
+    <row r="248" spans="1:9" ht="15">
       <c r="A248" s="22">
         <v>317.5</v>
       </c>
@@ -13499,17 +11986,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I248" s="31">
-        <v>500</v>
-      </c>
-      <c r="J248" s="31">
-        <v>160</v>
-      </c>
-      <c r="K248" s="10">
+      <c r="I248" s="10">
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="15">
+    <row r="249" spans="1:9" ht="15">
       <c r="A249" s="22">
         <v>219</v>
       </c>
@@ -13531,17 +12012,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I249" s="31">
-        <v>350</v>
-      </c>
-      <c r="J249" s="31">
-        <v>120</v>
-      </c>
-      <c r="K249" s="10">
+      <c r="I249" s="10">
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="15">
+    <row r="250" spans="1:9" ht="15">
       <c r="A250" s="22">
         <v>169</v>
       </c>
@@ -13563,17 +12038,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I250" s="31">
-        <v>285</v>
-      </c>
-      <c r="J250" s="31">
-        <v>95</v>
-      </c>
-      <c r="K250" s="10">
+      <c r="I250" s="10">
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="15">
+    <row r="251" spans="1:9" ht="15">
       <c r="A251">
         <v>299</v>
       </c>
@@ -13595,17 +12064,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I251" s="31">
-        <v>354</v>
-      </c>
-      <c r="J251" s="31">
-        <v>118</v>
-      </c>
-      <c r="K251" s="10">
+      <c r="I251" s="10">
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="15">
+    <row r="252" spans="1:9" ht="15">
       <c r="A252">
         <v>256</v>
       </c>
@@ -13625,17 +12088,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I252" s="31">
-        <v>350</v>
-      </c>
-      <c r="J252" s="31">
-        <v>120</v>
-      </c>
-      <c r="K252" s="10">
+      <c r="I252" s="10">
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="15">
+    <row r="253" spans="1:9" ht="15">
       <c r="A253">
         <v>139</v>
       </c>
@@ -13657,17 +12114,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I253" s="31">
-        <v>200</v>
-      </c>
-      <c r="J253" s="31">
-        <v>100</v>
-      </c>
-      <c r="K253" s="10">
+      <c r="I253" s="10">
         <v>252</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="15">
+    <row r="254" spans="1:9" ht="15">
       <c r="A254" s="22">
         <v>358</v>
       </c>
@@ -13689,17 +12140,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I254" s="31">
-        <v>450</v>
-      </c>
-      <c r="J254" s="31">
-        <v>250</v>
-      </c>
-      <c r="K254" s="10">
+      <c r="I254" s="10">
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="15">
+    <row r="255" spans="1:9" ht="15">
       <c r="A255" s="22">
         <v>215</v>
       </c>
@@ -13721,17 +12166,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I255" s="31">
-        <v>339</v>
-      </c>
-      <c r="J255" s="31">
-        <v>276</v>
-      </c>
-      <c r="K255" s="10">
+      <c r="I255" s="10">
         <v>254</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="15">
+    <row r="256" spans="1:9" ht="15">
       <c r="A256" s="22">
         <v>1047</v>
       </c>
@@ -13753,17 +12192,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I256" s="31">
-        <v>747</v>
-      </c>
-      <c r="J256" s="31">
-        <v>563</v>
-      </c>
-      <c r="K256" s="10">
+      <c r="I256" s="10">
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="15">
+    <row r="257" spans="1:9" ht="15">
       <c r="A257" s="22">
         <v>290</v>
       </c>
@@ -13785,17 +12218,11 @@
         <f t="shared" si="15"/>
         <v>1095</v>
       </c>
-      <c r="I257" s="31">
-        <v>161</v>
-      </c>
-      <c r="J257" s="31">
-        <v>120</v>
-      </c>
-      <c r="K257" s="10">
+      <c r="I257" s="10">
         <v>256</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="15">
+    <row r="258" spans="1:9" ht="15">
       <c r="A258" s="22">
         <v>217</v>
       </c>
@@ -13817,17 +12244,11 @@
         <f t="shared" ref="H258:H263" si="16">D258+1080</f>
         <v>1080</v>
       </c>
-      <c r="I258" s="31">
-        <v>276</v>
-      </c>
-      <c r="J258" s="31">
-        <v>212</v>
-      </c>
-      <c r="K258" s="10">
+      <c r="I258" s="10">
         <v>257</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="15">
+    <row r="259" spans="1:9" ht="15">
       <c r="A259" s="22">
         <v>499</v>
       </c>
@@ -13849,17 +12270,11 @@
         <f t="shared" si="16"/>
         <v>1080</v>
       </c>
-      <c r="I259" s="31">
-        <v>299</v>
-      </c>
-      <c r="J259" s="31">
-        <v>253</v>
-      </c>
-      <c r="K259" s="10">
+      <c r="I259" s="10">
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="15">
+    <row r="260" spans="1:9" ht="15">
       <c r="A260" s="23" t="s">
         <v>1111</v>
       </c>
@@ -13881,17 +12296,11 @@
         <f t="shared" si="16"/>
         <v>1080</v>
       </c>
-      <c r="I260" s="31">
-        <v>400</v>
-      </c>
-      <c r="J260" s="31">
-        <v>270</v>
-      </c>
-      <c r="K260" s="10">
+      <c r="I260" s="10">
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="1:11" ht="15">
+    <row r="261" spans="1:9" ht="15">
       <c r="A261" s="22">
         <v>200</v>
       </c>
@@ -13913,17 +12322,11 @@
         <f t="shared" si="16"/>
         <v>1080</v>
       </c>
-      <c r="I261" s="31">
-        <v>150</v>
-      </c>
-      <c r="J261" s="31">
-        <v>125</v>
-      </c>
-      <c r="K261" s="10">
+      <c r="I261" s="10">
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="1:11" ht="15">
+    <row r="262" spans="1:9" ht="15">
       <c r="A262" s="22">
         <v>229</v>
       </c>
@@ -13945,17 +12348,11 @@
         <f t="shared" si="16"/>
         <v>1080</v>
       </c>
-      <c r="I262" s="31">
-        <v>178</v>
-      </c>
-      <c r="J262" s="31">
-        <v>105</v>
-      </c>
-      <c r="K262" s="10">
+      <c r="I262" s="10">
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="15">
+    <row r="263" spans="1:9" ht="15">
       <c r="A263" s="22">
         <v>490</v>
       </c>
@@ -13977,17 +12374,11 @@
         <f t="shared" si="16"/>
         <v>1080</v>
       </c>
-      <c r="I263" s="31">
-        <v>506</v>
-      </c>
-      <c r="J263" s="31">
-        <v>360</v>
-      </c>
-      <c r="K263" s="10">
+      <c r="I263" s="10">
         <v>262</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="15">
+    <row r="264" spans="1:9" ht="15">
       <c r="A264" s="22">
         <v>598</v>
       </c>
@@ -14009,17 +12400,11 @@
         <f>D264+1095</f>
         <v>1095</v>
       </c>
-      <c r="I264" s="31">
-        <v>224</v>
-      </c>
-      <c r="J264" s="31">
-        <v>189</v>
-      </c>
-      <c r="K264" s="10">
+      <c r="I264" s="10">
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="1:11" ht="15">
+    <row r="265" spans="1:9" ht="15">
       <c r="A265" s="22">
         <v>218</v>
       </c>
@@ -14041,17 +12426,11 @@
         <f>D265+1095</f>
         <v>1095</v>
       </c>
-      <c r="I265" s="31">
-        <v>343</v>
-      </c>
-      <c r="J265" s="31">
-        <v>265</v>
-      </c>
-      <c r="K265" s="10">
+      <c r="I265" s="10">
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="15">
+    <row r="266" spans="1:9" ht="15">
       <c r="A266" s="22">
         <v>55.9</v>
       </c>
@@ -14073,17 +12452,11 @@
         <f>D266+1095</f>
         <v>1095</v>
       </c>
-      <c r="I266" s="31">
-        <v>60</v>
-      </c>
-      <c r="J266" s="31">
-        <v>150</v>
-      </c>
-      <c r="K266" s="10">
+      <c r="I266" s="10">
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="1:11" ht="15">
+    <row r="267" spans="1:9" ht="15">
       <c r="A267" s="22">
         <v>131</v>
       </c>
@@ -14105,17 +12478,11 @@
         <f>D267+1095</f>
         <v>1095</v>
       </c>
-      <c r="I267" s="31">
-        <v>300</v>
-      </c>
-      <c r="J267" s="31">
-        <v>300</v>
-      </c>
-      <c r="K267" s="10">
+      <c r="I267" s="10">
         <v>266</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="15">
+    <row r="268" spans="1:9" ht="15">
       <c r="A268" s="22">
         <v>300</v>
       </c>
@@ -14137,17 +12504,11 @@
         <f>D268+1095</f>
         <v>1095</v>
       </c>
-      <c r="I268" s="31">
-        <v>205</v>
-      </c>
-      <c r="J268" s="31">
-        <v>156</v>
-      </c>
-      <c r="K268" s="10">
+      <c r="I268" s="10">
         <v>267</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="15">
+    <row r="269" spans="1:9" ht="15">
       <c r="A269" s="22">
         <v>224</v>
       </c>
@@ -14169,17 +12530,11 @@
         <f>D269+1825</f>
         <v>1825</v>
       </c>
-      <c r="I269" s="31">
-        <v>330</v>
-      </c>
-      <c r="J269" s="31">
-        <v>270</v>
-      </c>
-      <c r="K269" s="10">
+      <c r="I269" s="10">
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="15">
+    <row r="270" spans="1:9" ht="15">
       <c r="A270" s="23" t="s">
         <v>1111</v>
       </c>
@@ -14201,17 +12556,11 @@
         <f>D270+1095</f>
         <v>1095</v>
       </c>
-      <c r="I270" s="31">
-        <v>265</v>
-      </c>
-      <c r="J270" s="31">
-        <v>182</v>
-      </c>
-      <c r="K270" s="10">
+      <c r="I270" s="10">
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="1:11" ht="15">
+    <row r="271" spans="1:9" ht="15">
       <c r="A271" s="22">
         <v>599</v>
       </c>
@@ -14233,17 +12582,11 @@
         <f>D271+1080</f>
         <v>1080</v>
       </c>
-      <c r="I271" s="31">
-        <v>475</v>
-      </c>
-      <c r="J271" s="31">
-        <v>404</v>
-      </c>
-      <c r="K271" s="10">
+      <c r="I271" s="10">
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="15">
+    <row r="272" spans="1:9" ht="15">
       <c r="A272" s="22">
         <v>395</v>
       </c>
@@ -14265,17 +12608,11 @@
         <f t="shared" ref="H272:H280" si="17">D272+1095</f>
         <v>1095</v>
       </c>
-      <c r="I272" s="31">
-        <v>405</v>
-      </c>
-      <c r="J272" s="31">
-        <v>330</v>
-      </c>
-      <c r="K272" s="10">
+      <c r="I272" s="10">
         <v>271</v>
       </c>
     </row>
-    <row r="273" spans="1:11" ht="15">
+    <row r="273" spans="1:9" ht="15">
       <c r="A273" s="22">
         <v>418</v>
       </c>
@@ -14297,17 +12634,11 @@
         <f t="shared" si="17"/>
         <v>1095</v>
       </c>
-      <c r="I273" s="31">
-        <v>400</v>
-      </c>
-      <c r="J273" s="31">
-        <v>355</v>
-      </c>
-      <c r="K273" s="10">
+      <c r="I273" s="10">
         <v>272</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="15">
+    <row r="274" spans="1:9" ht="15">
       <c r="A274" s="22">
         <v>689</v>
       </c>
@@ -14329,17 +12660,11 @@
         <f t="shared" si="17"/>
         <v>1095</v>
       </c>
-      <c r="I274" s="31">
-        <v>400</v>
-      </c>
-      <c r="J274" s="31">
-        <v>300</v>
-      </c>
-      <c r="K274" s="10">
+      <c r="I274" s="10">
         <v>273</v>
       </c>
     </row>
-    <row r="275" spans="1:11" ht="15">
+    <row r="275" spans="1:9" ht="15">
       <c r="A275" s="22">
         <v>1998</v>
       </c>
@@ -14361,17 +12686,11 @@
         <f t="shared" si="17"/>
         <v>1095</v>
       </c>
-      <c r="I275" s="31">
-        <v>950</v>
-      </c>
-      <c r="J275" s="31">
-        <v>650</v>
-      </c>
-      <c r="K275" s="10">
+      <c r="I275" s="10">
         <v>274</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="15">
+    <row r="276" spans="1:9" ht="15">
       <c r="A276" s="22">
         <v>389</v>
       </c>
@@ -14393,17 +12712,11 @@
         <f t="shared" si="17"/>
         <v>1095</v>
       </c>
-      <c r="I276" s="31">
-        <v>300</v>
-      </c>
-      <c r="J276" s="31">
-        <v>195</v>
-      </c>
-      <c r="K276" s="10">
+      <c r="I276" s="10">
         <v>275</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="15">
+    <row r="277" spans="1:9" ht="15">
       <c r="A277">
         <v>1160</v>
       </c>
@@ -14425,17 +12738,11 @@
         <f t="shared" si="17"/>
         <v>1095</v>
       </c>
-      <c r="I277" s="31">
-        <v>450</v>
-      </c>
-      <c r="J277" s="31">
-        <v>300</v>
-      </c>
-      <c r="K277" s="10">
+      <c r="I277" s="10">
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="15">
+    <row r="278" spans="1:9" ht="15">
       <c r="A278" s="22">
         <v>589</v>
       </c>
@@ -14457,17 +12764,11 @@
         <f t="shared" si="17"/>
         <v>1095</v>
       </c>
-      <c r="I278" s="31">
-        <v>400</v>
-      </c>
-      <c r="J278" s="31">
-        <v>304</v>
-      </c>
-      <c r="K278" s="10">
+      <c r="I278" s="10">
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="1:11" ht="15">
+    <row r="279" spans="1:9" ht="15">
       <c r="A279" s="22">
         <v>790</v>
       </c>
@@ -14489,17 +12790,11 @@
         <f t="shared" si="17"/>
         <v>1095</v>
       </c>
-      <c r="I279" s="31">
-        <v>450</v>
-      </c>
-      <c r="J279" s="31">
-        <v>300</v>
-      </c>
-      <c r="K279" s="10">
+      <c r="I279" s="10">
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="15">
+    <row r="280" spans="1:9" ht="15">
       <c r="A280" s="22">
         <v>659</v>
       </c>
@@ -14521,17 +12816,11 @@
         <f t="shared" si="17"/>
         <v>1095</v>
       </c>
-      <c r="I280" s="31">
-        <v>700</v>
-      </c>
-      <c r="J280" s="31">
-        <v>500</v>
-      </c>
-      <c r="K280" s="10">
+      <c r="I280" s="10">
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="15">
+    <row r="281" spans="1:9" ht="15">
       <c r="A281" s="22">
         <v>178.6</v>
       </c>
@@ -14553,17 +12842,11 @@
         <f>D281+1460</f>
         <v>1460</v>
       </c>
-      <c r="I281" s="31">
-        <v>300</v>
-      </c>
-      <c r="J281" s="31">
-        <v>60</v>
-      </c>
-      <c r="K281" s="10">
+      <c r="I281" s="10">
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="17">
+    <row r="282" spans="1:9" ht="17">
       <c r="A282" s="22">
         <v>544</v>
       </c>
@@ -14585,17 +12868,11 @@
         <f>D282+1095</f>
         <v>1095</v>
       </c>
-      <c r="I282" s="31">
-        <v>500</v>
-      </c>
-      <c r="J282" s="31">
-        <v>400</v>
-      </c>
-      <c r="K282" s="10">
+      <c r="I282" s="10">
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="17">
+    <row r="283" spans="1:9" ht="17">
       <c r="A283" s="22">
         <v>529</v>
       </c>
@@ -14617,17 +12894,11 @@
         <f>D283+1095</f>
         <v>1095</v>
       </c>
-      <c r="I283" s="31">
-        <v>500</v>
-      </c>
-      <c r="J283" s="31">
-        <v>400</v>
-      </c>
-      <c r="K283" s="10">
+      <c r="I283" s="10">
         <v>282</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="15">
+    <row r="284" spans="1:9" ht="15">
       <c r="A284" s="22">
         <v>82</v>
       </c>
@@ -14649,17 +12920,11 @@
         <f>D284+1095</f>
         <v>1095</v>
       </c>
-      <c r="I284" s="31">
-        <v>500</v>
-      </c>
-      <c r="J284" s="31">
-        <v>230</v>
-      </c>
-      <c r="K284" s="10">
+      <c r="I284" s="10">
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="15">
+    <row r="285" spans="1:9" ht="15">
       <c r="A285" s="22">
         <v>129.19999999999999</v>
       </c>
@@ -14681,17 +12946,11 @@
         <f>D285+1095</f>
         <v>1095</v>
       </c>
-      <c r="I285" s="31">
-        <v>80</v>
-      </c>
-      <c r="J285" s="31">
-        <v>50</v>
-      </c>
-      <c r="K285" s="10">
+      <c r="I285" s="10">
         <v>284</v>
       </c>
     </row>
-    <row r="286" spans="1:11" ht="15">
+    <row r="286" spans="1:9" ht="15">
       <c r="A286" s="22">
         <v>579</v>
       </c>
@@ -14713,17 +12972,11 @@
         <f>D286+1095</f>
         <v>1095</v>
       </c>
-      <c r="I286" s="31">
-        <v>300</v>
-      </c>
-      <c r="J286" s="31">
-        <v>180</v>
-      </c>
-      <c r="K286" s="10">
+      <c r="I286" s="10">
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:11" ht="15">
+    <row r="287" spans="1:9" ht="15">
       <c r="A287" s="22">
         <v>238</v>
       </c>
@@ -14745,17 +12998,11 @@
         <f>D287+1825</f>
         <v>1825</v>
       </c>
-      <c r="I287" s="31">
-        <v>600</v>
-      </c>
-      <c r="J287" s="31">
-        <v>450</v>
-      </c>
-      <c r="K287" s="10">
+      <c r="I287" s="10">
         <v>286</v>
       </c>
     </row>
-    <row r="288" spans="1:11" ht="15">
+    <row r="288" spans="1:9" ht="15">
       <c r="A288" s="22">
         <v>238</v>
       </c>
@@ -14777,17 +13024,11 @@
         <f>D288+1825</f>
         <v>1825</v>
       </c>
-      <c r="I288" s="31">
-        <v>400</v>
-      </c>
-      <c r="J288" s="31">
-        <v>300</v>
-      </c>
-      <c r="K288" s="10">
+      <c r="I288" s="10">
         <v>287</v>
       </c>
     </row>
-    <row r="289" spans="1:11" ht="15">
+    <row r="289" spans="1:9" ht="15">
       <c r="A289" s="22">
         <v>659</v>
       </c>
@@ -14809,17 +13050,11 @@
         <f>D289+1825</f>
         <v>1825</v>
       </c>
-      <c r="I289" s="31">
-        <v>400</v>
-      </c>
-      <c r="J289" s="31">
-        <v>300</v>
-      </c>
-      <c r="K289" s="10">
+      <c r="I289" s="10">
         <v>288</v>
       </c>
     </row>
-    <row r="290" spans="1:11" ht="15">
+    <row r="290" spans="1:9" ht="15">
       <c r="A290" s="22">
         <v>399</v>
       </c>
@@ -14841,17 +13076,11 @@
         <f>D290+1095</f>
         <v>1095</v>
       </c>
-      <c r="I290" s="31">
-        <v>400</v>
-      </c>
-      <c r="J290" s="31">
-        <v>200</v>
-      </c>
-      <c r="K290" s="10">
+      <c r="I290" s="10">
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="1:11" ht="15">
+    <row r="291" spans="1:9" ht="15">
       <c r="A291" s="22">
         <v>358</v>
       </c>
@@ -14873,17 +13102,11 @@
         <f>D291+1825</f>
         <v>1825</v>
       </c>
-      <c r="I291" s="31">
-        <v>400</v>
-      </c>
-      <c r="J291" s="31">
-        <v>250</v>
-      </c>
-      <c r="K291" s="10">
+      <c r="I291" s="10">
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="1:11" ht="15">
+    <row r="292" spans="1:9" ht="15">
       <c r="A292" s="22">
         <v>259</v>
       </c>
@@ -14905,17 +13128,11 @@
         <f t="shared" ref="H292:H297" si="18">D292+1095</f>
         <v>1095</v>
       </c>
-      <c r="I292" s="31">
-        <v>180</v>
-      </c>
-      <c r="J292" s="31">
-        <v>100</v>
-      </c>
-      <c r="K292" s="10">
+      <c r="I292" s="10">
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="1:11" ht="15">
+    <row r="293" spans="1:9" ht="15">
       <c r="A293" s="22">
         <v>328.9</v>
       </c>
@@ -14937,17 +13154,11 @@
         <f t="shared" si="18"/>
         <v>1095</v>
       </c>
-      <c r="I293" s="31">
-        <v>350</v>
-      </c>
-      <c r="J293" s="31">
-        <v>210</v>
-      </c>
-      <c r="K293" s="10">
+      <c r="I293" s="10">
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:11" ht="15">
+    <row r="294" spans="1:9" ht="15">
       <c r="A294" s="22">
         <v>1198</v>
       </c>
@@ -14969,17 +13180,11 @@
         <f t="shared" si="18"/>
         <v>1095</v>
       </c>
-      <c r="I294" s="31">
-        <v>300</v>
-      </c>
-      <c r="J294" s="31">
-        <v>180</v>
-      </c>
-      <c r="K294" s="10">
+      <c r="I294" s="10">
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:11" ht="15">
+    <row r="295" spans="1:9" ht="15">
       <c r="A295" s="22">
         <v>369</v>
       </c>
@@ -15001,17 +13206,11 @@
         <f t="shared" si="18"/>
         <v>1095</v>
       </c>
-      <c r="I295" s="31">
-        <v>400</v>
-      </c>
-      <c r="J295" s="31">
-        <v>300</v>
-      </c>
-      <c r="K295" s="10">
+      <c r="I295" s="10">
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="1:11" ht="15">
+    <row r="296" spans="1:9" ht="15">
       <c r="A296" s="23" t="s">
         <v>1111</v>
       </c>
@@ -15033,17 +13232,11 @@
         <f t="shared" si="18"/>
         <v>1095</v>
       </c>
-      <c r="I296" s="31">
-        <v>400</v>
-      </c>
-      <c r="J296" s="31">
-        <v>260</v>
-      </c>
-      <c r="K296" s="10">
+      <c r="I296" s="10">
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="1:11" ht="15">
+    <row r="297" spans="1:9" ht="15">
       <c r="A297" s="22">
         <v>169</v>
       </c>
@@ -15065,17 +13258,11 @@
         <f t="shared" si="18"/>
         <v>1095</v>
       </c>
-      <c r="I297" s="31">
-        <v>200</v>
-      </c>
-      <c r="J297" s="31">
-        <v>130</v>
-      </c>
-      <c r="K297" s="10">
+      <c r="I297" s="10">
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="1:11" ht="15">
+    <row r="298" spans="1:9" ht="15">
       <c r="A298">
         <v>139</v>
       </c>
@@ -15097,17 +13284,11 @@
         <f>D298+1825</f>
         <v>1825</v>
       </c>
-      <c r="I298" s="31">
-        <v>200</v>
-      </c>
-      <c r="J298" s="31">
-        <v>150</v>
-      </c>
-      <c r="K298" s="10">
+      <c r="I298" s="10">
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="1:11" ht="15">
+    <row r="299" spans="1:9" ht="15">
       <c r="A299">
         <v>299</v>
       </c>
@@ -15128,17 +13309,11 @@
         <f t="shared" ref="H299:H311" si="19">D299+1095</f>
         <v>1095</v>
       </c>
-      <c r="I299" s="31">
-        <v>200</v>
-      </c>
-      <c r="J299" s="31">
-        <v>130</v>
-      </c>
-      <c r="K299" s="10">
+      <c r="I299" s="10">
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="1:11" ht="15">
+    <row r="300" spans="1:9" ht="15">
       <c r="A300" s="22">
         <v>270</v>
       </c>
@@ -15160,17 +13335,11 @@
         <f t="shared" si="19"/>
         <v>1095</v>
       </c>
-      <c r="I300" s="31">
-        <v>280</v>
-      </c>
-      <c r="J300" s="31">
-        <v>200</v>
-      </c>
-      <c r="K300" s="10">
+      <c r="I300" s="10">
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="15">
+    <row r="301" spans="1:9" ht="15">
       <c r="A301" s="22">
         <v>150</v>
       </c>
@@ -15192,17 +13361,11 @@
         <f t="shared" si="19"/>
         <v>1095</v>
       </c>
-      <c r="I301" s="31">
+      <c r="I301" s="10">
         <v>300</v>
       </c>
-      <c r="J301" s="31">
-        <v>150</v>
-      </c>
-      <c r="K301" s="10">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="302" spans="1:11" ht="15">
+    </row>
+    <row r="302" spans="1:9" ht="15">
       <c r="A302" s="22"/>
       <c r="B302" s="20"/>
       <c r="C302" s="24" t="s">
@@ -15222,17 +13385,11 @@
         <f t="shared" si="19"/>
         <v>1095</v>
       </c>
-      <c r="I302" s="31">
-        <v>250</v>
-      </c>
-      <c r="J302" s="31">
-        <v>150</v>
-      </c>
-      <c r="K302" s="10">
+      <c r="I302" s="10">
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="1:11" ht="15">
+    <row r="303" spans="1:9" ht="15">
       <c r="B303" s="20"/>
       <c r="C303" s="24" t="s">
         <v>1411</v>
@@ -15251,17 +13408,11 @@
         <f t="shared" si="19"/>
         <v>1095</v>
       </c>
-      <c r="I303" s="31">
-        <v>750</v>
-      </c>
-      <c r="J303" s="31">
-        <v>650</v>
-      </c>
-      <c r="K303" s="10">
+      <c r="I303" s="10">
         <v>302</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="15">
+    <row r="304" spans="1:9" ht="15">
       <c r="A304" s="22">
         <v>385</v>
       </c>
@@ -15283,17 +13434,11 @@
         <f t="shared" si="19"/>
         <v>1095</v>
       </c>
-      <c r="I304" s="31">
-        <v>500</v>
-      </c>
-      <c r="J304" s="31">
-        <v>300</v>
-      </c>
-      <c r="K304" s="10">
+      <c r="I304" s="10">
         <v>303</v>
       </c>
     </row>
-    <row r="305" spans="1:11" ht="15">
+    <row r="305" spans="1:9" ht="15">
       <c r="A305" s="22">
         <v>599</v>
       </c>
@@ -15315,17 +13460,11 @@
         <f t="shared" si="19"/>
         <v>1095</v>
       </c>
-      <c r="I305" s="31">
-        <v>500</v>
-      </c>
-      <c r="J305" s="31">
-        <v>350</v>
-      </c>
-      <c r="K305" s="10">
+      <c r="I305" s="10">
         <v>304</v>
       </c>
     </row>
-    <row r="306" spans="1:11" ht="15">
+    <row r="306" spans="1:9" ht="15">
       <c r="A306" s="22">
         <v>699</v>
       </c>
@@ -15347,17 +13486,11 @@
         <f t="shared" si="19"/>
         <v>1095</v>
       </c>
-      <c r="I306" s="31">
-        <v>600</v>
-      </c>
-      <c r="J306" s="31">
-        <v>500</v>
-      </c>
-      <c r="K306" s="10">
+      <c r="I306" s="10">
         <v>305</v>
       </c>
     </row>
-    <row r="307" spans="1:11" ht="15">
+    <row r="307" spans="1:9" ht="15">
       <c r="A307">
         <v>1206</v>
       </c>
@@ -15379,17 +13512,11 @@
         <f t="shared" si="19"/>
         <v>1095</v>
       </c>
-      <c r="I307" s="31">
-        <v>750</v>
-      </c>
-      <c r="J307" s="31">
-        <v>450</v>
-      </c>
-      <c r="K307" s="10">
+      <c r="I307" s="10">
         <v>306</v>
       </c>
     </row>
-    <row r="308" spans="1:11" ht="15">
+    <row r="308" spans="1:9" ht="15">
       <c r="A308">
         <v>603</v>
       </c>
@@ -15411,17 +13538,11 @@
         <f t="shared" si="19"/>
         <v>1095</v>
       </c>
-      <c r="I308" s="31">
-        <v>700</v>
-      </c>
-      <c r="J308" s="31">
-        <v>300</v>
-      </c>
-      <c r="K308" s="10">
+      <c r="I308" s="10">
         <v>307</v>
       </c>
     </row>
-    <row r="309" spans="1:11" ht="15">
+    <row r="309" spans="1:9" ht="15">
       <c r="A309" s="22">
         <v>169.99</v>
       </c>
@@ -15443,17 +13564,11 @@
         <f t="shared" si="19"/>
         <v>1095</v>
       </c>
-      <c r="I309" s="31">
-        <v>200</v>
-      </c>
-      <c r="J309" s="31">
-        <v>120</v>
-      </c>
-      <c r="K309" s="10">
+      <c r="I309" s="10">
         <v>308</v>
       </c>
     </row>
-    <row r="310" spans="1:11" ht="15">
+    <row r="310" spans="1:9" ht="15">
       <c r="A310" s="22">
         <v>622</v>
       </c>
@@ -15475,17 +13590,11 @@
         <f t="shared" si="19"/>
         <v>1095</v>
       </c>
-      <c r="I310" s="31">
-        <v>1000</v>
-      </c>
-      <c r="J310" s="31">
-        <v>650</v>
-      </c>
-      <c r="K310" s="10">
+      <c r="I310" s="10">
         <v>309</v>
       </c>
     </row>
-    <row r="311" spans="1:11" ht="15">
+    <row r="311" spans="1:9" ht="15">
       <c r="A311">
         <v>498</v>
       </c>
@@ -15507,17 +13616,11 @@
         <f t="shared" si="19"/>
         <v>1095</v>
       </c>
-      <c r="I311" s="31">
-        <v>800</v>
-      </c>
-      <c r="J311" s="31">
-        <v>500</v>
-      </c>
-      <c r="K311" s="10">
+      <c r="I311" s="10">
         <v>310</v>
       </c>
     </row>
-    <row r="312" spans="1:11" ht="15">
+    <row r="312" spans="1:9" ht="15">
       <c r="A312" s="22">
         <v>781</v>
       </c>
@@ -15539,17 +13642,11 @@
         <f>D312+1096</f>
         <v>1096</v>
       </c>
-      <c r="I312" s="31">
-        <v>1200</v>
-      </c>
-      <c r="J312" s="31">
-        <v>900</v>
-      </c>
-      <c r="K312" s="10">
+      <c r="I312" s="10">
         <v>311</v>
       </c>
     </row>
-    <row r="313" spans="1:11" ht="15">
+    <row r="313" spans="1:9" ht="15">
       <c r="A313" s="22">
         <v>498</v>
       </c>
@@ -15571,17 +13668,11 @@
         <f t="shared" ref="H313:H319" si="20">D313+1095</f>
         <v>1095</v>
       </c>
-      <c r="I313" s="31">
-        <v>500</v>
-      </c>
-      <c r="J313" s="31">
-        <v>300</v>
-      </c>
-      <c r="K313" s="10">
+      <c r="I313" s="10">
         <v>312</v>
       </c>
     </row>
-    <row r="314" spans="1:11" ht="15">
+    <row r="314" spans="1:9" ht="15">
       <c r="A314" s="22">
         <v>245</v>
       </c>
@@ -15603,17 +13694,11 @@
         <f t="shared" si="20"/>
         <v>1095</v>
       </c>
-      <c r="I314" s="31">
-        <v>300</v>
-      </c>
-      <c r="J314" s="31">
-        <v>200</v>
-      </c>
-      <c r="K314" s="10">
+      <c r="I314" s="10">
         <v>313</v>
       </c>
     </row>
-    <row r="315" spans="1:11" ht="15">
+    <row r="315" spans="1:9" ht="15">
       <c r="A315">
         <v>468</v>
       </c>
@@ -15635,17 +13720,11 @@
         <f t="shared" si="20"/>
         <v>1095</v>
       </c>
-      <c r="I315" s="31">
-        <v>450</v>
-      </c>
-      <c r="J315" s="31">
-        <v>350</v>
-      </c>
-      <c r="K315" s="10">
+      <c r="I315" s="10">
         <v>314</v>
       </c>
     </row>
-    <row r="316" spans="1:11" ht="15">
+    <row r="316" spans="1:9" ht="15">
       <c r="A316">
         <v>468</v>
       </c>
@@ -15667,17 +13746,11 @@
         <f t="shared" si="20"/>
         <v>1095</v>
       </c>
-      <c r="I316" s="31">
-        <v>450</v>
-      </c>
-      <c r="J316" s="31">
-        <v>350</v>
-      </c>
-      <c r="K316" s="10">
+      <c r="I316" s="10">
         <v>315</v>
       </c>
     </row>
-    <row r="317" spans="1:11" ht="15">
+    <row r="317" spans="1:9" ht="15">
       <c r="A317" s="22">
         <v>735</v>
       </c>
@@ -15699,17 +13772,11 @@
         <f t="shared" si="20"/>
         <v>1095</v>
       </c>
-      <c r="I317" s="31">
-        <v>700</v>
-      </c>
-      <c r="J317" s="31">
-        <v>500</v>
-      </c>
-      <c r="K317" s="10">
+      <c r="I317" s="10">
         <v>316</v>
       </c>
     </row>
-    <row r="318" spans="1:11" ht="15">
+    <row r="318" spans="1:9" ht="15">
       <c r="A318">
         <v>189</v>
       </c>
@@ -15731,17 +13798,11 @@
         <f t="shared" si="20"/>
         <v>1095</v>
       </c>
-      <c r="I318" s="31">
-        <v>110</v>
-      </c>
-      <c r="J318" s="31">
-        <v>70</v>
-      </c>
-      <c r="K318" s="10">
+      <c r="I318" s="10">
         <v>317</v>
       </c>
     </row>
-    <row r="319" spans="1:11" ht="15">
+    <row r="319" spans="1:9" ht="15">
       <c r="A319">
         <v>245</v>
       </c>
@@ -15763,17 +13824,11 @@
         <f t="shared" si="20"/>
         <v>1095</v>
       </c>
-      <c r="I319" s="31">
-        <v>200</v>
-      </c>
-      <c r="J319" s="31">
-        <v>150</v>
-      </c>
-      <c r="K319" s="10">
+      <c r="I319" s="10">
         <v>318</v>
       </c>
     </row>
-    <row r="320" spans="1:11" ht="15">
+    <row r="320" spans="1:9" ht="15">
       <c r="A320" s="22">
         <v>127</v>
       </c>
@@ -15795,17 +13850,11 @@
         <f>D320+1800</f>
         <v>1800</v>
       </c>
-      <c r="I320" s="31">
-        <v>200</v>
-      </c>
-      <c r="J320" s="31">
-        <v>140</v>
-      </c>
-      <c r="K320" s="10">
+      <c r="I320" s="10">
         <v>319</v>
       </c>
     </row>
-    <row r="321" spans="1:11" ht="15">
+    <row r="321" spans="1:9" ht="15">
       <c r="A321" s="22">
         <v>501</v>
       </c>
@@ -15827,17 +13876,11 @@
         <f>D321+1095</f>
         <v>1095</v>
       </c>
-      <c r="I321" s="31">
-        <v>450</v>
-      </c>
-      <c r="J321" s="31">
-        <v>350</v>
-      </c>
-      <c r="K321" s="10">
+      <c r="I321" s="10">
         <v>320</v>
       </c>
     </row>
-    <row r="322" spans="1:11" ht="17">
+    <row r="322" spans="1:9" ht="17">
       <c r="A322">
         <v>1400</v>
       </c>
@@ -15859,17 +13902,11 @@
         <f>D322+1095</f>
         <v>1095</v>
       </c>
-      <c r="I322" s="31">
-        <v>1000</v>
-      </c>
-      <c r="J322" s="31">
-        <v>700</v>
-      </c>
-      <c r="K322" s="10">
+      <c r="I322" s="10">
         <v>321</v>
       </c>
     </row>
-    <row r="323" spans="1:11" ht="15">
+    <row r="323" spans="1:9" ht="15">
       <c r="A323" s="22">
         <v>1660</v>
       </c>
@@ -15891,17 +13928,11 @@
         <f>D323+1095</f>
         <v>1095</v>
       </c>
-      <c r="I323" s="31">
-        <v>1650</v>
-      </c>
-      <c r="J323" s="31">
-        <v>1250</v>
-      </c>
-      <c r="K323" s="10">
+      <c r="I323" s="10">
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="1:11" ht="15">
+    <row r="324" spans="1:9" ht="15">
       <c r="A324" s="22">
         <v>499</v>
       </c>
@@ -15923,17 +13954,11 @@
         <f>D324+1825</f>
         <v>1825</v>
       </c>
-      <c r="I324" s="31">
-        <v>450</v>
-      </c>
-      <c r="J324" s="31">
-        <v>300</v>
-      </c>
-      <c r="K324" s="10">
+      <c r="I324" s="10">
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="1:11" ht="15">
+    <row r="325" spans="1:9" ht="15">
       <c r="A325">
         <v>235</v>
       </c>
@@ -15955,17 +13980,11 @@
         <f>D325+1095</f>
         <v>1095</v>
       </c>
-      <c r="I325" s="31">
-        <v>220</v>
-      </c>
-      <c r="J325" s="31">
-        <v>120</v>
-      </c>
-      <c r="K325" s="10">
+      <c r="I325" s="10">
         <v>324</v>
       </c>
     </row>
-    <row r="326" spans="1:11" ht="15">
+    <row r="326" spans="1:9" ht="15">
       <c r="A326" s="22">
         <v>300</v>
       </c>
@@ -15987,17 +14006,11 @@
         <f>D326+1825</f>
         <v>1825</v>
       </c>
-      <c r="I326" s="31">
-        <v>250</v>
-      </c>
-      <c r="J326" s="31">
-        <v>160</v>
-      </c>
-      <c r="K326" s="10">
+      <c r="I326" s="10">
         <v>325</v>
       </c>
     </row>
-    <row r="327" spans="1:11" ht="15">
+    <row r="327" spans="1:9" ht="15">
       <c r="A327">
         <v>208</v>
       </c>
@@ -16019,17 +14032,11 @@
         <f>D327+1825</f>
         <v>1825</v>
       </c>
-      <c r="I327" s="31">
-        <v>180</v>
-      </c>
-      <c r="J327" s="31">
-        <v>100</v>
-      </c>
-      <c r="K327" s="10">
+      <c r="I327" s="10">
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="1:11" ht="15">
+    <row r="328" spans="1:9" ht="15">
       <c r="A328">
         <v>358</v>
       </c>
@@ -16051,17 +14058,11 @@
         <f>D328+1095</f>
         <v>1095</v>
       </c>
-      <c r="I328" s="31">
-        <v>200</v>
-      </c>
-      <c r="J328" s="31">
-        <v>120</v>
-      </c>
-      <c r="K328" s="10">
+      <c r="I328" s="10">
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="1:11" ht="15">
+    <row r="329" spans="1:9" ht="15">
       <c r="A329">
         <v>1954</v>
       </c>
@@ -16083,17 +14084,11 @@
         <f>D329+1096</f>
         <v>1096</v>
       </c>
-      <c r="I329" s="31">
-        <v>800</v>
-      </c>
-      <c r="J329" s="31">
-        <v>600</v>
-      </c>
-      <c r="K329" s="10">
+      <c r="I329" s="10">
         <v>328</v>
       </c>
     </row>
-    <row r="330" spans="1:11" ht="15">
+    <row r="330" spans="1:9" ht="15">
       <c r="B330" s="20"/>
       <c r="C330" s="24" t="s">
         <v>1411</v>
@@ -16112,17 +14107,11 @@
         <f t="shared" ref="H330:H335" si="21">D330+1095</f>
         <v>1095</v>
       </c>
-      <c r="I330" s="31">
-        <v>600</v>
-      </c>
-      <c r="J330" s="31">
-        <v>550</v>
-      </c>
-      <c r="K330" s="10">
+      <c r="I330" s="10">
         <v>329</v>
       </c>
     </row>
-    <row r="331" spans="1:11" ht="15">
+    <row r="331" spans="1:9" ht="15">
       <c r="B331" s="20"/>
       <c r="C331" s="24" t="s">
         <v>1411</v>
@@ -16141,17 +14130,11 @@
         <f t="shared" si="21"/>
         <v>1095</v>
       </c>
-      <c r="I331" s="31">
-        <v>160</v>
-      </c>
-      <c r="J331" s="31">
-        <v>130</v>
-      </c>
-      <c r="K331" s="10">
+      <c r="I331" s="10">
         <v>330</v>
       </c>
     </row>
-    <row r="332" spans="1:11" ht="15">
+    <row r="332" spans="1:9" ht="15">
       <c r="A332" s="22">
         <v>220</v>
       </c>
@@ -16173,17 +14156,11 @@
         <f t="shared" si="21"/>
         <v>1095</v>
       </c>
-      <c r="I332" s="31">
-        <v>300</v>
-      </c>
-      <c r="J332" s="31">
-        <v>250</v>
-      </c>
-      <c r="K332" s="10">
+      <c r="I332" s="10">
         <v>331</v>
       </c>
     </row>
-    <row r="333" spans="1:11" ht="15">
+    <row r="333" spans="1:9" ht="15">
       <c r="A333" s="22">
         <v>301</v>
       </c>
@@ -16205,17 +14182,11 @@
         <f t="shared" si="21"/>
         <v>1095</v>
       </c>
-      <c r="I333" s="31">
-        <v>550</v>
-      </c>
-      <c r="J333" s="31">
-        <v>350</v>
-      </c>
-      <c r="K333" s="10">
+      <c r="I333" s="10">
         <v>332</v>
       </c>
     </row>
-    <row r="334" spans="1:11" ht="15">
+    <row r="334" spans="1:9" ht="15">
       <c r="A334" s="22">
         <v>299</v>
       </c>
@@ -16237,17 +14208,11 @@
         <f t="shared" si="21"/>
         <v>1095</v>
       </c>
-      <c r="I334" s="31">
-        <v>300</v>
-      </c>
-      <c r="J334" s="31">
-        <v>200</v>
-      </c>
-      <c r="K334" s="10">
+      <c r="I334" s="10">
         <v>333</v>
       </c>
     </row>
-    <row r="335" spans="1:11" ht="15">
+    <row r="335" spans="1:9" ht="15">
       <c r="A335" s="22">
         <v>386</v>
       </c>
@@ -16269,17 +14234,11 @@
         <f t="shared" si="21"/>
         <v>1095</v>
       </c>
-      <c r="I335" s="31">
-        <v>300</v>
-      </c>
-      <c r="J335" s="31">
-        <v>180</v>
-      </c>
-      <c r="K335" s="10">
+      <c r="I335" s="10">
         <v>334</v>
       </c>
     </row>
-    <row r="336" spans="1:11" ht="15">
+    <row r="336" spans="1:9" ht="15">
       <c r="A336" s="22"/>
       <c r="B336" s="20"/>
       <c r="C336" s="24" t="s">
@@ -16299,17 +14258,11 @@
         <f>D336+1825</f>
         <v>1825</v>
       </c>
-      <c r="I336" s="31">
-        <v>120</v>
-      </c>
-      <c r="J336" s="31">
-        <v>80</v>
-      </c>
-      <c r="K336" s="10">
+      <c r="I336" s="10">
         <v>335</v>
       </c>
     </row>
-    <row r="337" spans="1:11" ht="17">
+    <row r="337" spans="1:9" ht="17">
       <c r="A337">
         <v>588</v>
       </c>
@@ -16331,17 +14284,11 @@
         <f>D337+1095</f>
         <v>1095</v>
       </c>
-      <c r="I337" s="31">
-        <v>480</v>
-      </c>
-      <c r="J337" s="31">
-        <v>400</v>
-      </c>
-      <c r="K337" s="10">
+      <c r="I337" s="10">
         <v>336</v>
       </c>
     </row>
-    <row r="338" spans="1:11" ht="15">
+    <row r="338" spans="1:9" ht="15">
       <c r="A338" s="22">
         <v>550</v>
       </c>
@@ -16363,17 +14310,11 @@
         <f>D338+1095</f>
         <v>1095</v>
       </c>
-      <c r="I338" s="31">
-        <v>420</v>
-      </c>
-      <c r="J338" s="31">
-        <v>350</v>
-      </c>
-      <c r="K338" s="10">
+      <c r="I338" s="10">
         <v>337</v>
       </c>
     </row>
-    <row r="339" spans="1:11" ht="15">
+    <row r="339" spans="1:9" ht="15">
       <c r="A339" s="22">
         <v>425</v>
       </c>
@@ -16395,17 +14336,11 @@
         <f>D339+1095</f>
         <v>1095</v>
       </c>
-      <c r="I339" s="31">
-        <v>500</v>
-      </c>
-      <c r="J339" s="31">
-        <v>350</v>
-      </c>
-      <c r="K339" s="10">
+      <c r="I339" s="10">
         <v>338</v>
       </c>
     </row>
-    <row r="340" spans="1:11" ht="15">
+    <row r="340" spans="1:9" ht="15">
       <c r="B340" s="20"/>
       <c r="C340" s="24" t="s">
         <v>1411</v>
@@ -16424,17 +14359,11 @@
         <f>D340+1095</f>
         <v>1095</v>
       </c>
-      <c r="I340" s="31">
-        <v>250</v>
-      </c>
-      <c r="J340" s="31">
-        <v>120</v>
-      </c>
-      <c r="K340" s="10">
+      <c r="I340" s="10">
         <v>339</v>
       </c>
     </row>
-    <row r="341" spans="1:11" ht="15">
+    <row r="341" spans="1:9" ht="15">
       <c r="A341" s="22">
         <v>325</v>
       </c>
@@ -16456,17 +14385,11 @@
         <f>D341+1825</f>
         <v>1825</v>
       </c>
-      <c r="I341" s="31">
-        <v>350</v>
-      </c>
-      <c r="J341" s="31">
-        <v>250</v>
-      </c>
-      <c r="K341" s="10">
+      <c r="I341" s="10">
         <v>340</v>
       </c>
     </row>
-    <row r="342" spans="1:11" ht="13.5" customHeight="1">
+    <row r="342" spans="1:9" ht="13.5" customHeight="1">
       <c r="A342" s="22">
         <v>471</v>
       </c>
@@ -16488,17 +14411,11 @@
         <f>D342+1095</f>
         <v>1095</v>
       </c>
-      <c r="I342" s="31">
-        <v>350</v>
-      </c>
-      <c r="J342" s="31">
-        <v>200</v>
-      </c>
-      <c r="K342" s="10">
+      <c r="I342" s="10">
         <v>341</v>
       </c>
     </row>
-    <row r="343" spans="1:11" ht="15">
+    <row r="343" spans="1:9" ht="15">
       <c r="A343" s="26">
         <v>350</v>
       </c>
@@ -16520,17 +14437,11 @@
         <f>D343+1095</f>
         <v>1095</v>
       </c>
-      <c r="I343" s="31">
-        <v>550</v>
-      </c>
-      <c r="J343" s="31">
-        <v>450</v>
-      </c>
-      <c r="K343" s="10">
+      <c r="I343" s="10">
         <v>342</v>
       </c>
     </row>
-    <row r="344" spans="1:11" ht="15">
+    <row r="344" spans="1:9" ht="15">
       <c r="A344" s="22">
         <v>310</v>
       </c>
@@ -16552,17 +14463,11 @@
         <f>D344+1095</f>
         <v>1095</v>
       </c>
-      <c r="I344" s="31">
-        <v>250</v>
-      </c>
-      <c r="J344" s="31">
-        <v>150</v>
-      </c>
-      <c r="K344" s="10">
+      <c r="I344" s="10">
         <v>343</v>
       </c>
     </row>
-    <row r="345" spans="1:11" ht="17">
+    <row r="345" spans="1:9" ht="17">
       <c r="A345" s="23" t="s">
         <v>1111</v>
       </c>
@@ -16584,17 +14489,11 @@
         <f>D345+1095</f>
         <v>1095</v>
       </c>
-      <c r="I345" s="31">
-        <v>300</v>
-      </c>
-      <c r="J345" s="31">
-        <v>100</v>
-      </c>
-      <c r="K345" s="10">
+      <c r="I345" s="10">
         <v>344</v>
       </c>
     </row>
-    <row r="346" spans="1:11" ht="15">
+    <row r="346" spans="1:9" ht="15">
       <c r="A346" s="22">
         <v>106</v>
       </c>
@@ -16616,17 +14515,11 @@
         <f>D346+1825</f>
         <v>1825</v>
       </c>
-      <c r="I346" s="31">
-        <v>350</v>
-      </c>
-      <c r="J346" s="31">
-        <v>150</v>
-      </c>
-      <c r="K346" s="10">
+      <c r="I346" s="10">
         <v>345</v>
       </c>
     </row>
-    <row r="347" spans="1:11" ht="15">
+    <row r="347" spans="1:9" ht="15">
       <c r="A347">
         <v>199</v>
       </c>
@@ -16648,17 +14541,11 @@
         <f>D347+1825</f>
         <v>1825</v>
       </c>
-      <c r="I347" s="31">
-        <v>250</v>
-      </c>
-      <c r="J347" s="31">
-        <v>150</v>
-      </c>
-      <c r="K347" s="10">
+      <c r="I347" s="10">
         <v>346</v>
       </c>
     </row>
-    <row r="348" spans="1:11" ht="15">
+    <row r="348" spans="1:9" ht="15">
       <c r="B348" s="22"/>
       <c r="C348" s="24" t="s">
         <v>1411</v>
@@ -16677,17 +14564,11 @@
         <f>D348+1825</f>
         <v>1825</v>
       </c>
-      <c r="I348" s="31">
-        <v>800</v>
-      </c>
-      <c r="J348" s="31">
-        <v>600</v>
-      </c>
-      <c r="K348" s="10">
+      <c r="I348" s="10">
         <v>347</v>
       </c>
     </row>
-    <row r="349" spans="1:11" ht="15">
+    <row r="349" spans="1:9" ht="15">
       <c r="A349">
         <v>149</v>
       </c>
@@ -16709,17 +14590,11 @@
         <f>D349+1825</f>
         <v>1825</v>
       </c>
-      <c r="I349" s="31">
-        <v>120</v>
-      </c>
-      <c r="J349" s="31">
-        <v>70</v>
-      </c>
-      <c r="K349" s="10">
+      <c r="I349" s="10">
         <v>348</v>
       </c>
     </row>
-    <row r="350" spans="1:11" ht="15">
+    <row r="350" spans="1:9" ht="15">
       <c r="A350">
         <v>149</v>
       </c>
@@ -16741,17 +14616,11 @@
         <f>D350+1095</f>
         <v>1095</v>
       </c>
-      <c r="I350" s="31">
-        <v>160</v>
-      </c>
-      <c r="J350" s="31">
-        <v>145</v>
-      </c>
-      <c r="K350" s="10">
+      <c r="I350" s="10">
         <v>349</v>
       </c>
     </row>
-    <row r="351" spans="1:11" ht="15">
+    <row r="351" spans="1:9" ht="15">
       <c r="A351" s="22">
         <v>423</v>
       </c>
@@ -16773,17 +14642,11 @@
         <f>D351+1095</f>
         <v>1095</v>
       </c>
-      <c r="I351" s="31">
-        <v>610</v>
-      </c>
-      <c r="J351" s="31">
-        <v>400</v>
-      </c>
-      <c r="K351" s="10">
+      <c r="I351" s="10">
         <v>350</v>
       </c>
     </row>
-    <row r="352" spans="1:11" ht="15">
+    <row r="352" spans="1:9" ht="15">
       <c r="A352" s="23" t="s">
         <v>1111</v>
       </c>
@@ -16805,17 +14668,11 @@
         <f>D352+1095</f>
         <v>1095</v>
       </c>
-      <c r="I352" s="31">
-        <v>260</v>
-      </c>
-      <c r="J352" s="31">
-        <v>165</v>
-      </c>
-      <c r="K352" s="10">
+      <c r="I352" s="10">
         <v>351</v>
       </c>
     </row>
-    <row r="353" spans="1:11" ht="15">
+    <row r="353" spans="1:9" ht="15">
       <c r="A353" s="22">
         <v>270</v>
       </c>
@@ -16837,17 +14694,11 @@
         <f>D353+1095</f>
         <v>1095</v>
       </c>
-      <c r="I353" s="31">
-        <v>200</v>
-      </c>
-      <c r="J353" s="31">
-        <v>155</v>
-      </c>
-      <c r="K353" s="10">
+      <c r="I353" s="10">
         <v>352</v>
       </c>
     </row>
-    <row r="354" spans="1:11" ht="15">
+    <row r="354" spans="1:9" ht="15">
       <c r="A354" s="22">
         <v>900</v>
       </c>
@@ -16869,17 +14720,11 @@
         <f>D354+1096</f>
         <v>1096</v>
       </c>
-      <c r="I354" s="31">
-        <v>900</v>
-      </c>
-      <c r="J354" s="31">
-        <v>750</v>
-      </c>
-      <c r="K354" s="10">
+      <c r="I354" s="10">
         <v>353</v>
       </c>
     </row>
-    <row r="355" spans="1:11" ht="15">
+    <row r="355" spans="1:9" ht="15">
       <c r="A355" s="22">
         <v>159</v>
       </c>
@@ -16901,17 +14746,11 @@
         <f t="shared" ref="H355:H386" si="22">D355+1095</f>
         <v>1095</v>
       </c>
-      <c r="I355" s="31">
-        <v>150</v>
-      </c>
-      <c r="J355" s="31">
-        <v>70</v>
-      </c>
-      <c r="K355" s="10">
+      <c r="I355" s="10">
         <v>354</v>
       </c>
     </row>
-    <row r="356" spans="1:11" ht="15">
+    <row r="356" spans="1:9" ht="15">
       <c r="A356">
         <v>295.2</v>
       </c>
@@ -16933,17 +14772,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I356" s="31">
-        <v>200</v>
-      </c>
-      <c r="J356" s="31">
-        <v>100</v>
-      </c>
-      <c r="K356" s="10">
+      <c r="I356" s="10">
         <v>355</v>
       </c>
     </row>
-    <row r="357" spans="1:11" ht="15">
+    <row r="357" spans="1:9" ht="15">
       <c r="A357">
         <v>295.2</v>
       </c>
@@ -16965,17 +14798,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I357" s="31">
-        <v>210</v>
-      </c>
-      <c r="J357" s="31">
-        <v>100</v>
-      </c>
-      <c r="K357" s="10">
+      <c r="I357" s="10">
         <v>356</v>
       </c>
     </row>
-    <row r="358" spans="1:11" ht="15">
+    <row r="358" spans="1:9" ht="15">
       <c r="A358">
         <v>135</v>
       </c>
@@ -16997,17 +14824,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I358" s="31">
-        <v>210</v>
-      </c>
-      <c r="J358" s="31">
-        <v>110</v>
-      </c>
-      <c r="K358" s="10">
+      <c r="I358" s="10">
         <v>357</v>
       </c>
     </row>
-    <row r="359" spans="1:11" ht="15">
+    <row r="359" spans="1:9" ht="15">
       <c r="A359">
         <v>136</v>
       </c>
@@ -17029,17 +14850,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I359" s="31">
-        <v>250</v>
-      </c>
-      <c r="J359" s="31">
-        <v>110</v>
-      </c>
-      <c r="K359" s="10">
+      <c r="I359" s="10">
         <v>358</v>
       </c>
     </row>
-    <row r="360" spans="1:11" ht="15">
+    <row r="360" spans="1:9" ht="15">
       <c r="A360" s="22">
         <v>150</v>
       </c>
@@ -17061,17 +14876,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I360" s="31">
-        <v>150</v>
-      </c>
-      <c r="J360" s="31">
-        <v>90</v>
-      </c>
-      <c r="K360" s="10">
+      <c r="I360" s="10">
         <v>359</v>
       </c>
     </row>
-    <row r="361" spans="1:11" ht="15">
+    <row r="361" spans="1:9" ht="15">
       <c r="A361" s="22">
         <v>1350</v>
       </c>
@@ -17093,17 +14902,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I361" s="31">
-        <v>1300</v>
-      </c>
-      <c r="J361" s="31">
-        <v>900</v>
-      </c>
-      <c r="K361" s="10">
+      <c r="I361" s="10">
         <v>360</v>
       </c>
     </row>
-    <row r="362" spans="1:11" ht="15">
+    <row r="362" spans="1:9" ht="15">
       <c r="A362" s="22">
         <v>679</v>
       </c>
@@ -17125,17 +14928,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I362" s="31">
-        <v>800</v>
-      </c>
-      <c r="J362" s="31">
-        <v>550</v>
-      </c>
-      <c r="K362" s="10">
+      <c r="I362" s="10">
         <v>361</v>
       </c>
     </row>
-    <row r="363" spans="1:11" ht="15">
+    <row r="363" spans="1:9" ht="15">
       <c r="A363" s="22">
         <v>801</v>
       </c>
@@ -17157,17 +14954,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I363" s="31">
-        <v>900</v>
-      </c>
-      <c r="J363" s="31">
-        <v>600</v>
-      </c>
-      <c r="K363" s="10">
+      <c r="I363" s="10">
         <v>362</v>
       </c>
     </row>
-    <row r="364" spans="1:11" ht="15">
+    <row r="364" spans="1:9" ht="15">
       <c r="A364" s="22">
         <v>147</v>
       </c>
@@ -17189,17 +14980,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I364" s="31">
-        <v>220</v>
-      </c>
-      <c r="J364" s="31">
-        <v>150</v>
-      </c>
-      <c r="K364" s="10">
+      <c r="I364" s="10">
         <v>363</v>
       </c>
     </row>
-    <row r="365" spans="1:11" ht="15">
+    <row r="365" spans="1:9" ht="15">
       <c r="A365" s="22">
         <v>782</v>
       </c>
@@ -17221,17 +15006,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I365" s="31">
-        <v>900</v>
-      </c>
-      <c r="J365" s="31">
-        <v>550</v>
-      </c>
-      <c r="K365" s="10">
+      <c r="I365" s="10">
         <v>364</v>
       </c>
     </row>
-    <row r="366" spans="1:11" ht="15">
+    <row r="366" spans="1:9" ht="15">
       <c r="A366" s="22">
         <v>315</v>
       </c>
@@ -17253,17 +15032,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I366" s="31">
-        <v>300</v>
-      </c>
-      <c r="J366" s="31">
-        <v>150</v>
-      </c>
-      <c r="K366" s="10">
+      <c r="I366" s="10">
         <v>365</v>
       </c>
     </row>
-    <row r="367" spans="1:11" ht="15">
+    <row r="367" spans="1:9" ht="15">
       <c r="A367">
         <v>801</v>
       </c>
@@ -17284,17 +15057,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I367" s="31">
-        <v>600</v>
-      </c>
-      <c r="J367" s="31">
-        <v>460</v>
-      </c>
-      <c r="K367" s="10">
+      <c r="I367" s="10">
         <v>366</v>
       </c>
     </row>
-    <row r="368" spans="1:11" ht="15">
+    <row r="368" spans="1:9" ht="15">
       <c r="A368">
         <v>768</v>
       </c>
@@ -17316,17 +15083,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I368" s="31">
-        <v>1000</v>
-      </c>
-      <c r="J368" s="31">
-        <v>790</v>
-      </c>
-      <c r="K368" s="10">
+      <c r="I368" s="10">
         <v>367</v>
       </c>
     </row>
-    <row r="369" spans="1:11" ht="15">
+    <row r="369" spans="1:9" ht="15">
       <c r="A369" s="22">
         <v>879.8</v>
       </c>
@@ -17348,17 +15109,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I369" s="31">
-        <v>800</v>
-      </c>
-      <c r="J369" s="31">
-        <v>660</v>
-      </c>
-      <c r="K369" s="10">
+      <c r="I369" s="10">
         <v>368</v>
       </c>
     </row>
-    <row r="370" spans="1:11" ht="15">
+    <row r="370" spans="1:9" ht="15">
       <c r="A370" s="22">
         <v>450</v>
       </c>
@@ -17380,17 +15135,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I370" s="31">
-        <v>500</v>
-      </c>
-      <c r="J370" s="31">
-        <v>375</v>
-      </c>
-      <c r="K370" s="10">
+      <c r="I370" s="10">
         <v>369</v>
       </c>
     </row>
-    <row r="371" spans="1:11" ht="15">
+    <row r="371" spans="1:9" ht="15">
       <c r="A371" s="22">
         <v>539</v>
       </c>
@@ -17412,17 +15161,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I371" s="31">
-        <v>800</v>
-      </c>
-      <c r="J371" s="31">
-        <v>500</v>
-      </c>
-      <c r="K371" s="10">
+      <c r="I371" s="10">
         <v>370</v>
       </c>
     </row>
-    <row r="372" spans="1:11" ht="15">
+    <row r="372" spans="1:9" ht="15">
       <c r="A372" s="22">
         <v>599</v>
       </c>
@@ -17444,17 +15187,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I372" s="31">
-        <v>600</v>
-      </c>
-      <c r="J372" s="31">
-        <v>400</v>
-      </c>
-      <c r="K372" s="10">
+      <c r="I372" s="10">
         <v>371</v>
       </c>
     </row>
-    <row r="373" spans="1:11" ht="15">
+    <row r="373" spans="1:9" ht="15">
       <c r="A373" s="22">
         <v>599</v>
       </c>
@@ -17476,17 +15213,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I373" s="31">
-        <v>550</v>
-      </c>
-      <c r="J373" s="31">
-        <v>330</v>
-      </c>
-      <c r="K373" s="10">
+      <c r="I373" s="10">
         <v>372</v>
       </c>
     </row>
-    <row r="374" spans="1:11" ht="15">
+    <row r="374" spans="1:9" ht="15">
       <c r="A374" s="22">
         <v>399</v>
       </c>
@@ -17508,17 +15239,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I374" s="31">
-        <v>550</v>
-      </c>
-      <c r="J374" s="31">
-        <v>400</v>
-      </c>
-      <c r="K374" s="10">
+      <c r="I374" s="10">
         <v>373</v>
       </c>
     </row>
-    <row r="375" spans="1:11" ht="15">
+    <row r="375" spans="1:9" ht="15">
       <c r="A375" s="22">
         <v>168.8</v>
       </c>
@@ -17540,17 +15265,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I375" s="31">
-        <v>250</v>
-      </c>
-      <c r="J375" s="31">
-        <v>150</v>
-      </c>
-      <c r="K375" s="10">
+      <c r="I375" s="10">
         <v>374</v>
       </c>
     </row>
-    <row r="376" spans="1:11" ht="15">
+    <row r="376" spans="1:9" ht="15">
       <c r="A376" s="22">
         <v>199</v>
       </c>
@@ -17572,17 +15291,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I376" s="31">
-        <v>120</v>
-      </c>
-      <c r="J376" s="31">
-        <v>90</v>
-      </c>
-      <c r="K376" s="10">
+      <c r="I376" s="10">
         <v>375</v>
       </c>
     </row>
-    <row r="377" spans="1:11" ht="15">
+    <row r="377" spans="1:9" ht="15">
       <c r="A377" s="22">
         <v>563.20000000000005</v>
       </c>
@@ -17604,17 +15317,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I377" s="31">
-        <v>800</v>
-      </c>
-      <c r="J377" s="31">
-        <v>600</v>
-      </c>
-      <c r="K377" s="10">
+      <c r="I377" s="10">
         <v>376</v>
       </c>
     </row>
-    <row r="378" spans="1:11" ht="15">
+    <row r="378" spans="1:9" ht="15">
       <c r="A378" s="22">
         <v>135</v>
       </c>
@@ -17636,17 +15343,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I378" s="31">
-        <v>200</v>
-      </c>
-      <c r="J378" s="31">
-        <v>120</v>
-      </c>
-      <c r="K378" s="10">
+      <c r="I378" s="10">
         <v>377</v>
       </c>
     </row>
-    <row r="379" spans="1:11" ht="15">
+    <row r="379" spans="1:9" ht="15">
       <c r="A379" s="23" t="s">
         <v>1111</v>
       </c>
@@ -17668,17 +15369,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I379" s="31">
-        <v>550</v>
-      </c>
-      <c r="J379" s="31">
-        <v>350</v>
-      </c>
-      <c r="K379" s="10">
+      <c r="I379" s="10">
         <v>378</v>
       </c>
     </row>
-    <row r="380" spans="1:11" ht="15">
+    <row r="380" spans="1:9" ht="15">
       <c r="A380" s="22"/>
       <c r="B380" s="20"/>
       <c r="C380" s="24" t="s">
@@ -17698,17 +15393,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I380" s="31">
-        <v>250</v>
-      </c>
-      <c r="J380" s="31">
-        <v>140</v>
-      </c>
-      <c r="K380" s="10">
+      <c r="I380" s="10">
         <v>379</v>
       </c>
     </row>
-    <row r="381" spans="1:11" ht="15">
+    <row r="381" spans="1:9" ht="15">
       <c r="A381" s="22">
         <v>289</v>
       </c>
@@ -17730,17 +15419,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I381" s="31">
-        <v>300</v>
-      </c>
-      <c r="J381" s="31">
-        <v>170</v>
-      </c>
-      <c r="K381" s="10">
+      <c r="I381" s="10">
         <v>380</v>
       </c>
     </row>
-    <row r="382" spans="1:11" ht="15">
+    <row r="382" spans="1:9" ht="15">
       <c r="A382" s="22">
         <v>109</v>
       </c>
@@ -17762,17 +15445,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I382" s="31">
-        <v>200</v>
-      </c>
-      <c r="J382" s="31">
-        <v>90</v>
-      </c>
-      <c r="K382" s="10">
+      <c r="I382" s="10">
         <v>381</v>
       </c>
     </row>
-    <row r="383" spans="1:11" ht="15">
+    <row r="383" spans="1:9" ht="15">
       <c r="A383" s="22">
         <v>149</v>
       </c>
@@ -17794,17 +15471,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I383" s="31">
-        <v>200</v>
-      </c>
-      <c r="J383" s="31">
-        <v>70</v>
-      </c>
-      <c r="K383" s="10">
+      <c r="I383" s="10">
         <v>382</v>
       </c>
     </row>
-    <row r="384" spans="1:11" ht="15">
+    <row r="384" spans="1:9" ht="15">
       <c r="A384" s="22">
         <v>258</v>
       </c>
@@ -17826,17 +15497,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I384" s="31">
-        <v>300</v>
-      </c>
-      <c r="J384" s="31">
-        <v>200</v>
-      </c>
-      <c r="K384" s="10">
+      <c r="I384" s="10">
         <v>383</v>
       </c>
     </row>
-    <row r="385" spans="1:11" ht="15">
+    <row r="385" spans="1:9" ht="15">
       <c r="A385" s="22">
         <v>112</v>
       </c>
@@ -17858,17 +15523,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I385" s="31">
-        <v>250</v>
-      </c>
-      <c r="J385" s="31">
-        <v>150</v>
-      </c>
-      <c r="K385" s="10">
+      <c r="I385" s="10">
         <v>384</v>
       </c>
     </row>
-    <row r="386" spans="1:11" ht="15">
+    <row r="386" spans="1:9" ht="15">
       <c r="A386" s="22">
         <v>259</v>
       </c>
@@ -17890,17 +15549,11 @@
         <f t="shared" si="22"/>
         <v>1095</v>
       </c>
-      <c r="I386" s="31">
-        <v>320</v>
-      </c>
-      <c r="J386" s="31">
-        <v>250</v>
-      </c>
-      <c r="K386" s="10">
+      <c r="I386" s="10">
         <v>385</v>
       </c>
     </row>
-    <row r="387" spans="1:11" ht="15">
+    <row r="387" spans="1:9" ht="15">
       <c r="A387" s="22">
         <v>320</v>
       </c>
@@ -17922,17 +15575,11 @@
         <f t="shared" ref="H387:H418" si="23">D387+1095</f>
         <v>1095</v>
       </c>
-      <c r="I387" s="31">
-        <v>320</v>
-      </c>
-      <c r="J387" s="31">
-        <v>250</v>
-      </c>
-      <c r="K387" s="10">
+      <c r="I387" s="10">
         <v>386</v>
       </c>
     </row>
-    <row r="388" spans="1:11" ht="15">
+    <row r="388" spans="1:9" ht="15">
       <c r="A388" s="22">
         <v>299</v>
       </c>
@@ -17954,17 +15601,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I388" s="31">
-        <v>320</v>
-      </c>
-      <c r="J388" s="31">
-        <v>250</v>
-      </c>
-      <c r="K388" s="10">
+      <c r="I388" s="10">
         <v>387</v>
       </c>
     </row>
-    <row r="389" spans="1:11" ht="15">
+    <row r="389" spans="1:9" ht="15">
       <c r="A389" s="22">
         <v>112</v>
       </c>
@@ -17986,17 +15627,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I389" s="31">
-        <v>120</v>
-      </c>
-      <c r="J389" s="31">
-        <v>50</v>
-      </c>
-      <c r="K389" s="10">
+      <c r="I389" s="10">
         <v>388</v>
       </c>
     </row>
-    <row r="390" spans="1:11" ht="15">
+    <row r="390" spans="1:9" ht="15">
       <c r="A390" s="22">
         <v>111</v>
       </c>
@@ -18018,17 +15653,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I390" s="31">
-        <v>100</v>
-      </c>
-      <c r="J390" s="31">
-        <v>60</v>
-      </c>
-      <c r="K390" s="10">
+      <c r="I390" s="10">
         <v>389</v>
       </c>
     </row>
-    <row r="391" spans="1:11" ht="15">
+    <row r="391" spans="1:9" ht="15">
       <c r="A391" s="22"/>
       <c r="B391" s="20"/>
       <c r="C391" s="24" t="s">
@@ -18048,17 +15677,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I391" s="31">
-        <v>100</v>
-      </c>
-      <c r="J391" s="31">
-        <v>60</v>
-      </c>
-      <c r="K391" s="10">
+      <c r="I391" s="10">
         <v>390</v>
       </c>
     </row>
-    <row r="392" spans="1:11" ht="15">
+    <row r="392" spans="1:9" ht="15">
       <c r="A392" s="22">
         <v>578</v>
       </c>
@@ -18080,17 +15703,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I392" s="31">
-        <v>350</v>
-      </c>
-      <c r="J392" s="31">
-        <v>250</v>
-      </c>
-      <c r="K392" s="10">
+      <c r="I392" s="10">
         <v>391</v>
       </c>
     </row>
-    <row r="393" spans="1:11" ht="15">
+    <row r="393" spans="1:9" ht="15">
       <c r="A393" s="22">
         <v>158</v>
       </c>
@@ -18112,17 +15729,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I393" s="31">
-        <v>250</v>
-      </c>
-      <c r="J393" s="31">
-        <v>140</v>
-      </c>
-      <c r="K393" s="10">
+      <c r="I393" s="10">
         <v>392</v>
       </c>
     </row>
-    <row r="394" spans="1:11" ht="15">
+    <row r="394" spans="1:9" ht="15">
       <c r="A394" s="22">
         <v>63</v>
       </c>
@@ -18144,17 +15755,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I394" s="31">
-        <v>100</v>
-      </c>
-      <c r="J394" s="31">
-        <v>60</v>
-      </c>
-      <c r="K394" s="10">
+      <c r="I394" s="10">
         <v>393</v>
       </c>
     </row>
-    <row r="395" spans="1:11" ht="15">
+    <row r="395" spans="1:9" ht="15">
       <c r="A395" s="22">
         <v>619</v>
       </c>
@@ -18176,17 +15781,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I395" s="31">
-        <v>400</v>
-      </c>
-      <c r="J395" s="31">
-        <v>250</v>
-      </c>
-      <c r="K395" s="10">
+      <c r="I395" s="10">
         <v>394</v>
       </c>
     </row>
-    <row r="396" spans="1:11" ht="15">
+    <row r="396" spans="1:9" ht="15">
       <c r="A396" s="23" t="s">
         <v>1111</v>
       </c>
@@ -18207,17 +15806,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I396" s="31">
-        <v>2000</v>
-      </c>
-      <c r="J396" s="31">
-        <v>1600</v>
-      </c>
-      <c r="K396" s="10">
+      <c r="I396" s="10">
         <v>395</v>
       </c>
     </row>
-    <row r="397" spans="1:11" ht="15">
+    <row r="397" spans="1:9" ht="15">
       <c r="A397" s="23" t="s">
         <v>1111</v>
       </c>
@@ -18239,17 +15832,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I397" s="31">
-        <v>2100</v>
-      </c>
-      <c r="J397" s="31">
-        <v>1900</v>
-      </c>
-      <c r="K397" s="10">
+      <c r="I397" s="10">
         <v>396</v>
       </c>
     </row>
-    <row r="398" spans="1:11" ht="15">
+    <row r="398" spans="1:9" ht="15">
       <c r="A398" s="22">
         <v>545</v>
       </c>
@@ -18271,17 +15858,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I398" s="31">
-        <v>650</v>
-      </c>
-      <c r="J398" s="31">
-        <v>500</v>
-      </c>
-      <c r="K398" s="10">
+      <c r="I398" s="10">
         <v>397</v>
       </c>
     </row>
-    <row r="399" spans="1:11" ht="15">
+    <row r="399" spans="1:9" ht="15">
       <c r="A399" s="22">
         <v>212</v>
       </c>
@@ -18303,17 +15884,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I399" s="31">
-        <v>250</v>
-      </c>
-      <c r="J399" s="31">
-        <v>100</v>
-      </c>
-      <c r="K399" s="10">
+      <c r="I399" s="10">
         <v>398</v>
       </c>
     </row>
-    <row r="400" spans="1:11" ht="15">
+    <row r="400" spans="1:9" ht="15">
       <c r="A400" s="22"/>
       <c r="B400" s="20"/>
       <c r="C400" s="24" t="s">
@@ -18333,17 +15908,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I400" s="31">
-        <v>850</v>
-      </c>
-      <c r="J400" s="31">
-        <v>680</v>
-      </c>
-      <c r="K400" s="10">
+      <c r="I400" s="10">
         <v>399</v>
       </c>
     </row>
-    <row r="401" spans="1:11" ht="15">
+    <row r="401" spans="1:9" ht="15">
       <c r="A401" s="22">
         <v>199</v>
       </c>
@@ -18365,17 +15934,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I401" s="31">
-        <v>250</v>
-      </c>
-      <c r="J401" s="31">
-        <v>150</v>
-      </c>
-      <c r="K401" s="10">
+      <c r="I401" s="10">
         <v>400</v>
       </c>
     </row>
-    <row r="402" spans="1:11" ht="15">
+    <row r="402" spans="1:9" ht="15">
       <c r="A402">
         <v>171</v>
       </c>
@@ -18397,17 +15960,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I402" s="31">
-        <v>200</v>
-      </c>
-      <c r="J402" s="31">
-        <v>80</v>
-      </c>
-      <c r="K402" s="10">
+      <c r="I402" s="10">
         <v>401</v>
       </c>
     </row>
-    <row r="403" spans="1:11" ht="15">
+    <row r="403" spans="1:9" ht="15">
       <c r="A403" s="22">
         <v>139</v>
       </c>
@@ -18429,17 +15986,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I403" s="31">
-        <v>250</v>
-      </c>
-      <c r="J403" s="31">
-        <v>170</v>
-      </c>
-      <c r="K403" s="10">
+      <c r="I403" s="10">
         <v>402</v>
       </c>
     </row>
-    <row r="404" spans="1:11" ht="15">
+    <row r="404" spans="1:9" ht="15">
       <c r="A404" s="22">
         <v>494</v>
       </c>
@@ -18461,17 +16012,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I404" s="31">
-        <v>500</v>
-      </c>
-      <c r="J404" s="31">
-        <v>200</v>
-      </c>
-      <c r="K404" s="10">
+      <c r="I404" s="10">
         <v>403</v>
       </c>
     </row>
-    <row r="405" spans="1:11" ht="15">
+    <row r="405" spans="1:9" ht="15">
       <c r="A405" s="22">
         <v>760</v>
       </c>
@@ -18493,17 +16038,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I405" s="31">
-        <v>460</v>
-      </c>
-      <c r="J405" s="31">
-        <v>320</v>
-      </c>
-      <c r="K405" s="10">
+      <c r="I405" s="10">
         <v>404</v>
       </c>
     </row>
-    <row r="406" spans="1:11" ht="15">
+    <row r="406" spans="1:9" ht="15">
       <c r="A406" s="23" t="s">
         <v>1111</v>
       </c>
@@ -18525,17 +16064,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I406" s="31">
-        <v>1500</v>
-      </c>
-      <c r="J406" s="31">
-        <v>1250</v>
-      </c>
-      <c r="K406" s="10">
+      <c r="I406" s="10">
         <v>405</v>
       </c>
     </row>
-    <row r="407" spans="1:11" ht="15">
+    <row r="407" spans="1:9" ht="15">
       <c r="A407" s="22"/>
       <c r="B407" s="23"/>
       <c r="C407" s="24" t="s">
@@ -18554,17 +16087,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I407" s="31">
-        <v>1800</v>
-      </c>
-      <c r="J407" s="31">
-        <v>1400</v>
-      </c>
-      <c r="K407" s="10">
+      <c r="I407" s="10">
         <v>406</v>
       </c>
     </row>
-    <row r="408" spans="1:11" ht="15">
+    <row r="408" spans="1:9" ht="15">
       <c r="A408">
         <v>133</v>
       </c>
@@ -18586,17 +16113,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I408" s="31">
-        <v>110</v>
-      </c>
-      <c r="J408" s="31">
-        <v>60</v>
-      </c>
-      <c r="K408" s="10">
+      <c r="I408" s="10">
         <v>407</v>
       </c>
     </row>
-    <row r="409" spans="1:11" ht="15">
+    <row r="409" spans="1:9" ht="15">
       <c r="A409" s="23" t="s">
         <v>1111</v>
       </c>
@@ -18617,17 +16138,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I409" s="31">
-        <v>200</v>
-      </c>
-      <c r="J409" s="31">
-        <v>160</v>
-      </c>
-      <c r="K409" s="10">
+      <c r="I409" s="10">
         <v>408</v>
       </c>
     </row>
-    <row r="410" spans="1:11" ht="15">
+    <row r="410" spans="1:9" ht="15">
       <c r="A410" s="23" t="s">
         <v>1111</v>
       </c>
@@ -18649,17 +16164,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I410" s="31">
-        <v>200</v>
-      </c>
-      <c r="J410" s="31">
-        <v>160</v>
-      </c>
-      <c r="K410" s="10">
+      <c r="I410" s="10">
         <v>409</v>
       </c>
     </row>
-    <row r="411" spans="1:11" ht="15">
+    <row r="411" spans="1:9" ht="15">
       <c r="A411">
         <v>199</v>
       </c>
@@ -18681,17 +16190,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I411" s="31">
-        <v>200</v>
-      </c>
-      <c r="J411" s="31">
-        <v>160</v>
-      </c>
-      <c r="K411" s="10">
+      <c r="I411" s="10">
         <v>410</v>
       </c>
     </row>
-    <row r="412" spans="1:11" ht="15">
+    <row r="412" spans="1:9" ht="15">
       <c r="A412" s="23" t="s">
         <v>1111</v>
       </c>
@@ -18713,17 +16216,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I412" s="31">
-        <v>230</v>
-      </c>
-      <c r="J412" s="31">
-        <v>160</v>
-      </c>
-      <c r="K412" s="10">
+      <c r="I412" s="10">
         <v>411</v>
       </c>
     </row>
-    <row r="413" spans="1:11" ht="15">
+    <row r="413" spans="1:9" ht="15">
       <c r="B413" s="20"/>
       <c r="C413" s="24" t="s">
         <v>1411</v>
@@ -18742,17 +16239,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I413" s="31">
-        <v>410</v>
-      </c>
-      <c r="J413" s="31">
-        <v>300</v>
-      </c>
-      <c r="K413" s="10">
+      <c r="I413" s="10">
         <v>412</v>
       </c>
     </row>
-    <row r="414" spans="1:11" ht="15">
+    <row r="414" spans="1:9" ht="15">
       <c r="A414" s="22">
         <v>135</v>
       </c>
@@ -18774,17 +16265,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I414" s="31">
-        <v>120</v>
-      </c>
-      <c r="J414" s="31">
-        <v>90</v>
-      </c>
-      <c r="K414" s="10">
+      <c r="I414" s="10">
         <v>413</v>
       </c>
     </row>
-    <row r="415" spans="1:11" ht="15">
+    <row r="415" spans="1:9" ht="15">
       <c r="A415" s="22">
         <v>510</v>
       </c>
@@ -18806,17 +16291,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I415" s="31">
-        <v>350</v>
-      </c>
-      <c r="J415" s="31">
-        <v>200</v>
-      </c>
-      <c r="K415" s="10">
+      <c r="I415" s="10">
         <v>414</v>
       </c>
     </row>
-    <row r="416" spans="1:11" ht="15">
+    <row r="416" spans="1:9" ht="15">
       <c r="A416" s="22">
         <v>625</v>
       </c>
@@ -18838,17 +16317,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I416" s="31">
-        <v>400</v>
-      </c>
-      <c r="J416" s="33">
-        <v>300</v>
-      </c>
-      <c r="K416" s="10">
+      <c r="I416" s="10">
         <v>415</v>
       </c>
     </row>
-    <row r="417" spans="1:11" ht="15">
+    <row r="417" spans="1:9" ht="15">
       <c r="A417" s="22">
         <v>338</v>
       </c>
@@ -18870,17 +16343,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I417" s="33">
-        <v>350</v>
-      </c>
-      <c r="J417" s="33">
-        <v>220</v>
-      </c>
-      <c r="K417" s="10">
+      <c r="I417" s="10">
         <v>416</v>
       </c>
     </row>
-    <row r="418" spans="1:11" ht="15">
+    <row r="418" spans="1:9" ht="15">
       <c r="A418" s="22">
         <v>785</v>
       </c>
@@ -18902,17 +16369,11 @@
         <f t="shared" si="23"/>
         <v>1095</v>
       </c>
-      <c r="I418" s="31">
-        <v>550</v>
-      </c>
-      <c r="J418" s="31">
-        <v>400</v>
-      </c>
-      <c r="K418" s="10">
+      <c r="I418" s="10">
         <v>417</v>
       </c>
     </row>
-    <row r="419" spans="1:11" ht="15">
+    <row r="419" spans="1:9" ht="15">
       <c r="A419" s="22">
         <v>528</v>
       </c>
@@ -18934,17 +16395,11 @@
         <f t="shared" ref="H419:H443" si="24">D419+1095</f>
         <v>1095</v>
       </c>
-      <c r="I419" s="31">
-        <v>500</v>
-      </c>
-      <c r="J419" s="31">
-        <v>400</v>
-      </c>
-      <c r="K419" s="10">
+      <c r="I419" s="10">
         <v>418</v>
       </c>
     </row>
-    <row r="420" spans="1:11" ht="15">
+    <row r="420" spans="1:9" ht="15">
       <c r="A420" s="22">
         <v>145</v>
       </c>
@@ -18966,17 +16421,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I420" s="31">
-        <v>150</v>
-      </c>
-      <c r="J420" s="31">
-        <v>90</v>
-      </c>
-      <c r="K420" s="10">
+      <c r="I420" s="10">
         <v>419</v>
       </c>
     </row>
-    <row r="421" spans="1:11" ht="15">
+    <row r="421" spans="1:9" ht="15">
       <c r="A421" s="22">
         <v>44.8</v>
       </c>
@@ -18998,17 +16447,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I421" s="31">
-        <v>80</v>
-      </c>
-      <c r="J421" s="31">
-        <v>45</v>
-      </c>
-      <c r="K421" s="10">
+      <c r="I421" s="10">
         <v>420</v>
       </c>
     </row>
-    <row r="422" spans="1:11" ht="15">
+    <row r="422" spans="1:9" ht="15">
       <c r="A422" s="22">
         <v>209</v>
       </c>
@@ -19030,17 +16473,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I422" s="31">
-        <v>350</v>
-      </c>
-      <c r="J422" s="31">
-        <v>280</v>
-      </c>
-      <c r="K422" s="10">
+      <c r="I422" s="10">
         <v>421</v>
       </c>
     </row>
-    <row r="423" spans="1:11" ht="15">
+    <row r="423" spans="1:9" ht="15">
       <c r="A423" s="22">
         <v>185</v>
       </c>
@@ -19062,17 +16499,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I423" s="31">
-        <v>250</v>
-      </c>
-      <c r="J423" s="31">
-        <v>150</v>
-      </c>
-      <c r="K423" s="10">
+      <c r="I423" s="10">
         <v>422</v>
       </c>
     </row>
-    <row r="424" spans="1:11" ht="15">
+    <row r="424" spans="1:9" ht="15">
       <c r="A424" s="22">
         <v>208</v>
       </c>
@@ -19094,17 +16525,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I424" s="31">
-        <v>200</v>
-      </c>
-      <c r="J424" s="31">
-        <v>150</v>
-      </c>
-      <c r="K424" s="10">
+      <c r="I424" s="10">
         <v>423</v>
       </c>
     </row>
-    <row r="425" spans="1:11" ht="15">
+    <row r="425" spans="1:9" ht="15">
       <c r="A425" s="23" t="s">
         <v>1111</v>
       </c>
@@ -19125,17 +16550,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I425" s="31">
-        <v>480</v>
-      </c>
-      <c r="J425" s="31">
-        <v>300</v>
-      </c>
-      <c r="K425" s="10">
+      <c r="I425" s="10">
         <v>424</v>
       </c>
     </row>
-    <row r="426" spans="1:11" ht="15">
+    <row r="426" spans="1:9" ht="15">
       <c r="A426" s="23" t="s">
         <v>1111</v>
       </c>
@@ -19156,17 +16575,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I426" s="31">
-        <v>200</v>
-      </c>
-      <c r="J426" s="31">
-        <v>80</v>
-      </c>
-      <c r="K426" s="10">
+      <c r="I426" s="10">
         <v>425</v>
       </c>
     </row>
-    <row r="427" spans="1:11" ht="15">
+    <row r="427" spans="1:9" ht="15">
       <c r="A427" s="23" t="s">
         <v>1111</v>
       </c>
@@ -19187,17 +16600,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I427" s="31">
-        <v>250</v>
-      </c>
-      <c r="J427" s="31">
-        <v>110</v>
-      </c>
-      <c r="K427" s="10">
+      <c r="I427" s="10">
         <v>426</v>
       </c>
     </row>
-    <row r="428" spans="1:11" ht="15">
+    <row r="428" spans="1:9" ht="15">
       <c r="A428" s="23" t="s">
         <v>1111</v>
       </c>
@@ -19219,17 +16626,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I428" s="31">
-        <v>200</v>
-      </c>
-      <c r="J428" s="31">
-        <v>100</v>
-      </c>
-      <c r="K428" s="10">
+      <c r="I428" s="10">
         <v>427</v>
       </c>
     </row>
-    <row r="429" spans="1:11" ht="15">
+    <row r="429" spans="1:9" ht="15">
       <c r="A429" s="23" t="s">
         <v>1111</v>
       </c>
@@ -19251,17 +16652,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I429" s="31">
-        <v>250</v>
-      </c>
-      <c r="J429" s="31">
-        <v>150</v>
-      </c>
-      <c r="K429" s="10">
+      <c r="I429" s="10">
         <v>428</v>
       </c>
     </row>
-    <row r="430" spans="1:11" ht="15">
+    <row r="430" spans="1:9" ht="15">
       <c r="A430" s="22">
         <v>99</v>
       </c>
@@ -19283,17 +16678,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I430" s="31">
-        <v>150</v>
-      </c>
-      <c r="J430" s="31">
-        <v>90</v>
-      </c>
-      <c r="K430" s="10">
+      <c r="I430" s="10">
         <v>429</v>
       </c>
     </row>
-    <row r="431" spans="1:11" ht="15">
+    <row r="431" spans="1:9" ht="15">
       <c r="A431" s="23" t="s">
         <v>1111</v>
       </c>
@@ -19315,17 +16704,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I431" s="31">
-        <v>200</v>
-      </c>
-      <c r="J431" s="31">
-        <v>100</v>
-      </c>
-      <c r="K431" s="10">
+      <c r="I431" s="10">
         <v>430</v>
       </c>
     </row>
-    <row r="432" spans="1:11" ht="15">
+    <row r="432" spans="1:9" ht="15">
       <c r="A432" s="22">
         <v>86</v>
       </c>
@@ -19346,17 +16729,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I432" s="31">
-        <v>180</v>
-      </c>
-      <c r="J432" s="31">
-        <v>100</v>
-      </c>
-      <c r="K432" s="10">
+      <c r="I432" s="10">
         <v>431</v>
       </c>
     </row>
-    <row r="433" spans="1:11" ht="15">
+    <row r="433" spans="1:9" ht="15">
       <c r="A433" s="22">
         <v>82.6</v>
       </c>
@@ -19378,17 +16755,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I433" s="31">
-        <v>150</v>
-      </c>
-      <c r="J433" s="31">
-        <v>100</v>
-      </c>
-      <c r="K433" s="10">
+      <c r="I433" s="10">
         <v>432</v>
       </c>
     </row>
-    <row r="434" spans="1:11" ht="15">
+    <row r="434" spans="1:9" ht="15">
       <c r="A434" s="22">
         <v>615</v>
       </c>
@@ -19410,17 +16781,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I434" s="31">
-        <v>550</v>
-      </c>
-      <c r="J434" s="31">
-        <v>400</v>
-      </c>
-      <c r="K434" s="10">
+      <c r="I434" s="10">
         <v>433</v>
       </c>
     </row>
-    <row r="435" spans="1:11" ht="15">
+    <row r="435" spans="1:9" ht="15">
       <c r="A435" s="22">
         <v>188</v>
       </c>
@@ -19442,17 +16807,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I435" s="31">
-        <v>120</v>
-      </c>
-      <c r="J435" s="31">
-        <v>70</v>
-      </c>
-      <c r="K435" s="10">
+      <c r="I435" s="10">
         <v>434</v>
       </c>
     </row>
-    <row r="436" spans="1:11" ht="15">
+    <row r="436" spans="1:9" ht="15">
       <c r="A436" s="23" t="s">
         <v>1111</v>
       </c>
@@ -19473,17 +16832,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I436" s="31">
-        <v>150</v>
-      </c>
-      <c r="J436" s="31">
-        <v>90</v>
-      </c>
-      <c r="K436" s="10">
+      <c r="I436" s="10">
         <v>435</v>
       </c>
     </row>
-    <row r="437" spans="1:11" ht="15">
+    <row r="437" spans="1:9" ht="15">
       <c r="A437" s="23" t="s">
         <v>1111</v>
       </c>
@@ -19505,17 +16858,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I437" s="31">
-        <v>180</v>
-      </c>
-      <c r="J437" s="31">
-        <v>120</v>
-      </c>
-      <c r="K437" s="10">
+      <c r="I437" s="10">
         <v>436</v>
       </c>
     </row>
-    <row r="438" spans="1:11" ht="15">
+    <row r="438" spans="1:9" ht="15">
       <c r="A438" s="22">
         <v>205</v>
       </c>
@@ -19537,17 +16884,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I438" s="31">
-        <v>250</v>
-      </c>
-      <c r="J438" s="31">
-        <v>120</v>
-      </c>
-      <c r="K438" s="10">
+      <c r="I438" s="10">
         <v>437</v>
       </c>
     </row>
-    <row r="439" spans="1:11" ht="15">
+    <row r="439" spans="1:9" ht="15">
       <c r="A439" s="22">
         <v>190</v>
       </c>
@@ -19569,17 +16910,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I439" s="31">
-        <v>100</v>
-      </c>
-      <c r="J439" s="31">
-        <v>70</v>
-      </c>
-      <c r="K439" s="10">
+      <c r="I439" s="10">
         <v>438</v>
       </c>
     </row>
-    <row r="440" spans="1:11" ht="15">
+    <row r="440" spans="1:9" ht="15">
       <c r="A440">
         <v>245</v>
       </c>
@@ -19601,17 +16936,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I440" s="31">
-        <v>300</v>
-      </c>
-      <c r="J440" s="31">
-        <v>120</v>
-      </c>
-      <c r="K440" s="10">
+      <c r="I440" s="10">
         <v>439</v>
       </c>
     </row>
-    <row r="441" spans="1:11" ht="15">
+    <row r="441" spans="1:9" ht="15">
       <c r="A441" s="22">
         <v>562.29</v>
       </c>
@@ -19633,17 +16962,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I441" s="31">
-        <v>650</v>
-      </c>
-      <c r="J441" s="31">
-        <v>500</v>
-      </c>
-      <c r="K441" s="10">
+      <c r="I441" s="10">
         <v>440</v>
       </c>
     </row>
-    <row r="442" spans="1:11" ht="15">
+    <row r="442" spans="1:9" ht="15">
       <c r="A442" s="22">
         <v>193.8</v>
       </c>
@@ -19665,17 +16988,11 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I442" s="31">
-        <v>230</v>
-      </c>
-      <c r="J442" s="31">
-        <v>150</v>
-      </c>
-      <c r="K442" s="10">
+      <c r="I442" s="10">
         <v>441</v>
       </c>
     </row>
-    <row r="443" spans="1:11" ht="15">
+    <row r="443" spans="1:9" ht="15">
       <c r="A443" s="22" t="s">
         <v>1334</v>
       </c>
@@ -19697,192 +17014,183 @@
         <f t="shared" si="24"/>
         <v>1095</v>
       </c>
-      <c r="I443" s="31">
-        <v>120</v>
-      </c>
-      <c r="J443" s="31">
-        <v>85</v>
-      </c>
-      <c r="K443" s="10">
+      <c r="I443" s="10">
         <v>442</v>
       </c>
-    </row>
-    <row r="444" spans="1:11">
-      <c r="J444" s="31"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:K443" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E2:K365">
+  <autoFilter ref="A1:I443" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E2:I365">
     <sortCondition ref="F1:F365"/>
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="A1:H1 J1:K1">
-    <cfRule type="duplicateValues" dxfId="65" priority="422"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E2:E237">
-    <cfRule type="duplicateValues" dxfId="64" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E348">
-    <cfRule type="duplicateValues" dxfId="63" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E424">
-    <cfRule type="duplicateValues" dxfId="62" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E425:E431 E433:E443 E2:E423">
-    <cfRule type="duplicateValues" dxfId="61" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E432">
-    <cfRule type="duplicateValues" dxfId="59" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E444:E1048576">
-    <cfRule type="duplicateValues" dxfId="58" priority="1498"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="1499"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="1500"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="1498"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="1499"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F308">
-    <cfRule type="duplicateValues" dxfId="55" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F346:F378 F321 F247:F279 F281 F284:F292 F294:F307 F323:F336 F309:F319 F2:F187 F338:F344 F380:F423">
-    <cfRule type="duplicateValues" dxfId="54" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F379">
-    <cfRule type="duplicateValues" dxfId="53" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F425:F443">
-    <cfRule type="duplicateValues" dxfId="52" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F444:F1048576">
-    <cfRule type="duplicateValues" dxfId="50" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F424:G424">
-    <cfRule type="duplicateValues" dxfId="49" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G416 G418 G420:G423">
-    <cfRule type="duplicateValues" dxfId="47" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="duplicateValues" dxfId="46" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="duplicateValues" dxfId="45" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G93">
-    <cfRule type="duplicateValues" dxfId="44" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G126">
-    <cfRule type="duplicateValues" dxfId="43" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G142">
-    <cfRule type="duplicateValues" dxfId="42" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G154">
-    <cfRule type="duplicateValues" dxfId="41" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G155">
-    <cfRule type="duplicateValues" dxfId="40" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G156">
-    <cfRule type="duplicateValues" dxfId="39" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G164">
-    <cfRule type="duplicateValues" dxfId="38" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G284">
-    <cfRule type="duplicateValues" dxfId="37" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G294">
-    <cfRule type="duplicateValues" dxfId="36" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G295">
-    <cfRule type="duplicateValues" dxfId="35" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G296">
-    <cfRule type="duplicateValues" dxfId="34" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G300">
-    <cfRule type="duplicateValues" dxfId="33" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G303:G304 G307:G308">
-    <cfRule type="duplicateValues" dxfId="32" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G305">
-    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G306">
-    <cfRule type="duplicateValues" dxfId="30" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G312">
-    <cfRule type="duplicateValues" dxfId="29" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G313">
-    <cfRule type="duplicateValues" dxfId="28" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G321">
-    <cfRule type="duplicateValues" dxfId="27" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G323">
-    <cfRule type="duplicateValues" dxfId="26" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G338">
-    <cfRule type="duplicateValues" dxfId="25" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G339">
-    <cfRule type="duplicateValues" dxfId="24" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G340">
-    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G341">
-    <cfRule type="duplicateValues" dxfId="22" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G343">
-    <cfRule type="duplicateValues" dxfId="21" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G344">
-    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G346">
-    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G347">
-    <cfRule type="duplicateValues" dxfId="18" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G348">
-    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G349:G350">
-    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G356:G359">
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G363">
-    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G364">
-    <cfRule type="duplicateValues" dxfId="13" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G366:G371">
-    <cfRule type="duplicateValues" dxfId="12" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G417">
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G425:G433 G436:G443">
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G434">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G435">
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:I1">
+    <cfRule type="duplicateValues" dxfId="0" priority="1501"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -21199,25 +18507,33 @@
   <autoFilter ref="C1:F58" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B3 A4:A44 A49:A58">
-    <cfRule type="duplicateValues" dxfId="3" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B6 B8:B9 B11:B12 B14:B15 B17:B18 B20:B21 B23:B24 B26:B27 B29:B30 B32:B33 B35:B36 B38:B39 B41:B42 B44:B45 B47:B48">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207:C243 B1:C1 B622:C1048576 B277:C487">
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="154"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <pixelatorList sheetStid="1"/>
+  <pixelatorList sheetStid="2"/>
+  <pixelatorList sheetStid="3"/>
+</pixelators>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <woProps xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <woSheetsProps>
     <woSheetProps sheetStid="1" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
@@ -21235,16 +18551,8 @@
 </woProps>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <pixelatorList sheetStid="1"/>
-  <pixelatorList sheetStid="2"/>
-  <pixelatorList sheetStid="3"/>
-</pixelators>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
@@ -21253,7 +18561,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>

--- a/模块开发/录入表.xlsx
+++ b/模块开发/录入表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentli/PycharmProjects/PythonProject/2026-4 群控/yolo/整合详情页采集/模块开发/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20EAEF3-08F5-2847-9F26-9DBEB3199658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2B1257-95CC-074E-A3C5-5295BA08DEAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19940" yWindow="1200" windowWidth="29820" windowHeight="25020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3855,9 +3855,6 @@
     <t>3346130010647</t>
   </si>
   <si>
-    <t>Hermes爱马仕大地淡香对装50m*2</t>
-  </si>
-  <si>
     <t>爱马仕大地淡香对装50ml</t>
   </si>
   <si>
@@ -4334,6 +4331,10 @@
   </si>
   <si>
     <t xml:space="preserve">否 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hermes爱马仕大地淡香对装50ml*2</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -4520,13 +4521,6 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="83">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4956,6 +4950,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -4983,13 +4984,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -5006,6 +5000,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5555,7 +5556,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>909</v>
@@ -5564,10 +5565,10 @@
         <v>6</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>1</v>
@@ -5588,11 +5589,11 @@
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="24" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="D2" s="27"/>
       <c r="E2" s="15" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="F2" s="15" t="s">
         <v>15</v>
@@ -5614,7 +5615,7 @@
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D3" s="27"/>
       <c r="E3" s="15" t="s">
@@ -5640,7 +5641,7 @@
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D4" s="28"/>
       <c r="E4" s="15" t="s">
@@ -5666,7 +5667,7 @@
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="15" t="s">
@@ -5692,7 +5693,7 @@
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D6" s="27"/>
       <c r="E6" s="15" t="s">
@@ -5718,7 +5719,7 @@
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="15" t="s">
@@ -5744,7 +5745,7 @@
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D8" s="27"/>
       <c r="E8" s="15" t="s">
@@ -5770,7 +5771,7 @@
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="15" t="s">
@@ -5796,7 +5797,7 @@
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D10" s="28"/>
       <c r="E10" s="15" t="s">
@@ -5822,7 +5823,7 @@
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D11" s="27"/>
       <c r="E11" s="15" t="s">
@@ -5848,7 +5849,7 @@
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="15" t="s">
@@ -5874,7 +5875,7 @@
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="15" t="s">
@@ -5900,7 +5901,7 @@
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="15" t="s">
@@ -5926,7 +5927,7 @@
       </c>
       <c r="B15" s="23"/>
       <c r="C15" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>924</v>
@@ -5951,7 +5952,7 @@
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="15" t="s">
@@ -5977,7 +5978,7 @@
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="15" t="s">
@@ -6003,7 +6004,7 @@
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="15" t="s">
@@ -6029,11 +6030,11 @@
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="15" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="F19" s="15" t="s">
         <v>93</v>
@@ -6055,7 +6056,7 @@
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="15" t="s">
@@ -6081,7 +6082,7 @@
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D21" s="20"/>
       <c r="E21" s="15" t="s">
@@ -6107,7 +6108,7 @@
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D22" s="20"/>
       <c r="E22" s="15" t="s">
@@ -6133,7 +6134,7 @@
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="15" t="s">
@@ -6159,7 +6160,7 @@
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="15" t="s">
@@ -6185,7 +6186,7 @@
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D25" s="28"/>
       <c r="E25" s="15" t="s">
@@ -6211,7 +6212,7 @@
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D26" s="20"/>
       <c r="E26" s="15" t="s">
@@ -6237,7 +6238,7 @@
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D27" s="20"/>
       <c r="E27" s="15" t="s">
@@ -6263,7 +6264,7 @@
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D28" s="28"/>
       <c r="E28" s="15" t="s">
@@ -6289,11 +6290,11 @@
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D29" s="20"/>
       <c r="E29" s="15" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="F29" s="15" t="s">
         <v>933</v>
@@ -6315,11 +6316,11 @@
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D30" s="20"/>
       <c r="E30" s="15" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F30" s="15" t="s">
         <v>933</v>
@@ -6341,7 +6342,7 @@
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D31" s="27"/>
       <c r="E31" s="15" t="s">
@@ -6351,7 +6352,7 @@
         <v>130</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="2"/>
@@ -6367,7 +6368,7 @@
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="15" t="s">
@@ -6393,11 +6394,11 @@
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D33" s="20"/>
       <c r="E33" s="15" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F33" s="15" t="s">
         <v>149</v>
@@ -6419,7 +6420,7 @@
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D34" s="20"/>
       <c r="E34" s="15" t="s">
@@ -6445,7 +6446,7 @@
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D35" s="20"/>
       <c r="E35" s="15" t="s">
@@ -6455,7 +6456,7 @@
         <v>151</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="2"/>
@@ -6471,7 +6472,7 @@
       </c>
       <c r="B36" s="20"/>
       <c r="C36" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D36" s="20"/>
       <c r="E36" s="15" t="s">
@@ -6481,7 +6482,7 @@
         <v>939</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="2"/>
@@ -6497,7 +6498,7 @@
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D37" s="20"/>
       <c r="E37" s="15" t="s">
@@ -6523,7 +6524,7 @@
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="15" t="s">
@@ -6549,7 +6550,7 @@
       </c>
       <c r="B39" s="22"/>
       <c r="C39" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D39" s="28"/>
       <c r="E39" s="15" t="s">
@@ -6575,14 +6576,14 @@
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="15" t="s">
         <v>942</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="G40" s="15" t="s">
         <v>160</v>
@@ -6601,7 +6602,7 @@
       </c>
       <c r="B41" s="23"/>
       <c r="C41" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>161</v>
@@ -6626,17 +6627,17 @@
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D42" s="27"/>
       <c r="E42" s="15" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="F42" s="15" t="s">
         <v>943</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" si="2"/>
@@ -6652,17 +6653,17 @@
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="15" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="F43" s="15" t="s">
         <v>943</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" si="2"/>
@@ -6678,7 +6679,7 @@
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D44" s="20"/>
       <c r="E44" s="15" t="s">
@@ -6704,7 +6705,7 @@
       </c>
       <c r="B45" s="22"/>
       <c r="C45" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D45" s="28"/>
       <c r="E45" s="15" t="s">
@@ -6730,7 +6731,7 @@
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D46" s="27"/>
       <c r="E46" s="15" t="s">
@@ -6756,7 +6757,7 @@
       </c>
       <c r="B47" s="22"/>
       <c r="C47" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D47" s="28"/>
       <c r="E47" s="15" t="s">
@@ -6782,7 +6783,7 @@
       </c>
       <c r="B48" s="22"/>
       <c r="C48" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D48" s="28"/>
       <c r="E48" s="15" t="s">
@@ -6807,7 +6808,7 @@
         <v>278</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="15" t="s">
@@ -6833,7 +6834,7 @@
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D50" s="20"/>
       <c r="E50" s="15" t="s">
@@ -6859,14 +6860,14 @@
       </c>
       <c r="B51" s="22"/>
       <c r="C51" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D51" s="28"/>
       <c r="E51" s="15" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="G51" s="15" t="s">
         <v>176</v>
@@ -6883,17 +6884,17 @@
       <c r="A52" s="26"/>
       <c r="B52" s="22"/>
       <c r="C52" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D52" s="26"/>
       <c r="E52" s="15" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="F52" s="15" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G52" s="15" t="s">
         <v>1348</v>
-      </c>
-      <c r="G52" s="15" t="s">
-        <v>1349</v>
       </c>
       <c r="H52" s="4">
         <f t="shared" ref="H52:H53" si="3">D52+1095</f>
@@ -6909,7 +6910,7 @@
       </c>
       <c r="B53" s="22"/>
       <c r="C53" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D53" s="28"/>
       <c r="E53" s="15" t="s">
@@ -6935,7 +6936,7 @@
       </c>
       <c r="B54" s="22"/>
       <c r="C54" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D54" s="28"/>
       <c r="E54" s="15" t="s">
@@ -6945,7 +6946,7 @@
         <v>949</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H54" s="4">
         <f>D54+1095</f>
@@ -6961,7 +6962,7 @@
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D55" s="27"/>
       <c r="E55" s="15" t="s">
@@ -6987,7 +6988,7 @@
       </c>
       <c r="B56" s="20"/>
       <c r="C56" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D56" s="27"/>
       <c r="E56" s="15" t="s">
@@ -7013,14 +7014,14 @@
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D57" s="27"/>
       <c r="E57" s="15" t="s">
         <v>951</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="G57" s="15" t="s">
         <v>200</v>
@@ -7039,7 +7040,7 @@
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D58" s="20"/>
       <c r="E58" s="15" t="s">
@@ -7065,7 +7066,7 @@
       </c>
       <c r="B59" s="20"/>
       <c r="C59" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D59" s="27"/>
       <c r="E59" s="15" t="s">
@@ -7091,7 +7092,7 @@
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D60" s="20"/>
       <c r="E60" s="15" t="s">
@@ -7117,7 +7118,7 @@
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D61" s="27"/>
       <c r="E61" s="15" t="s">
@@ -7143,7 +7144,7 @@
       </c>
       <c r="B62" s="22"/>
       <c r="C62" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D62" s="28"/>
       <c r="E62" s="15" t="s">
@@ -7169,7 +7170,7 @@
       </c>
       <c r="B63" s="22"/>
       <c r="C63" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D63" s="28"/>
       <c r="E63" s="15" t="s">
@@ -7195,7 +7196,7 @@
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D64" s="20"/>
       <c r="E64" s="15" t="s">
@@ -7221,7 +7222,7 @@
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D65" s="20"/>
       <c r="E65" s="15" t="s">
@@ -7247,7 +7248,7 @@
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D66" s="27"/>
       <c r="E66" s="15" t="s">
@@ -7273,7 +7274,7 @@
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D67" s="27"/>
       <c r="E67" s="15" t="s">
@@ -7299,7 +7300,7 @@
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D68" s="27"/>
       <c r="E68" s="15" t="s">
@@ -7325,7 +7326,7 @@
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D69" s="27"/>
       <c r="E69" s="15" t="s">
@@ -7351,17 +7352,17 @@
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D70" s="27"/>
       <c r="E70" s="15" t="s">
         <v>959</v>
       </c>
       <c r="F70" s="15" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G70" s="15" t="s">
         <v>1361</v>
-      </c>
-      <c r="G70" s="15" t="s">
-        <v>1362</v>
       </c>
       <c r="H70" s="4">
         <f t="shared" si="4"/>
@@ -7377,7 +7378,7 @@
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D71" s="27"/>
       <c r="E71" s="15" t="s">
@@ -7403,7 +7404,7 @@
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D72" s="20"/>
       <c r="E72" s="15" t="s">
@@ -7429,7 +7430,7 @@
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D73" s="20"/>
       <c r="E73" s="15" t="s">
@@ -7455,7 +7456,7 @@
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="15" t="s">
@@ -7481,7 +7482,7 @@
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="15" t="s">
@@ -7507,7 +7508,7 @@
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D76" s="20"/>
       <c r="E76" s="15" t="s">
@@ -7533,7 +7534,7 @@
       </c>
       <c r="B77" s="20"/>
       <c r="C77" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="15" t="s">
@@ -7559,7 +7560,7 @@
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="15" t="s">
@@ -7585,14 +7586,14 @@
       </c>
       <c r="B79" s="20"/>
       <c r="C79" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="15" t="s">
         <v>968</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="G79" s="15" t="s">
         <v>264</v>
@@ -7611,7 +7612,7 @@
       </c>
       <c r="B80" s="20"/>
       <c r="C80" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="15" t="s">
@@ -7637,7 +7638,7 @@
       </c>
       <c r="B81" s="20"/>
       <c r="C81" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="15" t="s">
@@ -7663,7 +7664,7 @@
       </c>
       <c r="B82" s="20"/>
       <c r="C82" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D82" s="20"/>
       <c r="E82" s="15" t="s">
@@ -7689,7 +7690,7 @@
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="15" t="s">
@@ -7715,7 +7716,7 @@
       </c>
       <c r="B84" s="20"/>
       <c r="C84" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="15" t="s">
@@ -7741,7 +7742,7 @@
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D85" s="27"/>
       <c r="E85" s="15" t="s">
@@ -7767,7 +7768,7 @@
       </c>
       <c r="B86" s="20"/>
       <c r="C86" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D86" s="20"/>
       <c r="E86" s="15" t="s">
@@ -7793,7 +7794,7 @@
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D87" s="27"/>
       <c r="E87" s="15" t="s">
@@ -7819,7 +7820,7 @@
       </c>
       <c r="B88" s="20"/>
       <c r="C88" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D88" s="27"/>
       <c r="E88" s="15" t="s">
@@ -7845,7 +7846,7 @@
       </c>
       <c r="B89" s="20"/>
       <c r="C89" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D89" s="27"/>
       <c r="E89" s="15" t="s">
@@ -7871,7 +7872,7 @@
       </c>
       <c r="B90" s="22"/>
       <c r="C90" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D90" s="28"/>
       <c r="E90" s="15" t="s">
@@ -7897,7 +7898,7 @@
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D91" s="27"/>
       <c r="E91" s="15" t="s">
@@ -7923,7 +7924,7 @@
       </c>
       <c r="B92" s="20"/>
       <c r="C92" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D92" s="27"/>
       <c r="E92" s="15" t="s">
@@ -7949,7 +7950,7 @@
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D93" s="27"/>
       <c r="E93" s="15" t="s">
@@ -7959,7 +7960,7 @@
         <v>314</v>
       </c>
       <c r="G93" s="15" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H93" s="4">
         <f>D93+1095</f>
@@ -7975,7 +7976,7 @@
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D94" s="27"/>
       <c r="E94" s="15" t="s">
@@ -8001,7 +8002,7 @@
       </c>
       <c r="B95" s="20"/>
       <c r="C95" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D95" s="20"/>
       <c r="E95" s="15" t="s">
@@ -8027,7 +8028,7 @@
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D96" s="27"/>
       <c r="E96" s="15" t="s">
@@ -8053,14 +8054,14 @@
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="15" t="s">
         <v>319</v>
       </c>
       <c r="F97" s="15" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="G97" s="15" t="s">
         <v>320</v>
@@ -8079,7 +8080,7 @@
       </c>
       <c r="B98" s="20"/>
       <c r="C98" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="15" t="s">
@@ -8105,7 +8106,7 @@
       </c>
       <c r="B99" s="20"/>
       <c r="C99" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D99" s="20"/>
       <c r="E99" s="15" t="s">
@@ -8131,7 +8132,7 @@
       </c>
       <c r="B100" s="20"/>
       <c r="C100" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D100" s="27"/>
       <c r="E100" s="15" t="s">
@@ -8157,7 +8158,7 @@
       </c>
       <c r="B101" s="20"/>
       <c r="C101" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D101" s="27"/>
       <c r="E101" s="15" t="s">
@@ -8183,7 +8184,7 @@
       </c>
       <c r="B102" s="20"/>
       <c r="C102" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D102" s="27"/>
       <c r="E102" s="15" t="s">
@@ -8209,7 +8210,7 @@
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D103" s="27"/>
       <c r="E103" s="15" t="s">
@@ -8235,7 +8236,7 @@
       </c>
       <c r="B104" s="20"/>
       <c r="C104" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D104" s="27"/>
       <c r="E104" s="15" t="s">
@@ -8261,7 +8262,7 @@
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D105" s="27"/>
       <c r="E105" s="15" t="s">
@@ -8287,7 +8288,7 @@
       </c>
       <c r="B106" s="20"/>
       <c r="C106" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D106" s="27"/>
       <c r="E106" s="15" t="s">
@@ -8313,7 +8314,7 @@
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D107" s="27"/>
       <c r="E107" s="15" t="s">
@@ -8339,7 +8340,7 @@
       </c>
       <c r="B108" s="23"/>
       <c r="C108" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E108" s="15" t="s">
         <v>344</v>
@@ -8364,7 +8365,7 @@
       </c>
       <c r="B109" s="20"/>
       <c r="C109" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D109" s="20"/>
       <c r="E109" s="15" t="s">
@@ -8390,7 +8391,7 @@
       </c>
       <c r="B110" s="22"/>
       <c r="C110" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D110" s="27"/>
       <c r="E110" s="15" t="s">
@@ -8416,7 +8417,7 @@
       </c>
       <c r="B111" s="20"/>
       <c r="C111" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D111" s="27"/>
       <c r="E111" s="15" t="s">
@@ -8442,7 +8443,7 @@
       </c>
       <c r="B112" s="20"/>
       <c r="C112" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D112" s="27"/>
       <c r="E112" s="15" t="s">
@@ -8468,7 +8469,7 @@
       </c>
       <c r="B113" s="20"/>
       <c r="C113" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D113" s="27"/>
       <c r="E113" s="15" t="s">
@@ -8478,7 +8479,7 @@
         <v>363</v>
       </c>
       <c r="G113" s="15" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H113" s="4">
         <f t="shared" si="6"/>
@@ -8494,7 +8495,7 @@
       </c>
       <c r="B114" s="20"/>
       <c r="C114" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D114" s="20"/>
       <c r="E114" s="15" t="s">
@@ -8520,7 +8521,7 @@
       </c>
       <c r="B115" s="20"/>
       <c r="C115" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D115" s="27"/>
       <c r="E115" s="15" t="s">
@@ -8546,7 +8547,7 @@
       </c>
       <c r="B116" s="20"/>
       <c r="C116" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D116" s="27"/>
       <c r="E116" s="15" t="s">
@@ -8572,7 +8573,7 @@
       </c>
       <c r="B117" s="20"/>
       <c r="C117" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D117" s="27"/>
       <c r="E117" s="15" t="s">
@@ -8598,7 +8599,7 @@
       </c>
       <c r="B118" s="20"/>
       <c r="C118" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D118" s="27"/>
       <c r="E118" s="15" t="s">
@@ -8624,17 +8625,17 @@
       </c>
       <c r="B119" s="20"/>
       <c r="C119" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D119" s="27"/>
       <c r="E119" s="15" t="s">
         <v>989</v>
       </c>
       <c r="F119" s="15" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G119" s="15" t="s">
         <v>1367</v>
-      </c>
-      <c r="G119" s="15" t="s">
-        <v>1368</v>
       </c>
       <c r="H119" s="4">
         <f t="shared" si="6"/>
@@ -8650,7 +8651,7 @@
       </c>
       <c r="B120" s="20"/>
       <c r="C120" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="15" t="s">
@@ -8676,14 +8677,14 @@
       </c>
       <c r="B121" s="20"/>
       <c r="C121" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="15" t="s">
         <v>381</v>
       </c>
       <c r="F121" s="15" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="G121" s="15" t="s">
         <v>382</v>
@@ -8702,7 +8703,7 @@
       </c>
       <c r="B122" s="20"/>
       <c r="C122" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D122" s="20"/>
       <c r="E122" s="15" t="s">
@@ -8728,7 +8729,7 @@
       </c>
       <c r="B123" s="23"/>
       <c r="C123" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D123" s="27"/>
       <c r="E123" s="15" t="s">
@@ -8754,7 +8755,7 @@
       </c>
       <c r="B124" s="22"/>
       <c r="C124" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="15" t="s">
@@ -8780,7 +8781,7 @@
       </c>
       <c r="B125" s="20"/>
       <c r="C125" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="15" t="s">
@@ -8806,17 +8807,17 @@
       </c>
       <c r="B126" s="20"/>
       <c r="C126" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="15" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="F126" s="15" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G126" s="15" t="s">
         <v>1370</v>
-      </c>
-      <c r="G126" s="15" t="s">
-        <v>1371</v>
       </c>
       <c r="H126" s="4">
         <f t="shared" si="6"/>
@@ -8832,7 +8833,7 @@
       </c>
       <c r="B127" s="20"/>
       <c r="C127" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D127" s="27"/>
       <c r="E127" s="15" t="s">
@@ -8858,14 +8859,14 @@
       </c>
       <c r="B128" s="20"/>
       <c r="C128" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D128" s="27"/>
       <c r="E128" s="15" t="s">
         <v>991</v>
       </c>
       <c r="F128" s="15" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="G128" s="15" t="s">
         <v>415</v>
@@ -8884,7 +8885,7 @@
       </c>
       <c r="B129" s="20"/>
       <c r="C129" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D129" s="27"/>
       <c r="E129" s="15" t="s">
@@ -8910,7 +8911,7 @@
       </c>
       <c r="B130" s="20"/>
       <c r="C130" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D130" s="27"/>
       <c r="E130" s="15" t="s">
@@ -8936,7 +8937,7 @@
       </c>
       <c r="B131" s="20"/>
       <c r="C131" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D131" s="27"/>
       <c r="E131" s="15" t="s">
@@ -8962,7 +8963,7 @@
       </c>
       <c r="B132" s="20"/>
       <c r="C132" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D132" s="27"/>
       <c r="E132" s="15" t="s">
@@ -8988,7 +8989,7 @@
       </c>
       <c r="B133" s="20"/>
       <c r="C133" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D133" s="27"/>
       <c r="E133" s="15" t="s">
@@ -9014,7 +9015,7 @@
       </c>
       <c r="B134" s="20"/>
       <c r="C134" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D134" s="20"/>
       <c r="E134" s="15" t="s">
@@ -9040,7 +9041,7 @@
       </c>
       <c r="B135" s="20"/>
       <c r="C135" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D135" s="20"/>
       <c r="E135" s="15" t="s">
@@ -9066,7 +9067,7 @@
       </c>
       <c r="B136" s="20"/>
       <c r="C136" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D136" s="20"/>
       <c r="E136" s="15" t="s">
@@ -9092,7 +9093,7 @@
       </c>
       <c r="B137" s="20"/>
       <c r="C137" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D137" s="27"/>
       <c r="E137" s="15" t="s">
@@ -9118,7 +9119,7 @@
       </c>
       <c r="B138" s="20"/>
       <c r="C138" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D138" s="27"/>
       <c r="E138" s="15" t="s">
@@ -9144,7 +9145,7 @@
       </c>
       <c r="B139" s="22"/>
       <c r="C139" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D139" s="27"/>
       <c r="E139" s="15" t="s">
@@ -9170,7 +9171,7 @@
       </c>
       <c r="B140" s="20"/>
       <c r="C140" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D140" s="27"/>
       <c r="E140" s="15" t="s">
@@ -9196,7 +9197,7 @@
       </c>
       <c r="B141" s="20"/>
       <c r="C141" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D141" s="27"/>
       <c r="E141" s="15" t="s">
@@ -9222,7 +9223,7 @@
       </c>
       <c r="B142" s="20"/>
       <c r="C142" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D142" s="27"/>
       <c r="E142" s="15" t="s">
@@ -9248,7 +9249,7 @@
       </c>
       <c r="B143" s="20"/>
       <c r="C143" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D143" s="27"/>
       <c r="E143" s="15" t="s">
@@ -9274,7 +9275,7 @@
       </c>
       <c r="B144" s="20"/>
       <c r="C144" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D144" s="20"/>
       <c r="E144" s="15" t="s">
@@ -9300,7 +9301,7 @@
       </c>
       <c r="B145" s="23"/>
       <c r="C145" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E145" s="15" t="s">
         <v>1000</v>
@@ -9325,7 +9326,7 @@
       </c>
       <c r="B146" s="23"/>
       <c r="C146" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D146" s="28"/>
       <c r="E146" s="15" t="s">
@@ -9335,7 +9336,7 @@
         <v>466</v>
       </c>
       <c r="G146" s="15" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H146" s="4">
         <f>D146+1895</f>
@@ -9351,7 +9352,7 @@
       </c>
       <c r="B147" s="23"/>
       <c r="C147" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D147" s="14"/>
       <c r="E147" s="15" t="s">
@@ -9377,7 +9378,7 @@
       </c>
       <c r="B148" s="23"/>
       <c r="C148" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E148" s="15" t="s">
         <v>470</v>
@@ -9402,7 +9403,7 @@
       </c>
       <c r="B149" s="23"/>
       <c r="C149" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D149" s="14"/>
       <c r="E149" s="15" t="s">
@@ -9428,7 +9429,7 @@
       </c>
       <c r="B150" s="23"/>
       <c r="C150" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D150" s="14"/>
       <c r="E150" s="15" t="s">
@@ -9454,7 +9455,7 @@
       </c>
       <c r="B151" s="23"/>
       <c r="C151" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E151" s="15" t="s">
         <v>478</v>
@@ -9479,7 +9480,7 @@
       </c>
       <c r="B152" s="23"/>
       <c r="C152" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D152" s="14"/>
       <c r="E152" s="15" t="s">
@@ -9505,7 +9506,7 @@
       </c>
       <c r="B153" s="23"/>
       <c r="C153" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D153" s="14"/>
       <c r="E153" s="15" t="s">
@@ -9515,7 +9516,7 @@
         <v>484</v>
       </c>
       <c r="G153" s="15" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H153" s="4">
         <f t="shared" si="8"/>
@@ -9531,7 +9532,7 @@
       </c>
       <c r="B154" s="23"/>
       <c r="C154" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D154" s="22"/>
       <c r="E154" s="15" t="s">
@@ -9557,7 +9558,7 @@
       </c>
       <c r="B155" s="23"/>
       <c r="C155" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D155" s="14"/>
       <c r="E155" s="15" t="s">
@@ -9567,7 +9568,7 @@
         <v>487</v>
       </c>
       <c r="G155" s="15" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H155" s="4">
         <f t="shared" si="9"/>
@@ -9583,7 +9584,7 @@
       </c>
       <c r="B156" s="20"/>
       <c r="C156" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D156" s="27"/>
       <c r="E156" s="15" t="s">
@@ -9609,7 +9610,7 @@
       </c>
       <c r="B157" s="20"/>
       <c r="C157" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D157" s="27"/>
       <c r="E157" s="15" t="s">
@@ -9635,7 +9636,7 @@
       </c>
       <c r="B158" s="22"/>
       <c r="C158" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D158" s="27"/>
       <c r="E158" s="15" t="s">
@@ -9661,7 +9662,7 @@
       </c>
       <c r="B159" s="20"/>
       <c r="C159" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D159" s="20"/>
       <c r="E159" s="15" t="s">
@@ -9687,7 +9688,7 @@
       </c>
       <c r="B160" s="20"/>
       <c r="C160" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D160" s="27"/>
       <c r="E160" s="15" t="s">
@@ -9713,7 +9714,7 @@
       </c>
       <c r="B161" s="20"/>
       <c r="C161" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D161" s="20"/>
       <c r="E161" s="15" t="s">
@@ -9739,7 +9740,7 @@
       </c>
       <c r="B162" s="20"/>
       <c r="C162" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D162" s="27"/>
       <c r="E162" s="15" t="s">
@@ -9765,7 +9766,7 @@
       </c>
       <c r="B163" s="20"/>
       <c r="C163" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D163" s="27"/>
       <c r="E163" s="15" t="s">
@@ -9791,7 +9792,7 @@
       </c>
       <c r="B164" s="20"/>
       <c r="C164" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D164" s="20"/>
       <c r="E164" s="15" t="s">
@@ -9817,7 +9818,7 @@
       </c>
       <c r="B165" s="20"/>
       <c r="C165" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D165" s="27"/>
       <c r="E165" s="15" t="s">
@@ -9843,7 +9844,7 @@
       </c>
       <c r="B166" s="22"/>
       <c r="C166" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D166" s="27"/>
       <c r="E166" s="15" t="s">
@@ -9869,7 +9870,7 @@
       </c>
       <c r="B167" s="20"/>
       <c r="C167" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D167" s="20"/>
       <c r="E167" s="15" t="s">
@@ -9879,7 +9880,7 @@
         <v>518</v>
       </c>
       <c r="G167" s="15" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H167" s="4">
         <f t="shared" si="9"/>
@@ -9895,14 +9896,14 @@
       </c>
       <c r="B168" s="20"/>
       <c r="C168" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D168" s="27"/>
       <c r="E168" s="15" t="s">
         <v>1007</v>
       </c>
       <c r="F168" s="15" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="G168" s="15" t="s">
         <v>521</v>
@@ -9921,7 +9922,7 @@
       </c>
       <c r="B169" s="20"/>
       <c r="C169" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D169" s="27"/>
       <c r="E169" s="15" t="s">
@@ -9947,7 +9948,7 @@
       </c>
       <c r="B170" s="20"/>
       <c r="C170" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D170" s="27"/>
       <c r="E170" s="15" t="s">
@@ -9973,7 +9974,7 @@
       </c>
       <c r="B171" s="20"/>
       <c r="C171" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D171" s="27"/>
       <c r="E171" s="15" t="s">
@@ -9999,17 +10000,17 @@
       </c>
       <c r="B172" s="20"/>
       <c r="C172" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D172" s="27"/>
       <c r="E172" s="15" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="F172" s="15" t="s">
         <v>534</v>
       </c>
       <c r="G172" s="15" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H172" s="4">
         <f>D172+1095</f>
@@ -10025,7 +10026,7 @@
       </c>
       <c r="B173" s="20"/>
       <c r="C173" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D173" s="20"/>
       <c r="E173" s="15" t="s">
@@ -10051,7 +10052,7 @@
       </c>
       <c r="B174" s="22"/>
       <c r="C174" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D174" s="28"/>
       <c r="E174" s="15" t="s">
@@ -10077,7 +10078,7 @@
       </c>
       <c r="B175" s="20"/>
       <c r="C175" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D175" s="27"/>
       <c r="E175" s="15" t="s">
@@ -10103,7 +10104,7 @@
       </c>
       <c r="B176" s="22"/>
       <c r="C176" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D176" s="28"/>
       <c r="E176" s="15" t="s">
@@ -10129,7 +10130,7 @@
       </c>
       <c r="B177" s="22"/>
       <c r="C177" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D177" s="28"/>
       <c r="E177" s="15" t="s">
@@ -10155,7 +10156,7 @@
       </c>
       <c r="B178" s="20"/>
       <c r="C178" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D178" s="20"/>
       <c r="E178" s="15" t="s">
@@ -10181,7 +10182,7 @@
       </c>
       <c r="B179" s="22"/>
       <c r="C179" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D179" s="28"/>
       <c r="E179" s="15" t="s">
@@ -10207,7 +10208,7 @@
       </c>
       <c r="B180" s="23"/>
       <c r="C180" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E180" s="15" t="s">
         <v>1011</v>
@@ -10232,7 +10233,7 @@
       </c>
       <c r="B181" s="20"/>
       <c r="C181" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D181" s="27"/>
       <c r="E181" s="15" t="s">
@@ -10258,7 +10259,7 @@
       </c>
       <c r="B182" s="20"/>
       <c r="C182" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D182" s="20"/>
       <c r="E182" s="15" t="s">
@@ -10284,7 +10285,7 @@
       </c>
       <c r="B183" s="20"/>
       <c r="C183" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D183" s="27"/>
       <c r="E183" s="15" t="s">
@@ -10310,7 +10311,7 @@
       </c>
       <c r="B184" s="23"/>
       <c r="C184" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D184" s="28"/>
       <c r="E184" s="15" t="s">
@@ -10336,7 +10337,7 @@
       </c>
       <c r="B185" s="20"/>
       <c r="C185" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D185" s="27"/>
       <c r="E185" s="15" t="s">
@@ -10362,7 +10363,7 @@
       </c>
       <c r="B186" s="20"/>
       <c r="C186" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D186" s="27"/>
       <c r="E186" s="15" t="s">
@@ -10388,7 +10389,7 @@
       </c>
       <c r="B187" s="20"/>
       <c r="C187" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D187" s="27"/>
       <c r="E187" s="15" t="s">
@@ -10398,7 +10399,7 @@
         <v>606</v>
       </c>
       <c r="G187" s="17" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H187" s="4">
         <f>D187+1095</f>
@@ -10414,7 +10415,7 @@
       </c>
       <c r="B188" s="20"/>
       <c r="C188" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D188" s="27"/>
       <c r="E188" s="15" t="s">
@@ -10440,7 +10441,7 @@
       </c>
       <c r="B189" s="22"/>
       <c r="C189" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D189" s="28"/>
       <c r="E189" s="15" t="s">
@@ -10466,7 +10467,7 @@
       </c>
       <c r="B190" s="22"/>
       <c r="C190" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D190" s="28"/>
       <c r="E190" s="15" t="s">
@@ -10476,7 +10477,7 @@
         <v>631</v>
       </c>
       <c r="G190" s="15" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H190" s="4">
         <f>D190+1095</f>
@@ -10492,7 +10493,7 @@
       </c>
       <c r="B191" s="21"/>
       <c r="C191" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D191" s="28"/>
       <c r="E191" s="15" t="s">
@@ -10518,7 +10519,7 @@
       </c>
       <c r="B192" s="20"/>
       <c r="C192" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D192" s="20"/>
       <c r="E192" s="15" t="s">
@@ -10544,7 +10545,7 @@
       </c>
       <c r="B193" s="22"/>
       <c r="C193" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D193" s="28"/>
       <c r="E193" s="15" t="s">
@@ -10570,7 +10571,7 @@
       </c>
       <c r="B194" s="20"/>
       <c r="C194" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D194" s="27"/>
       <c r="E194" s="15" t="s">
@@ -10596,7 +10597,7 @@
       </c>
       <c r="B195" s="20"/>
       <c r="C195" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D195" s="20"/>
       <c r="E195" s="15" t="s">
@@ -10622,7 +10623,7 @@
       </c>
       <c r="B196" s="20"/>
       <c r="C196" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D196" s="27"/>
       <c r="E196" s="15" t="s">
@@ -10648,7 +10649,7 @@
       </c>
       <c r="B197" s="20"/>
       <c r="C197" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D197" s="20"/>
       <c r="E197" s="15" t="s">
@@ -10674,7 +10675,7 @@
       </c>
       <c r="B198" s="22"/>
       <c r="C198" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D198" s="28"/>
       <c r="E198" s="15" t="s">
@@ -10684,7 +10685,7 @@
         <v>654</v>
       </c>
       <c r="G198" s="15" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H198" s="4">
         <f t="shared" ref="H198:H216" si="12">D198+1095</f>
@@ -10700,7 +10701,7 @@
       </c>
       <c r="B199" s="22"/>
       <c r="C199" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D199" s="28"/>
       <c r="E199" s="15" t="s">
@@ -10726,7 +10727,7 @@
       </c>
       <c r="B200" s="20"/>
       <c r="C200" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D200" s="27"/>
       <c r="E200" s="15" t="s">
@@ -10752,7 +10753,7 @@
       </c>
       <c r="B201" s="20"/>
       <c r="C201" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D201" s="27"/>
       <c r="E201" s="15" t="s">
@@ -10778,7 +10779,7 @@
       </c>
       <c r="B202" s="20"/>
       <c r="C202" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D202" s="27"/>
       <c r="E202" s="15" t="s">
@@ -10804,7 +10805,7 @@
       </c>
       <c r="B203" s="20"/>
       <c r="C203" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D203" s="27"/>
       <c r="E203" s="15" t="s">
@@ -10830,7 +10831,7 @@
       </c>
       <c r="B204" s="20"/>
       <c r="C204" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D204" s="27"/>
       <c r="E204" s="15" t="s">
@@ -10856,7 +10857,7 @@
       </c>
       <c r="B205" s="20"/>
       <c r="C205" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D205" s="27"/>
       <c r="E205" s="15" t="s">
@@ -10882,7 +10883,7 @@
       </c>
       <c r="B206" s="20"/>
       <c r="C206" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D206" s="27"/>
       <c r="E206" s="15" t="s">
@@ -10908,7 +10909,7 @@
       </c>
       <c r="B207" s="20"/>
       <c r="C207" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D207" s="20"/>
       <c r="E207" s="15" t="s">
@@ -10934,7 +10935,7 @@
       </c>
       <c r="B208" s="20"/>
       <c r="C208" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D208" s="27"/>
       <c r="E208" s="15" t="s">
@@ -10960,7 +10961,7 @@
       </c>
       <c r="B209" s="20"/>
       <c r="C209" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D209" s="20"/>
       <c r="E209" s="15" t="s">
@@ -10986,7 +10987,7 @@
       </c>
       <c r="B210" s="20"/>
       <c r="C210" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D210" s="27"/>
       <c r="E210" s="15" t="s">
@@ -11012,7 +11013,7 @@
       </c>
       <c r="B211" s="20"/>
       <c r="C211" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D211" s="27"/>
       <c r="E211" s="15" t="s">
@@ -11038,7 +11039,7 @@
       </c>
       <c r="B212" s="20"/>
       <c r="C212" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D212" s="20"/>
       <c r="E212" s="15" t="s">
@@ -11064,7 +11065,7 @@
       </c>
       <c r="B213" s="20"/>
       <c r="C213" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D213" s="27"/>
       <c r="E213" s="15" t="s">
@@ -11090,7 +11091,7 @@
       </c>
       <c r="B214" s="21"/>
       <c r="C214" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D214" s="22"/>
       <c r="E214" s="15" t="s">
@@ -11116,7 +11117,7 @@
       </c>
       <c r="B215" s="21"/>
       <c r="C215" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D215" s="22"/>
       <c r="E215" s="15" t="s">
@@ -11142,7 +11143,7 @@
       </c>
       <c r="B216" s="20"/>
       <c r="C216" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D216" s="27"/>
       <c r="E216" s="15" t="s">
@@ -11168,7 +11169,7 @@
       </c>
       <c r="B217" s="20"/>
       <c r="C217" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D217" s="27"/>
       <c r="E217" s="15" t="s">
@@ -11194,7 +11195,7 @@
       </c>
       <c r="B218" s="20"/>
       <c r="C218" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D218" s="27"/>
       <c r="E218" s="15" t="s">
@@ -11220,7 +11221,7 @@
       </c>
       <c r="B219" s="20"/>
       <c r="C219" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D219" s="27"/>
       <c r="E219" s="15" t="s">
@@ -11246,7 +11247,7 @@
       </c>
       <c r="B220" s="20"/>
       <c r="C220" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D220" s="27"/>
       <c r="E220" s="15" t="s">
@@ -11272,7 +11273,7 @@
       </c>
       <c r="B221" s="20"/>
       <c r="C221" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D221" s="27"/>
       <c r="E221" s="15" t="s">
@@ -11298,14 +11299,14 @@
       </c>
       <c r="B222" s="20"/>
       <c r="C222" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D222" s="27"/>
       <c r="E222" s="15" t="s">
         <v>1030</v>
       </c>
       <c r="F222" s="15" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="G222" s="15" t="s">
         <v>218</v>
@@ -11323,14 +11324,14 @@
         <v>298</v>
       </c>
       <c r="C223" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D223" s="14"/>
       <c r="E223" s="15" t="s">
         <v>216</v>
       </c>
       <c r="F223" s="15" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="G223" s="15" t="s">
         <v>217</v>
@@ -11349,7 +11350,7 @@
       </c>
       <c r="B224" s="20"/>
       <c r="C224" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D224" s="27"/>
       <c r="E224" s="15" t="s">
@@ -11375,7 +11376,7 @@
       </c>
       <c r="B225" s="20"/>
       <c r="C225" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D225" s="27"/>
       <c r="E225" s="15" t="s">
@@ -11401,7 +11402,7 @@
       </c>
       <c r="B226" s="20"/>
       <c r="C226" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D226" s="27"/>
       <c r="E226" s="15" t="s">
@@ -11427,7 +11428,7 @@
       </c>
       <c r="B227" s="20"/>
       <c r="C227" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D227" s="27"/>
       <c r="E227" s="15" t="s">
@@ -11453,7 +11454,7 @@
       </c>
       <c r="B228" s="20"/>
       <c r="C228" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D228" s="27"/>
       <c r="E228" s="15" t="s">
@@ -11479,7 +11480,7 @@
       </c>
       <c r="B229" s="20"/>
       <c r="C229" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D229" s="27"/>
       <c r="E229" s="15" t="s">
@@ -11505,7 +11506,7 @@
       </c>
       <c r="B230" s="23"/>
       <c r="C230" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E230" s="15" t="s">
         <v>1037</v>
@@ -11530,7 +11531,7 @@
       </c>
       <c r="B231" s="23"/>
       <c r="C231" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D231" s="14"/>
       <c r="E231" s="15" t="s">
@@ -11556,7 +11557,7 @@
       </c>
       <c r="B232" s="23"/>
       <c r="C232" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D232" s="14"/>
       <c r="E232" s="15" t="s">
@@ -11582,7 +11583,7 @@
       </c>
       <c r="B233" s="23"/>
       <c r="C233" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D233" s="14"/>
       <c r="E233" s="15" t="s">
@@ -11608,7 +11609,7 @@
       </c>
       <c r="B234" s="23"/>
       <c r="C234" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D234" s="14"/>
       <c r="E234" s="15" t="s">
@@ -11634,7 +11635,7 @@
       </c>
       <c r="B235" s="23"/>
       <c r="C235" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D235" s="14"/>
       <c r="E235" s="15" t="s">
@@ -11660,7 +11661,7 @@
       </c>
       <c r="B236" s="23"/>
       <c r="C236" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E236" s="15" t="s">
         <v>559</v>
@@ -11685,7 +11686,7 @@
       </c>
       <c r="B237" s="23"/>
       <c r="C237" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E237" s="15" t="s">
         <v>551</v>
@@ -11710,7 +11711,7 @@
       </c>
       <c r="B238" s="20"/>
       <c r="C238" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D238" s="27"/>
       <c r="E238" s="16" t="s">
@@ -11736,7 +11737,7 @@
       </c>
       <c r="B239" s="20"/>
       <c r="C239" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D239" s="27"/>
       <c r="E239" s="16" t="s">
@@ -11762,7 +11763,7 @@
       </c>
       <c r="B240" s="22"/>
       <c r="C240" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D240" s="28"/>
       <c r="E240" s="16" t="s">
@@ -11788,7 +11789,7 @@
       </c>
       <c r="B241" s="20"/>
       <c r="C241" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D241" s="27"/>
       <c r="E241" s="16" t="s">
@@ -11814,7 +11815,7 @@
       </c>
       <c r="B242" s="20"/>
       <c r="C242" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D242" s="27"/>
       <c r="E242" s="16" t="s">
@@ -11840,14 +11841,14 @@
       </c>
       <c r="B243" s="20"/>
       <c r="C243" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D243" s="27"/>
       <c r="E243" s="16" t="s">
         <v>679</v>
       </c>
       <c r="F243" s="15" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="G243" s="15" t="s">
         <v>680</v>
@@ -11866,7 +11867,7 @@
       </c>
       <c r="B244" s="20"/>
       <c r="C244" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D244" s="27"/>
       <c r="E244" s="16" t="s">
@@ -11892,7 +11893,7 @@
       </c>
       <c r="B245" s="20"/>
       <c r="C245" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D245" s="27"/>
       <c r="E245" s="16" t="s">
@@ -11918,7 +11919,7 @@
       </c>
       <c r="B246" s="20"/>
       <c r="C246" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D246" s="27"/>
       <c r="E246" s="16" t="s">
@@ -11944,7 +11945,7 @@
       </c>
       <c r="B247" s="20"/>
       <c r="C247" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D247" s="27"/>
       <c r="E247" s="16" t="s">
@@ -11970,7 +11971,7 @@
       </c>
       <c r="B248" s="20"/>
       <c r="C248" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D248" s="27"/>
       <c r="E248" s="16" t="s">
@@ -11996,17 +11997,17 @@
       </c>
       <c r="B249" s="20"/>
       <c r="C249" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D249" s="27"/>
       <c r="E249" s="16" t="s">
         <v>245</v>
       </c>
       <c r="F249" s="15" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G249" s="15" t="s">
         <v>1384</v>
-      </c>
-      <c r="G249" s="15" t="s">
-        <v>1385</v>
       </c>
       <c r="H249" s="4">
         <f t="shared" si="15"/>
@@ -12022,7 +12023,7 @@
       </c>
       <c r="B250" s="20"/>
       <c r="C250" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D250" s="27"/>
       <c r="E250" s="16" t="s">
@@ -12048,7 +12049,7 @@
       </c>
       <c r="B251" s="20"/>
       <c r="C251" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D251" s="27"/>
       <c r="E251" s="16" t="s">
@@ -12073,7 +12074,7 @@
         <v>256</v>
       </c>
       <c r="C252" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E252" s="16" t="s">
         <v>1044</v>
@@ -12098,7 +12099,7 @@
       </c>
       <c r="B253" s="23"/>
       <c r="C253" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D253" s="14"/>
       <c r="E253" s="16" t="s">
@@ -12124,7 +12125,7 @@
       </c>
       <c r="B254" s="20"/>
       <c r="C254" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D254" s="20"/>
       <c r="E254" s="16" t="s">
@@ -12134,7 +12135,7 @@
         <v>1047</v>
       </c>
       <c r="G254" s="15" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H254" s="4">
         <f t="shared" si="15"/>
@@ -12150,7 +12151,7 @@
       </c>
       <c r="B255" s="20"/>
       <c r="C255" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D255" s="27"/>
       <c r="E255" s="16" t="s">
@@ -12160,7 +12161,7 @@
         <v>411</v>
       </c>
       <c r="G255" s="15" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H255" s="4">
         <f t="shared" si="15"/>
@@ -12176,7 +12177,7 @@
       </c>
       <c r="B256" s="20"/>
       <c r="C256" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D256" s="27"/>
       <c r="E256" s="16" t="s">
@@ -12202,7 +12203,7 @@
       </c>
       <c r="B257" s="20"/>
       <c r="C257" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D257" s="27"/>
       <c r="E257" s="16" t="s">
@@ -12228,7 +12229,7 @@
       </c>
       <c r="B258" s="20"/>
       <c r="C258" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D258" s="27"/>
       <c r="E258" s="16" t="s">
@@ -12254,7 +12255,7 @@
       </c>
       <c r="B259" s="20"/>
       <c r="C259" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D259" s="20"/>
       <c r="E259" s="16" t="s">
@@ -12280,7 +12281,7 @@
       </c>
       <c r="B260" s="23"/>
       <c r="C260" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D260" s="14"/>
       <c r="E260" s="16" t="s">
@@ -12290,7 +12291,7 @@
         <v>599</v>
       </c>
       <c r="G260" s="15" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H260" s="4">
         <f t="shared" si="16"/>
@@ -12306,7 +12307,7 @@
       </c>
       <c r="B261" s="20"/>
       <c r="C261" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D261" s="20"/>
       <c r="E261" s="16" t="s">
@@ -12332,7 +12333,7 @@
       </c>
       <c r="B262" s="20"/>
       <c r="C262" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D262" s="27"/>
       <c r="E262" s="16" t="s">
@@ -12358,7 +12359,7 @@
       </c>
       <c r="B263" s="20"/>
       <c r="C263" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D263" s="20"/>
       <c r="E263" s="16" t="s">
@@ -12384,7 +12385,7 @@
       </c>
       <c r="B264" s="20"/>
       <c r="C264" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D264" s="27"/>
       <c r="E264" s="16" t="s">
@@ -12410,7 +12411,7 @@
       </c>
       <c r="B265" s="20"/>
       <c r="C265" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D265" s="27"/>
       <c r="E265" s="16" t="s">
@@ -12436,7 +12437,7 @@
       </c>
       <c r="B266" s="22"/>
       <c r="C266" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D266" s="28"/>
       <c r="E266" s="16" t="s">
@@ -12462,17 +12463,17 @@
       </c>
       <c r="B267" s="20"/>
       <c r="C267" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D267" s="27"/>
       <c r="E267" s="16" t="s">
         <v>355</v>
       </c>
       <c r="F267" s="15" t="s">
+        <v>1388</v>
+      </c>
+      <c r="G267" s="15" t="s">
         <v>1389</v>
-      </c>
-      <c r="G267" s="15" t="s">
-        <v>1390</v>
       </c>
       <c r="H267" s="4">
         <f>D267+1095</f>
@@ -12488,7 +12489,7 @@
       </c>
       <c r="B268" s="20"/>
       <c r="C268" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D268" s="27"/>
       <c r="E268" s="16" t="s">
@@ -12514,7 +12515,7 @@
       </c>
       <c r="B269" s="20"/>
       <c r="C269" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D269" s="27"/>
       <c r="E269" s="16" t="s">
@@ -12540,7 +12541,7 @@
       </c>
       <c r="B270" s="23"/>
       <c r="C270" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D270" s="14"/>
       <c r="E270" s="16" t="s">
@@ -12566,7 +12567,7 @@
       </c>
       <c r="B271" s="20"/>
       <c r="C271" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D271" s="27"/>
       <c r="E271" s="16" t="s">
@@ -12592,7 +12593,7 @@
       </c>
       <c r="B272" s="20"/>
       <c r="C272" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D272" s="27"/>
       <c r="E272" s="16" t="s">
@@ -12618,7 +12619,7 @@
       </c>
       <c r="B273" s="20"/>
       <c r="C273" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D273" s="27"/>
       <c r="E273" s="16" t="s">
@@ -12644,7 +12645,7 @@
       </c>
       <c r="B274" s="20"/>
       <c r="C274" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D274" s="20"/>
       <c r="E274" s="16" t="s">
@@ -12654,7 +12655,7 @@
         <v>119</v>
       </c>
       <c r="G274" s="15" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H274" s="4">
         <f t="shared" si="17"/>
@@ -12670,7 +12671,7 @@
       </c>
       <c r="B275" s="22"/>
       <c r="C275" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D275" s="28"/>
       <c r="E275" s="16" t="s">
@@ -12680,7 +12681,7 @@
         <v>121</v>
       </c>
       <c r="G275" s="15" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H275" s="4">
         <f t="shared" si="17"/>
@@ -12696,7 +12697,7 @@
       </c>
       <c r="B276" s="20"/>
       <c r="C276" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D276" s="27"/>
       <c r="E276" s="16" t="s">
@@ -12722,7 +12723,7 @@
       </c>
       <c r="B277" s="20"/>
       <c r="C277" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D277" s="27"/>
       <c r="E277" s="16" t="s">
@@ -12732,7 +12733,7 @@
         <v>678</v>
       </c>
       <c r="G277" s="15" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H277" s="4">
         <f t="shared" si="17"/>
@@ -12748,7 +12749,7 @@
       </c>
       <c r="B278" s="20"/>
       <c r="C278" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D278" s="27"/>
       <c r="E278" s="16" t="s">
@@ -12774,7 +12775,7 @@
       </c>
       <c r="B279" s="20"/>
       <c r="C279" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D279" s="20"/>
       <c r="E279" s="16" t="s">
@@ -12784,7 +12785,7 @@
         <v>520</v>
       </c>
       <c r="G279" s="15" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H279" s="4">
         <f t="shared" si="17"/>
@@ -12800,7 +12801,7 @@
       </c>
       <c r="B280" s="22"/>
       <c r="C280" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D280" s="28"/>
       <c r="E280" s="16" t="s">
@@ -12826,7 +12827,7 @@
       </c>
       <c r="B281" s="22"/>
       <c r="C281" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D281" s="28"/>
       <c r="E281" s="16" t="s">
@@ -12852,14 +12853,14 @@
       </c>
       <c r="B282" s="20"/>
       <c r="C282" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D282" s="27"/>
       <c r="E282" s="16" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F282" s="18" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="G282" s="18" t="s">
         <v>398</v>
@@ -12878,14 +12879,14 @@
       </c>
       <c r="B283" s="20"/>
       <c r="C283" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D283" s="27"/>
       <c r="E283" s="16" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="F283" s="18" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="G283" s="18" t="s">
         <v>398</v>
@@ -12904,7 +12905,7 @@
       </c>
       <c r="B284" s="20"/>
       <c r="C284" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D284" s="27"/>
       <c r="E284" s="16" t="s">
@@ -12930,7 +12931,7 @@
       </c>
       <c r="B285" s="20"/>
       <c r="C285" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D285" s="27"/>
       <c r="E285" s="16" t="s">
@@ -12956,7 +12957,7 @@
       </c>
       <c r="B286" s="20"/>
       <c r="C286" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D286" s="27"/>
       <c r="E286" s="16" t="s">
@@ -12982,7 +12983,7 @@
       </c>
       <c r="B287" s="20"/>
       <c r="C287" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D287" s="27"/>
       <c r="E287" s="16" t="s">
@@ -13008,7 +13009,7 @@
       </c>
       <c r="B288" s="20"/>
       <c r="C288" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D288" s="27"/>
       <c r="E288" s="16" t="s">
@@ -13034,7 +13035,7 @@
       </c>
       <c r="B289" s="20"/>
       <c r="C289" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D289" s="27"/>
       <c r="E289" s="16" t="s">
@@ -13060,7 +13061,7 @@
       </c>
       <c r="B290" s="20"/>
       <c r="C290" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D290" s="27"/>
       <c r="E290" s="16" t="s">
@@ -13070,7 +13071,7 @@
         <v>533</v>
       </c>
       <c r="G290" s="15" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H290" s="4">
         <f>D290+1095</f>
@@ -13086,7 +13087,7 @@
       </c>
       <c r="B291" s="20"/>
       <c r="C291" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D291" s="27"/>
       <c r="E291" s="16" t="s">
@@ -13112,7 +13113,7 @@
       </c>
       <c r="B292" s="20"/>
       <c r="C292" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D292" s="27"/>
       <c r="E292" s="16" t="s">
@@ -13122,7 +13123,7 @@
         <v>706</v>
       </c>
       <c r="G292" s="15" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H292" s="4">
         <f t="shared" ref="H292:H297" si="18">D292+1095</f>
@@ -13138,7 +13139,7 @@
       </c>
       <c r="B293" s="20"/>
       <c r="C293" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D293" s="27"/>
       <c r="E293" s="16" t="s">
@@ -13164,7 +13165,7 @@
       </c>
       <c r="B294" s="20"/>
       <c r="C294" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D294" s="27"/>
       <c r="E294" s="16" t="s">
@@ -13190,7 +13191,7 @@
       </c>
       <c r="B295" s="20"/>
       <c r="C295" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D295" s="27"/>
       <c r="E295" s="16" t="s">
@@ -13200,7 +13201,7 @@
         <v>55</v>
       </c>
       <c r="G295" s="15" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H295" s="4">
         <f t="shared" si="18"/>
@@ -13216,7 +13217,7 @@
       </c>
       <c r="B296" s="20"/>
       <c r="C296" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D296" s="27"/>
       <c r="E296" s="16" t="s">
@@ -13242,7 +13243,7 @@
       </c>
       <c r="B297" s="21"/>
       <c r="C297" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D297" s="22"/>
       <c r="E297" s="16" t="s">
@@ -13268,7 +13269,7 @@
       </c>
       <c r="B298" s="20"/>
       <c r="C298" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D298" s="20"/>
       <c r="E298" s="16" t="s">
@@ -13294,7 +13295,7 @@
       </c>
       <c r="B299" s="23"/>
       <c r="C299" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E299" s="16" t="s">
         <v>66</v>
@@ -13319,7 +13320,7 @@
       </c>
       <c r="B300" s="20"/>
       <c r="C300" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D300" s="27"/>
       <c r="E300" s="16" t="s">
@@ -13345,7 +13346,7 @@
       </c>
       <c r="B301" s="20"/>
       <c r="C301" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D301" s="27"/>
       <c r="E301" s="16" t="s">
@@ -13355,7 +13356,7 @@
         <v>270</v>
       </c>
       <c r="G301" s="15" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H301" s="4">
         <f t="shared" si="19"/>
@@ -13369,7 +13370,7 @@
       <c r="A302" s="22"/>
       <c r="B302" s="20"/>
       <c r="C302" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D302" s="20"/>
       <c r="E302" s="16" t="s">
@@ -13392,7 +13393,7 @@
     <row r="303" spans="1:9" ht="15">
       <c r="B303" s="20"/>
       <c r="C303" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D303" s="27"/>
       <c r="E303" s="16" t="s">
@@ -13418,7 +13419,7 @@
       </c>
       <c r="B304" s="20"/>
       <c r="C304" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D304" s="20"/>
       <c r="E304" s="16" t="s">
@@ -13444,7 +13445,7 @@
       </c>
       <c r="B305" s="20"/>
       <c r="C305" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D305" s="20"/>
       <c r="E305" s="16" t="s">
@@ -13470,7 +13471,7 @@
       </c>
       <c r="B306" s="20"/>
       <c r="C306" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D306" s="27"/>
       <c r="E306" s="16" t="s">
@@ -13496,7 +13497,7 @@
       </c>
       <c r="B307" s="23"/>
       <c r="C307" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D307" s="14"/>
       <c r="E307" s="16" t="s">
@@ -13522,7 +13523,7 @@
       </c>
       <c r="B308" s="22"/>
       <c r="C308" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D308" s="28"/>
       <c r="E308" s="16" t="s">
@@ -13548,7 +13549,7 @@
       </c>
       <c r="B309" s="20"/>
       <c r="C309" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D309" s="27"/>
       <c r="E309" s="16" t="s">
@@ -13574,7 +13575,7 @@
       </c>
       <c r="B310" s="20"/>
       <c r="C310" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D310" s="27"/>
       <c r="E310" s="16" t="s">
@@ -13600,7 +13601,7 @@
       </c>
       <c r="B311" s="20"/>
       <c r="C311" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D311" s="27"/>
       <c r="E311" s="16" t="s">
@@ -13626,7 +13627,7 @@
       </c>
       <c r="B312" s="20"/>
       <c r="C312" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D312" s="27"/>
       <c r="E312" s="16" t="s">
@@ -13652,7 +13653,7 @@
       </c>
       <c r="B313" s="20"/>
       <c r="C313" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D313" s="27"/>
       <c r="E313" s="16" t="s">
@@ -13678,7 +13679,7 @@
       </c>
       <c r="B314" s="20"/>
       <c r="C314" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D314" s="20"/>
       <c r="E314" s="16" t="s">
@@ -13704,17 +13705,17 @@
       </c>
       <c r="B315" s="20"/>
       <c r="C315" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D315" s="27"/>
       <c r="E315" s="16" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="F315" s="15" t="s">
         <v>143</v>
       </c>
       <c r="G315" s="8" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H315" s="4">
         <f t="shared" si="20"/>
@@ -13730,11 +13731,11 @@
       </c>
       <c r="B316" s="20"/>
       <c r="C316" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D316" s="27"/>
       <c r="E316" s="16" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="F316" s="15" t="s">
         <v>143</v>
@@ -13756,7 +13757,7 @@
       </c>
       <c r="B317" s="20"/>
       <c r="C317" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D317" s="27"/>
       <c r="E317" s="16" t="s">
@@ -13782,7 +13783,7 @@
       </c>
       <c r="B318" s="20"/>
       <c r="C318" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D318" s="20"/>
       <c r="E318" s="16" t="s">
@@ -13808,7 +13809,7 @@
       </c>
       <c r="B319" s="20"/>
       <c r="C319" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D319" s="20"/>
       <c r="E319" s="16" t="s">
@@ -13834,7 +13835,7 @@
       </c>
       <c r="B320" s="22"/>
       <c r="C320" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D320" s="22"/>
       <c r="E320" s="16" t="s">
@@ -13860,7 +13861,7 @@
       </c>
       <c r="B321" s="20"/>
       <c r="C321" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D321" s="20"/>
       <c r="E321" s="16" t="s">
@@ -13886,7 +13887,7 @@
       </c>
       <c r="B322" s="20"/>
       <c r="C322" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D322" s="27"/>
       <c r="E322" s="16" t="s">
@@ -13912,7 +13913,7 @@
       </c>
       <c r="B323" s="20"/>
       <c r="C323" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D323" s="27"/>
       <c r="E323" s="16" t="s">
@@ -13938,7 +13939,7 @@
       </c>
       <c r="B324" s="20"/>
       <c r="C324" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D324" s="27"/>
       <c r="E324" s="16" t="s">
@@ -13964,7 +13965,7 @@
       </c>
       <c r="B325" s="22"/>
       <c r="C325" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D325" s="28"/>
       <c r="E325" s="16" t="s">
@@ -13990,7 +13991,7 @@
       </c>
       <c r="B326" s="20"/>
       <c r="C326" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D326" s="27"/>
       <c r="E326" s="16" t="s">
@@ -14016,7 +14017,7 @@
       </c>
       <c r="B327" s="20"/>
       <c r="C327" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D327" s="27"/>
       <c r="E327" s="16" t="s">
@@ -14026,7 +14027,7 @@
         <v>659</v>
       </c>
       <c r="G327" s="15" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H327" s="4">
         <f>D327+1825</f>
@@ -14042,7 +14043,7 @@
       </c>
       <c r="B328" s="22"/>
       <c r="C328" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D328" s="14"/>
       <c r="E328" s="16" t="s">
@@ -14052,7 +14053,7 @@
         <v>663</v>
       </c>
       <c r="G328" s="15" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H328" s="4">
         <f>D328+1095</f>
@@ -14068,7 +14069,7 @@
       </c>
       <c r="B329" s="20"/>
       <c r="C329" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D329" s="27"/>
       <c r="E329" s="16" t="s">
@@ -14078,7 +14079,7 @@
         <v>123</v>
       </c>
       <c r="G329" s="15" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H329" s="4">
         <f>D329+1096</f>
@@ -14091,7 +14092,7 @@
     <row r="330" spans="1:9" ht="15">
       <c r="B330" s="20"/>
       <c r="C330" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D330" s="27"/>
       <c r="E330" s="16" t="s">
@@ -14114,7 +14115,7 @@
     <row r="331" spans="1:9" ht="15">
       <c r="B331" s="20"/>
       <c r="C331" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D331" s="27"/>
       <c r="E331" s="16" t="s">
@@ -14140,7 +14141,7 @@
       </c>
       <c r="B332" s="20"/>
       <c r="C332" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D332" s="27"/>
       <c r="E332" s="16" t="s">
@@ -14166,7 +14167,7 @@
       </c>
       <c r="B333" s="20"/>
       <c r="C333" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D333" s="27"/>
       <c r="E333" s="16" t="s">
@@ -14176,7 +14177,7 @@
         <v>295</v>
       </c>
       <c r="G333" s="15" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H333" s="4">
         <f t="shared" si="21"/>
@@ -14192,7 +14193,7 @@
       </c>
       <c r="B334" s="20"/>
       <c r="C334" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D334" s="20"/>
       <c r="E334" s="16" t="s">
@@ -14218,7 +14219,7 @@
       </c>
       <c r="B335" s="20"/>
       <c r="C335" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D335" s="27"/>
       <c r="E335" s="16" t="s">
@@ -14228,7 +14229,7 @@
         <v>297</v>
       </c>
       <c r="G335" s="15" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H335" s="4">
         <f t="shared" si="21"/>
@@ -14242,7 +14243,7 @@
       <c r="A336" s="22"/>
       <c r="B336" s="20"/>
       <c r="C336" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D336" s="27"/>
       <c r="E336" s="16" t="s">
@@ -14268,7 +14269,7 @@
       </c>
       <c r="B337" s="20"/>
       <c r="C337" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D337" s="27"/>
       <c r="E337" s="16" t="s">
@@ -14294,7 +14295,7 @@
       </c>
       <c r="B338" s="20"/>
       <c r="C338" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D338" s="27"/>
       <c r="E338" s="16" t="s">
@@ -14320,7 +14321,7 @@
       </c>
       <c r="B339" s="20"/>
       <c r="C339" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D339" s="27"/>
       <c r="E339" s="16" t="s">
@@ -14343,7 +14344,7 @@
     <row r="340" spans="1:9" ht="15">
       <c r="B340" s="20"/>
       <c r="C340" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D340" s="20"/>
       <c r="E340" s="16" t="s">
@@ -14369,7 +14370,7 @@
       </c>
       <c r="B341" s="20"/>
       <c r="C341" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D341" s="27"/>
       <c r="E341" s="16" t="s">
@@ -14395,14 +14396,14 @@
       </c>
       <c r="B342" s="20"/>
       <c r="C342" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D342" s="27"/>
       <c r="E342" s="16" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="F342" s="15" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="G342" s="15" t="s">
         <v>417</v>
@@ -14421,7 +14422,7 @@
       </c>
       <c r="B343" s="20"/>
       <c r="C343" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D343" s="27"/>
       <c r="E343" s="16" t="s">
@@ -14447,7 +14448,7 @@
       </c>
       <c r="B344" s="20"/>
       <c r="C344" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D344" s="20"/>
       <c r="E344" s="16" t="s">
@@ -14473,7 +14474,7 @@
       </c>
       <c r="B345" s="22"/>
       <c r="C345" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D345" s="28"/>
       <c r="E345" s="16" t="s">
@@ -14499,7 +14500,7 @@
       </c>
       <c r="B346" s="20"/>
       <c r="C346" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D346" s="20"/>
       <c r="E346" s="16" t="s">
@@ -14525,7 +14526,7 @@
       </c>
       <c r="B347" s="20"/>
       <c r="C347" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D347" s="27"/>
       <c r="E347" s="16" t="s">
@@ -14548,7 +14549,7 @@
     <row r="348" spans="1:9" ht="15">
       <c r="B348" s="22"/>
       <c r="C348" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D348" s="14"/>
       <c r="E348" s="15" t="s">
@@ -14558,7 +14559,7 @@
         <v>1088</v>
       </c>
       <c r="G348" s="15" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H348" s="4">
         <f>D348+1825</f>
@@ -14574,7 +14575,7 @@
       </c>
       <c r="B349" s="20"/>
       <c r="C349" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D349" s="20"/>
       <c r="E349" s="16" t="s">
@@ -14600,7 +14601,7 @@
       </c>
       <c r="B350" s="20"/>
       <c r="C350" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D350" s="20"/>
       <c r="E350" s="16" t="s">
@@ -14626,7 +14627,7 @@
       </c>
       <c r="B351" s="20"/>
       <c r="C351" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D351" s="20"/>
       <c r="E351" s="16" t="s">
@@ -14652,7 +14653,7 @@
       </c>
       <c r="B352" s="20"/>
       <c r="C352" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D352" s="20"/>
       <c r="E352" s="16" t="s">
@@ -14678,7 +14679,7 @@
       </c>
       <c r="B353" s="20"/>
       <c r="C353" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D353" s="27"/>
       <c r="E353" s="16" t="s">
@@ -14704,7 +14705,7 @@
       </c>
       <c r="B354" s="20"/>
       <c r="C354" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D354" s="27"/>
       <c r="E354" s="16" t="s">
@@ -14730,7 +14731,7 @@
       </c>
       <c r="B355" s="20"/>
       <c r="C355" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D355" s="27"/>
       <c r="E355" s="16" t="s">
@@ -14756,7 +14757,7 @@
       </c>
       <c r="B356" s="20"/>
       <c r="C356" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D356" s="20"/>
       <c r="E356" s="16" t="s">
@@ -14782,7 +14783,7 @@
       </c>
       <c r="B357" s="20"/>
       <c r="C357" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D357" s="20"/>
       <c r="E357" s="16" t="s">
@@ -14808,7 +14809,7 @@
       </c>
       <c r="B358" s="20"/>
       <c r="C358" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D358" s="20"/>
       <c r="E358" s="16" t="s">
@@ -14834,7 +14835,7 @@
       </c>
       <c r="B359" s="20"/>
       <c r="C359" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D359" s="20"/>
       <c r="E359" s="16" t="s">
@@ -14860,7 +14861,7 @@
       </c>
       <c r="B360" s="20"/>
       <c r="C360" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D360" s="27"/>
       <c r="E360" s="16" t="s">
@@ -14886,7 +14887,7 @@
       </c>
       <c r="B361" s="20"/>
       <c r="C361" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D361" s="27"/>
       <c r="E361" s="16" t="s">
@@ -14912,7 +14913,7 @@
       </c>
       <c r="B362" s="20"/>
       <c r="C362" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D362" s="27"/>
       <c r="E362" s="16" t="s">
@@ -14922,7 +14923,7 @@
         <v>912</v>
       </c>
       <c r="G362" s="15" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H362" s="4">
         <f t="shared" si="22"/>
@@ -14938,7 +14939,7 @@
       </c>
       <c r="B363" s="20"/>
       <c r="C363" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D363" s="27"/>
       <c r="E363" s="16" t="s">
@@ -14964,7 +14965,7 @@
       </c>
       <c r="B364" s="22"/>
       <c r="C364" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D364" s="28"/>
       <c r="E364" s="16" t="s">
@@ -14990,7 +14991,7 @@
       </c>
       <c r="B365" s="20"/>
       <c r="C365" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D365" s="27"/>
       <c r="E365" s="16" t="s">
@@ -15016,7 +15017,7 @@
       </c>
       <c r="B366" s="20"/>
       <c r="C366" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D366" s="27"/>
       <c r="E366" s="16" t="s">
@@ -15042,7 +15043,7 @@
       </c>
       <c r="B367" s="22"/>
       <c r="C367" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E367" s="16" t="s">
         <v>1117</v>
@@ -15067,7 +15068,7 @@
       </c>
       <c r="B368" s="22"/>
       <c r="C368" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D368" s="29"/>
       <c r="E368" s="16" t="s">
@@ -15093,7 +15094,7 @@
       </c>
       <c r="B369" s="20"/>
       <c r="C369" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D369" s="27"/>
       <c r="E369" s="16" t="s">
@@ -15119,7 +15120,7 @@
       </c>
       <c r="B370" s="20"/>
       <c r="C370" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D370" s="27"/>
       <c r="E370" s="16" t="s">
@@ -15145,7 +15146,7 @@
       </c>
       <c r="B371" s="22"/>
       <c r="C371" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D371" s="29"/>
       <c r="E371" s="16" t="s">
@@ -15171,7 +15172,7 @@
       </c>
       <c r="B372" s="22"/>
       <c r="C372" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D372" s="28"/>
       <c r="E372" s="16" t="s">
@@ -15197,7 +15198,7 @@
       </c>
       <c r="B373" s="20"/>
       <c r="C373" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D373" s="27"/>
       <c r="E373" s="16" t="s">
@@ -15223,7 +15224,7 @@
       </c>
       <c r="B374" s="20"/>
       <c r="C374" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D374" s="27"/>
       <c r="E374" s="16" t="s">
@@ -15249,7 +15250,7 @@
       </c>
       <c r="B375" s="20"/>
       <c r="C375" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D375" s="27"/>
       <c r="E375" s="16" t="s">
@@ -15275,14 +15276,14 @@
       </c>
       <c r="B376" s="22"/>
       <c r="C376" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D376" s="28"/>
       <c r="E376" s="16" t="s">
         <v>1142</v>
       </c>
       <c r="F376" s="15" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="G376" s="15" t="s">
         <v>1143</v>
@@ -15301,7 +15302,7 @@
       </c>
       <c r="B377" s="20"/>
       <c r="C377" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D377" s="27"/>
       <c r="E377" s="16" t="s">
@@ -15327,7 +15328,7 @@
       </c>
       <c r="B378" s="20"/>
       <c r="C378" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D378" s="20"/>
       <c r="E378" s="16" t="s">
@@ -15353,7 +15354,7 @@
       </c>
       <c r="B379" s="20"/>
       <c r="C379" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D379" s="20"/>
       <c r="E379" s="16" t="s">
@@ -15377,7 +15378,7 @@
       <c r="A380" s="22"/>
       <c r="B380" s="20"/>
       <c r="C380" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D380" s="27"/>
       <c r="E380" s="16" t="s">
@@ -15403,7 +15404,7 @@
       </c>
       <c r="B381" s="20"/>
       <c r="C381" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D381" s="27"/>
       <c r="E381" s="16" t="s">
@@ -15429,7 +15430,7 @@
       </c>
       <c r="B382" s="20"/>
       <c r="C382" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D382" s="27"/>
       <c r="E382" s="16" t="s">
@@ -15455,7 +15456,7 @@
       </c>
       <c r="B383" s="20"/>
       <c r="C383" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D383" s="20"/>
       <c r="E383" s="16" t="s">
@@ -15481,7 +15482,7 @@
       </c>
       <c r="B384" s="20"/>
       <c r="C384" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D384" s="20"/>
       <c r="E384" s="16" t="s">
@@ -15507,7 +15508,7 @@
       </c>
       <c r="B385" s="20"/>
       <c r="C385" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D385" s="27"/>
       <c r="E385" s="16" t="s">
@@ -15533,7 +15534,7 @@
       </c>
       <c r="B386" s="20"/>
       <c r="C386" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D386" s="20"/>
       <c r="E386" s="16" t="s">
@@ -15559,14 +15560,14 @@
       </c>
       <c r="B387" s="20"/>
       <c r="C387" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D387" s="27"/>
       <c r="E387" s="16" t="s">
         <v>1170</v>
       </c>
       <c r="F387" s="15" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="G387" s="15" t="s">
         <v>1171</v>
@@ -15585,7 +15586,7 @@
       </c>
       <c r="B388" s="20"/>
       <c r="C388" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D388" s="20"/>
       <c r="E388" s="16" t="s">
@@ -15611,7 +15612,7 @@
       </c>
       <c r="B389" s="20"/>
       <c r="C389" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D389" s="20"/>
       <c r="E389" s="16" t="s">
@@ -15637,7 +15638,7 @@
       </c>
       <c r="B390" s="20"/>
       <c r="C390" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D390" s="27"/>
       <c r="E390" s="16" t="s">
@@ -15661,7 +15662,7 @@
       <c r="A391" s="22"/>
       <c r="B391" s="20"/>
       <c r="C391" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D391" s="27"/>
       <c r="E391" s="16" t="s">
@@ -15687,7 +15688,7 @@
       </c>
       <c r="B392" s="20"/>
       <c r="C392" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D392" s="27"/>
       <c r="E392" s="16" t="s">
@@ -15713,7 +15714,7 @@
       </c>
       <c r="B393" s="20"/>
       <c r="C393" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D393" s="27"/>
       <c r="E393" s="16" t="s">
@@ -15739,7 +15740,7 @@
       </c>
       <c r="B394" s="20"/>
       <c r="C394" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D394" s="27"/>
       <c r="E394" s="16" t="s">
@@ -15765,7 +15766,7 @@
       </c>
       <c r="B395" s="20"/>
       <c r="C395" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D395" s="27"/>
       <c r="E395" s="16" t="s">
@@ -15791,7 +15792,7 @@
       </c>
       <c r="B396" s="23"/>
       <c r="C396" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E396" s="16" t="s">
         <v>1195</v>
@@ -15816,7 +15817,7 @@
       </c>
       <c r="B397" s="23"/>
       <c r="C397" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D397" s="29"/>
       <c r="E397" s="16" t="s">
@@ -15842,7 +15843,7 @@
       </c>
       <c r="B398" s="23"/>
       <c r="C398" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D398" s="29"/>
       <c r="E398" s="16" t="s">
@@ -15868,7 +15869,7 @@
       </c>
       <c r="B399" s="20"/>
       <c r="C399" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D399" s="20"/>
       <c r="E399" s="16" t="s">
@@ -15892,7 +15893,7 @@
       <c r="A400" s="22"/>
       <c r="B400" s="20"/>
       <c r="C400" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D400" s="27"/>
       <c r="E400" s="16" t="s">
@@ -15918,7 +15919,7 @@
       </c>
       <c r="B401" s="20"/>
       <c r="C401" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D401" s="20"/>
       <c r="E401" s="16" t="s">
@@ -15944,7 +15945,7 @@
       </c>
       <c r="B402" s="20"/>
       <c r="C402" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D402" s="27"/>
       <c r="E402" s="16" t="s">
@@ -15970,7 +15971,7 @@
       </c>
       <c r="B403" s="20"/>
       <c r="C403" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D403" s="27"/>
       <c r="E403" s="16" t="s">
@@ -15996,7 +15997,7 @@
       </c>
       <c r="B404" s="20"/>
       <c r="C404" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D404" s="20"/>
       <c r="E404" s="16" t="s">
@@ -16022,7 +16023,7 @@
       </c>
       <c r="B405" s="20"/>
       <c r="C405" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D405" s="27"/>
       <c r="E405" s="16" t="s">
@@ -16048,7 +16049,7 @@
       </c>
       <c r="B406" s="21"/>
       <c r="C406" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D406" s="29"/>
       <c r="E406" s="16" t="s">
@@ -16072,7 +16073,7 @@
       <c r="A407" s="22"/>
       <c r="B407" s="23"/>
       <c r="C407" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E407" s="16" t="s">
         <v>1224</v>
@@ -16097,7 +16098,7 @@
       </c>
       <c r="B408" s="20"/>
       <c r="C408" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D408" s="27"/>
       <c r="E408" s="16" t="s">
@@ -16123,7 +16124,7 @@
       </c>
       <c r="B409" s="23"/>
       <c r="C409" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E409" s="16" t="s">
         <v>1230</v>
@@ -16148,7 +16149,7 @@
       </c>
       <c r="B410" s="23"/>
       <c r="C410" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D410" s="14"/>
       <c r="E410" s="16" t="s">
@@ -16174,7 +16175,7 @@
       </c>
       <c r="B411" s="23"/>
       <c r="C411" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D411" s="14"/>
       <c r="E411" s="16" t="s">
@@ -16200,7 +16201,7 @@
       </c>
       <c r="B412" s="20"/>
       <c r="C412" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D412" s="27"/>
       <c r="E412" s="16" t="s">
@@ -16223,7 +16224,7 @@
     <row r="413" spans="1:9" ht="15">
       <c r="B413" s="20"/>
       <c r="C413" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D413" s="27"/>
       <c r="E413" s="16" t="s">
@@ -16249,7 +16250,7 @@
       </c>
       <c r="B414" s="20"/>
       <c r="C414" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D414" s="27"/>
       <c r="E414" s="16" t="s">
@@ -16275,7 +16276,7 @@
       </c>
       <c r="B415" s="20"/>
       <c r="C415" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D415" s="27"/>
       <c r="E415" s="16" t="s">
@@ -16301,7 +16302,7 @@
       </c>
       <c r="B416" s="20"/>
       <c r="C416" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D416" s="20"/>
       <c r="E416" s="16" t="s">
@@ -16327,7 +16328,7 @@
       </c>
       <c r="B417" s="20"/>
       <c r="C417" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D417" s="20"/>
       <c r="E417" s="16" t="s">
@@ -16353,7 +16354,7 @@
       </c>
       <c r="B418" s="20"/>
       <c r="C418" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D418" s="27"/>
       <c r="E418" s="16" t="s">
@@ -16379,17 +16380,17 @@
       </c>
       <c r="B419" s="20"/>
       <c r="C419" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D419" s="27"/>
       <c r="E419" s="16" t="s">
         <v>1264</v>
       </c>
       <c r="F419" s="15" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G419" s="8" t="s">
         <v>1265</v>
-      </c>
-      <c r="G419" s="8" t="s">
-        <v>1266</v>
       </c>
       <c r="H419" s="4">
         <f t="shared" ref="H419:H443" si="24">D419+1095</f>
@@ -16405,17 +16406,17 @@
       </c>
       <c r="B420" s="25"/>
       <c r="C420" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D420" s="25"/>
       <c r="E420" s="16" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F420" s="15" t="s">
         <v>1267</v>
       </c>
-      <c r="F420" s="15" t="s">
+      <c r="G420" s="15" t="s">
         <v>1268</v>
-      </c>
-      <c r="G420" s="15" t="s">
-        <v>1269</v>
       </c>
       <c r="H420" s="4">
         <f t="shared" si="24"/>
@@ -16431,17 +16432,17 @@
       </c>
       <c r="B421" s="20"/>
       <c r="C421" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D421" s="20"/>
       <c r="E421" s="16" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F421" s="15" t="s">
         <v>1270</v>
       </c>
-      <c r="F421" s="15" t="s">
-        <v>1271</v>
-      </c>
       <c r="G421" s="15" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H421" s="4">
         <f t="shared" si="24"/>
@@ -16457,17 +16458,17 @@
       </c>
       <c r="B422" s="20"/>
       <c r="C422" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D422" s="27"/>
       <c r="E422" s="16" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F422" s="15" t="s">
         <v>1272</v>
       </c>
-      <c r="F422" s="15" t="s">
+      <c r="G422" s="15" t="s">
         <v>1273</v>
-      </c>
-      <c r="G422" s="15" t="s">
-        <v>1274</v>
       </c>
       <c r="H422" s="4">
         <f t="shared" si="24"/>
@@ -16483,17 +16484,17 @@
       </c>
       <c r="B423" s="20"/>
       <c r="C423" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D423" s="27"/>
       <c r="E423" s="16" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F423" s="15" t="s">
         <v>1275</v>
       </c>
-      <c r="F423" s="15" t="s">
+      <c r="G423" s="15" t="s">
         <v>1276</v>
-      </c>
-      <c r="G423" s="15" t="s">
-        <v>1277</v>
       </c>
       <c r="H423" s="4">
         <f t="shared" si="24"/>
@@ -16509,17 +16510,17 @@
       </c>
       <c r="B424" s="20"/>
       <c r="C424" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D424" s="27"/>
       <c r="E424" s="15" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F424" s="16" t="s">
         <v>1278</v>
       </c>
-      <c r="F424" s="16" t="s">
+      <c r="G424" s="16" t="s">
         <v>1279</v>
-      </c>
-      <c r="G424" s="16" t="s">
-        <v>1280</v>
       </c>
       <c r="H424" s="4">
         <f t="shared" si="24"/>
@@ -16535,16 +16536,16 @@
       </c>
       <c r="B425" s="23"/>
       <c r="C425" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E425" s="16" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F425" s="16" t="s">
         <v>1281</v>
       </c>
-      <c r="F425" s="16" t="s">
+      <c r="G425" s="16" t="s">
         <v>1282</v>
-      </c>
-      <c r="G425" s="16" t="s">
-        <v>1283</v>
       </c>
       <c r="H425" s="4">
         <f t="shared" si="24"/>
@@ -16560,16 +16561,16 @@
       </c>
       <c r="B426" s="23"/>
       <c r="C426" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E426" s="16" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F426" s="16" t="s">
         <v>1284</v>
       </c>
-      <c r="F426" s="16" t="s">
+      <c r="G426" s="16" t="s">
         <v>1285</v>
-      </c>
-      <c r="G426" s="16" t="s">
-        <v>1286</v>
       </c>
       <c r="H426" s="4">
         <f t="shared" si="24"/>
@@ -16585,16 +16586,16 @@
       </c>
       <c r="B427" s="23"/>
       <c r="C427" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E427" s="16" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F427" s="16" t="s">
         <v>1287</v>
       </c>
-      <c r="F427" s="16" t="s">
+      <c r="G427" s="16" t="s">
         <v>1288</v>
-      </c>
-      <c r="G427" s="16" t="s">
-        <v>1289</v>
       </c>
       <c r="H427" s="4">
         <f t="shared" si="24"/>
@@ -16610,17 +16611,17 @@
       </c>
       <c r="B428" s="20"/>
       <c r="C428" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D428" s="20"/>
       <c r="E428" s="16" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F428" s="16" t="s">
         <v>1290</v>
       </c>
-      <c r="F428" s="16" t="s">
+      <c r="G428" s="16" t="s">
         <v>1291</v>
-      </c>
-      <c r="G428" s="16" t="s">
-        <v>1292</v>
       </c>
       <c r="H428" s="4">
         <f t="shared" si="24"/>
@@ -16636,17 +16637,17 @@
       </c>
       <c r="B429" s="20"/>
       <c r="C429" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D429" s="27"/>
       <c r="E429" s="16" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F429" s="16" t="s">
         <v>1293</v>
       </c>
-      <c r="F429" s="16" t="s">
+      <c r="G429" s="16" t="s">
         <v>1294</v>
-      </c>
-      <c r="G429" s="16" t="s">
-        <v>1295</v>
       </c>
       <c r="H429" s="4">
         <f t="shared" si="24"/>
@@ -16662,17 +16663,17 @@
       </c>
       <c r="B430" s="20"/>
       <c r="C430" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D430" s="27"/>
       <c r="E430" s="16" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F430" s="16" t="s">
         <v>1296</v>
       </c>
-      <c r="F430" s="16" t="s">
+      <c r="G430" s="16" t="s">
         <v>1297</v>
-      </c>
-      <c r="G430" s="16" t="s">
-        <v>1298</v>
       </c>
       <c r="H430" s="4">
         <f t="shared" si="24"/>
@@ -16688,17 +16689,17 @@
       </c>
       <c r="B431" s="20"/>
       <c r="C431" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D431" s="27"/>
       <c r="E431" s="16" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F431" s="16" t="s">
         <v>1299</v>
       </c>
-      <c r="F431" s="16" t="s">
-        <v>1300</v>
-      </c>
       <c r="G431" s="16" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H431" s="4">
         <f t="shared" si="24"/>
@@ -16714,16 +16715,16 @@
       </c>
       <c r="B432" s="20"/>
       <c r="C432" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E432" s="15">
         <v>88300196814</v>
       </c>
       <c r="F432" s="16" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="G432" s="16" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H432" s="4">
         <f t="shared" si="24"/>
@@ -16739,17 +16740,17 @@
       </c>
       <c r="B433" s="20"/>
       <c r="C433" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D433" s="27"/>
       <c r="E433" s="16" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F433" s="16" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G433" s="16" t="s">
         <v>1302</v>
-      </c>
-      <c r="F433" s="16" t="s">
-        <v>1409</v>
-      </c>
-      <c r="G433" s="16" t="s">
-        <v>1303</v>
       </c>
       <c r="H433" s="4">
         <f t="shared" si="24"/>
@@ -16765,17 +16766,17 @@
       </c>
       <c r="B434" s="20"/>
       <c r="C434" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D434" s="27"/>
       <c r="E434" s="16" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F434" s="16" t="s">
         <v>1304</v>
       </c>
-      <c r="F434" s="16" t="s">
+      <c r="G434" s="16" t="s">
         <v>1305</v>
-      </c>
-      <c r="G434" s="16" t="s">
-        <v>1306</v>
       </c>
       <c r="H434" s="4">
         <f t="shared" si="24"/>
@@ -16791,17 +16792,17 @@
       </c>
       <c r="B435" s="20"/>
       <c r="C435" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D435" s="20"/>
       <c r="E435" s="16" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F435" s="16" t="s">
         <v>1307</v>
       </c>
-      <c r="F435" s="16" t="s">
+      <c r="G435" s="16" t="s">
         <v>1308</v>
-      </c>
-      <c r="G435" s="16" t="s">
-        <v>1309</v>
       </c>
       <c r="H435" s="4">
         <f t="shared" si="24"/>
@@ -16817,16 +16818,16 @@
       </c>
       <c r="B436" s="23"/>
       <c r="C436" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E436" s="16" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F436" s="16" t="s">
         <v>1310</v>
       </c>
-      <c r="F436" s="16" t="s">
+      <c r="G436" s="16" t="s">
         <v>1311</v>
-      </c>
-      <c r="G436" s="16" t="s">
-        <v>1312</v>
       </c>
       <c r="H436" s="4">
         <f t="shared" si="24"/>
@@ -16842,17 +16843,17 @@
       </c>
       <c r="B437" s="20"/>
       <c r="C437" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D437" s="20"/>
       <c r="E437" s="16" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F437" s="16" t="s">
         <v>1313</v>
       </c>
-      <c r="F437" s="16" t="s">
+      <c r="G437" s="16" t="s">
         <v>1314</v>
-      </c>
-      <c r="G437" s="16" t="s">
-        <v>1315</v>
       </c>
       <c r="H437" s="4">
         <f t="shared" si="24"/>
@@ -16868,17 +16869,17 @@
       </c>
       <c r="B438" s="20"/>
       <c r="C438" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D438" s="20"/>
       <c r="E438" s="16" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F438" s="16" t="s">
         <v>1316</v>
       </c>
-      <c r="F438" s="16" t="s">
+      <c r="G438" s="16" t="s">
         <v>1317</v>
-      </c>
-      <c r="G438" s="16" t="s">
-        <v>1318</v>
       </c>
       <c r="H438" s="4">
         <f t="shared" si="24"/>
@@ -16894,17 +16895,17 @@
       </c>
       <c r="B439" s="20"/>
       <c r="C439" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D439" s="27"/>
       <c r="E439" s="16" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F439" s="16" t="s">
         <v>1319</v>
       </c>
-      <c r="F439" s="16" t="s">
+      <c r="G439" s="16" t="s">
         <v>1320</v>
-      </c>
-      <c r="G439" s="16" t="s">
-        <v>1321</v>
       </c>
       <c r="H439" s="4">
         <f t="shared" si="24"/>
@@ -16920,17 +16921,17 @@
       </c>
       <c r="B440" s="23"/>
       <c r="C440" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D440" s="28"/>
       <c r="E440" s="16" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F440" s="16" t="s">
         <v>1322</v>
       </c>
-      <c r="F440" s="16" t="s">
+      <c r="G440" s="16" t="s">
         <v>1323</v>
-      </c>
-      <c r="G440" s="16" t="s">
-        <v>1324</v>
       </c>
       <c r="H440" s="4">
         <f t="shared" si="24"/>
@@ -16946,17 +16947,17 @@
       </c>
       <c r="B441" s="20"/>
       <c r="C441" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D441" s="27"/>
       <c r="E441" s="16" t="s">
+        <v>1324</v>
+      </c>
+      <c r="F441" s="16" t="s">
         <v>1325</v>
       </c>
-      <c r="F441" s="16" t="s">
+      <c r="G441" s="16" t="s">
         <v>1326</v>
-      </c>
-      <c r="G441" s="16" t="s">
-        <v>1327</v>
       </c>
       <c r="H441" s="4">
         <f t="shared" si="24"/>
@@ -16972,17 +16973,17 @@
       </c>
       <c r="B442" s="23"/>
       <c r="C442" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D442" s="28"/>
       <c r="E442" s="16" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F442" s="16" t="s">
         <v>1328</v>
       </c>
-      <c r="F442" s="16" t="s">
+      <c r="G442" s="16" t="s">
         <v>1329</v>
-      </c>
-      <c r="G442" s="16" t="s">
-        <v>1330</v>
       </c>
       <c r="H442" s="4">
         <f t="shared" si="24"/>
@@ -16994,21 +16995,21 @@
     </row>
     <row r="443" spans="1:9" ht="15">
       <c r="A443" s="22" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B443" s="20"/>
       <c r="C443" s="24" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D443" s="20"/>
       <c r="E443" s="16" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F443" s="16" t="s">
         <v>1331</v>
       </c>
-      <c r="F443" s="16" t="s">
+      <c r="G443" s="16" t="s">
         <v>1332</v>
-      </c>
-      <c r="G443" s="16" t="s">
-        <v>1333</v>
       </c>
       <c r="H443" s="4">
         <f t="shared" si="24"/>
@@ -17025,172 +17026,172 @@
     <sortCondition ref="F1:F365"/>
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="A1:I1">
+    <cfRule type="duplicateValues" dxfId="65" priority="1501"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E2:E237">
-    <cfRule type="duplicateValues" dxfId="65" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E348">
-    <cfRule type="duplicateValues" dxfId="64" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E424">
-    <cfRule type="duplicateValues" dxfId="63" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E425:E431 E433:E443 E2:E423">
-    <cfRule type="duplicateValues" dxfId="62" priority="15"/>
     <cfRule type="duplicateValues" dxfId="61" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E432">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E444:E1048576">
-    <cfRule type="duplicateValues" dxfId="59" priority="1498"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="1499"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="1500"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="1500"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1499"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1498"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F308">
-    <cfRule type="duplicateValues" dxfId="56" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F346:F378 F321 F247:F279 F281 F284:F292 F294:F307 F323:F336 F309:F319 F2:F187 F338:F344 F380:F423">
-    <cfRule type="duplicateValues" dxfId="55" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F379">
-    <cfRule type="duplicateValues" dxfId="54" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F425:F443">
-    <cfRule type="duplicateValues" dxfId="53" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F444:F1048576">
-    <cfRule type="duplicateValues" dxfId="51" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F424:G424">
-    <cfRule type="duplicateValues" dxfId="50" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G416 G418 G420:G423">
-    <cfRule type="duplicateValues" dxfId="48" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="duplicateValues" dxfId="47" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="duplicateValues" dxfId="46" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G93">
-    <cfRule type="duplicateValues" dxfId="45" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G126">
-    <cfRule type="duplicateValues" dxfId="44" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G142">
-    <cfRule type="duplicateValues" dxfId="43" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G154">
-    <cfRule type="duplicateValues" dxfId="42" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G155">
-    <cfRule type="duplicateValues" dxfId="41" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G156">
-    <cfRule type="duplicateValues" dxfId="40" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G164">
-    <cfRule type="duplicateValues" dxfId="39" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G284">
-    <cfRule type="duplicateValues" dxfId="38" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G294">
-    <cfRule type="duplicateValues" dxfId="37" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G295">
-    <cfRule type="duplicateValues" dxfId="36" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G296">
-    <cfRule type="duplicateValues" dxfId="35" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G300">
-    <cfRule type="duplicateValues" dxfId="34" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G303:G304 G307:G308">
-    <cfRule type="duplicateValues" dxfId="33" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G305">
-    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G306">
-    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G312">
-    <cfRule type="duplicateValues" dxfId="30" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G313">
-    <cfRule type="duplicateValues" dxfId="29" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G321">
-    <cfRule type="duplicateValues" dxfId="28" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G323">
-    <cfRule type="duplicateValues" dxfId="27" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G338">
-    <cfRule type="duplicateValues" dxfId="26" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G339">
-    <cfRule type="duplicateValues" dxfId="25" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G340">
-    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G341">
-    <cfRule type="duplicateValues" dxfId="23" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G343">
-    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G344">
-    <cfRule type="duplicateValues" dxfId="21" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G346">
-    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G347">
-    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G348">
-    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G349:G350">
-    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G356:G359">
-    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G363">
-    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G364">
-    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G366:G371">
-    <cfRule type="duplicateValues" dxfId="13" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G417">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G425:G433 G436:G443">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G434">
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G435">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
     <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:I1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1501"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -18507,33 +18508,25 @@
   <autoFilter ref="C1:F58" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B3 A4:A44 A49:A58">
-    <cfRule type="duplicateValues" dxfId="4" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B6 B8:B9 B11:B12 B14:B15 B17:B18 B20:B21 B23:B24 B26:B27 B29:B30 B32:B33 B35:B36 B38:B39 B41:B42 B44:B45 B47:B48">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207:C243 B1:C1 B622:C1048576 B277:C487">
-    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="1" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <pixelatorList sheetStid="1"/>
-  <pixelatorList sheetStid="2"/>
-  <pixelatorList sheetStid="3"/>
-</pixelators>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <woProps xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <woSheetsProps>
     <woSheetProps sheetStid="1" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
@@ -18551,8 +18544,16 @@
 </woProps>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <pixelatorList sheetStid="1"/>
+  <pixelatorList sheetStid="2"/>
+  <pixelatorList sheetStid="3"/>
+</pixelators>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
@@ -18561,7 +18562,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>

--- a/模块开发/录入表.xlsx
+++ b/模块开发/录入表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentli/PycharmProjects/PythonProject/2026-4 群控/yolo/整合详情页采集/模块开发/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53FFF88-DD4E-8249-9EF7-5EBD868B2FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F53C59D-5B0B-3F4A-BAB9-3A7D5DA86B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19940" yWindow="1200" windowWidth="29820" windowHeight="25020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42340" yWindow="-4380" windowWidth="28800" windowHeight="19680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="单支" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="1420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="1422">
   <si>
     <t>商品条码</t>
   </si>
@@ -4343,6 +4343,12 @@
   <si>
     <t>没有合适的商品</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>729238222939</t>
+  </si>
+  <si>
+    <t>资生堂 小针管眼霜（新款）20mL</t>
   </si>
 </sst>
 </file>
@@ -4538,7 +4544,67 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="87">
+  <dxfs count="93">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -5295,25 +5361,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
     <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{3AD70849-3F6B-ADC2-5487-646933379502}">
-      <tableStyleElement type="wholeTable" dxfId="86"/>
+      <tableStyleElement type="wholeTable" dxfId="92"/>
+      <tableStyleElement type="headerRow" dxfId="91"/>
+      <tableStyleElement type="totalRow" dxfId="90"/>
+      <tableStyleElement type="firstColumn" dxfId="89"/>
+      <tableStyleElement type="lastColumn" dxfId="88"/>
+      <tableStyleElement type="firstRowStripe" dxfId="87"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="86"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{B0E6D76F-EA8E-7237-5487-6469988B1DE4}">
       <tableStyleElement type="headerRow" dxfId="85"/>
       <tableStyleElement type="totalRow" dxfId="84"/>
-      <tableStyleElement type="firstColumn" dxfId="83"/>
-      <tableStyleElement type="lastColumn" dxfId="82"/>
-      <tableStyleElement type="firstRowStripe" dxfId="81"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="80"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{B0E6D76F-EA8E-7237-5487-6469988B1DE4}">
-      <tableStyleElement type="headerRow" dxfId="79"/>
-      <tableStyleElement type="totalRow" dxfId="78"/>
-      <tableStyleElement type="firstRowStripe" dxfId="77"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="76"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="75"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="74"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="73"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="72"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="71"/>
-      <tableStyleElement type="pageFieldValues" dxfId="70"/>
+      <tableStyleElement type="firstRowStripe" dxfId="83"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="82"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="81"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="80"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="79"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="78"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="77"/>
+      <tableStyleElement type="pageFieldValues" dxfId="76"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -5593,7 +5659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I444"/>
+  <dimension ref="A1:I445"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="8.33203125" customWidth="1"/>
@@ -17126,6 +17192,27 @@
         <v>443</v>
       </c>
     </row>
+    <row r="445" spans="1:9" ht="15">
+      <c r="C445" s="24" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E445" s="16" t="s">
+        <v>1420</v>
+      </c>
+      <c r="F445" s="16" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G445" s="16" t="s">
+        <v>725</v>
+      </c>
+      <c r="H445" s="4">
+        <f t="shared" ref="H445" si="25">D445+1095</f>
+        <v>1095</v>
+      </c>
+      <c r="I445" s="10">
+        <v>444</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <autoFilter ref="A1:I444" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -17134,179 +17221,191 @@
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:I1">
-    <cfRule type="duplicateValues" dxfId="68" priority="1505"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="1511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E12 E14:E238">
-    <cfRule type="duplicateValues" dxfId="67" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="66" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E349">
-    <cfRule type="duplicateValues" dxfId="63" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E425">
-    <cfRule type="duplicateValues" dxfId="62" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E426:E432 E434:E444 E2:E12 E14:E424">
-    <cfRule type="duplicateValues" dxfId="61" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E433">
-    <cfRule type="duplicateValues" dxfId="59" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E445:E1048576">
-    <cfRule type="duplicateValues" dxfId="58" priority="1504"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="1503"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="1502"/>
+  <conditionalFormatting sqref="E446:E1048576">
+    <cfRule type="duplicateValues" dxfId="64" priority="1510"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1509"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="1508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F309">
-    <cfRule type="duplicateValues" dxfId="55" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F347:F379 F322 F248:F280 F282 F285:F293 F295:F308 F324:F337 F310:F320 F2:F12 F339:F345 F381:F424 F14:F188">
-    <cfRule type="duplicateValues" dxfId="54" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F380">
-    <cfRule type="duplicateValues" dxfId="53" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F426:F444">
-    <cfRule type="duplicateValues" dxfId="52" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F445:F1048576">
-    <cfRule type="duplicateValues" dxfId="50" priority="189"/>
+  <conditionalFormatting sqref="F446:F1048576">
+    <cfRule type="duplicateValues" dxfId="56" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F425:G425">
-    <cfRule type="duplicateValues" dxfId="49" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G12 G419 G421:G424 G14:G417">
-    <cfRule type="duplicateValues" dxfId="47" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14">
-    <cfRule type="duplicateValues" dxfId="45" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G94">
-    <cfRule type="duplicateValues" dxfId="44" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G127">
-    <cfRule type="duplicateValues" dxfId="43" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G143">
-    <cfRule type="duplicateValues" dxfId="42" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G155">
-    <cfRule type="duplicateValues" dxfId="41" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G156">
-    <cfRule type="duplicateValues" dxfId="40" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G157">
-    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G165">
-    <cfRule type="duplicateValues" dxfId="38" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G285">
-    <cfRule type="duplicateValues" dxfId="37" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G295">
-    <cfRule type="duplicateValues" dxfId="36" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G296">
-    <cfRule type="duplicateValues" dxfId="35" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G297">
-    <cfRule type="duplicateValues" dxfId="34" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G301">
-    <cfRule type="duplicateValues" dxfId="33" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G304:G305 G308:G309">
-    <cfRule type="duplicateValues" dxfId="32" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G306">
-    <cfRule type="duplicateValues" dxfId="31" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G307">
-    <cfRule type="duplicateValues" dxfId="30" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G313">
-    <cfRule type="duplicateValues" dxfId="29" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G314">
+    <cfRule type="duplicateValues" dxfId="34" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G322">
+    <cfRule type="duplicateValues" dxfId="33" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G324">
+    <cfRule type="duplicateValues" dxfId="32" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G339">
+    <cfRule type="duplicateValues" dxfId="31" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G340">
+    <cfRule type="duplicateValues" dxfId="30" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G341">
+    <cfRule type="duplicateValues" dxfId="29" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G342">
     <cfRule type="duplicateValues" dxfId="28" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G322">
-    <cfRule type="duplicateValues" dxfId="27" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G324">
-    <cfRule type="duplicateValues" dxfId="26" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G339">
-    <cfRule type="duplicateValues" dxfId="25" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G340">
-    <cfRule type="duplicateValues" dxfId="24" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G341">
-    <cfRule type="duplicateValues" dxfId="23" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G342">
-    <cfRule type="duplicateValues" dxfId="22" priority="40"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G344">
-    <cfRule type="duplicateValues" dxfId="21" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G345">
-    <cfRule type="duplicateValues" dxfId="20" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G347">
-    <cfRule type="duplicateValues" dxfId="19" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G348">
-    <cfRule type="duplicateValues" dxfId="18" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G349">
-    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G350:G351">
-    <cfRule type="duplicateValues" dxfId="16" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G357:G360">
-    <cfRule type="duplicateValues" dxfId="15" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G364">
-    <cfRule type="duplicateValues" dxfId="14" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G365">
-    <cfRule type="duplicateValues" dxfId="13" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G367:G372">
-    <cfRule type="duplicateValues" dxfId="12" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G418">
-    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G426:G434 G437:G444">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G435">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G436">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E445">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F445">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G445">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -18623,19 +18722,19 @@
   <autoFilter ref="C1:F58" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B3 A4:A44 A49:A58">
-    <cfRule type="duplicateValues" dxfId="3" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B6 B8:B9 B11:B12 B14:B15 B17:B18 B20:B21 B23:B24 B26:B27 B29:B30 B32:B33 B35:B36 B38:B39 B41:B42 B44:B45 B47:B48">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207:C243 B1:C1 B622:C1048576 B277:C487">
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="154"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/模块开发/录入表.xlsx
+++ b/模块开发/录入表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentli/PycharmProjects/PythonProject/2026-4 群控/yolo/整合详情页采集/模块开发/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F53C59D-5B0B-3F4A-BAB9-3A7D5DA86B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F12739-FCBA-5945-A699-AE9729D62577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42340" yWindow="-4380" windowWidth="28800" windowHeight="19680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43200" yWindow="-5620" windowWidth="28800" windowHeight="19680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="单支" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="1422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="1424">
   <si>
     <t>商品条码</t>
   </si>
@@ -4307,48 +4307,53 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>194251000374</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>888066106139</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>生产日期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">否 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hermes爱马仕大地淡香对装50ml*2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>194251070384</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NARS 超方瓶粉底液#L2</t>
+  </si>
+  <si>
+    <t>NARS超方瓶粉底液L2</t>
+  </si>
+  <si>
+    <t>729238222939</t>
+  </si>
+  <si>
+    <t>资生堂 小针管眼霜（新款）20mL</t>
+  </si>
+  <si>
     <t>上次价格</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>194251000374</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>888066106139</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>生产日期</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">否 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hermes爱马仕大地淡香对装50ml*2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>194251070384</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>NARS 超方瓶粉底液#L2</t>
-  </si>
-  <si>
-    <t>NARS超方瓶粉底液L2</t>
-  </si>
-  <si>
-    <t>没有合适的商品</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>729238222939</t>
-  </si>
-  <si>
-    <t>资生堂 小针管眼霜（新款）20mL</t>
+    <t>729238220089</t>
+  </si>
+  <si>
+    <t>资生堂 蓝胖子防晒乳霜（新款）50mL</t>
+  </si>
+  <si>
+    <t>资生堂蓝胖子（新款）50ml</t>
   </si>
 </sst>
 </file>
@@ -4358,7 +4363,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -4405,14 +4410,6 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -4454,7 +4451,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4537,21 +4534,43 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="93">
+  <dxfs count="99">
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4592,51 +4611,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5020,6 +4994,46 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFF9900"/>
@@ -5037,6 +5051,46 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5102,19 +5156,19 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5361,25 +5415,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
     <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{3AD70849-3F6B-ADC2-5487-646933379502}">
-      <tableStyleElement type="wholeTable" dxfId="92"/>
+      <tableStyleElement type="wholeTable" dxfId="98"/>
+      <tableStyleElement type="headerRow" dxfId="97"/>
+      <tableStyleElement type="totalRow" dxfId="96"/>
+      <tableStyleElement type="firstColumn" dxfId="95"/>
+      <tableStyleElement type="lastColumn" dxfId="94"/>
+      <tableStyleElement type="firstRowStripe" dxfId="93"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="92"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{B0E6D76F-EA8E-7237-5487-6469988B1DE4}">
       <tableStyleElement type="headerRow" dxfId="91"/>
       <tableStyleElement type="totalRow" dxfId="90"/>
-      <tableStyleElement type="firstColumn" dxfId="89"/>
-      <tableStyleElement type="lastColumn" dxfId="88"/>
-      <tableStyleElement type="firstRowStripe" dxfId="87"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="86"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{B0E6D76F-EA8E-7237-5487-6469988B1DE4}">
-      <tableStyleElement type="headerRow" dxfId="85"/>
-      <tableStyleElement type="totalRow" dxfId="84"/>
-      <tableStyleElement type="firstRowStripe" dxfId="83"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="82"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="81"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="80"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="79"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="78"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="77"/>
-      <tableStyleElement type="pageFieldValues" dxfId="76"/>
+      <tableStyleElement type="firstRowStripe" dxfId="89"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="88"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="87"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="86"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="85"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="84"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="83"/>
+      <tableStyleElement type="pageFieldValues" dxfId="82"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -5659,7 +5713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I445"/>
+  <dimension ref="A1:I446"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="8.33203125" customWidth="1"/>
@@ -5674,7 +5728,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>909</v>
@@ -5683,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1347</v>
@@ -5702,12 +5756,12 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="15">
-      <c r="A2">
-        <v>348</v>
+      <c r="A2" s="20">
+        <v>320</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="24" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="D2" s="27"/>
       <c r="E2" s="15" t="s">
@@ -5728,8 +5782,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15">
-      <c r="A3">
-        <v>249.5</v>
+      <c r="A3" s="20">
+        <v>200</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="24" t="s">
@@ -5754,8 +5808,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
-      <c r="A4">
-        <v>308</v>
+      <c r="A4" s="20">
+        <v>380</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="24" t="s">
@@ -5780,8 +5834,8 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
-      <c r="A5">
-        <v>225</v>
+      <c r="A5" s="20">
+        <v>184</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="24" t="s">
@@ -5806,8 +5860,8 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
-      <c r="A6">
-        <v>149</v>
+      <c r="A6" s="20">
+        <v>128</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="24" t="s">
@@ -5832,8 +5886,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
-      <c r="A7">
-        <v>81</v>
+      <c r="A7" s="20">
+        <v>72</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="24" t="s">
@@ -5858,8 +5912,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
-      <c r="A8">
-        <v>148</v>
+      <c r="A8" s="20">
+        <v>130</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="24" t="s">
@@ -5884,8 +5938,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
-      <c r="A9">
-        <v>397</v>
+      <c r="A9" s="20">
+        <v>472</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="24" t="s">
@@ -5910,8 +5964,8 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
-      <c r="A10">
-        <v>199</v>
+      <c r="A10" s="20">
+        <v>290</v>
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="24" t="s">
@@ -5936,8 +5990,8 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
-      <c r="A11">
-        <v>324</v>
+      <c r="A11" s="20">
+        <v>156</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="24" t="s">
@@ -5962,8 +6016,8 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
-      <c r="A12">
-        <v>176.3</v>
+      <c r="A12" s="20">
+        <v>169</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="24" t="s">
@@ -5988,19 +6042,22 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
+      <c r="A13" s="20">
+        <v>219</v>
+      </c>
       <c r="B13" s="20"/>
       <c r="C13" s="24" t="s">
         <v>1408</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="15" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>1416</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="G13" s="11" t="s">
         <v>1417</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>1418</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="1"/>
@@ -6011,8 +6068,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
-      <c r="A14">
-        <v>278</v>
+      <c r="A14" s="20">
+        <v>210</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="24" t="s">
@@ -6037,8 +6094,8 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
-      <c r="A15">
-        <v>245</v>
+      <c r="A15" s="20">
+        <v>152.5</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="24" t="s">
@@ -6063,7 +6120,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
-      <c r="A16">
+      <c r="A16" s="20">
         <v>84.9</v>
       </c>
       <c r="B16" s="23"/>
@@ -6088,8 +6145,8 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
-      <c r="A17">
-        <v>188</v>
+      <c r="A17" s="20">
+        <v>156</v>
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="24" t="s">
@@ -6114,8 +6171,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
-      <c r="A18">
-        <v>218</v>
+      <c r="A18" s="20">
+        <v>179</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="24" t="s">
@@ -6140,7 +6197,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
-      <c r="A19">
+      <c r="A19" s="20">
         <v>88</v>
       </c>
       <c r="B19" s="23"/>
@@ -6166,8 +6223,8 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
-      <c r="A20">
-        <v>69.8</v>
+      <c r="A20" s="20">
+        <v>63.8</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="24" t="s">
@@ -6175,7 +6232,7 @@
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="15" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>93</v>
@@ -6192,8 +6249,8 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
-      <c r="A21">
-        <v>99</v>
+      <c r="A21" s="20">
+        <v>53.9</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="24" t="s">
@@ -6218,8 +6275,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
-      <c r="A22">
-        <v>59.9</v>
+      <c r="A22" s="20">
+        <v>53.9</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="24" t="s">
@@ -6244,8 +6301,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
-      <c r="A23">
-        <v>59.9</v>
+      <c r="A23" s="20">
+        <v>79.8</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="24" t="s">
@@ -6270,8 +6327,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
-      <c r="A24">
-        <v>17.899999999999999</v>
+      <c r="A24" s="20">
+        <v>18</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="24" t="s">
@@ -6296,8 +6353,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
-      <c r="A25">
-        <v>847</v>
+      <c r="A25" s="20">
+        <v>859</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="24" t="s">
@@ -6322,8 +6379,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
-      <c r="A26">
-        <v>959</v>
+      <c r="A26" s="20">
+        <v>949</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="24" t="s">
@@ -6348,8 +6405,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
-      <c r="A27">
-        <v>1098</v>
+      <c r="A27" s="20">
+        <v>948</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="24" t="s">
@@ -6374,8 +6431,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
-      <c r="A28">
-        <v>245</v>
+      <c r="A28" s="20">
+        <v>285</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="24" t="s">
@@ -6400,8 +6457,8 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
-      <c r="A29">
-        <v>847</v>
+      <c r="A29" s="20">
+        <v>999</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="24" t="s">
@@ -6426,7 +6483,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
-      <c r="A30">
+      <c r="A30" s="20">
         <v>2290</v>
       </c>
       <c r="B30" s="20"/>
@@ -6452,8 +6509,8 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
-      <c r="A31">
-        <v>1200</v>
+      <c r="A31" s="20">
+        <v>2290</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="24" t="s">
@@ -6478,8 +6535,8 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
-      <c r="A32">
-        <v>2598</v>
+      <c r="A32" s="20">
+        <v>2560</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="24" t="s">
@@ -6504,8 +6561,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
-      <c r="A33">
-        <v>1788</v>
+      <c r="A33" s="20">
+        <v>1430</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="24" t="s">
@@ -6530,8 +6587,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
-      <c r="A34">
-        <v>164</v>
+      <c r="A34" s="20">
+        <v>245</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="24" t="s">
@@ -6539,7 +6596,7 @@
       </c>
       <c r="D34" s="20"/>
       <c r="E34" s="15" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>149</v>
@@ -6556,8 +6613,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
-      <c r="A35">
-        <v>151</v>
+      <c r="A35" s="20">
+        <v>86.5</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="24" t="s">
@@ -6582,8 +6639,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
-      <c r="A36">
-        <v>298</v>
+      <c r="A36" s="20">
+        <v>310</v>
       </c>
       <c r="B36" s="20"/>
       <c r="C36" s="24" t="s">
@@ -6608,8 +6665,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
-      <c r="A37" t="s">
-        <v>1419</v>
+      <c r="A37" s="20">
+        <v>615</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="24" t="s">
@@ -6634,8 +6691,8 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
-      <c r="A38">
-        <v>197</v>
+      <c r="A38" s="20">
+        <v>166</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="24" t="s">
@@ -6660,8 +6717,8 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
-      <c r="A39">
-        <v>1519.99</v>
+      <c r="A39" s="20">
+        <v>2988</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="24" t="s">
@@ -6686,8 +6743,8 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
-      <c r="A40">
-        <v>183</v>
+      <c r="A40" s="20">
+        <v>213</v>
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="24" t="s">
@@ -6712,8 +6769,8 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
-      <c r="A41">
-        <v>41.89</v>
+      <c r="A41" s="20">
+        <v>22.22</v>
       </c>
       <c r="B41" s="22"/>
       <c r="C41" s="24" t="s">
@@ -6738,8 +6795,8 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
-      <c r="A42">
-        <v>138</v>
+      <c r="A42" s="20">
+        <v>125</v>
       </c>
       <c r="B42" s="23"/>
       <c r="C42" s="24" t="s">
@@ -6763,7 +6820,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
-      <c r="A43">
+      <c r="A43" s="20">
         <v>158</v>
       </c>
       <c r="B43" s="20"/>
@@ -6789,8 +6846,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
-      <c r="A44">
-        <v>146</v>
+      <c r="A44" s="20">
+        <v>121.3</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="24" t="s">
@@ -6815,8 +6872,8 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
-      <c r="A45">
-        <v>489</v>
+      <c r="A45" s="20">
+        <v>544</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="24" t="s">
@@ -6841,8 +6898,8 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
-      <c r="A46">
-        <v>243</v>
+      <c r="A46" s="20">
+        <v>328</v>
       </c>
       <c r="B46" s="22"/>
       <c r="C46" s="24" t="s">
@@ -6867,8 +6924,8 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
-      <c r="A47">
-        <v>458</v>
+      <c r="A47" s="20">
+        <v>696</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="24" t="s">
@@ -6893,8 +6950,8 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
-      <c r="A48">
-        <v>283.5</v>
+      <c r="A48" s="20">
+        <v>293.89999999999998</v>
       </c>
       <c r="B48" s="22"/>
       <c r="C48" s="24" t="s">
@@ -6919,8 +6976,8 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
-      <c r="A49">
-        <v>444.9</v>
+      <c r="A49" s="20">
+        <v>393</v>
       </c>
       <c r="B49" s="22"/>
       <c r="C49" s="24" t="s">
@@ -6945,8 +7002,8 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
-      <c r="A50">
-        <v>268</v>
+      <c r="A50" s="20">
+        <v>265</v>
       </c>
       <c r="C50" s="24" t="s">
         <v>1408</v>
@@ -6970,8 +7027,8 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
-      <c r="A51">
-        <v>289</v>
+      <c r="A51" s="20">
+        <v>305</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="24" t="s">
@@ -6996,8 +7053,8 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
-      <c r="A52">
-        <v>298</v>
+      <c r="A52" s="20">
+        <v>388</v>
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="24" t="s">
@@ -7022,8 +7079,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
-      <c r="A53">
-        <v>377.88</v>
+      <c r="A53" s="20">
+        <v>388</v>
       </c>
       <c r="B53" s="22"/>
       <c r="C53" s="24" t="s">
@@ -7048,8 +7105,8 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
-      <c r="A54">
-        <v>135</v>
+      <c r="A54" s="20">
+        <v>170</v>
       </c>
       <c r="B54" s="22"/>
       <c r="C54" s="24" t="s">
@@ -7074,8 +7131,8 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
-      <c r="A55">
-        <v>500.4</v>
+      <c r="A55" s="20">
+        <v>438</v>
       </c>
       <c r="B55" s="22"/>
       <c r="C55" s="24" t="s">
@@ -7100,8 +7157,8 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
-      <c r="A56">
-        <v>699</v>
+      <c r="A56" s="20">
+        <v>459</v>
       </c>
       <c r="B56" s="20"/>
       <c r="C56" s="24" t="s">
@@ -7126,8 +7183,8 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
-      <c r="A57">
-        <v>749</v>
+      <c r="A57" s="20">
+        <v>798</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="24" t="s">
@@ -7152,7 +7209,7 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
-      <c r="A58">
+      <c r="A58" s="20">
         <v>379</v>
       </c>
       <c r="B58" s="20"/>
@@ -7178,8 +7235,8 @@
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
-      <c r="A59">
-        <v>238</v>
+      <c r="A59" s="20">
+        <v>250</v>
       </c>
       <c r="B59" s="20"/>
       <c r="C59" s="24" t="s">
@@ -7204,7 +7261,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
-      <c r="A60">
+      <c r="A60" s="20">
         <v>266</v>
       </c>
       <c r="B60" s="20"/>
@@ -7230,8 +7287,8 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
-      <c r="A61">
-        <v>400</v>
+      <c r="A61" s="20">
+        <v>230</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="24" t="s">
@@ -7256,7 +7313,7 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
-      <c r="A62">
+      <c r="A62" s="20">
         <v>98.99</v>
       </c>
       <c r="B62" s="20"/>
@@ -7282,8 +7339,8 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
-      <c r="A63">
-        <v>299</v>
+      <c r="A63" s="20">
+        <v>219</v>
       </c>
       <c r="B63" s="22"/>
       <c r="C63" s="24" t="s">
@@ -7308,8 +7365,8 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
-      <c r="A64">
-        <v>145</v>
+      <c r="A64" s="20">
+        <v>146</v>
       </c>
       <c r="B64" s="22"/>
       <c r="C64" s="24" t="s">
@@ -7334,8 +7391,8 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
-      <c r="A65">
-        <v>68</v>
+      <c r="A65" s="20">
+        <v>63</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="24" t="s">
@@ -7360,8 +7417,8 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
-      <c r="A66">
-        <v>299</v>
+      <c r="A66" s="20">
+        <v>175</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="24" t="s">
@@ -7386,8 +7443,8 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
-      <c r="A67">
-        <v>198</v>
+      <c r="A67" s="20">
+        <v>196</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="24" t="s">
@@ -7412,7 +7469,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
-      <c r="A68">
+      <c r="A68" s="20">
         <v>295</v>
       </c>
       <c r="B68" s="20"/>
@@ -7438,8 +7495,8 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
-      <c r="A69">
-        <v>350</v>
+      <c r="A69" s="20">
+        <v>249</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="24" t="s">
@@ -7464,8 +7521,8 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
-      <c r="A70">
-        <v>1970</v>
+      <c r="A70" s="20">
+        <v>753</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="24" t="s">
@@ -7490,8 +7547,8 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
-      <c r="A71">
-        <v>199</v>
+      <c r="A71" s="20">
+        <v>160</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="24" t="s">
@@ -7516,7 +7573,7 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
-      <c r="A72">
+      <c r="A72" s="20">
         <v>121</v>
       </c>
       <c r="B72" s="20"/>
@@ -7542,8 +7599,8 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
-      <c r="A73">
-        <v>118</v>
+      <c r="A73" s="20">
+        <v>91</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="24" t="s">
@@ -7568,8 +7625,8 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
-      <c r="A74">
-        <v>99</v>
+      <c r="A74" s="20">
+        <v>107.91</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="24" t="s">
@@ -7594,8 +7651,8 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
-      <c r="A75">
-        <v>145</v>
+      <c r="A75" s="20">
+        <v>89</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="24" t="s">
@@ -7620,8 +7677,8 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
-      <c r="A76">
-        <v>580</v>
+      <c r="A76" s="20">
+        <v>235</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="24" t="s">
@@ -7646,8 +7703,8 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
-      <c r="A77">
-        <v>218</v>
+      <c r="A77" s="20">
+        <v>218.99</v>
       </c>
       <c r="B77" s="20"/>
       <c r="C77" s="24" t="s">
@@ -7672,8 +7729,8 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
-      <c r="A78">
-        <v>580</v>
+      <c r="A78" s="20">
+        <v>235</v>
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="24" t="s">
@@ -7698,8 +7755,8 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
-      <c r="A79">
-        <v>218.97</v>
+      <c r="A79" s="20">
+        <v>218.99</v>
       </c>
       <c r="B79" s="20"/>
       <c r="C79" s="24" t="s">
@@ -7724,8 +7781,8 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
-      <c r="A80">
-        <v>305</v>
+      <c r="A80" s="20">
+        <v>235</v>
       </c>
       <c r="B80" s="20"/>
       <c r="C80" s="24" t="s">
@@ -7750,8 +7807,8 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
-      <c r="A81">
-        <v>169</v>
+      <c r="A81" s="20">
+        <v>159</v>
       </c>
       <c r="B81" s="20"/>
       <c r="C81" s="24" t="s">
@@ -7776,8 +7833,8 @@
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
-      <c r="A82">
-        <v>102.7</v>
+      <c r="A82" s="20">
+        <v>94</v>
       </c>
       <c r="B82" s="20"/>
       <c r="C82" s="24" t="s">
@@ -7802,8 +7859,8 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
-      <c r="A83">
-        <v>129.99</v>
+      <c r="A83" s="20">
+        <v>99</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="24" t="s">
@@ -7828,8 +7885,8 @@
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
-      <c r="A84">
-        <v>149</v>
+      <c r="A84" s="20">
+        <v>169</v>
       </c>
       <c r="B84" s="20"/>
       <c r="C84" s="24" t="s">
@@ -7854,8 +7911,8 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
-      <c r="A85">
-        <v>175</v>
+      <c r="A85" s="20">
+        <v>159</v>
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="24" t="s">
@@ -7880,8 +7937,8 @@
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
-      <c r="A86">
-        <v>289</v>
+      <c r="A86" s="20">
+        <v>165</v>
       </c>
       <c r="B86" s="20"/>
       <c r="C86" s="24" t="s">
@@ -7906,8 +7963,8 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
-      <c r="A87">
-        <v>104.09</v>
+      <c r="A87" s="20">
+        <v>94.99</v>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="24" t="s">
@@ -7932,8 +7989,8 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
-      <c r="A88">
-        <v>199.5</v>
+      <c r="A88" s="20">
+        <v>128.80000000000001</v>
       </c>
       <c r="B88" s="20"/>
       <c r="C88" s="24" t="s">
@@ -7958,8 +8015,8 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
-      <c r="A89">
-        <v>69.900000000000006</v>
+      <c r="A89" s="20">
+        <v>78</v>
       </c>
       <c r="B89" s="20"/>
       <c r="C89" s="24" t="s">
@@ -7984,8 +8041,8 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
-      <c r="A90">
-        <v>93.2</v>
+      <c r="A90" s="20">
+        <v>52.2</v>
       </c>
       <c r="B90" s="20"/>
       <c r="C90" s="24" t="s">
@@ -8010,8 +8067,8 @@
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
-      <c r="A91">
-        <v>374</v>
+      <c r="A91" s="20">
+        <v>388</v>
       </c>
       <c r="B91" s="22"/>
       <c r="C91" s="24" t="s">
@@ -8036,8 +8093,8 @@
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
-      <c r="A92">
-        <v>168</v>
+      <c r="A92" s="20">
+        <v>165</v>
       </c>
       <c r="B92" s="20"/>
       <c r="C92" s="24" t="s">
@@ -8062,8 +8119,8 @@
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
-      <c r="A93">
-        <v>123</v>
+      <c r="A93" s="20">
+        <v>199</v>
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="24" t="s">
@@ -8088,8 +8145,8 @@
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
-      <c r="A94">
-        <v>266</v>
+      <c r="A94" s="20">
+        <v>183</v>
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="24" t="s">
@@ -8114,8 +8171,8 @@
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
-      <c r="A95">
-        <v>179</v>
+      <c r="A95" s="20">
+        <v>188</v>
       </c>
       <c r="B95" s="20"/>
       <c r="C95" s="24" t="s">
@@ -8140,8 +8197,8 @@
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
-      <c r="A96">
-        <v>200</v>
+      <c r="A96" s="20">
+        <v>189</v>
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="24" t="s">
@@ -8166,8 +8223,8 @@
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
-      <c r="A97">
-        <v>148.28</v>
+      <c r="A97" s="20">
+        <v>189</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="24" t="s">
@@ -8192,8 +8249,8 @@
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
-      <c r="A98">
-        <v>338</v>
+      <c r="A98" s="20">
+        <v>299</v>
       </c>
       <c r="B98" s="20"/>
       <c r="C98" s="24" t="s">
@@ -8218,8 +8275,8 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
-      <c r="A99">
-        <v>389</v>
+      <c r="A99" s="20">
+        <v>279</v>
       </c>
       <c r="B99" s="20"/>
       <c r="C99" s="24" t="s">
@@ -8244,8 +8301,8 @@
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
-      <c r="A100">
-        <v>273</v>
+      <c r="A100" s="20">
+        <v>292</v>
       </c>
       <c r="B100" s="20"/>
       <c r="C100" s="24" t="s">
@@ -8270,8 +8327,8 @@
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
-      <c r="A101">
-        <v>799.5</v>
+      <c r="A101" s="20">
+        <v>999</v>
       </c>
       <c r="B101" s="20"/>
       <c r="C101" s="24" t="s">
@@ -8296,8 +8353,8 @@
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
-      <c r="A102">
-        <v>880</v>
+      <c r="A102" s="20">
+        <v>568</v>
       </c>
       <c r="B102" s="20"/>
       <c r="C102" s="24" t="s">
@@ -8322,8 +8379,8 @@
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
-      <c r="A103">
-        <v>1239</v>
+      <c r="A103" s="20">
+        <v>1777</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="24" t="s">
@@ -8348,8 +8405,8 @@
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
-      <c r="A104">
-        <v>776.8</v>
+      <c r="A104" s="20">
+        <v>799</v>
       </c>
       <c r="B104" s="20"/>
       <c r="C104" s="24" t="s">
@@ -8374,8 +8431,8 @@
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
-      <c r="A105">
-        <v>2700</v>
+      <c r="A105" s="20">
+        <v>2099</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="24" t="s">
@@ -8400,8 +8457,8 @@
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
-      <c r="A106">
-        <v>798</v>
+      <c r="A106" s="20">
+        <v>809</v>
       </c>
       <c r="B106" s="20"/>
       <c r="C106" s="24" t="s">
@@ -8426,8 +8483,8 @@
       </c>
     </row>
     <row r="107" spans="1:9" ht="15">
-      <c r="A107">
-        <v>1855</v>
+      <c r="A107" s="20">
+        <v>1675</v>
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="24" t="s">
@@ -8452,8 +8509,8 @@
       </c>
     </row>
     <row r="108" spans="1:9" ht="15">
-      <c r="A108">
-        <v>2784</v>
+      <c r="A108" s="20">
+        <v>2676</v>
       </c>
       <c r="B108" s="20"/>
       <c r="C108" s="24" t="s">
@@ -8478,9 +8535,7 @@
       </c>
     </row>
     <row r="109" spans="1:9" ht="15">
-      <c r="A109" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A109" s="20"/>
       <c r="B109" s="23"/>
       <c r="C109" s="24" t="s">
         <v>1408</v>
@@ -8503,8 +8558,8 @@
       </c>
     </row>
     <row r="110" spans="1:9" ht="15">
-      <c r="A110">
-        <v>818</v>
+      <c r="A110" s="20">
+        <v>999</v>
       </c>
       <c r="B110" s="20"/>
       <c r="C110" s="24" t="s">
@@ -8529,8 +8584,8 @@
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
-      <c r="A111">
-        <v>1484</v>
+      <c r="A111" s="20">
+        <v>1844</v>
       </c>
       <c r="B111" s="22"/>
       <c r="C111" s="24" t="s">
@@ -8555,8 +8610,8 @@
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
-      <c r="A112">
-        <v>1000</v>
+      <c r="A112" s="20">
+        <v>899</v>
       </c>
       <c r="B112" s="20"/>
       <c r="C112" s="24" t="s">
@@ -8581,8 +8636,8 @@
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
-      <c r="A113">
-        <v>140.19999999999999</v>
+      <c r="A113" s="20">
+        <v>96.8</v>
       </c>
       <c r="B113" s="20"/>
       <c r="C113" s="24" t="s">
@@ -8607,8 +8662,8 @@
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
-      <c r="A114">
-        <v>81.099999999999994</v>
+      <c r="A114" s="20">
+        <v>63.3</v>
       </c>
       <c r="B114" s="20"/>
       <c r="C114" s="24" t="s">
@@ -8633,8 +8688,8 @@
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
-      <c r="A115">
-        <v>99</v>
+      <c r="A115" s="20">
+        <v>77.599999999999994</v>
       </c>
       <c r="B115" s="20"/>
       <c r="C115" s="24" t="s">
@@ -8659,7 +8714,7 @@
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
-      <c r="A116">
+      <c r="A116" s="20">
         <v>105.6</v>
       </c>
       <c r="B116" s="20"/>
@@ -8685,8 +8740,8 @@
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
-      <c r="A117">
-        <v>98.4</v>
+      <c r="A117" s="20">
+        <v>94</v>
       </c>
       <c r="B117" s="20"/>
       <c r="C117" s="24" t="s">
@@ -8711,8 +8766,8 @@
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
-      <c r="A118">
-        <v>115</v>
+      <c r="A118" s="20">
+        <v>94.3</v>
       </c>
       <c r="B118" s="20"/>
       <c r="C118" s="24" t="s">
@@ -8737,8 +8792,8 @@
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
-      <c r="A119">
-        <v>215</v>
+      <c r="A119" s="20">
+        <v>199</v>
       </c>
       <c r="B119" s="20"/>
       <c r="C119" s="24" t="s">
@@ -8763,8 +8818,8 @@
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
-      <c r="A120">
-        <v>93.2</v>
+      <c r="A120" s="20">
+        <v>61.56</v>
       </c>
       <c r="B120" s="20"/>
       <c r="C120" s="24" t="s">
@@ -8789,8 +8844,8 @@
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
-      <c r="A121">
-        <v>141</v>
+      <c r="A121" s="20">
+        <v>143</v>
       </c>
       <c r="B121" s="20"/>
       <c r="C121" s="24" t="s">
@@ -8815,8 +8870,8 @@
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
-      <c r="A122">
-        <v>165</v>
+      <c r="A122" s="20">
+        <v>202</v>
       </c>
       <c r="B122" s="20"/>
       <c r="C122" s="24" t="s">
@@ -8841,7 +8896,7 @@
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
-      <c r="A123">
+      <c r="A123" s="20">
         <v>115</v>
       </c>
       <c r="B123" s="20"/>
@@ -8867,8 +8922,8 @@
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
-      <c r="A124">
-        <v>202</v>
+      <c r="A124" s="20">
+        <v>186</v>
       </c>
       <c r="B124" s="23"/>
       <c r="C124" s="24" t="s">
@@ -8893,8 +8948,8 @@
       </c>
     </row>
     <row r="125" spans="1:9" ht="15">
-      <c r="A125">
-        <v>235</v>
+      <c r="A125" s="20">
+        <v>228</v>
       </c>
       <c r="B125" s="22"/>
       <c r="C125" s="24" t="s">
@@ -8919,8 +8974,8 @@
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
-      <c r="A126">
-        <v>299</v>
+      <c r="A126" s="20">
+        <v>279</v>
       </c>
       <c r="B126" s="20"/>
       <c r="C126" s="24" t="s">
@@ -8945,8 +9000,8 @@
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
-      <c r="A127">
-        <v>567</v>
+      <c r="A127" s="20">
+        <v>599</v>
       </c>
       <c r="B127" s="20"/>
       <c r="C127" s="24" t="s">
@@ -8971,8 +9026,8 @@
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
-      <c r="A128">
-        <v>289</v>
+      <c r="A128" s="20">
+        <v>259</v>
       </c>
       <c r="B128" s="20"/>
       <c r="C128" s="24" t="s">
@@ -8997,7 +9052,7 @@
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
-      <c r="A129">
+      <c r="A129" s="20">
         <v>1040</v>
       </c>
       <c r="B129" s="20"/>
@@ -9023,8 +9078,8 @@
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
-      <c r="A130">
-        <v>599</v>
+      <c r="A130" s="20">
+        <v>599.5</v>
       </c>
       <c r="B130" s="20"/>
       <c r="C130" s="24" t="s">
@@ -9049,8 +9104,8 @@
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
-      <c r="A131">
-        <v>495</v>
+      <c r="A131" s="20">
+        <v>599</v>
       </c>
       <c r="B131" s="20"/>
       <c r="C131" s="24" t="s">
@@ -9075,8 +9130,8 @@
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
-      <c r="A132">
-        <v>206</v>
+      <c r="A132" s="20">
+        <v>224</v>
       </c>
       <c r="B132" s="20"/>
       <c r="C132" s="24" t="s">
@@ -9101,8 +9156,8 @@
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
-      <c r="A133">
-        <v>196.7</v>
+      <c r="A133" s="20">
+        <v>110.9</v>
       </c>
       <c r="B133" s="20"/>
       <c r="C133" s="24" t="s">
@@ -9127,8 +9182,8 @@
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
-      <c r="A134">
-        <v>250</v>
+      <c r="A134" s="20">
+        <v>350</v>
       </c>
       <c r="B134" s="20"/>
       <c r="C134" s="24" t="s">
@@ -9153,8 +9208,8 @@
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
-      <c r="A135">
-        <v>121.5</v>
+      <c r="A135" s="20">
+        <v>114</v>
       </c>
       <c r="B135" s="20"/>
       <c r="C135" s="24" t="s">
@@ -9179,8 +9234,8 @@
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
-      <c r="A136">
-        <v>606</v>
+      <c r="A136" s="20">
+        <v>499</v>
       </c>
       <c r="B136" s="20"/>
       <c r="C136" s="24" t="s">
@@ -9205,8 +9260,8 @@
       </c>
     </row>
     <row r="137" spans="1:9" ht="15">
-      <c r="A137">
-        <v>322</v>
+      <c r="A137" s="20">
+        <v>235</v>
       </c>
       <c r="B137" s="20"/>
       <c r="C137" s="24" t="s">
@@ -9231,8 +9286,8 @@
       </c>
     </row>
     <row r="138" spans="1:9" ht="15">
-      <c r="A138">
-        <v>104</v>
+      <c r="A138" s="20">
+        <v>131.9</v>
       </c>
       <c r="B138" s="20"/>
       <c r="C138" s="24" t="s">
@@ -9257,8 +9312,8 @@
       </c>
     </row>
     <row r="139" spans="1:9" ht="15">
-      <c r="A139">
-        <v>232</v>
+      <c r="A139" s="20">
+        <v>249</v>
       </c>
       <c r="B139" s="20"/>
       <c r="C139" s="24" t="s">
@@ -9283,8 +9338,8 @@
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
-      <c r="A140">
-        <v>555</v>
+      <c r="A140" s="20">
+        <v>528</v>
       </c>
       <c r="B140" s="22"/>
       <c r="C140" s="24" t="s">
@@ -9309,7 +9364,7 @@
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
-      <c r="A141">
+      <c r="A141" s="20">
         <v>599</v>
       </c>
       <c r="B141" s="20"/>
@@ -9335,8 +9390,8 @@
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
-      <c r="A142">
-        <v>148</v>
+      <c r="A142" s="20">
+        <v>170</v>
       </c>
       <c r="B142" s="20"/>
       <c r="C142" s="24" t="s">
@@ -9361,8 +9416,8 @@
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
-      <c r="A143">
-        <v>130.5</v>
+      <c r="A143" s="20">
+        <v>178</v>
       </c>
       <c r="B143" s="20"/>
       <c r="C143" s="24" t="s">
@@ -9387,8 +9442,8 @@
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
-      <c r="A144">
-        <v>149</v>
+      <c r="A144" s="20">
+        <v>132.80000000000001</v>
       </c>
       <c r="B144" s="20"/>
       <c r="C144" s="24" t="s">
@@ -9413,8 +9468,8 @@
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
-      <c r="A145">
-        <v>859</v>
+      <c r="A145" s="20">
+        <v>460</v>
       </c>
       <c r="B145" s="20"/>
       <c r="C145" s="24" t="s">
@@ -9439,8 +9494,8 @@
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
-      <c r="A146">
-        <v>279</v>
+      <c r="A146" s="20">
+        <v>277</v>
       </c>
       <c r="B146" s="23"/>
       <c r="C146" s="24" t="s">
@@ -9464,8 +9519,8 @@
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
-      <c r="A147">
-        <v>458</v>
+      <c r="A147" s="20">
+        <v>252</v>
       </c>
       <c r="B147" s="23"/>
       <c r="C147" s="24" t="s">
@@ -9490,9 +9545,7 @@
       </c>
     </row>
     <row r="148" spans="1:9" ht="15">
-      <c r="A148">
-        <v>279</v>
-      </c>
+      <c r="A148" s="20"/>
       <c r="B148" s="23"/>
       <c r="C148" s="24" t="s">
         <v>1408</v>
@@ -9516,9 +9569,7 @@
       </c>
     </row>
     <row r="149" spans="1:9" ht="15">
-      <c r="A149" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A149" s="20"/>
       <c r="B149" s="23"/>
       <c r="C149" s="24" t="s">
         <v>1408</v>
@@ -9541,9 +9592,7 @@
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
-      <c r="A150" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A150" s="20"/>
       <c r="B150" s="23"/>
       <c r="C150" s="24" t="s">
         <v>1408</v>
@@ -9567,9 +9616,7 @@
       </c>
     </row>
     <row r="151" spans="1:9" ht="15">
-      <c r="A151">
-        <v>279</v>
-      </c>
+      <c r="A151" s="20"/>
       <c r="B151" s="23"/>
       <c r="C151" s="24" t="s">
         <v>1408</v>
@@ -9593,9 +9640,7 @@
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
-      <c r="A152" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A152" s="20"/>
       <c r="B152" s="23"/>
       <c r="C152" s="24" t="s">
         <v>1408</v>
@@ -9618,9 +9663,7 @@
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
-      <c r="A153">
-        <v>599</v>
-      </c>
+      <c r="A153" s="20"/>
       <c r="B153" s="23"/>
       <c r="C153" s="24" t="s">
         <v>1408</v>
@@ -9644,9 +9687,7 @@
       </c>
     </row>
     <row r="154" spans="1:9" ht="15">
-      <c r="A154">
-        <v>458</v>
-      </c>
+      <c r="A154" s="20"/>
       <c r="B154" s="23"/>
       <c r="C154" s="24" t="s">
         <v>1408</v>
@@ -9670,8 +9711,8 @@
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
-      <c r="A155" t="s">
-        <v>1419</v>
+      <c r="A155" s="20">
+        <v>251</v>
       </c>
       <c r="B155" s="23"/>
       <c r="C155" s="24" t="s">
@@ -9696,9 +9737,7 @@
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
-      <c r="A156" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A156" s="20"/>
       <c r="B156" s="23"/>
       <c r="C156" s="24" t="s">
         <v>1408</v>
@@ -9722,8 +9761,8 @@
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
-      <c r="A157">
-        <v>111.9</v>
+      <c r="A157" s="20">
+        <v>75</v>
       </c>
       <c r="B157" s="20"/>
       <c r="C157" s="24" t="s">
@@ -9748,8 +9787,8 @@
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
-      <c r="A158">
-        <v>2850</v>
+      <c r="A158" s="20">
+        <v>2327</v>
       </c>
       <c r="B158" s="20"/>
       <c r="C158" s="24" t="s">
@@ -9774,8 +9813,8 @@
       </c>
     </row>
     <row r="159" spans="1:9" ht="15">
-      <c r="A159">
-        <v>299</v>
+      <c r="A159" s="20">
+        <v>269</v>
       </c>
       <c r="B159" s="22"/>
       <c r="C159" s="24" t="s">
@@ -9800,8 +9839,8 @@
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
-      <c r="A160">
-        <v>333</v>
+      <c r="A160" s="20">
+        <v>198</v>
       </c>
       <c r="B160" s="20"/>
       <c r="C160" s="24" t="s">
@@ -9826,8 +9865,8 @@
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
-      <c r="A161">
-        <v>550</v>
+      <c r="A161" s="20">
+        <v>599</v>
       </c>
       <c r="B161" s="20"/>
       <c r="C161" s="24" t="s">
@@ -9852,8 +9891,8 @@
       </c>
     </row>
     <row r="162" spans="1:9" ht="15">
-      <c r="A162">
-        <v>679.5</v>
+      <c r="A162" s="20">
+        <v>799</v>
       </c>
       <c r="B162" s="20"/>
       <c r="C162" s="24" t="s">
@@ -9878,8 +9917,8 @@
       </c>
     </row>
     <row r="163" spans="1:9" ht="15">
-      <c r="A163">
-        <v>180</v>
+      <c r="A163" s="20">
+        <v>155</v>
       </c>
       <c r="B163" s="20"/>
       <c r="C163" s="24" t="s">
@@ -9904,7 +9943,7 @@
       </c>
     </row>
     <row r="164" spans="1:9" ht="15">
-      <c r="A164">
+      <c r="A164" s="20">
         <v>180</v>
       </c>
       <c r="B164" s="20"/>
@@ -9930,8 +9969,8 @@
       </c>
     </row>
     <row r="165" spans="1:9" ht="15">
-      <c r="A165">
-        <v>386</v>
+      <c r="A165" s="20">
+        <v>519</v>
       </c>
       <c r="B165" s="20"/>
       <c r="C165" s="24" t="s">
@@ -9956,8 +9995,8 @@
       </c>
     </row>
     <row r="166" spans="1:9" ht="15">
-      <c r="A166">
-        <v>483.12</v>
+      <c r="A166" s="20">
+        <v>335</v>
       </c>
       <c r="B166" s="20"/>
       <c r="C166" s="24" t="s">
@@ -9982,8 +10021,8 @@
       </c>
     </row>
     <row r="167" spans="1:9" ht="15">
-      <c r="A167">
-        <v>119.2</v>
+      <c r="A167" s="20">
+        <v>230</v>
       </c>
       <c r="B167" s="22"/>
       <c r="C167" s="24" t="s">
@@ -10008,8 +10047,8 @@
       </c>
     </row>
     <row r="168" spans="1:9" ht="15">
-      <c r="A168">
-        <v>168</v>
+      <c r="A168" s="20">
+        <v>198</v>
       </c>
       <c r="B168" s="20"/>
       <c r="C168" s="24" t="s">
@@ -10034,7 +10073,7 @@
       </c>
     </row>
     <row r="169" spans="1:9" ht="15">
-      <c r="A169">
+      <c r="A169" s="20">
         <v>299</v>
       </c>
       <c r="B169" s="20"/>
@@ -10060,8 +10099,8 @@
       </c>
     </row>
     <row r="170" spans="1:9" ht="15">
-      <c r="A170">
-        <v>350</v>
+      <c r="A170" s="20">
+        <v>309</v>
       </c>
       <c r="B170" s="20"/>
       <c r="C170" s="24" t="s">
@@ -10086,8 +10125,8 @@
       </c>
     </row>
     <row r="171" spans="1:9" ht="15">
-      <c r="A171">
-        <v>449</v>
+      <c r="A171" s="20">
+        <v>519</v>
       </c>
       <c r="B171" s="20"/>
       <c r="C171" s="24" t="s">
@@ -10112,7 +10151,7 @@
       </c>
     </row>
     <row r="172" spans="1:9" ht="15">
-      <c r="A172">
+      <c r="A172" s="20">
         <v>329</v>
       </c>
       <c r="B172" s="20"/>
@@ -10138,8 +10177,8 @@
       </c>
     </row>
     <row r="173" spans="1:9" ht="15">
-      <c r="A173">
-        <v>772</v>
+      <c r="A173" s="20">
+        <v>830</v>
       </c>
       <c r="B173" s="20"/>
       <c r="C173" s="24" t="s">
@@ -10164,8 +10203,8 @@
       </c>
     </row>
     <row r="174" spans="1:9" ht="15">
-      <c r="A174">
-        <v>388</v>
+      <c r="A174" s="20">
+        <v>255</v>
       </c>
       <c r="B174" s="20"/>
       <c r="C174" s="24" t="s">
@@ -10190,8 +10229,8 @@
       </c>
     </row>
     <row r="175" spans="1:9" ht="15">
-      <c r="A175">
-        <v>186</v>
+      <c r="A175" s="20">
+        <v>278</v>
       </c>
       <c r="B175" s="22"/>
       <c r="C175" s="24" t="s">
@@ -10216,8 +10255,8 @@
       </c>
     </row>
     <row r="176" spans="1:9" ht="15">
-      <c r="A176">
-        <v>129</v>
+      <c r="A176" s="20">
+        <v>105</v>
       </c>
       <c r="B176" s="20"/>
       <c r="C176" s="24" t="s">
@@ -10242,8 +10281,8 @@
       </c>
     </row>
     <row r="177" spans="1:9" ht="15">
-      <c r="A177">
-        <v>518</v>
+      <c r="A177" s="20">
+        <v>499</v>
       </c>
       <c r="B177" s="22"/>
       <c r="C177" s="24" t="s">
@@ -10268,8 +10307,8 @@
       </c>
     </row>
     <row r="178" spans="1:9" ht="15">
-      <c r="A178">
-        <v>469</v>
+      <c r="A178" s="20">
+        <v>359</v>
       </c>
       <c r="B178" s="22"/>
       <c r="C178" s="24" t="s">
@@ -10294,8 +10333,8 @@
       </c>
     </row>
     <row r="179" spans="1:9" ht="15">
-      <c r="A179">
-        <v>111.9</v>
+      <c r="A179" s="20">
+        <v>75</v>
       </c>
       <c r="B179" s="20"/>
       <c r="C179" s="24" t="s">
@@ -10320,7 +10359,7 @@
       </c>
     </row>
     <row r="180" spans="1:9" ht="15">
-      <c r="A180">
+      <c r="A180" s="20">
         <v>599</v>
       </c>
       <c r="B180" s="22"/>
@@ -10346,8 +10385,8 @@
       </c>
     </row>
     <row r="181" spans="1:9" ht="15">
-      <c r="A181" t="s">
-        <v>1419</v>
+      <c r="A181" s="20">
+        <v>566</v>
       </c>
       <c r="B181" s="23"/>
       <c r="C181" s="24" t="s">
@@ -10371,8 +10410,8 @@
       </c>
     </row>
     <row r="182" spans="1:9" ht="15">
-      <c r="A182">
-        <v>285</v>
+      <c r="A182" s="20">
+        <v>308</v>
       </c>
       <c r="B182" s="20"/>
       <c r="C182" s="24" t="s">
@@ -10397,8 +10436,8 @@
       </c>
     </row>
     <row r="183" spans="1:9" ht="15">
-      <c r="A183">
-        <v>399</v>
+      <c r="A183" s="20">
+        <v>325</v>
       </c>
       <c r="B183" s="20"/>
       <c r="C183" s="24" t="s">
@@ -10423,7 +10462,7 @@
       </c>
     </row>
     <row r="184" spans="1:9" ht="15">
-      <c r="A184">
+      <c r="A184" s="20">
         <v>258</v>
       </c>
       <c r="B184" s="20"/>
@@ -10449,9 +10488,7 @@
       </c>
     </row>
     <row r="185" spans="1:9" ht="15">
-      <c r="A185" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A185" s="20"/>
       <c r="B185" s="23"/>
       <c r="C185" s="24" t="s">
         <v>1408</v>
@@ -10475,8 +10512,8 @@
       </c>
     </row>
     <row r="186" spans="1:9" ht="15">
-      <c r="A186">
-        <v>14.9</v>
+      <c r="A186" s="20">
+        <v>21.7</v>
       </c>
       <c r="B186" s="20"/>
       <c r="C186" s="24" t="s">
@@ -10501,8 +10538,8 @@
       </c>
     </row>
     <row r="187" spans="1:9" ht="15">
-      <c r="A187">
-        <v>154.5</v>
+      <c r="A187" s="20">
+        <v>155</v>
       </c>
       <c r="B187" s="20"/>
       <c r="C187" s="24" t="s">
@@ -10527,8 +10564,8 @@
       </c>
     </row>
     <row r="188" spans="1:9" ht="15">
-      <c r="A188">
-        <v>91.8</v>
+      <c r="A188" s="20">
+        <v>170</v>
       </c>
       <c r="B188" s="20"/>
       <c r="C188" s="24" t="s">
@@ -10553,8 +10590,8 @@
       </c>
     </row>
     <row r="189" spans="1:9" ht="15">
-      <c r="A189">
-        <v>119</v>
+      <c r="A189" s="20">
+        <v>99.99</v>
       </c>
       <c r="B189" s="20"/>
       <c r="C189" s="24" t="s">
@@ -10579,8 +10616,8 @@
       </c>
     </row>
     <row r="190" spans="1:9" ht="15">
-      <c r="A190">
-        <v>70.599999999999994</v>
+      <c r="A190" s="20">
+        <v>119</v>
       </c>
       <c r="B190" s="22"/>
       <c r="C190" s="24" t="s">
@@ -10605,8 +10642,8 @@
       </c>
     </row>
     <row r="191" spans="1:9" ht="15">
-      <c r="A191">
-        <v>388</v>
+      <c r="A191" s="20">
+        <v>183</v>
       </c>
       <c r="B191" s="22"/>
       <c r="C191" s="24" t="s">
@@ -10631,8 +10668,8 @@
       </c>
     </row>
     <row r="192" spans="1:9" ht="15">
-      <c r="A192">
-        <v>167</v>
+      <c r="A192" s="20">
+        <v>185</v>
       </c>
       <c r="B192" s="21"/>
       <c r="C192" s="24" t="s">
@@ -10657,8 +10694,8 @@
       </c>
     </row>
     <row r="193" spans="1:9" ht="15">
-      <c r="A193">
-        <v>389</v>
+      <c r="A193" s="20">
+        <v>458</v>
       </c>
       <c r="B193" s="20"/>
       <c r="C193" s="24" t="s">
@@ -10683,8 +10720,8 @@
       </c>
     </row>
     <row r="194" spans="1:9" ht="15">
-      <c r="A194">
-        <v>442</v>
+      <c r="A194" s="20">
+        <v>519</v>
       </c>
       <c r="B194" s="22"/>
       <c r="C194" s="24" t="s">
@@ -10709,8 +10746,8 @@
       </c>
     </row>
     <row r="195" spans="1:9" ht="15">
-      <c r="A195">
-        <v>112</v>
+      <c r="A195" s="20">
+        <v>135</v>
       </c>
       <c r="B195" s="20"/>
       <c r="C195" s="24" t="s">
@@ -10735,8 +10772,8 @@
       </c>
     </row>
     <row r="196" spans="1:9" ht="15">
-      <c r="A196">
-        <v>326</v>
+      <c r="A196" s="20">
+        <v>399</v>
       </c>
       <c r="B196" s="20"/>
       <c r="C196" s="24" t="s">
@@ -10761,8 +10798,8 @@
       </c>
     </row>
     <row r="197" spans="1:9" ht="15">
-      <c r="A197">
-        <v>365</v>
+      <c r="A197" s="20">
+        <v>244</v>
       </c>
       <c r="B197" s="20"/>
       <c r="C197" s="24" t="s">
@@ -10787,8 +10824,8 @@
       </c>
     </row>
     <row r="198" spans="1:9" ht="15">
-      <c r="A198">
-        <v>54.4</v>
+      <c r="A198" s="20">
+        <v>55</v>
       </c>
       <c r="B198" s="20"/>
       <c r="C198" s="24" t="s">
@@ -10813,8 +10850,8 @@
       </c>
     </row>
     <row r="199" spans="1:9" ht="15">
-      <c r="A199">
-        <v>1038</v>
+      <c r="A199" s="20">
+        <v>1039</v>
       </c>
       <c r="B199" s="22"/>
       <c r="C199" s="24" t="s">
@@ -10839,8 +10876,8 @@
       </c>
     </row>
     <row r="200" spans="1:9" ht="15">
-      <c r="A200">
-        <v>409</v>
+      <c r="A200" s="20">
+        <v>315</v>
       </c>
       <c r="B200" s="22"/>
       <c r="C200" s="24" t="s">
@@ -10865,7 +10902,7 @@
       </c>
     </row>
     <row r="201" spans="1:9" ht="15">
-      <c r="A201">
+      <c r="A201" s="20">
         <v>279</v>
       </c>
       <c r="B201" s="20"/>
@@ -10891,8 +10928,8 @@
       </c>
     </row>
     <row r="202" spans="1:9" ht="15">
-      <c r="A202">
-        <v>1299</v>
+      <c r="A202" s="20">
+        <v>1590</v>
       </c>
       <c r="B202" s="20"/>
       <c r="C202" s="24" t="s">
@@ -10917,8 +10954,8 @@
       </c>
     </row>
     <row r="203" spans="1:9" ht="15">
-      <c r="A203">
-        <v>126</v>
+      <c r="A203" s="20">
+        <v>128</v>
       </c>
       <c r="B203" s="20"/>
       <c r="C203" s="24" t="s">
@@ -10943,8 +10980,8 @@
       </c>
     </row>
     <row r="204" spans="1:9" ht="15">
-      <c r="A204">
-        <v>77.48</v>
+      <c r="A204" s="20">
+        <v>70</v>
       </c>
       <c r="B204" s="20"/>
       <c r="C204" s="24" t="s">
@@ -10969,8 +11006,8 @@
       </c>
     </row>
     <row r="205" spans="1:9" ht="15">
-      <c r="A205">
-        <v>366</v>
+      <c r="A205" s="20">
+        <v>275</v>
       </c>
       <c r="B205" s="20"/>
       <c r="C205" s="24" t="s">
@@ -10995,8 +11032,8 @@
       </c>
     </row>
     <row r="206" spans="1:9" ht="15">
-      <c r="A206">
-        <v>139</v>
+      <c r="A206" s="20">
+        <v>156</v>
       </c>
       <c r="B206" s="20"/>
       <c r="C206" s="24" t="s">
@@ -11021,8 +11058,8 @@
       </c>
     </row>
     <row r="207" spans="1:9" ht="15">
-      <c r="A207">
-        <v>182</v>
+      <c r="A207" s="20">
+        <v>94</v>
       </c>
       <c r="B207" s="20"/>
       <c r="C207" s="24" t="s">
@@ -11047,8 +11084,8 @@
       </c>
     </row>
     <row r="208" spans="1:9" ht="15">
-      <c r="A208">
-        <v>182</v>
+      <c r="A208" s="20">
+        <v>149</v>
       </c>
       <c r="B208" s="20"/>
       <c r="C208" s="24" t="s">
@@ -11073,8 +11110,8 @@
       </c>
     </row>
     <row r="209" spans="1:9" ht="15">
-      <c r="A209">
-        <v>113</v>
+      <c r="A209" s="20">
+        <v>115</v>
       </c>
       <c r="B209" s="20"/>
       <c r="C209" s="24" t="s">
@@ -11099,8 +11136,8 @@
       </c>
     </row>
     <row r="210" spans="1:9" ht="15">
-      <c r="A210">
-        <v>43</v>
+      <c r="A210" s="20">
+        <v>43.5</v>
       </c>
       <c r="B210" s="20"/>
       <c r="C210" s="24" t="s">
@@ -11125,7 +11162,7 @@
       </c>
     </row>
     <row r="211" spans="1:9" ht="15">
-      <c r="A211">
+      <c r="A211" s="20">
         <v>78.900000000000006</v>
       </c>
       <c r="B211" s="20"/>
@@ -11151,8 +11188,8 @@
       </c>
     </row>
     <row r="212" spans="1:9" ht="15">
-      <c r="A212">
-        <v>92.1</v>
+      <c r="A212" s="20">
+        <v>85</v>
       </c>
       <c r="B212" s="20"/>
       <c r="C212" s="24" t="s">
@@ -11177,8 +11214,8 @@
       </c>
     </row>
     <row r="213" spans="1:9" ht="15">
-      <c r="A213">
-        <v>95</v>
+      <c r="A213" s="20">
+        <v>165</v>
       </c>
       <c r="B213" s="20"/>
       <c r="C213" s="24" t="s">
@@ -11203,8 +11240,8 @@
       </c>
     </row>
     <row r="214" spans="1:9" ht="15">
-      <c r="A214">
-        <v>88.29</v>
+      <c r="A214" s="20">
+        <v>91</v>
       </c>
       <c r="B214" s="20"/>
       <c r="C214" s="24" t="s">
@@ -11229,8 +11266,8 @@
       </c>
     </row>
     <row r="215" spans="1:9" ht="15">
-      <c r="A215" t="s">
-        <v>1419</v>
+      <c r="A215" s="20">
+        <v>208</v>
       </c>
       <c r="B215" s="21"/>
       <c r="C215" s="24" t="s">
@@ -11255,8 +11292,8 @@
       </c>
     </row>
     <row r="216" spans="1:9" ht="15">
-      <c r="A216">
-        <v>200.84</v>
+      <c r="A216" s="20">
+        <v>219</v>
       </c>
       <c r="B216" s="21"/>
       <c r="C216" s="24" t="s">
@@ -11281,8 +11318,8 @@
       </c>
     </row>
     <row r="217" spans="1:9" ht="15">
-      <c r="A217">
-        <v>256</v>
+      <c r="A217" s="20">
+        <v>248</v>
       </c>
       <c r="B217" s="20"/>
       <c r="C217" s="24" t="s">
@@ -11307,8 +11344,8 @@
       </c>
     </row>
     <row r="218" spans="1:9" ht="15">
-      <c r="A218">
-        <v>185</v>
+      <c r="A218" s="20">
+        <v>167</v>
       </c>
       <c r="B218" s="20"/>
       <c r="C218" s="24" t="s">
@@ -11333,8 +11370,8 @@
       </c>
     </row>
     <row r="219" spans="1:9" ht="15">
-      <c r="A219">
-        <v>185</v>
+      <c r="A219" s="20">
+        <v>208</v>
       </c>
       <c r="B219" s="20"/>
       <c r="C219" s="24" t="s">
@@ -11359,8 +11396,8 @@
       </c>
     </row>
     <row r="220" spans="1:9" ht="15">
-      <c r="A220">
-        <v>628</v>
+      <c r="A220" s="20">
+        <v>478</v>
       </c>
       <c r="B220" s="20"/>
       <c r="C220" s="24" t="s">
@@ -11385,8 +11422,8 @@
       </c>
     </row>
     <row r="221" spans="1:9" ht="15">
-      <c r="A221">
-        <v>277.5</v>
+      <c r="A221" s="20">
+        <v>319</v>
       </c>
       <c r="B221" s="20"/>
       <c r="C221" s="24" t="s">
@@ -11411,8 +11448,8 @@
       </c>
     </row>
     <row r="222" spans="1:9" ht="15">
-      <c r="A222">
-        <v>269</v>
+      <c r="A222" s="20">
+        <v>289</v>
       </c>
       <c r="B222" s="20"/>
       <c r="C222" s="24" t="s">
@@ -11437,8 +11474,8 @@
       </c>
     </row>
     <row r="223" spans="1:9" ht="15">
-      <c r="A223">
-        <v>223.99</v>
+      <c r="A223" s="20">
+        <v>279</v>
       </c>
       <c r="B223" s="20"/>
       <c r="C223" s="24" t="s">
@@ -11463,8 +11500,8 @@
       </c>
     </row>
     <row r="224" spans="1:9" ht="15">
-      <c r="A224">
-        <v>208</v>
+      <c r="A224" s="20">
+        <v>219</v>
       </c>
       <c r="C224" s="24" t="s">
         <v>1408</v>
@@ -11488,8 +11525,8 @@
       </c>
     </row>
     <row r="225" spans="1:9" ht="15">
-      <c r="A225">
-        <v>193</v>
+      <c r="A225" s="20">
+        <v>299</v>
       </c>
       <c r="B225" s="20"/>
       <c r="C225" s="24" t="s">
@@ -11514,8 +11551,8 @@
       </c>
     </row>
     <row r="226" spans="1:9" ht="15">
-      <c r="A226">
-        <v>63</v>
+      <c r="A226" s="20">
+        <v>81</v>
       </c>
       <c r="B226" s="20"/>
       <c r="C226" s="24" t="s">
@@ -11540,7 +11577,7 @@
       </c>
     </row>
     <row r="227" spans="1:9" ht="15">
-      <c r="A227">
+      <c r="A227" s="20">
         <v>239</v>
       </c>
       <c r="B227" s="20"/>
@@ -11566,8 +11603,8 @@
       </c>
     </row>
     <row r="228" spans="1:9" ht="15">
-      <c r="A228">
-        <v>499</v>
+      <c r="A228" s="20">
+        <v>415</v>
       </c>
       <c r="B228" s="20"/>
       <c r="C228" s="24" t="s">
@@ -11592,8 +11629,8 @@
       </c>
     </row>
     <row r="229" spans="1:9" ht="15">
-      <c r="A229">
-        <v>339</v>
+      <c r="A229" s="20">
+        <v>274</v>
       </c>
       <c r="B229" s="20"/>
       <c r="C229" s="24" t="s">
@@ -11618,8 +11655,8 @@
       </c>
     </row>
     <row r="230" spans="1:9" ht="15">
-      <c r="A230">
-        <v>592</v>
+      <c r="A230" s="20">
+        <v>599</v>
       </c>
       <c r="B230" s="20"/>
       <c r="C230" s="24" t="s">
@@ -11644,9 +11681,7 @@
       </c>
     </row>
     <row r="231" spans="1:9" ht="15">
-      <c r="A231" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A231" s="20"/>
       <c r="B231" s="23"/>
       <c r="C231" s="24" t="s">
         <v>1408</v>
@@ -11669,9 +11704,7 @@
       </c>
     </row>
     <row r="232" spans="1:9" ht="15">
-      <c r="A232" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A232" s="20"/>
       <c r="B232" s="23"/>
       <c r="C232" s="24" t="s">
         <v>1408</v>
@@ -11695,9 +11728,7 @@
       </c>
     </row>
     <row r="233" spans="1:9" ht="15">
-      <c r="A233" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A233" s="20"/>
       <c r="B233" s="23"/>
       <c r="C233" s="24" t="s">
         <v>1408</v>
@@ -11721,8 +11752,8 @@
       </c>
     </row>
     <row r="234" spans="1:9" ht="15">
-      <c r="A234">
-        <v>87.7</v>
+      <c r="A234" s="20">
+        <v>33</v>
       </c>
       <c r="B234" s="23"/>
       <c r="C234" s="24" t="s">
@@ -11747,9 +11778,7 @@
       </c>
     </row>
     <row r="235" spans="1:9" ht="15">
-      <c r="A235" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A235" s="20"/>
       <c r="B235" s="23"/>
       <c r="C235" s="24" t="s">
         <v>1408</v>
@@ -11773,9 +11802,7 @@
       </c>
     </row>
     <row r="236" spans="1:9" ht="15">
-      <c r="A236" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A236" s="20"/>
       <c r="B236" s="23"/>
       <c r="C236" s="24" t="s">
         <v>1408</v>
@@ -11799,9 +11826,7 @@
       </c>
     </row>
     <row r="237" spans="1:9" ht="15">
-      <c r="A237" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A237" s="20"/>
       <c r="B237" s="23"/>
       <c r="C237" s="24" t="s">
         <v>1408</v>
@@ -11824,9 +11849,7 @@
       </c>
     </row>
     <row r="238" spans="1:9" ht="15">
-      <c r="A238" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A238" s="20"/>
       <c r="B238" s="23"/>
       <c r="C238" s="24" t="s">
         <v>1408</v>
@@ -11849,8 +11872,8 @@
       </c>
     </row>
     <row r="239" spans="1:9" ht="15">
-      <c r="A239">
-        <v>169</v>
+      <c r="A239" s="20">
+        <v>137.54</v>
       </c>
       <c r="B239" s="20"/>
       <c r="C239" s="24" t="s">
@@ -11875,8 +11898,8 @@
       </c>
     </row>
     <row r="240" spans="1:9" ht="15">
-      <c r="A240">
-        <v>680</v>
+      <c r="A240" s="20">
+        <v>701</v>
       </c>
       <c r="B240" s="20"/>
       <c r="C240" s="24" t="s">
@@ -11901,8 +11924,8 @@
       </c>
     </row>
     <row r="241" spans="1:9" ht="15">
-      <c r="A241">
-        <v>106.8</v>
+      <c r="A241" s="20">
+        <v>88</v>
       </c>
       <c r="B241" s="22"/>
       <c r="C241" s="24" t="s">
@@ -11927,8 +11950,8 @@
       </c>
     </row>
     <row r="242" spans="1:9" ht="15">
-      <c r="A242">
-        <v>149.5</v>
+      <c r="A242" s="20">
+        <v>158</v>
       </c>
       <c r="B242" s="20"/>
       <c r="C242" s="24" t="s">
@@ -11953,8 +11976,8 @@
       </c>
     </row>
     <row r="243" spans="1:9" ht="15">
-      <c r="A243">
-        <v>244.3</v>
+      <c r="A243" s="20">
+        <v>309.5</v>
       </c>
       <c r="B243" s="20"/>
       <c r="C243" s="24" t="s">
@@ -11979,7 +12002,7 @@
       </c>
     </row>
     <row r="244" spans="1:9" ht="15">
-      <c r="A244">
+      <c r="A244" s="20">
         <v>339</v>
       </c>
       <c r="B244" s="20"/>
@@ -12005,8 +12028,8 @@
       </c>
     </row>
     <row r="245" spans="1:9" ht="15">
-      <c r="A245">
-        <v>305.99</v>
+      <c r="A245" s="20">
+        <v>264</v>
       </c>
       <c r="B245" s="20"/>
       <c r="C245" s="24" t="s">
@@ -12031,8 +12054,8 @@
       </c>
     </row>
     <row r="246" spans="1:9" ht="15">
-      <c r="A246">
-        <v>185</v>
+      <c r="A246" s="20">
+        <v>225</v>
       </c>
       <c r="B246" s="20"/>
       <c r="C246" s="24" t="s">
@@ -12057,8 +12080,8 @@
       </c>
     </row>
     <row r="247" spans="1:9" ht="15">
-      <c r="A247">
-        <v>267.5</v>
+      <c r="A247" s="20">
+        <v>299</v>
       </c>
       <c r="B247" s="20"/>
       <c r="C247" s="24" t="s">
@@ -12083,8 +12106,8 @@
       </c>
     </row>
     <row r="248" spans="1:9" ht="15">
-      <c r="A248">
-        <v>429</v>
+      <c r="A248" s="20">
+        <v>308</v>
       </c>
       <c r="B248" s="20"/>
       <c r="C248" s="24" t="s">
@@ -12109,8 +12132,8 @@
       </c>
     </row>
     <row r="249" spans="1:9" ht="15">
-      <c r="A249">
-        <v>389</v>
+      <c r="A249" s="20">
+        <v>829</v>
       </c>
       <c r="B249" s="20"/>
       <c r="C249" s="24" t="s">
@@ -12135,8 +12158,8 @@
       </c>
     </row>
     <row r="250" spans="1:9" ht="15">
-      <c r="A250">
-        <v>198</v>
+      <c r="A250" s="20">
+        <v>150</v>
       </c>
       <c r="B250" s="20"/>
       <c r="C250" s="24" t="s">
@@ -12161,7 +12184,7 @@
       </c>
     </row>
     <row r="251" spans="1:9" ht="15">
-      <c r="A251">
+      <c r="A251" s="20">
         <v>160</v>
       </c>
       <c r="B251" s="20"/>
@@ -12187,8 +12210,8 @@
       </c>
     </row>
     <row r="252" spans="1:9" ht="15">
-      <c r="A252">
-        <v>216</v>
+      <c r="A252" s="20">
+        <v>248</v>
       </c>
       <c r="B252" s="20"/>
       <c r="C252" s="24" t="s">
@@ -12213,7 +12236,7 @@
       </c>
     </row>
     <row r="253" spans="1:9" ht="15">
-      <c r="A253">
+      <c r="A253" s="20">
         <v>234</v>
       </c>
       <c r="C253" s="24" t="s">
@@ -12237,7 +12260,7 @@
       </c>
     </row>
     <row r="254" spans="1:9" ht="15">
-      <c r="A254">
+      <c r="A254" s="20">
         <v>139</v>
       </c>
       <c r="B254" s="23"/>
@@ -12263,8 +12286,8 @@
       </c>
     </row>
     <row r="255" spans="1:9" ht="15">
-      <c r="A255">
-        <v>628</v>
+      <c r="A255" s="20">
+        <v>230</v>
       </c>
       <c r="B255" s="20"/>
       <c r="C255" s="24" t="s">
@@ -12289,8 +12312,8 @@
       </c>
     </row>
     <row r="256" spans="1:9" ht="15">
-      <c r="A256">
-        <v>341</v>
+      <c r="A256" s="20">
+        <v>215</v>
       </c>
       <c r="B256" s="20"/>
       <c r="C256" s="24" t="s">
@@ -12315,7 +12338,7 @@
       </c>
     </row>
     <row r="257" spans="1:9" ht="15">
-      <c r="A257">
+      <c r="A257" s="20">
         <v>699</v>
       </c>
       <c r="B257" s="20"/>
@@ -12341,8 +12364,8 @@
       </c>
     </row>
     <row r="258" spans="1:9" ht="15">
-      <c r="A258">
-        <v>290</v>
+      <c r="A258" s="20">
+        <v>105</v>
       </c>
       <c r="B258" s="20"/>
       <c r="C258" s="24" t="s">
@@ -12367,8 +12390,8 @@
       </c>
     </row>
     <row r="259" spans="1:9" ht="15">
-      <c r="A259">
-        <v>299.5</v>
+      <c r="A259" s="20">
+        <v>298</v>
       </c>
       <c r="B259" s="20"/>
       <c r="C259" s="24" t="s">
@@ -12393,8 +12416,8 @@
       </c>
     </row>
     <row r="260" spans="1:9" ht="15">
-      <c r="A260">
-        <v>245</v>
+      <c r="A260" s="20">
+        <v>359</v>
       </c>
       <c r="B260" s="20"/>
       <c r="C260" s="24" t="s">
@@ -12419,9 +12442,7 @@
       </c>
     </row>
     <row r="261" spans="1:9" ht="15">
-      <c r="A261">
-        <v>60</v>
-      </c>
+      <c r="A261" s="20"/>
       <c r="B261" s="23"/>
       <c r="C261" s="24" t="s">
         <v>1408</v>
@@ -12445,8 +12466,8 @@
       </c>
     </row>
     <row r="262" spans="1:9" ht="15">
-      <c r="A262">
-        <v>146</v>
+      <c r="A262" s="20">
+        <v>127</v>
       </c>
       <c r="B262" s="20"/>
       <c r="C262" s="24" t="s">
@@ -12471,8 +12492,8 @@
       </c>
     </row>
     <row r="263" spans="1:9" ht="15">
-      <c r="A263">
-        <v>107</v>
+      <c r="A263" s="20">
+        <v>185</v>
       </c>
       <c r="B263" s="20"/>
       <c r="C263" s="24" t="s">
@@ -12497,8 +12518,8 @@
       </c>
     </row>
     <row r="264" spans="1:9" ht="15">
-      <c r="A264">
-        <v>468</v>
+      <c r="A264" s="20">
+        <v>489</v>
       </c>
       <c r="B264" s="20"/>
       <c r="C264" s="24" t="s">
@@ -12523,8 +12544,8 @@
       </c>
     </row>
     <row r="265" spans="1:9" ht="15">
-      <c r="A265">
-        <v>239</v>
+      <c r="A265" s="20">
+        <v>152</v>
       </c>
       <c r="B265" s="20"/>
       <c r="C265" s="24" t="s">
@@ -12549,7 +12570,7 @@
       </c>
     </row>
     <row r="266" spans="1:9" ht="15">
-      <c r="A266">
+      <c r="A266" s="20">
         <v>255</v>
       </c>
       <c r="B266" s="20"/>
@@ -12575,8 +12596,8 @@
       </c>
     </row>
     <row r="267" spans="1:9" ht="15">
-      <c r="A267">
-        <v>86.9</v>
+      <c r="A267" s="20">
+        <v>119.8</v>
       </c>
       <c r="B267" s="22"/>
       <c r="C267" s="24" t="s">
@@ -12601,8 +12622,8 @@
       </c>
     </row>
     <row r="268" spans="1:9" ht="15">
-      <c r="A268">
-        <v>179</v>
+      <c r="A268" s="20">
+        <v>119</v>
       </c>
       <c r="B268" s="20"/>
       <c r="C268" s="24" t="s">
@@ -12627,8 +12648,8 @@
       </c>
     </row>
     <row r="269" spans="1:9" ht="15">
-      <c r="A269">
-        <v>239</v>
+      <c r="A269" s="20">
+        <v>288</v>
       </c>
       <c r="B269" s="20"/>
       <c r="C269" s="24" t="s">
@@ -12653,7 +12674,7 @@
       </c>
     </row>
     <row r="270" spans="1:9" ht="15">
-      <c r="A270">
+      <c r="A270" s="20">
         <v>399</v>
       </c>
       <c r="B270" s="20"/>
@@ -12679,9 +12700,7 @@
       </c>
     </row>
     <row r="271" spans="1:9" ht="15">
-      <c r="A271" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A271" s="20"/>
       <c r="B271" s="23"/>
       <c r="C271" s="24" t="s">
         <v>1408</v>
@@ -12705,8 +12724,8 @@
       </c>
     </row>
     <row r="272" spans="1:9" ht="15">
-      <c r="A272">
-        <v>674</v>
+      <c r="A272" s="20">
+        <v>475</v>
       </c>
       <c r="B272" s="20"/>
       <c r="C272" s="24" t="s">
@@ -12731,8 +12750,8 @@
       </c>
     </row>
     <row r="273" spans="1:9" ht="15">
-      <c r="A273">
-        <v>432</v>
+      <c r="A273" s="20">
+        <v>498</v>
       </c>
       <c r="B273" s="20"/>
       <c r="C273" s="24" t="s">
@@ -12757,8 +12776,8 @@
       </c>
     </row>
     <row r="274" spans="1:9" ht="15">
-      <c r="A274">
-        <v>340</v>
+      <c r="A274" s="20">
+        <v>418</v>
       </c>
       <c r="B274" s="20"/>
       <c r="C274" s="24" t="s">
@@ -12783,8 +12802,8 @@
       </c>
     </row>
     <row r="275" spans="1:9" ht="15">
-      <c r="A275">
-        <v>710</v>
+      <c r="A275" s="20">
+        <v>1140</v>
       </c>
       <c r="B275" s="20"/>
       <c r="C275" s="24" t="s">
@@ -12809,7 +12828,7 @@
       </c>
     </row>
     <row r="276" spans="1:9" ht="15">
-      <c r="A276">
+      <c r="A276" s="20">
         <v>2598</v>
       </c>
       <c r="B276" s="22"/>
@@ -12835,8 +12854,8 @@
       </c>
     </row>
     <row r="277" spans="1:9" ht="15">
-      <c r="A277">
-        <v>323</v>
+      <c r="A277" s="20">
+        <v>200.55</v>
       </c>
       <c r="B277" s="20"/>
       <c r="C277" s="24" t="s">
@@ -12861,8 +12880,8 @@
       </c>
     </row>
     <row r="278" spans="1:9" ht="15">
-      <c r="A278">
-        <v>731.4</v>
+      <c r="A278" s="20">
+        <v>826</v>
       </c>
       <c r="B278" s="20"/>
       <c r="C278" s="24" t="s">
@@ -12887,8 +12906,8 @@
       </c>
     </row>
     <row r="279" spans="1:9" ht="15">
-      <c r="A279">
-        <v>327</v>
+      <c r="A279" s="20">
+        <v>399</v>
       </c>
       <c r="B279" s="20"/>
       <c r="C279" s="24" t="s">
@@ -12913,8 +12932,8 @@
       </c>
     </row>
     <row r="280" spans="1:9" ht="15">
-      <c r="A280">
-        <v>1200</v>
+      <c r="A280" s="20">
+        <v>1160</v>
       </c>
       <c r="B280" s="20"/>
       <c r="C280" s="24" t="s">
@@ -12939,8 +12958,8 @@
       </c>
     </row>
     <row r="281" spans="1:9" ht="15">
-      <c r="A281">
-        <v>659</v>
+      <c r="A281" s="20">
+        <v>856</v>
       </c>
       <c r="B281" s="22"/>
       <c r="C281" s="24" t="s">
@@ -12965,8 +12984,8 @@
       </c>
     </row>
     <row r="282" spans="1:9" ht="15">
-      <c r="A282">
-        <v>57</v>
+      <c r="A282" s="20">
+        <v>97.99</v>
       </c>
       <c r="B282" s="22"/>
       <c r="C282" s="24" t="s">
@@ -12991,8 +13010,8 @@
       </c>
     </row>
     <row r="283" spans="1:9" ht="17">
-      <c r="A283">
-        <v>577.76</v>
+      <c r="A283" s="20">
+        <v>405.72</v>
       </c>
       <c r="B283" s="20"/>
       <c r="C283" s="24" t="s">
@@ -13017,8 +13036,8 @@
       </c>
     </row>
     <row r="284" spans="1:9" ht="17">
-      <c r="A284">
-        <v>424</v>
+      <c r="A284" s="20">
+        <v>405.72</v>
       </c>
       <c r="B284" s="20"/>
       <c r="C284" s="24" t="s">
@@ -13043,8 +13062,8 @@
       </c>
     </row>
     <row r="285" spans="1:9" ht="15">
-      <c r="A285">
-        <v>256</v>
+      <c r="A285" s="20">
+        <v>420</v>
       </c>
       <c r="B285" s="20"/>
       <c r="C285" s="24" t="s">
@@ -13069,7 +13088,7 @@
       </c>
     </row>
     <row r="286" spans="1:9" ht="15">
-      <c r="A286">
+      <c r="A286" s="20">
         <v>188</v>
       </c>
       <c r="B286" s="20"/>
@@ -13095,8 +13114,8 @@
       </c>
     </row>
     <row r="287" spans="1:9" ht="15">
-      <c r="A287">
-        <v>144</v>
+      <c r="A287" s="20">
+        <v>199</v>
       </c>
       <c r="B287" s="20"/>
       <c r="C287" s="24" t="s">
@@ -13121,8 +13140,8 @@
       </c>
     </row>
     <row r="288" spans="1:9" ht="15">
-      <c r="A288">
-        <v>589</v>
+      <c r="A288" s="20">
+        <v>899</v>
       </c>
       <c r="B288" s="20"/>
       <c r="C288" s="24" t="s">
@@ -13147,7 +13166,7 @@
       </c>
     </row>
     <row r="289" spans="1:9" ht="15">
-      <c r="A289">
+      <c r="A289" s="20">
         <v>399</v>
       </c>
       <c r="B289" s="20"/>
@@ -13173,8 +13192,8 @@
       </c>
     </row>
     <row r="290" spans="1:9" ht="15">
-      <c r="A290">
-        <v>259.3</v>
+      <c r="A290" s="20">
+        <v>399</v>
       </c>
       <c r="B290" s="20"/>
       <c r="C290" s="24" t="s">
@@ -13199,8 +13218,8 @@
       </c>
     </row>
     <row r="291" spans="1:9" ht="15">
-      <c r="A291">
-        <v>658</v>
+      <c r="A291" s="20">
+        <v>659</v>
       </c>
       <c r="B291" s="20"/>
       <c r="C291" s="24" t="s">
@@ -13225,8 +13244,8 @@
       </c>
     </row>
     <row r="292" spans="1:9" ht="15">
-      <c r="A292">
-        <v>289</v>
+      <c r="A292" s="20">
+        <v>399</v>
       </c>
       <c r="B292" s="20"/>
       <c r="C292" s="24" t="s">
@@ -13251,8 +13270,8 @@
       </c>
     </row>
     <row r="293" spans="1:9" ht="15">
-      <c r="A293">
-        <v>336</v>
+      <c r="A293" s="20">
+        <v>364</v>
       </c>
       <c r="B293" s="20"/>
       <c r="C293" s="24" t="s">
@@ -13277,8 +13296,8 @@
       </c>
     </row>
     <row r="294" spans="1:9" ht="15">
-      <c r="A294">
-        <v>279</v>
+      <c r="A294" s="20">
+        <v>259</v>
       </c>
       <c r="B294" s="20"/>
       <c r="C294" s="24" t="s">
@@ -13303,8 +13322,8 @@
       </c>
     </row>
     <row r="295" spans="1:9" ht="15">
-      <c r="A295">
-        <v>202</v>
+      <c r="A295" s="20">
+        <v>279</v>
       </c>
       <c r="B295" s="20"/>
       <c r="C295" s="24" t="s">
@@ -13329,8 +13348,8 @@
       </c>
     </row>
     <row r="296" spans="1:9" ht="15">
-      <c r="A296">
-        <v>1538</v>
+      <c r="A296" s="20">
+        <v>2440</v>
       </c>
       <c r="B296" s="20"/>
       <c r="C296" s="24" t="s">
@@ -13355,8 +13374,8 @@
       </c>
     </row>
     <row r="297" spans="1:9" ht="15">
-      <c r="A297">
-        <v>388</v>
+      <c r="A297" s="20">
+        <v>279</v>
       </c>
       <c r="B297" s="20"/>
       <c r="C297" s="24" t="s">
@@ -13381,8 +13400,8 @@
       </c>
     </row>
     <row r="298" spans="1:9" ht="15">
-      <c r="A298">
-        <v>143</v>
+      <c r="A298" s="20">
+        <v>126</v>
       </c>
       <c r="B298" s="21"/>
       <c r="C298" s="24" t="s">
@@ -13407,8 +13426,8 @@
       </c>
     </row>
     <row r="299" spans="1:9" ht="15">
-      <c r="A299">
-        <v>300</v>
+      <c r="A299" s="20">
+        <v>390</v>
       </c>
       <c r="B299" s="20"/>
       <c r="C299" s="24" t="s">
@@ -13433,8 +13452,8 @@
       </c>
     </row>
     <row r="300" spans="1:9" ht="15">
-      <c r="A300">
-        <v>119</v>
+      <c r="A300" s="20">
+        <v>157</v>
       </c>
       <c r="B300" s="23"/>
       <c r="C300" s="24" t="s">
@@ -13458,8 +13477,8 @@
       </c>
     </row>
     <row r="301" spans="1:9" ht="15">
-      <c r="A301">
-        <v>201</v>
+      <c r="A301" s="20">
+        <v>299</v>
       </c>
       <c r="B301" s="20"/>
       <c r="C301" s="24" t="s">
@@ -13484,7 +13503,7 @@
       </c>
     </row>
     <row r="302" spans="1:9" ht="15">
-      <c r="A302">
+      <c r="A302" s="20">
         <v>318</v>
       </c>
       <c r="B302" s="20"/>
@@ -13510,8 +13529,8 @@
       </c>
     </row>
     <row r="303" spans="1:9" ht="15">
-      <c r="A303">
-        <v>170.8</v>
+      <c r="A303" s="20">
+        <v>258</v>
       </c>
       <c r="B303" s="20"/>
       <c r="C303" s="24" t="s">
@@ -13536,8 +13555,8 @@
       </c>
     </row>
     <row r="304" spans="1:9" ht="15">
-      <c r="A304">
-        <v>799</v>
+      <c r="A304" s="20">
+        <v>609</v>
       </c>
       <c r="B304" s="20"/>
       <c r="C304" s="24" t="s">
@@ -13562,8 +13581,8 @@
       </c>
     </row>
     <row r="305" spans="1:9" ht="15">
-      <c r="A305">
-        <v>852</v>
+      <c r="A305" s="20">
+        <v>599</v>
       </c>
       <c r="B305" s="20"/>
       <c r="C305" s="24" t="s">
@@ -13588,8 +13607,8 @@
       </c>
     </row>
     <row r="306" spans="1:9" ht="15">
-      <c r="A306">
-        <v>888</v>
+      <c r="A306" s="20">
+        <v>436</v>
       </c>
       <c r="B306" s="20"/>
       <c r="C306" s="24" t="s">
@@ -13614,8 +13633,8 @@
       </c>
     </row>
     <row r="307" spans="1:9" ht="15">
-      <c r="A307">
-        <v>432</v>
+      <c r="A307" s="20">
+        <v>698</v>
       </c>
       <c r="B307" s="20"/>
       <c r="C307" s="24" t="s">
@@ -13640,8 +13659,8 @@
       </c>
     </row>
     <row r="308" spans="1:9" ht="15">
-      <c r="A308">
-        <v>532</v>
+      <c r="A308" s="20">
+        <v>609</v>
       </c>
       <c r="B308" s="23"/>
       <c r="C308" s="24" t="s">
@@ -13666,8 +13685,8 @@
       </c>
     </row>
     <row r="309" spans="1:9" ht="15">
-      <c r="A309">
-        <v>455</v>
+      <c r="A309" s="20">
+        <v>679</v>
       </c>
       <c r="B309" s="22"/>
       <c r="C309" s="24" t="s">
@@ -13692,8 +13711,8 @@
       </c>
     </row>
     <row r="310" spans="1:9" ht="15">
-      <c r="A310">
-        <v>158.99</v>
+      <c r="A310" s="20">
+        <v>198</v>
       </c>
       <c r="B310" s="20"/>
       <c r="C310" s="24" t="s">
@@ -13718,8 +13737,8 @@
       </c>
     </row>
     <row r="311" spans="1:9" ht="15">
-      <c r="A311">
-        <v>749</v>
+      <c r="A311" s="20">
+        <v>702</v>
       </c>
       <c r="B311" s="20"/>
       <c r="C311" s="24" t="s">
@@ -13744,8 +13763,8 @@
       </c>
     </row>
     <row r="312" spans="1:9" ht="15">
-      <c r="A312">
-        <v>679.5</v>
+      <c r="A312" s="20">
+        <v>699</v>
       </c>
       <c r="B312" s="20"/>
       <c r="C312" s="24" t="s">
@@ -13770,8 +13789,8 @@
       </c>
     </row>
     <row r="313" spans="1:9" ht="15">
-      <c r="A313">
-        <v>825</v>
+      <c r="A313" s="20">
+        <v>822</v>
       </c>
       <c r="B313" s="20"/>
       <c r="C313" s="24" t="s">
@@ -13796,8 +13815,8 @@
       </c>
     </row>
     <row r="314" spans="1:9" ht="15">
-      <c r="A314">
-        <v>432</v>
+      <c r="A314" s="20">
+        <v>498</v>
       </c>
       <c r="B314" s="20"/>
       <c r="C314" s="24" t="s">
@@ -13822,8 +13841,8 @@
       </c>
     </row>
     <row r="315" spans="1:9" ht="15">
-      <c r="A315">
-        <v>354</v>
+      <c r="A315" s="20">
+        <v>299.5</v>
       </c>
       <c r="B315" s="20"/>
       <c r="C315" s="24" t="s">
@@ -13848,8 +13867,8 @@
       </c>
     </row>
     <row r="316" spans="1:9" ht="15">
-      <c r="A316">
-        <v>695</v>
+      <c r="A316" s="20">
+        <v>856</v>
       </c>
       <c r="B316" s="20"/>
       <c r="C316" s="24" t="s">
@@ -13874,8 +13893,8 @@
       </c>
     </row>
     <row r="317" spans="1:9" ht="15">
-      <c r="A317">
-        <v>699</v>
+      <c r="A317" s="20">
+        <v>525</v>
       </c>
       <c r="B317" s="20"/>
       <c r="C317" s="24" t="s">
@@ -13900,8 +13919,8 @@
       </c>
     </row>
     <row r="318" spans="1:9" ht="15">
-      <c r="A318">
-        <v>879</v>
+      <c r="A318" s="20">
+        <v>999</v>
       </c>
       <c r="B318" s="20"/>
       <c r="C318" s="24" t="s">
@@ -13926,8 +13945,8 @@
       </c>
     </row>
     <row r="319" spans="1:9" ht="15">
-      <c r="A319">
-        <v>129</v>
+      <c r="A319" s="20">
+        <v>118.99</v>
       </c>
       <c r="B319" s="20"/>
       <c r="C319" s="24" t="s">
@@ -13952,8 +13971,8 @@
       </c>
     </row>
     <row r="320" spans="1:9" ht="15">
-      <c r="A320">
-        <v>245</v>
+      <c r="A320" s="20">
+        <v>242</v>
       </c>
       <c r="B320" s="20"/>
       <c r="C320" s="24" t="s">
@@ -13978,8 +13997,8 @@
       </c>
     </row>
     <row r="321" spans="1:9" ht="15">
-      <c r="A321">
-        <v>146</v>
+      <c r="A321" s="20">
+        <v>121</v>
       </c>
       <c r="B321" s="22"/>
       <c r="C321" s="24" t="s">
@@ -14004,8 +14023,8 @@
       </c>
     </row>
     <row r="322" spans="1:9" ht="15">
-      <c r="A322">
-        <v>440</v>
+      <c r="A322" s="20">
+        <v>387</v>
       </c>
       <c r="B322" s="20"/>
       <c r="C322" s="24" t="s">
@@ -14030,8 +14049,8 @@
       </c>
     </row>
     <row r="323" spans="1:9" ht="17">
-      <c r="A323">
-        <v>825</v>
+      <c r="A323" s="20">
+        <v>893</v>
       </c>
       <c r="B323" s="20"/>
       <c r="C323" s="24" t="s">
@@ -14056,8 +14075,8 @@
       </c>
     </row>
     <row r="324" spans="1:9" ht="15">
-      <c r="A324">
-        <v>1398</v>
+      <c r="A324" s="20">
+        <v>1559</v>
       </c>
       <c r="B324" s="20"/>
       <c r="C324" s="24" t="s">
@@ -14082,8 +14101,8 @@
       </c>
     </row>
     <row r="325" spans="1:9" ht="15">
-      <c r="A325">
-        <v>499</v>
+      <c r="A325" s="20">
+        <v>278</v>
       </c>
       <c r="B325" s="20"/>
       <c r="C325" s="24" t="s">
@@ -14108,8 +14127,8 @@
       </c>
     </row>
     <row r="326" spans="1:9" ht="15">
-      <c r="A326">
-        <v>113</v>
+      <c r="A326" s="20">
+        <v>158</v>
       </c>
       <c r="B326" s="22"/>
       <c r="C326" s="24" t="s">
@@ -14134,8 +14153,8 @@
       </c>
     </row>
     <row r="327" spans="1:9" ht="15">
-      <c r="A327">
-        <v>235</v>
+      <c r="A327" s="20">
+        <v>138.44</v>
       </c>
       <c r="B327" s="20"/>
       <c r="C327" s="24" t="s">
@@ -14160,8 +14179,8 @@
       </c>
     </row>
     <row r="328" spans="1:9" ht="15">
-      <c r="A328">
-        <v>299</v>
+      <c r="A328" s="20">
+        <v>187.6</v>
       </c>
       <c r="B328" s="20"/>
       <c r="C328" s="24" t="s">
@@ -14186,8 +14205,8 @@
       </c>
     </row>
     <row r="329" spans="1:9" ht="15">
-      <c r="A329">
-        <v>468</v>
+      <c r="A329" s="20">
+        <v>286</v>
       </c>
       <c r="B329" s="22"/>
       <c r="C329" s="24" t="s">
@@ -14212,7 +14231,7 @@
       </c>
     </row>
     <row r="330" spans="1:9" ht="15">
-      <c r="A330">
+      <c r="A330" s="20">
         <v>2600</v>
       </c>
       <c r="B330" s="20"/>
@@ -14238,8 +14257,8 @@
       </c>
     </row>
     <row r="331" spans="1:9" ht="15">
-      <c r="A331">
-        <v>860</v>
+      <c r="A331" s="20">
+        <v>575</v>
       </c>
       <c r="B331" s="20"/>
       <c r="C331" s="24" t="s">
@@ -14264,8 +14283,8 @@
       </c>
     </row>
     <row r="332" spans="1:9" ht="15">
-      <c r="A332">
-        <v>99.5</v>
+      <c r="A332" s="20">
+        <v>91.5</v>
       </c>
       <c r="B332" s="20"/>
       <c r="C332" s="24" t="s">
@@ -14290,8 +14309,8 @@
       </c>
     </row>
     <row r="333" spans="1:9" ht="15">
-      <c r="A333">
-        <v>239.5</v>
+      <c r="A333" s="20">
+        <v>219</v>
       </c>
       <c r="B333" s="20"/>
       <c r="C333" s="24" t="s">
@@ -14316,8 +14335,8 @@
       </c>
     </row>
     <row r="334" spans="1:9" ht="15">
-      <c r="A334">
-        <v>698</v>
+      <c r="A334" s="20">
+        <v>446.9</v>
       </c>
       <c r="B334" s="20"/>
       <c r="C334" s="24" t="s">
@@ -14342,8 +14361,8 @@
       </c>
     </row>
     <row r="335" spans="1:9" ht="15">
-      <c r="A335">
-        <v>292</v>
+      <c r="A335" s="20">
+        <v>249</v>
       </c>
       <c r="B335" s="20"/>
       <c r="C335" s="24" t="s">
@@ -14368,8 +14387,8 @@
       </c>
     </row>
     <row r="336" spans="1:9" ht="15">
-      <c r="A336">
-        <v>378</v>
+      <c r="A336" s="20">
+        <v>360.62</v>
       </c>
       <c r="B336" s="20"/>
       <c r="C336" s="24" t="s">
@@ -14394,8 +14413,8 @@
       </c>
     </row>
     <row r="337" spans="1:9" ht="15">
-      <c r="A337">
-        <v>115</v>
+      <c r="A337" s="20">
+        <v>92</v>
       </c>
       <c r="B337" s="20"/>
       <c r="C337" s="24" t="s">
@@ -14420,8 +14439,8 @@
       </c>
     </row>
     <row r="338" spans="1:9" ht="17">
-      <c r="A338">
-        <v>559</v>
+      <c r="A338" s="20">
+        <v>459</v>
       </c>
       <c r="B338" s="20"/>
       <c r="C338" s="24" t="s">
@@ -14446,7 +14465,7 @@
       </c>
     </row>
     <row r="339" spans="1:9" ht="15">
-      <c r="A339">
+      <c r="A339" s="20">
         <v>550</v>
       </c>
       <c r="B339" s="20"/>
@@ -14472,7 +14491,7 @@
       </c>
     </row>
     <row r="340" spans="1:9" ht="15">
-      <c r="A340">
+      <c r="A340" s="20">
         <v>568</v>
       </c>
       <c r="B340" s="20"/>
@@ -14498,8 +14517,8 @@
       </c>
     </row>
     <row r="341" spans="1:9" ht="15">
-      <c r="A341">
-        <v>336</v>
+      <c r="A341" s="20">
+        <v>177</v>
       </c>
       <c r="B341" s="20"/>
       <c r="C341" s="24" t="s">
@@ -14524,7 +14543,7 @@
       </c>
     </row>
     <row r="342" spans="1:9" ht="15">
-      <c r="A342">
+      <c r="A342" s="20">
         <v>312.64</v>
       </c>
       <c r="B342" s="20"/>
@@ -14550,8 +14569,8 @@
       </c>
     </row>
     <row r="343" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A343">
-        <v>298</v>
+      <c r="A343" s="20">
+        <v>294</v>
       </c>
       <c r="B343" s="20"/>
       <c r="C343" s="24" t="s">
@@ -14576,8 +14595,8 @@
       </c>
     </row>
     <row r="344" spans="1:9" ht="15">
-      <c r="A344">
-        <v>453.5</v>
+      <c r="A344" s="20">
+        <v>604.5</v>
       </c>
       <c r="B344" s="20"/>
       <c r="C344" s="24" t="s">
@@ -14602,8 +14621,8 @@
       </c>
     </row>
     <row r="345" spans="1:9" ht="15">
-      <c r="A345">
-        <v>209</v>
+      <c r="A345" s="20">
+        <v>356</v>
       </c>
       <c r="B345" s="20"/>
       <c r="C345" s="24" t="s">
@@ -14628,8 +14647,8 @@
       </c>
     </row>
     <row r="346" spans="1:9" ht="17">
-      <c r="A346">
-        <v>259</v>
+      <c r="A346" s="20">
+        <v>189.05</v>
       </c>
       <c r="B346" s="22"/>
       <c r="C346" s="24" t="s">
@@ -14654,7 +14673,7 @@
       </c>
     </row>
     <row r="347" spans="1:9" ht="15">
-      <c r="A347">
+      <c r="A347" s="20">
         <v>169</v>
       </c>
       <c r="B347" s="20"/>
@@ -14680,7 +14699,7 @@
       </c>
     </row>
     <row r="348" spans="1:9" ht="15">
-      <c r="A348">
+      <c r="A348" s="20">
         <v>199</v>
       </c>
       <c r="B348" s="20"/>
@@ -14706,7 +14725,7 @@
       </c>
     </row>
     <row r="349" spans="1:9" ht="15">
-      <c r="A349">
+      <c r="A349" s="20">
         <v>899</v>
       </c>
       <c r="B349" s="22"/>
@@ -14732,8 +14751,8 @@
       </c>
     </row>
     <row r="350" spans="1:9" ht="15">
-      <c r="A350">
-        <v>119</v>
+      <c r="A350" s="20">
+        <v>117.7</v>
       </c>
       <c r="B350" s="20"/>
       <c r="C350" s="24" t="s">
@@ -14758,8 +14777,8 @@
       </c>
     </row>
     <row r="351" spans="1:9" ht="15">
-      <c r="A351">
-        <v>147</v>
+      <c r="A351" s="20">
+        <v>148</v>
       </c>
       <c r="B351" s="20"/>
       <c r="C351" s="24" t="s">
@@ -14784,8 +14803,8 @@
       </c>
     </row>
     <row r="352" spans="1:9" ht="15">
-      <c r="A352">
-        <v>439</v>
+      <c r="A352" s="20">
+        <v>445</v>
       </c>
       <c r="B352" s="20"/>
       <c r="C352" s="24" t="s">
@@ -14810,8 +14829,8 @@
       </c>
     </row>
     <row r="353" spans="1:9" ht="15">
-      <c r="A353">
-        <v>125</v>
+      <c r="A353" s="20">
+        <v>135</v>
       </c>
       <c r="B353" s="20"/>
       <c r="C353" s="24" t="s">
@@ -14836,8 +14855,8 @@
       </c>
     </row>
     <row r="354" spans="1:9" ht="15">
-      <c r="A354">
-        <v>269</v>
+      <c r="A354" s="20">
+        <v>315</v>
       </c>
       <c r="B354" s="20"/>
       <c r="C354" s="24" t="s">
@@ -14862,7 +14881,7 @@
       </c>
     </row>
     <row r="355" spans="1:9" ht="15">
-      <c r="A355">
+      <c r="A355" s="20">
         <v>899</v>
       </c>
       <c r="B355" s="20"/>
@@ -14888,8 +14907,8 @@
       </c>
     </row>
     <row r="356" spans="1:9" ht="15">
-      <c r="A356" t="s">
-        <v>1419</v>
+      <c r="A356" s="20">
+        <v>75.88</v>
       </c>
       <c r="B356" s="20"/>
       <c r="C356" s="24" t="s">
@@ -14914,8 +14933,8 @@
       </c>
     </row>
     <row r="357" spans="1:9" ht="15">
-      <c r="A357">
-        <v>367</v>
+      <c r="A357" s="20">
+        <v>390</v>
       </c>
       <c r="B357" s="20"/>
       <c r="C357" s="24" t="s">
@@ -14940,8 +14959,8 @@
       </c>
     </row>
     <row r="358" spans="1:9" ht="15">
-      <c r="A358" s="30">
-        <v>295.2</v>
+      <c r="A358" s="20">
+        <v>127.8</v>
       </c>
       <c r="B358" s="20"/>
       <c r="C358" s="24" t="s">
@@ -14966,8 +14985,8 @@
       </c>
     </row>
     <row r="359" spans="1:9" ht="15">
-      <c r="A359">
-        <v>118</v>
+      <c r="A359" s="20">
+        <v>386</v>
       </c>
       <c r="B359" s="20"/>
       <c r="C359" s="24" t="s">
@@ -14992,8 +15011,8 @@
       </c>
     </row>
     <row r="360" spans="1:9" ht="15">
-      <c r="A360">
-        <v>112.1</v>
+      <c r="A360" s="20">
+        <v>137</v>
       </c>
       <c r="B360" s="20"/>
       <c r="C360" s="24" t="s">
@@ -15018,8 +15037,8 @@
       </c>
     </row>
     <row r="361" spans="1:9" ht="15">
-      <c r="A361">
-        <v>121.3</v>
+      <c r="A361" s="20">
+        <v>79.5</v>
       </c>
       <c r="B361" s="20"/>
       <c r="C361" s="24" t="s">
@@ -15044,8 +15063,8 @@
       </c>
     </row>
     <row r="362" spans="1:9" ht="15">
-      <c r="A362">
-        <v>999</v>
+      <c r="A362" s="20">
+        <v>1299</v>
       </c>
       <c r="B362" s="20"/>
       <c r="C362" s="24" t="s">
@@ -15070,8 +15089,8 @@
       </c>
     </row>
     <row r="363" spans="1:9" ht="15">
-      <c r="A363">
-        <v>607</v>
+      <c r="A363" s="20">
+        <v>628.80999999999995</v>
       </c>
       <c r="B363" s="20"/>
       <c r="C363" s="24" t="s">
@@ -15096,8 +15115,8 @@
       </c>
     </row>
     <row r="364" spans="1:9" ht="15">
-      <c r="A364">
-        <v>879</v>
+      <c r="A364" s="20">
+        <v>589</v>
       </c>
       <c r="B364" s="20"/>
       <c r="C364" s="24" t="s">
@@ -15122,8 +15141,8 @@
       </c>
     </row>
     <row r="365" spans="1:9" ht="15">
-      <c r="A365">
-        <v>234</v>
+      <c r="A365" s="20">
+        <v>199</v>
       </c>
       <c r="B365" s="22"/>
       <c r="C365" s="24" t="s">
@@ -15148,7 +15167,7 @@
       </c>
     </row>
     <row r="366" spans="1:9" ht="15">
-      <c r="A366">
+      <c r="A366" s="20">
         <v>1300</v>
       </c>
       <c r="B366" s="20"/>
@@ -15174,8 +15193,8 @@
       </c>
     </row>
     <row r="367" spans="1:9" ht="15">
-      <c r="A367">
-        <v>269</v>
+      <c r="A367" s="20">
+        <v>289</v>
       </c>
       <c r="B367" s="20"/>
       <c r="C367" s="24" t="s">
@@ -15200,8 +15219,8 @@
       </c>
     </row>
     <row r="368" spans="1:9" ht="15">
-      <c r="A368">
-        <v>830</v>
+      <c r="A368" s="20">
+        <v>872</v>
       </c>
       <c r="B368" s="22"/>
       <c r="C368" s="24" t="s">
@@ -15225,7 +15244,7 @@
       </c>
     </row>
     <row r="369" spans="1:9" ht="15">
-      <c r="A369">
+      <c r="A369" s="20">
         <v>879.8</v>
       </c>
       <c r="B369" s="22"/>
@@ -15251,8 +15270,8 @@
       </c>
     </row>
     <row r="370" spans="1:9" ht="15">
-      <c r="A370">
-        <v>879.8</v>
+      <c r="A370" s="20">
+        <v>668</v>
       </c>
       <c r="B370" s="20"/>
       <c r="C370" s="24" t="s">
@@ -15277,8 +15296,8 @@
       </c>
     </row>
     <row r="371" spans="1:9" ht="15">
-      <c r="A371">
-        <v>449</v>
+      <c r="A371" s="20">
+        <v>330.4</v>
       </c>
       <c r="B371" s="20"/>
       <c r="C371" s="24" t="s">
@@ -15303,8 +15322,8 @@
       </c>
     </row>
     <row r="372" spans="1:9" ht="15">
-      <c r="A372">
-        <v>789</v>
+      <c r="A372" s="20">
+        <v>588</v>
       </c>
       <c r="B372" s="22"/>
       <c r="C372" s="24" t="s">
@@ -15329,8 +15348,8 @@
       </c>
     </row>
     <row r="373" spans="1:9" ht="15">
-      <c r="A373" t="s">
-        <v>1419</v>
+      <c r="A373" s="20">
+        <v>699</v>
       </c>
       <c r="B373" s="22"/>
       <c r="C373" s="24" t="s">
@@ -15355,8 +15374,8 @@
       </c>
     </row>
     <row r="374" spans="1:9" ht="15">
-      <c r="A374">
-        <v>589</v>
+      <c r="A374" s="20">
+        <v>379</v>
       </c>
       <c r="B374" s="20"/>
       <c r="C374" s="24" t="s">
@@ -15381,8 +15400,8 @@
       </c>
     </row>
     <row r="375" spans="1:9" ht="15">
-      <c r="A375">
-        <v>440</v>
+      <c r="A375" s="20">
+        <v>461</v>
       </c>
       <c r="B375" s="20"/>
       <c r="C375" s="24" t="s">
@@ -15407,8 +15426,8 @@
       </c>
     </row>
     <row r="376" spans="1:9" ht="15">
-      <c r="A376">
-        <v>110</v>
+      <c r="A376" s="20">
+        <v>152</v>
       </c>
       <c r="B376" s="20"/>
       <c r="C376" s="24" t="s">
@@ -15433,8 +15452,8 @@
       </c>
     </row>
     <row r="377" spans="1:9" ht="15">
-      <c r="A377" t="s">
-        <v>1419</v>
+      <c r="A377" s="20">
+        <v>64.5</v>
       </c>
       <c r="B377" s="22"/>
       <c r="C377" s="24" t="s">
@@ -15459,8 +15478,8 @@
       </c>
     </row>
     <row r="378" spans="1:9" ht="15">
-      <c r="A378">
-        <v>292.99</v>
+      <c r="A378" s="20">
+        <v>750</v>
       </c>
       <c r="B378" s="20"/>
       <c r="C378" s="24" t="s">
@@ -15485,8 +15504,8 @@
       </c>
     </row>
     <row r="379" spans="1:9" ht="15">
-      <c r="A379">
-        <v>134</v>
+      <c r="A379" s="20">
+        <v>199</v>
       </c>
       <c r="B379" s="20"/>
       <c r="C379" s="24" t="s">
@@ -15511,8 +15530,8 @@
       </c>
     </row>
     <row r="380" spans="1:9" ht="15">
-      <c r="A380">
-        <v>87</v>
+      <c r="A380" s="20">
+        <v>199</v>
       </c>
       <c r="B380" s="20"/>
       <c r="C380" s="24" t="s">
@@ -15537,8 +15556,8 @@
       </c>
     </row>
     <row r="381" spans="1:9" ht="15">
-      <c r="A381">
-        <v>245</v>
+      <c r="A381" s="20">
+        <v>239</v>
       </c>
       <c r="B381" s="20"/>
       <c r="C381" s="24" t="s">
@@ -15563,8 +15582,8 @@
       </c>
     </row>
     <row r="382" spans="1:9" ht="15">
-      <c r="A382">
-        <v>119</v>
+      <c r="A382" s="20">
+        <v>154.66</v>
       </c>
       <c r="B382" s="20"/>
       <c r="C382" s="24" t="s">
@@ -15589,8 +15608,8 @@
       </c>
     </row>
     <row r="383" spans="1:9" ht="15">
-      <c r="A383">
-        <v>158</v>
+      <c r="A383" s="20">
+        <v>93.8</v>
       </c>
       <c r="B383" s="20"/>
       <c r="C383" s="24" t="s">
@@ -15615,8 +15634,8 @@
       </c>
     </row>
     <row r="384" spans="1:9" ht="15">
-      <c r="A384">
-        <v>149</v>
+      <c r="A384" s="20">
+        <v>148</v>
       </c>
       <c r="B384" s="20"/>
       <c r="C384" s="24" t="s">
@@ -15641,8 +15660,8 @@
       </c>
     </row>
     <row r="385" spans="1:9" ht="15">
-      <c r="A385">
-        <v>138</v>
+      <c r="A385" s="20">
+        <v>328</v>
       </c>
       <c r="B385" s="20"/>
       <c r="C385" s="24" t="s">
@@ -15667,8 +15686,8 @@
       </c>
     </row>
     <row r="386" spans="1:9" ht="15">
-      <c r="A386">
-        <v>118</v>
+      <c r="A386" s="20">
+        <v>112.6</v>
       </c>
       <c r="B386" s="20"/>
       <c r="C386" s="24" t="s">
@@ -15693,8 +15712,8 @@
       </c>
     </row>
     <row r="387" spans="1:9" ht="15">
-      <c r="A387">
-        <v>293</v>
+      <c r="A387" s="20">
+        <v>223.8</v>
       </c>
       <c r="B387" s="20"/>
       <c r="C387" s="24" t="s">
@@ -15719,8 +15738,8 @@
       </c>
     </row>
     <row r="388" spans="1:9" ht="15">
-      <c r="A388">
-        <v>249</v>
+      <c r="A388" s="20">
+        <v>315</v>
       </c>
       <c r="B388" s="20"/>
       <c r="C388" s="24" t="s">
@@ -15745,8 +15764,8 @@
       </c>
     </row>
     <row r="389" spans="1:9" ht="15">
-      <c r="A389">
-        <v>224</v>
+      <c r="A389" s="20">
+        <v>388</v>
       </c>
       <c r="B389" s="20"/>
       <c r="C389" s="24" t="s">
@@ -15771,8 +15790,8 @@
       </c>
     </row>
     <row r="390" spans="1:9" ht="15">
-      <c r="A390">
-        <v>112</v>
+      <c r="A390" s="20">
+        <v>95</v>
       </c>
       <c r="B390" s="20"/>
       <c r="C390" s="24" t="s">
@@ -15797,8 +15816,8 @@
       </c>
     </row>
     <row r="391" spans="1:9" ht="15">
-      <c r="A391">
-        <v>86</v>
+      <c r="A391" s="20">
+        <v>79.989999999999995</v>
       </c>
       <c r="B391" s="20"/>
       <c r="C391" s="24" t="s">
@@ -15823,8 +15842,8 @@
       </c>
     </row>
     <row r="392" spans="1:9" ht="15">
-      <c r="A392">
-        <v>68.900000000000006</v>
+      <c r="A392" s="20">
+        <v>66</v>
       </c>
       <c r="B392" s="20"/>
       <c r="C392" s="24" t="s">
@@ -15849,8 +15868,8 @@
       </c>
     </row>
     <row r="393" spans="1:9" ht="15">
-      <c r="A393">
-        <v>286</v>
+      <c r="A393" s="20">
+        <v>309</v>
       </c>
       <c r="B393" s="20"/>
       <c r="C393" s="24" t="s">
@@ -15875,8 +15894,8 @@
       </c>
     </row>
     <row r="394" spans="1:9" ht="15">
-      <c r="A394">
-        <v>169</v>
+      <c r="A394" s="20">
+        <v>162</v>
       </c>
       <c r="B394" s="20"/>
       <c r="C394" s="24" t="s">
@@ -15901,8 +15920,8 @@
       </c>
     </row>
     <row r="395" spans="1:9" ht="15">
-      <c r="A395">
-        <v>119.9</v>
+      <c r="A395" s="20">
+        <v>79.8</v>
       </c>
       <c r="B395" s="20"/>
       <c r="C395" s="24" t="s">
@@ -15927,7 +15946,7 @@
       </c>
     </row>
     <row r="396" spans="1:9" ht="15">
-      <c r="A396">
+      <c r="A396" s="20">
         <v>398</v>
       </c>
       <c r="B396" s="20"/>
@@ -15953,7 +15972,7 @@
       </c>
     </row>
     <row r="397" spans="1:9" ht="15">
-      <c r="A397">
+      <c r="A397" s="20">
         <v>736.36</v>
       </c>
       <c r="B397" s="23"/>
@@ -15978,9 +15997,7 @@
       </c>
     </row>
     <row r="398" spans="1:9" ht="15">
-      <c r="A398">
-        <v>736.36</v>
-      </c>
+      <c r="A398" s="20"/>
       <c r="B398" s="23"/>
       <c r="C398" s="24" t="s">
         <v>1408</v>
@@ -16004,8 +16021,8 @@
       </c>
     </row>
     <row r="399" spans="1:9" ht="15">
-      <c r="A399">
-        <v>418</v>
+      <c r="A399" s="20">
+        <v>499</v>
       </c>
       <c r="B399" s="23"/>
       <c r="C399" s="24" t="s">
@@ -16030,8 +16047,8 @@
       </c>
     </row>
     <row r="400" spans="1:9" ht="15">
-      <c r="A400">
-        <v>154.69999999999999</v>
+      <c r="A400" s="20">
+        <v>186</v>
       </c>
       <c r="B400" s="20"/>
       <c r="C400" s="24" t="s">
@@ -16056,8 +16073,8 @@
       </c>
     </row>
     <row r="401" spans="1:9" ht="15">
-      <c r="A401">
-        <v>899</v>
+      <c r="A401" s="20">
+        <v>919</v>
       </c>
       <c r="B401" s="20"/>
       <c r="C401" s="24" t="s">
@@ -16082,7 +16099,7 @@
       </c>
     </row>
     <row r="402" spans="1:9" ht="15">
-      <c r="A402">
+      <c r="A402" s="20">
         <v>380</v>
       </c>
       <c r="B402" s="20"/>
@@ -16108,8 +16125,8 @@
       </c>
     </row>
     <row r="403" spans="1:9" ht="15">
-      <c r="A403">
-        <v>89.9</v>
+      <c r="A403" s="20">
+        <v>66.8</v>
       </c>
       <c r="B403" s="20"/>
       <c r="C403" s="24" t="s">
@@ -16134,8 +16151,8 @@
       </c>
     </row>
     <row r="404" spans="1:9" ht="15">
-      <c r="A404">
-        <v>88</v>
+      <c r="A404" s="20">
+        <v>139</v>
       </c>
       <c r="B404" s="20"/>
       <c r="C404" s="24" t="s">
@@ -16160,8 +16177,8 @@
       </c>
     </row>
     <row r="405" spans="1:9" ht="15">
-      <c r="A405">
-        <v>225</v>
+      <c r="A405" s="20">
+        <v>295</v>
       </c>
       <c r="B405" s="20"/>
       <c r="C405" s="24" t="s">
@@ -16186,8 +16203,8 @@
       </c>
     </row>
     <row r="406" spans="1:9" ht="15">
-      <c r="A406">
-        <v>360</v>
+      <c r="A406" s="20">
+        <v>659</v>
       </c>
       <c r="B406" s="20"/>
       <c r="C406" s="24" t="s">
@@ -16212,9 +16229,7 @@
       </c>
     </row>
     <row r="407" spans="1:9" ht="15">
-      <c r="A407" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A407" s="20"/>
       <c r="B407" s="21"/>
       <c r="C407" s="24" t="s">
         <v>1408</v>
@@ -16238,9 +16253,7 @@
       </c>
     </row>
     <row r="408" spans="1:9" ht="15">
-      <c r="A408" t="s">
-        <v>1419</v>
-      </c>
+      <c r="A408" s="20"/>
       <c r="B408" s="23"/>
       <c r="C408" s="24" t="s">
         <v>1408</v>
@@ -16263,8 +16276,8 @@
       </c>
     </row>
     <row r="409" spans="1:9" ht="15">
-      <c r="A409">
-        <v>89</v>
+      <c r="A409" s="20">
+        <v>87</v>
       </c>
       <c r="B409" s="20"/>
       <c r="C409" s="24" t="s">
@@ -16289,8 +16302,8 @@
       </c>
     </row>
     <row r="410" spans="1:9" ht="15">
-      <c r="A410">
-        <v>184</v>
+      <c r="A410" s="20">
+        <v>128</v>
       </c>
       <c r="B410" s="23"/>
       <c r="C410" s="24" t="s">
@@ -16314,8 +16327,8 @@
       </c>
     </row>
     <row r="411" spans="1:9" ht="15">
-      <c r="A411">
-        <v>184</v>
+      <c r="A411" s="20">
+        <v>179</v>
       </c>
       <c r="B411" s="23"/>
       <c r="C411" s="24" t="s">
@@ -16340,8 +16353,8 @@
       </c>
     </row>
     <row r="412" spans="1:9" ht="15">
-      <c r="A412">
-        <v>311</v>
+      <c r="A412" s="20">
+        <v>111</v>
       </c>
       <c r="B412" s="23"/>
       <c r="C412" s="24" t="s">
@@ -16366,8 +16379,8 @@
       </c>
     </row>
     <row r="413" spans="1:9" ht="15">
-      <c r="A413">
-        <v>88</v>
+      <c r="A413" s="20">
+        <v>139</v>
       </c>
       <c r="B413" s="20"/>
       <c r="C413" s="24" t="s">
@@ -16392,8 +16405,8 @@
       </c>
     </row>
     <row r="414" spans="1:9" ht="15">
-      <c r="A414">
-        <v>763</v>
+      <c r="A414" s="20">
+        <v>439</v>
       </c>
       <c r="B414" s="20"/>
       <c r="C414" s="24" t="s">
@@ -16418,8 +16431,8 @@
       </c>
     </row>
     <row r="415" spans="1:9" ht="15">
-      <c r="A415">
-        <v>19.899999999999999</v>
+      <c r="A415" s="20">
+        <v>94.7</v>
       </c>
       <c r="B415" s="20"/>
       <c r="C415" s="24" t="s">
@@ -16444,8 +16457,8 @@
       </c>
     </row>
     <row r="416" spans="1:9" ht="15">
-      <c r="A416">
-        <v>399</v>
+      <c r="A416" s="20">
+        <v>329</v>
       </c>
       <c r="B416" s="20"/>
       <c r="C416" s="24" t="s">
@@ -16470,8 +16483,8 @@
       </c>
     </row>
     <row r="417" spans="1:9" ht="15">
-      <c r="A417">
-        <v>499</v>
+      <c r="A417" s="20">
+        <v>535</v>
       </c>
       <c r="B417" s="20"/>
       <c r="C417" s="24" t="s">
@@ -16496,8 +16509,8 @@
       </c>
     </row>
     <row r="418" spans="1:9" ht="15">
-      <c r="A418">
-        <v>359</v>
+      <c r="A418" s="20">
+        <v>428</v>
       </c>
       <c r="B418" s="20"/>
       <c r="C418" s="24" t="s">
@@ -16522,8 +16535,8 @@
       </c>
     </row>
     <row r="419" spans="1:9" ht="15">
-      <c r="A419">
-        <v>353</v>
+      <c r="A419" s="20">
+        <v>499</v>
       </c>
       <c r="B419" s="20"/>
       <c r="C419" s="24" t="s">
@@ -16548,8 +16561,8 @@
       </c>
     </row>
     <row r="420" spans="1:9" ht="15">
-      <c r="A420">
-        <v>468.79</v>
+      <c r="A420" s="20">
+        <v>499</v>
       </c>
       <c r="B420" s="20"/>
       <c r="C420" s="24" t="s">
@@ -16560,7 +16573,7 @@
         <v>1263</v>
       </c>
       <c r="F420" s="15" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="G420" s="8" t="s">
         <v>1264</v>
@@ -16574,8 +16587,8 @@
       </c>
     </row>
     <row r="421" spans="1:9" ht="15">
-      <c r="A421">
-        <v>145</v>
+      <c r="A421" s="20">
+        <v>100</v>
       </c>
       <c r="B421" s="25"/>
       <c r="C421" s="24" t="s">
@@ -16600,8 +16613,8 @@
       </c>
     </row>
     <row r="422" spans="1:9" ht="15">
-      <c r="A422">
-        <v>55.55</v>
+      <c r="A422" s="20">
+        <v>119.98</v>
       </c>
       <c r="B422" s="20"/>
       <c r="C422" s="24" t="s">
@@ -16626,8 +16639,8 @@
       </c>
     </row>
     <row r="423" spans="1:9" ht="15">
-      <c r="A423">
-        <v>309</v>
+      <c r="A423" s="20">
+        <v>295</v>
       </c>
       <c r="B423" s="20"/>
       <c r="C423" s="24" t="s">
@@ -16652,8 +16665,8 @@
       </c>
     </row>
     <row r="424" spans="1:9" ht="15">
-      <c r="A424">
-        <v>179</v>
+      <c r="A424" s="20">
+        <v>198</v>
       </c>
       <c r="B424" s="20"/>
       <c r="C424" s="24" t="s">
@@ -16678,7 +16691,7 @@
       </c>
     </row>
     <row r="425" spans="1:9" ht="15">
-      <c r="A425">
+      <c r="A425" s="20">
         <v>185</v>
       </c>
       <c r="B425" s="20"/>
@@ -16704,8 +16717,8 @@
       </c>
     </row>
     <row r="426" spans="1:9" ht="15">
-      <c r="A426" t="s">
-        <v>1419</v>
+      <c r="A426" s="20">
+        <v>583</v>
       </c>
       <c r="B426" s="23"/>
       <c r="C426" s="24" t="s">
@@ -16729,8 +16742,8 @@
       </c>
     </row>
     <row r="427" spans="1:9" ht="15">
-      <c r="A427">
-        <v>123</v>
+      <c r="A427" s="20">
+        <v>145</v>
       </c>
       <c r="B427" s="23"/>
       <c r="C427" s="24" t="s">
@@ -16754,8 +16767,8 @@
       </c>
     </row>
     <row r="428" spans="1:9" ht="15">
-      <c r="A428">
-        <v>162</v>
+      <c r="A428" s="20">
+        <v>188</v>
       </c>
       <c r="B428" s="23"/>
       <c r="C428" s="24" t="s">
@@ -16779,8 +16792,8 @@
       </c>
     </row>
     <row r="429" spans="1:9" ht="15">
-      <c r="A429">
-        <v>124</v>
+      <c r="A429" s="20">
+        <v>123</v>
       </c>
       <c r="B429" s="20"/>
       <c r="C429" s="24" t="s">
@@ -16805,8 +16818,8 @@
       </c>
     </row>
     <row r="430" spans="1:9" ht="15">
-      <c r="A430">
-        <v>171</v>
+      <c r="A430" s="20">
+        <v>133</v>
       </c>
       <c r="B430" s="20"/>
       <c r="C430" s="24" t="s">
@@ -16831,8 +16844,8 @@
       </c>
     </row>
     <row r="431" spans="1:9" ht="15">
-      <c r="A431">
-        <v>190.1</v>
+      <c r="A431" s="20">
+        <v>99</v>
       </c>
       <c r="B431" s="20"/>
       <c r="C431" s="24" t="s">
@@ -16857,8 +16870,8 @@
       </c>
     </row>
     <row r="432" spans="1:9" ht="15">
-      <c r="A432">
-        <v>130.80000000000001</v>
+      <c r="A432" s="20">
+        <v>149</v>
       </c>
       <c r="B432" s="20"/>
       <c r="C432" s="24" t="s">
@@ -16883,8 +16896,8 @@
       </c>
     </row>
     <row r="433" spans="1:9" ht="15">
-      <c r="A433">
-        <v>105.9</v>
+      <c r="A433" s="20">
+        <v>77.23</v>
       </c>
       <c r="B433" s="20"/>
       <c r="C433" s="24" t="s">
@@ -16908,8 +16921,8 @@
       </c>
     </row>
     <row r="434" spans="1:9" ht="15">
-      <c r="A434">
-        <v>149</v>
+      <c r="A434" s="20">
+        <v>115</v>
       </c>
       <c r="B434" s="20"/>
       <c r="C434" s="24" t="s">
@@ -16934,8 +16947,8 @@
       </c>
     </row>
     <row r="435" spans="1:9" ht="15">
-      <c r="A435">
-        <v>559</v>
+      <c r="A435" s="20">
+        <v>615</v>
       </c>
       <c r="B435" s="20"/>
       <c r="C435" s="24" t="s">
@@ -16960,8 +16973,8 @@
       </c>
     </row>
     <row r="436" spans="1:9" ht="15">
-      <c r="A436">
-        <v>87</v>
+      <c r="A436" s="20">
+        <v>104</v>
       </c>
       <c r="B436" s="20"/>
       <c r="C436" s="24" t="s">
@@ -16986,8 +16999,8 @@
       </c>
     </row>
     <row r="437" spans="1:9" ht="15">
-      <c r="A437">
-        <v>86.5</v>
+      <c r="A437" s="20">
+        <v>189</v>
       </c>
       <c r="B437" s="23"/>
       <c r="C437" s="24" t="s">
@@ -17011,8 +17024,8 @@
       </c>
     </row>
     <row r="438" spans="1:9" ht="15">
-      <c r="A438">
-        <v>175</v>
+      <c r="A438" s="20">
+        <v>113</v>
       </c>
       <c r="B438" s="20"/>
       <c r="C438" s="24" t="s">
@@ -17037,8 +17050,8 @@
       </c>
     </row>
     <row r="439" spans="1:9" ht="15">
-      <c r="A439">
-        <v>148</v>
+      <c r="A439" s="20">
+        <v>129</v>
       </c>
       <c r="B439" s="20"/>
       <c r="C439" s="24" t="s">
@@ -17063,8 +17076,8 @@
       </c>
     </row>
     <row r="440" spans="1:9" ht="15">
-      <c r="A440">
-        <v>148</v>
+      <c r="A440" s="20">
+        <v>152</v>
       </c>
       <c r="B440" s="20"/>
       <c r="C440" s="24" t="s">
@@ -17089,8 +17102,8 @@
       </c>
     </row>
     <row r="441" spans="1:9" ht="15">
-      <c r="A441">
-        <v>142</v>
+      <c r="A441" s="20">
+        <v>238</v>
       </c>
       <c r="B441" s="23"/>
       <c r="C441" s="24" t="s">
@@ -17115,8 +17128,8 @@
       </c>
     </row>
     <row r="442" spans="1:9" ht="15">
-      <c r="A442">
-        <v>589</v>
+      <c r="A442" s="20">
+        <v>799</v>
       </c>
       <c r="B442" s="20"/>
       <c r="C442" s="24" t="s">
@@ -17141,8 +17154,8 @@
       </c>
     </row>
     <row r="443" spans="1:9" ht="15">
-      <c r="A443">
-        <v>152.88</v>
+      <c r="A443" s="20">
+        <v>87</v>
       </c>
       <c r="B443" s="23"/>
       <c r="C443" s="24" t="s">
@@ -17167,7 +17180,7 @@
       </c>
     </row>
     <row r="444" spans="1:9" ht="15">
-      <c r="A444">
+      <c r="A444" s="20">
         <v>38.85</v>
       </c>
       <c r="B444" s="20"/>
@@ -17193,24 +17206,51 @@
       </c>
     </row>
     <row r="445" spans="1:9" ht="15">
+      <c r="A445" s="20">
+        <v>210</v>
+      </c>
       <c r="C445" s="24" t="s">
         <v>1408</v>
       </c>
       <c r="E445" s="16" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F445" s="16" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="G445" s="16" t="s">
         <v>725</v>
       </c>
       <c r="H445" s="4">
-        <f t="shared" ref="H445" si="25">D445+1095</f>
+        <f t="shared" ref="H445:H446" si="25">D445+1095</f>
         <v>1095</v>
       </c>
       <c r="I445" s="10">
         <v>444</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" ht="15">
+      <c r="A446" s="20">
+        <v>108.8</v>
+      </c>
+      <c r="C446" s="24" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E446" s="16" t="s">
+        <v>1421</v>
+      </c>
+      <c r="F446" s="16" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G446" s="16" t="s">
+        <v>1423</v>
+      </c>
+      <c r="H446" s="4">
+        <f t="shared" si="25"/>
+        <v>1095</v>
+      </c>
+      <c r="I446" s="10">
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -17221,191 +17261,203 @@
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="75" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:I1">
-    <cfRule type="duplicateValues" dxfId="74" priority="1511"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="1518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E12 E14:E238">
-    <cfRule type="duplicateValues" dxfId="73" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="72" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E349">
-    <cfRule type="duplicateValues" dxfId="69" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E425">
-    <cfRule type="duplicateValues" dxfId="68" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E426:E432 E434:E444 E2:E12 E14:E424">
-    <cfRule type="duplicateValues" dxfId="67" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E433">
-    <cfRule type="duplicateValues" dxfId="65" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E446:E1048576">
-    <cfRule type="duplicateValues" dxfId="64" priority="1510"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="1509"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="1508"/>
+  <conditionalFormatting sqref="E445">
+    <cfRule type="duplicateValues" dxfId="70" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E446">
+    <cfRule type="duplicateValues" dxfId="68" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E447:E1048576">
+    <cfRule type="duplicateValues" dxfId="66" priority="1517"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1516"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="1515"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F309">
-    <cfRule type="duplicateValues" dxfId="61" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F347:F379 F322 F248:F280 F282 F285:F293 F295:F308 F324:F337 F310:F320 F2:F12 F339:F345 F381:F424 F14:F188">
-    <cfRule type="duplicateValues" dxfId="60" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F380">
-    <cfRule type="duplicateValues" dxfId="59" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F426:F444">
-    <cfRule type="duplicateValues" dxfId="58" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F446:F1048576">
-    <cfRule type="duplicateValues" dxfId="56" priority="195"/>
+  <conditionalFormatting sqref="F445">
+    <cfRule type="duplicateValues" dxfId="58" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F446">
+    <cfRule type="duplicateValues" dxfId="56" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F447:F1048576">
+    <cfRule type="duplicateValues" dxfId="54" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F425:G425">
-    <cfRule type="duplicateValues" dxfId="55" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G12 G419 G421:G424 G14:G417">
-    <cfRule type="duplicateValues" dxfId="53" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="duplicateValues" dxfId="52" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14">
-    <cfRule type="duplicateValues" dxfId="51" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G94">
-    <cfRule type="duplicateValues" dxfId="50" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G127">
-    <cfRule type="duplicateValues" dxfId="49" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G143">
-    <cfRule type="duplicateValues" dxfId="48" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G155">
-    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G156">
-    <cfRule type="duplicateValues" dxfId="46" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G157">
-    <cfRule type="duplicateValues" dxfId="45" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G165">
-    <cfRule type="duplicateValues" dxfId="44" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G285">
-    <cfRule type="duplicateValues" dxfId="43" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G295">
-    <cfRule type="duplicateValues" dxfId="42" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G296">
-    <cfRule type="duplicateValues" dxfId="41" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G297">
-    <cfRule type="duplicateValues" dxfId="40" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G301">
-    <cfRule type="duplicateValues" dxfId="39" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G304:G305 G308:G309">
-    <cfRule type="duplicateValues" dxfId="38" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G306">
-    <cfRule type="duplicateValues" dxfId="37" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G307">
-    <cfRule type="duplicateValues" dxfId="36" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G313">
-    <cfRule type="duplicateValues" dxfId="35" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G314">
-    <cfRule type="duplicateValues" dxfId="34" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G322">
-    <cfRule type="duplicateValues" dxfId="33" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G324">
-    <cfRule type="duplicateValues" dxfId="32" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G339">
-    <cfRule type="duplicateValues" dxfId="31" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G340">
-    <cfRule type="duplicateValues" dxfId="30" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G341">
-    <cfRule type="duplicateValues" dxfId="29" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G342">
-    <cfRule type="duplicateValues" dxfId="28" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G344">
-    <cfRule type="duplicateValues" dxfId="27" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G345">
-    <cfRule type="duplicateValues" dxfId="26" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G347">
-    <cfRule type="duplicateValues" dxfId="25" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G348">
-    <cfRule type="duplicateValues" dxfId="24" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G349">
-    <cfRule type="duplicateValues" dxfId="23" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G350:G351">
-    <cfRule type="duplicateValues" dxfId="22" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G357:G360">
-    <cfRule type="duplicateValues" dxfId="21" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G364">
-    <cfRule type="duplicateValues" dxfId="20" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G365">
-    <cfRule type="duplicateValues" dxfId="19" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G367:G372">
-    <cfRule type="duplicateValues" dxfId="18" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G418">
-    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G426:G434 G437:G444">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G435">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G436">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E445">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F445">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G445">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G446">
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -18722,19 +18774,19 @@
   <autoFilter ref="C1:F58" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B3 A4:A44 A49:A58">
-    <cfRule type="duplicateValues" dxfId="9" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B6 B8:B9 B11:B12 B14:B15 B17:B18 B20:B21 B23:B24 B26:B27 B29:B30 B32:B33 B35:B36 B38:B39 B41:B42 B44:B45 B47:B48">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207:C243 B1:C1 B622:C1048576 B277:C487">
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="6" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/模块开发/录入表.xlsx
+++ b/模块开发/录入表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentli/PycharmProjects/PythonProject/2026-4 群控/yolo/整合详情页采集/模块开发/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F12739-FCBA-5945-A699-AE9729D62577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE9FC7A-A759-7248-B25E-B6CA0F614A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43200" yWindow="-5620" windowWidth="28800" windowHeight="19680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="1424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="1426">
   <si>
     <t>商品条码</t>
   </si>
@@ -4354,6 +4354,12 @@
   </si>
   <si>
     <t>资生堂蓝胖子（新款）50ml</t>
+  </si>
+  <si>
+    <t>3253581597705</t>
+  </si>
+  <si>
+    <t>欧舒丹乳木果护手霜150ml</t>
   </si>
 </sst>
 </file>
@@ -4538,7 +4544,67 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="99">
+  <dxfs count="105">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -5415,25 +5481,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
     <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{3AD70849-3F6B-ADC2-5487-646933379502}">
-      <tableStyleElement type="wholeTable" dxfId="98"/>
+      <tableStyleElement type="wholeTable" dxfId="104"/>
+      <tableStyleElement type="headerRow" dxfId="103"/>
+      <tableStyleElement type="totalRow" dxfId="102"/>
+      <tableStyleElement type="firstColumn" dxfId="101"/>
+      <tableStyleElement type="lastColumn" dxfId="100"/>
+      <tableStyleElement type="firstRowStripe" dxfId="99"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="98"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{B0E6D76F-EA8E-7237-5487-6469988B1DE4}">
       <tableStyleElement type="headerRow" dxfId="97"/>
       <tableStyleElement type="totalRow" dxfId="96"/>
-      <tableStyleElement type="firstColumn" dxfId="95"/>
-      <tableStyleElement type="lastColumn" dxfId="94"/>
-      <tableStyleElement type="firstRowStripe" dxfId="93"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="92"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{B0E6D76F-EA8E-7237-5487-6469988B1DE4}">
-      <tableStyleElement type="headerRow" dxfId="91"/>
-      <tableStyleElement type="totalRow" dxfId="90"/>
-      <tableStyleElement type="firstRowStripe" dxfId="89"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="88"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="87"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="86"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="85"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="84"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="83"/>
-      <tableStyleElement type="pageFieldValues" dxfId="82"/>
+      <tableStyleElement type="firstRowStripe" dxfId="95"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="94"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="93"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="92"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="91"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="90"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="89"/>
+      <tableStyleElement type="pageFieldValues" dxfId="88"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -5713,7 +5779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I446"/>
+  <dimension ref="A1:I447"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="8.33203125" customWidth="1"/>
@@ -9840,7 +9906,7 @@
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" s="20">
-        <v>198</v>
+        <v>445</v>
       </c>
       <c r="B160" s="20"/>
       <c r="C160" s="24" t="s">
@@ -17222,7 +17288,7 @@
         <v>725</v>
       </c>
       <c r="H445" s="4">
-        <f t="shared" ref="H445:H446" si="25">D445+1095</f>
+        <f t="shared" ref="H445:H447" si="25">D445+1095</f>
         <v>1095</v>
       </c>
       <c r="I445" s="10">
@@ -17251,6 +17317,27 @@
       </c>
       <c r="I446" s="10">
         <v>445</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" ht="15">
+      <c r="C447" s="24" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E447" s="16" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F447" s="16" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G447" s="16" t="s">
+        <v>1425</v>
+      </c>
+      <c r="H447" s="4">
+        <f t="shared" si="25"/>
+        <v>1095</v>
+      </c>
+      <c r="I447" s="10">
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -17261,203 +17348,215 @@
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="81" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:I1">
-    <cfRule type="duplicateValues" dxfId="80" priority="1518"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="1524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E12 E14:E238">
-    <cfRule type="duplicateValues" dxfId="79" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="78" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E349">
-    <cfRule type="duplicateValues" dxfId="75" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E425">
-    <cfRule type="duplicateValues" dxfId="74" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E426:E432 E434:E444 E2:E12 E14:E424">
-    <cfRule type="duplicateValues" dxfId="73" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E433">
-    <cfRule type="duplicateValues" dxfId="71" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E445">
-    <cfRule type="duplicateValues" dxfId="70" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E446">
-    <cfRule type="duplicateValues" dxfId="68" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E447:E1048576">
-    <cfRule type="duplicateValues" dxfId="66" priority="1517"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="1516"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="1515"/>
+  <conditionalFormatting sqref="E448:E1048576">
+    <cfRule type="duplicateValues" dxfId="72" priority="1523"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="1522"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="1521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F309">
-    <cfRule type="duplicateValues" dxfId="63" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F347:F379 F322 F248:F280 F282 F285:F293 F295:F308 F324:F337 F310:F320 F2:F12 F339:F345 F381:F424 F14:F188">
-    <cfRule type="duplicateValues" dxfId="62" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F380">
-    <cfRule type="duplicateValues" dxfId="61" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F426:F444">
-    <cfRule type="duplicateValues" dxfId="60" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F445">
-    <cfRule type="duplicateValues" dxfId="58" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F446">
-    <cfRule type="duplicateValues" dxfId="56" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F447:F1048576">
-    <cfRule type="duplicateValues" dxfId="54" priority="202"/>
+  <conditionalFormatting sqref="F448:F1048576">
+    <cfRule type="duplicateValues" dxfId="60" priority="208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F425:G425">
-    <cfRule type="duplicateValues" dxfId="53" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G12 G419 G421:G424 G14:G417">
-    <cfRule type="duplicateValues" dxfId="51" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14">
-    <cfRule type="duplicateValues" dxfId="49" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G94">
-    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G127">
-    <cfRule type="duplicateValues" dxfId="47" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G143">
-    <cfRule type="duplicateValues" dxfId="46" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G155">
-    <cfRule type="duplicateValues" dxfId="45" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G156">
-    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G157">
-    <cfRule type="duplicateValues" dxfId="43" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G165">
-    <cfRule type="duplicateValues" dxfId="42" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G285">
-    <cfRule type="duplicateValues" dxfId="41" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G295">
-    <cfRule type="duplicateValues" dxfId="40" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G296">
-    <cfRule type="duplicateValues" dxfId="39" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G297">
-    <cfRule type="duplicateValues" dxfId="38" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G301">
-    <cfRule type="duplicateValues" dxfId="37" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G304:G305 G308:G309">
-    <cfRule type="duplicateValues" dxfId="36" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G306">
-    <cfRule type="duplicateValues" dxfId="35" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G307">
-    <cfRule type="duplicateValues" dxfId="34" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G313">
-    <cfRule type="duplicateValues" dxfId="33" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G314">
+    <cfRule type="duplicateValues" dxfId="38" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G322">
+    <cfRule type="duplicateValues" dxfId="37" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G324">
+    <cfRule type="duplicateValues" dxfId="36" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G339">
+    <cfRule type="duplicateValues" dxfId="35" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G340">
+    <cfRule type="duplicateValues" dxfId="34" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G341">
+    <cfRule type="duplicateValues" dxfId="33" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G342">
     <cfRule type="duplicateValues" dxfId="32" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G322">
-    <cfRule type="duplicateValues" dxfId="31" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G324">
-    <cfRule type="duplicateValues" dxfId="30" priority="57"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G339">
-    <cfRule type="duplicateValues" dxfId="29" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G340">
-    <cfRule type="duplicateValues" dxfId="28" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G341">
-    <cfRule type="duplicateValues" dxfId="27" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G342">
-    <cfRule type="duplicateValues" dxfId="26" priority="53"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G344">
-    <cfRule type="duplicateValues" dxfId="25" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G345">
-    <cfRule type="duplicateValues" dxfId="24" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G347">
-    <cfRule type="duplicateValues" dxfId="23" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G348">
-    <cfRule type="duplicateValues" dxfId="22" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G349">
-    <cfRule type="duplicateValues" dxfId="21" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G350:G351">
-    <cfRule type="duplicateValues" dxfId="20" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G357:G360">
-    <cfRule type="duplicateValues" dxfId="19" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G364">
-    <cfRule type="duplicateValues" dxfId="18" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G365">
-    <cfRule type="duplicateValues" dxfId="17" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G367:G372">
-    <cfRule type="duplicateValues" dxfId="16" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G418">
-    <cfRule type="duplicateValues" dxfId="15" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G426:G434 G437:G444">
-    <cfRule type="duplicateValues" dxfId="14" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G435">
-    <cfRule type="duplicateValues" dxfId="12" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G436">
-    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G445">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G446">
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E447">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F447">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G447">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -18774,19 +18873,19 @@
   <autoFilter ref="C1:F58" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B3 A4:A44 A49:A58">
-    <cfRule type="duplicateValues" dxfId="3" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B6 B8:B9 B11:B12 B14:B15 B17:B18 B20:B21 B23:B24 B26:B27 B29:B30 B32:B33 B35:B36 B38:B39 B41:B42 B44:B45 B47:B48">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207:C243 B1:C1 B622:C1048576 B277:C487">
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="154"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
